--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C466"/>
+  <dimension ref="A1:C478"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4562,211 +4562,211 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>REPORT</v>
+        <v>HDR</v>
       </c>
       <c r="B378" t="str">
-        <v>RELATÓRIO</v>
+        <v>HDR</v>
       </c>
       <c r="C378" t="str">
-        <v>RELATÓRIO</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>FAIL</v>
+        <v>Code points</v>
       </c>
       <c r="B379" t="str">
-        <v>REPROVADO</v>
+        <v>Pontos de código</v>
       </c>
       <c r="C379" t="str">
-        <v>REPROVADO</v>
+        <v>Pontos de código</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>checks</v>
+        <v>Gain curve</v>
       </c>
       <c r="B380" t="str">
-        <v>verificações</v>
+        <v>Curva de ganho</v>
       </c>
       <c r="C380" t="str">
-        <v>verificações</v>
+        <v>Curva de ganho</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B381" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C381" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B382" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C382" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B383" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C383" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Powered by {lib}</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B384" t="str">
-        <v>Com {lib}</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C384" t="str">
-        <v>Com {lib}</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Subscribe</v>
+        <v>Full range</v>
       </c>
       <c r="B385" t="str">
-        <v>Subscrever</v>
+        <v>Gama completa</v>
       </c>
       <c r="C385" t="str">
-        <v>Inscrever-se</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Narrow range</v>
       </c>
       <c r="B386" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C386" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Get notified about new releases</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B387" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C387" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Close</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B388" t="str">
-        <v>Fechar</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C388" t="str">
-        <v>Fechar</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B389" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C389" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Email address</v>
+        <v>REPORT</v>
       </c>
       <c r="B390" t="str">
-        <v>Endereço de e-mail</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C390" t="str">
-        <v>Endereço de e-mail</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>you@example.com</v>
+        <v>FAIL</v>
       </c>
       <c r="B391" t="str">
-        <v>voce@exemplo.com</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C391" t="str">
-        <v>voce@exemplo.com</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>How will you use profiletool?</v>
+        <v>checks</v>
       </c>
       <c r="B392" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>verificações</v>
       </c>
       <c r="C392" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>(optional)</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B393" t="str">
-        <v>(opcional)</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C393" t="str">
-        <v>(opcional)</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B394" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C394" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B395" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C395" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Cancel</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B396" t="str">
-        <v>Cancelar</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C396" t="str">
-        <v>Cancelar</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="397">
@@ -4782,24 +4782,24 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B398" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C398" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B399" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C399" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="400">
@@ -4815,733 +4815,865 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Privacy notice</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B401" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C401" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Email address</v>
       </c>
       <c r="B402" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C402" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B403" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C403" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Please check the form and try again.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B404" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C404" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B405" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>(opcional)</v>
       </c>
       <c r="C405" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Network error. Please try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B406" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C406" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Error:</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B407" t="str">
-        <v>Erro:</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C407" t="str">
-        <v>Erro:</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Convert to XML</v>
+        <v>Cancel</v>
       </c>
       <c r="B408" t="str">
-        <v>Converter para XML</v>
+        <v>Cancelar</v>
       </c>
       <c r="C408" t="str">
-        <v>Converter para XML</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Convert to JSON</v>
+        <v>Subscribe</v>
       </c>
       <c r="B409" t="str">
-        <v>Converter para JSON</v>
+        <v>Subscrever</v>
       </c>
       <c r="C409" t="str">
-        <v>Converter para JSON</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Convert to ICC</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B410" t="str">
-        <v>Converter para ICC</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C410" t="str">
-        <v>Converter para ICC</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Converting to XML…</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B411" t="str">
-        <v>A converter para XML…</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C411" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Converting to JSON…</v>
+        <v>Close</v>
       </c>
       <c r="B412" t="str">
-        <v>A converter para JSON…</v>
+        <v>Fechar</v>
       </c>
       <c r="C412" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Converting to ICC…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B413" t="str">
-        <v>A converter para ICC…</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C413" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Load ICC profile</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B414" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C414" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B415" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C415" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile ID</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B416" t="str">
-        <v>ID do perfil</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C416" t="str">
-        <v>ID do perfil</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>No tags found.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B417" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C417" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Tag Name</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B418" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C418" t="str">
-        <v>Nome da tag</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ID</v>
+        <v>Error:</v>
       </c>
       <c r="B419" t="str">
-        <v>ID</v>
+        <v>Erro:</v>
       </c>
       <c r="C419" t="str">
-        <v>ID</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Offset</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B420" t="str">
-        <v>Deslocamento</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C420" t="str">
-        <v>Deslocamento</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Size</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B421" t="str">
-        <v>Tamanho</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C421" t="str">
-        <v>Tamanho</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Pad</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B422" t="str">
-        <v>Preenchimento</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C422" t="str">
-        <v>Preenchimento</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B423" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C423" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Type</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B424" t="str">
-        <v>Tipo</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C424" t="str">
-        <v>Tipo</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Array of {type}</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B425" t="str">
-        <v>Vetor de {type}</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C425" t="str">
-        <v>Array de {type}</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>(No content)</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B426" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C426" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bytes</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B427" t="str">
-        <v>bytes</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C427" t="str">
-        <v>bytes</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Loading full description…</v>
+        <v>Profile ID</v>
       </c>
       <c r="B428" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C428" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not load full description:</v>
+        <v>No tags found.</v>
       </c>
       <c r="B429" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C429" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B430" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C430" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>ID</v>
       </c>
       <c r="B431" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>ID</v>
       </c>
       <c r="C431" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No validation output</v>
+        <v>Offset</v>
       </c>
       <c r="B432" t="str">
-        <v>Sem saída de validação</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C432" t="str">
-        <v>Sem saída de validação</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Profile is valid</v>
+        <v>Size</v>
       </c>
       <c r="B433" t="str">
-        <v>O perfil é válido</v>
+        <v>Tamanho</v>
       </c>
       <c r="C433" t="str">
-        <v>O perfil é válido</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Pad</v>
       </c>
       <c r="B434" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C434" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B435" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C435" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Critical validation error</v>
+        <v>Type</v>
       </c>
       <c r="B436" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Tipo</v>
       </c>
       <c r="C436" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Unknown validation status</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B437" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C437" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>(No content)</v>
       </c>
       <c r="B438" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C438" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>No warnings or errors found.</v>
+        <v>bytes</v>
       </c>
       <c r="B439" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>bytes</v>
       </c>
       <c r="C439" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Valid</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B440" t="str">
-        <v>Válido</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C440" t="str">
-        <v>Válido</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Warning</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B441" t="str">
-        <v>Aviso</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C441" t="str">
-        <v>Aviso</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Error</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B442" t="str">
-        <v>Erro</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C442" t="str">
-        <v>Erro</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Unknown</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B443" t="str">
-        <v>Desconhecido</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C443" t="str">
-        <v>Desconhecido</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Pass</v>
+        <v>No validation output</v>
       </c>
       <c r="B444" t="str">
-        <v>Aprovado</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C444" t="str">
-        <v>Aprovado</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Fail</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B445" t="str">
-        <v>Reprovado</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C445" t="str">
-        <v>Reprovado</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>View in context</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B446" t="str">
-        <v>Ver no contexto</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C446" t="str">
-        <v>Ver no contexto</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Validation detail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B447" t="str">
-        <v>Detalhe de validação</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C447" t="str">
-        <v>Detalhe de validação</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Triggered by</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B448" t="str">
-        <v>Acionado por</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C448" t="str">
-        <v>Acionado por</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Field</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B449" t="str">
-        <v>Campo</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C449" t="str">
-        <v>Campo</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Current value</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B450" t="str">
-        <v>Valor atual</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C450" t="str">
-        <v>Valor atual</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Required: 0</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B451" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C451" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Expected: {value}</v>
+        <v>Valid</v>
       </c>
       <c r="B452" t="str">
-        <v>Esperado: {value}</v>
+        <v>Válido</v>
       </c>
       <c r="C452" t="str">
-        <v>Esperado: {value}</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Invalid</v>
+        <v>Warning</v>
       </c>
       <c r="B453" t="str">
-        <v>Inválido</v>
+        <v>Aviso</v>
       </c>
       <c r="C453" t="str">
-        <v>Inválido</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Error</v>
       </c>
       <c r="B454" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Erro</v>
       </c>
       <c r="C454" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Close</v>
+        <v>Unknown</v>
       </c>
       <c r="B455" t="str">
-        <v>Fechar</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C455" t="str">
-        <v>Fechar</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Loading XML editor…</v>
+        <v>Pass</v>
       </c>
       <c r="B456" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Aprovado</v>
       </c>
       <c r="C456" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Fail</v>
       </c>
       <c r="B457" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Reprovado</v>
       </c>
       <c r="C457" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>View in context</v>
       </c>
       <c r="B458" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C458" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B459" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C459" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Triggered by</v>
       </c>
       <c r="B460" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Acionado por</v>
       </c>
       <c r="C460" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Field</v>
       </c>
       <c r="B461" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Campo</v>
       </c>
       <c r="C461" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Current value</v>
       </c>
       <c r="B462" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Valor atual</v>
       </c>
       <c r="C462" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B463" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C463" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>indent</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B464" t="str">
-        <v>indentação</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C464" t="str">
-        <v>indentação</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>sort keys</v>
+        <v>Invalid</v>
       </c>
       <c r="B465" t="str">
-        <v>ordenar chaves</v>
+        <v>Inválido</v>
       </c>
       <c r="C465" t="str">
-        <v>ordenar chaves</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B466" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+      <c r="C466" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B467" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C467" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B468" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C468" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B469" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C469" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B470" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C470" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B471" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C471" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B472" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C472" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B473" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C473" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B474" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C474" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B475" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C475" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B476" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C476" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B477" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C477" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B466" t="str">
+      <c r="B478" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C466" t="str">
+      <c r="C478" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C466"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C478"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C478"/>
+  <dimension ref="A1:C498"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4595,1085 +4595,1305 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Colour primaries</v>
+        <v>Environment</v>
       </c>
       <c r="B381" t="str">
-        <v>Primárias de cor</v>
+        <v>Ambiente</v>
       </c>
       <c r="C381" t="str">
-        <v>Primárias de cor</v>
+        <v>Ambiente</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Transfer characteristics</v>
+        <v>Detecting…</v>
       </c>
       <c r="B382" t="str">
-        <v>Características de transferência</v>
+        <v>A detetar…</v>
       </c>
       <c r="C382" t="str">
-        <v>Características de transferência</v>
+        <v>Detectando…</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Matrix coefficients</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B383" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Não foi possível detetar o ambiente.</v>
       </c>
       <c r="C383" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Não foi possível detectar o ambiente.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Video full-range flag</v>
+        <v>HDR display</v>
       </c>
       <c r="B384" t="str">
-        <v>Sinalizador de gama completa de vídeo</v>
+        <v>Ecrã HDR</v>
       </c>
       <c r="C384" t="str">
-        <v>Sinalizador de faixa completa de vídeo</v>
+        <v>Tela HDR</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Full range</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B385" t="str">
-        <v>Gama completa</v>
+        <v>Gamut alargado</v>
       </c>
       <c r="C385" t="str">
-        <v>Faixa completa</v>
+        <v>Gamut amplo</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Narrow range</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B386" t="str">
-        <v>Gama reduzida</v>
+        <v>Caminho de canvas HDR</v>
       </c>
       <c r="C386" t="str">
-        <v>Faixa reduzida</v>
+        <v>Caminho de canvas HDR</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>sRGB</v>
       </c>
       <c r="B387" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>sRGB</v>
       </c>
       <c r="C387" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>none</v>
       </c>
       <c r="B388" t="str">
-        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
+        <v>nenhum</v>
       </c>
       <c r="C388" t="str">
-        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
+        <v>nenhum</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>yes</v>
       </c>
       <c r="B389" t="str">
-        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
+        <v>sim</v>
       </c>
       <c r="C389" t="str">
-        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
+        <v>sim</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>REPORT</v>
+        <v>no</v>
       </c>
       <c r="B390" t="str">
-        <v>RELATÓRIO</v>
+        <v>não</v>
       </c>
       <c r="C390" t="str">
-        <v>RELATÓRIO</v>
+        <v>não</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>FAIL</v>
+        <v>not reported</v>
       </c>
       <c r="B391" t="str">
-        <v>REPROVADO</v>
+        <v>não reportado</v>
       </c>
       <c r="C391" t="str">
-        <v>REPROVADO</v>
+        <v>não informado</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>checks</v>
+        <v>Format</v>
       </c>
       <c r="B392" t="str">
-        <v>verificações</v>
+        <v>Formato</v>
       </c>
       <c r="C392" t="str">
-        <v>verificações</v>
+        <v>Formato</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Inspect</v>
       </c>
       <c r="B393" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Inspecionar</v>
       </c>
       <c r="C393" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Inspecionar</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Display</v>
       </c>
       <c r="B394" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Mostrar</v>
       </c>
       <c r="C394" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Exibir</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR</v>
       </c>
       <c r="B395" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>HDR</v>
       </c>
       <c r="C395" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Powered by {lib}</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B396" t="str">
-        <v>Com {lib}</v>
+        <v>Ler o perfil ICC incorporado — não precisa de codec</v>
       </c>
       <c r="C396" t="str">
-        <v>Com {lib}</v>
+        <v>Ler o perfil ICC incorporado — não precisa de codec</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Subscribe</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B397" t="str">
-        <v>Subscrever</v>
+        <v>Mostrar os pixels</v>
       </c>
       <c r="C397" t="str">
-        <v>Inscrever-se</v>
+        <v>Mostrar os pixels</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B398" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Representar mais claro do que o branco</v>
       </c>
       <c r="C398" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Renderizar mais claro que o branco</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Get notified about new releases</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B399" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Descodificado pelo profiletool, logo independente do navegador</v>
       </c>
       <c r="C399" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Decodificado pelo profiletool, portanto independente do navegador</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
       </c>
       <c r="B400" t="str">
-        <v>Fechar</v>
+        <v>Os navegadores não conseguem reportar a margem HDR de um ecrã, apenas se existe um caminho HDR.</v>
       </c>
       <c r="C400" t="str">
-        <v>Fechar</v>
+        <v>Os navegadores não conseguem informar a margem HDR de uma tela, apenas se existe um caminho HDR.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B401" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C401" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Email address</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B402" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C402" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>you@example.com</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B403" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C403" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B404" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C404" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>(optional)</v>
+        <v>Full range</v>
       </c>
       <c r="B405" t="str">
-        <v>(opcional)</v>
+        <v>Gama completa</v>
       </c>
       <c r="C405" t="str">
-        <v>(opcional)</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Narrow range</v>
       </c>
       <c r="B406" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C406" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B407" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C407" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Cancel</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B408" t="str">
-        <v>Cancelar</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C408" t="str">
-        <v>Cancelar</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Subscribe</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B409" t="str">
-        <v>Subscrever</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C409" t="str">
-        <v>Inscrever-se</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>REPORT</v>
       </c>
       <c r="B410" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C410" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>FAIL</v>
       </c>
       <c r="B411" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C411" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Close</v>
+        <v>checks</v>
       </c>
       <c r="B412" t="str">
-        <v>Fechar</v>
+        <v>verificações</v>
       </c>
       <c r="C412" t="str">
-        <v>Fechar</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Privacy notice</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B413" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C413" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B414" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C414" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B415" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C415" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B416" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C416" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B417" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C417" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B418" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C418" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Error:</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B419" t="str">
-        <v>Erro:</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C419" t="str">
-        <v>Erro:</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Convert to XML</v>
+        <v>Close</v>
       </c>
       <c r="B420" t="str">
-        <v>Converter para XML</v>
+        <v>Fechar</v>
       </c>
       <c r="C420" t="str">
-        <v>Converter para XML</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Convert to JSON</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B421" t="str">
-        <v>Converter para JSON</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C421" t="str">
-        <v>Converter para JSON</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Convert to ICC</v>
+        <v>Email address</v>
       </c>
       <c r="B422" t="str">
-        <v>Converter para ICC</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C422" t="str">
-        <v>Converter para ICC</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Converting to XML…</v>
+        <v>you@example.com</v>
       </c>
       <c r="B423" t="str">
-        <v>A converter para XML…</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C423" t="str">
-        <v>Convertendo para XML…</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Converting to JSON…</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B424" t="str">
-        <v>A converter para JSON…</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C424" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Converting to ICC…</v>
+        <v>(optional)</v>
       </c>
       <c r="B425" t="str">
-        <v>A converter para ICC…</v>
+        <v>(opcional)</v>
       </c>
       <c r="C425" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Load ICC profile</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B426" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C426" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B427" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C427" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Profile ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B428" t="str">
-        <v>ID do perfil</v>
+        <v>Cancelar</v>
       </c>
       <c r="C428" t="str">
-        <v>ID do perfil</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>No tags found.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B429" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C429" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Tag Name</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B430" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C430" t="str">
-        <v>Nome da tag</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B431" t="str">
-        <v>ID</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C431" t="str">
-        <v>ID</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Offset</v>
+        <v>Close</v>
       </c>
       <c r="B432" t="str">
-        <v>Deslocamento</v>
+        <v>Fechar</v>
       </c>
       <c r="C432" t="str">
-        <v>Deslocamento</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Size</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B433" t="str">
-        <v>Tamanho</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C433" t="str">
-        <v>Tamanho</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Pad</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B434" t="str">
-        <v>Preenchimento</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C434" t="str">
-        <v>Preenchimento</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Bytes changed since load</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B435" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C435" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Type</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B436" t="str">
-        <v>Tipo</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C436" t="str">
-        <v>Tipo</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Array of {type}</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B437" t="str">
-        <v>Vetor de {type}</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C437" t="str">
-        <v>Array de {type}</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>(No content)</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B438" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C438" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>bytes</v>
+        <v>Error:</v>
       </c>
       <c r="B439" t="str">
-        <v>bytes</v>
+        <v>Erro:</v>
       </c>
       <c r="C439" t="str">
-        <v>bytes</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Loading full description…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B440" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C440" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Could not load full description:</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B441" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C441" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B442" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C442" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B443" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C443" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>No validation output</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B444" t="str">
-        <v>Sem saída de validação</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C444" t="str">
-        <v>Sem saída de validação</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Profile is valid</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B445" t="str">
-        <v>O perfil é válido</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C445" t="str">
-        <v>O perfil é válido</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B446" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C446" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B447" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C447" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Critical validation error</v>
+        <v>Profile ID</v>
       </c>
       <c r="B448" t="str">
-        <v>Erro de validação crítico</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C448" t="str">
-        <v>Erro de validação crítico</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Unknown validation status</v>
+        <v>No tags found.</v>
       </c>
       <c r="B449" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C449" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Tag Name</v>
       </c>
       <c r="B450" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C450" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>No warnings or errors found.</v>
+        <v>ID</v>
       </c>
       <c r="B451" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>ID</v>
       </c>
       <c r="C451" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Valid</v>
+        <v>Offset</v>
       </c>
       <c r="B452" t="str">
-        <v>Válido</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C452" t="str">
-        <v>Válido</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Warning</v>
+        <v>Size</v>
       </c>
       <c r="B453" t="str">
-        <v>Aviso</v>
+        <v>Tamanho</v>
       </c>
       <c r="C453" t="str">
-        <v>Aviso</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Error</v>
+        <v>Pad</v>
       </c>
       <c r="B454" t="str">
-        <v>Erro</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C454" t="str">
-        <v>Erro</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Unknown</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B455" t="str">
-        <v>Desconhecido</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C455" t="str">
-        <v>Desconhecido</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Pass</v>
+        <v>Type</v>
       </c>
       <c r="B456" t="str">
-        <v>Aprovado</v>
+        <v>Tipo</v>
       </c>
       <c r="C456" t="str">
-        <v>Aprovado</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Fail</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B457" t="str">
-        <v>Reprovado</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C457" t="str">
-        <v>Reprovado</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>View in context</v>
+        <v>(No content)</v>
       </c>
       <c r="B458" t="str">
-        <v>Ver no contexto</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C458" t="str">
-        <v>Ver no contexto</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Validation detail</v>
+        <v>bytes</v>
       </c>
       <c r="B459" t="str">
-        <v>Detalhe de validação</v>
+        <v>bytes</v>
       </c>
       <c r="C459" t="str">
-        <v>Detalhe de validação</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Triggered by</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B460" t="str">
-        <v>Acionado por</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C460" t="str">
-        <v>Acionado por</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Field</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B461" t="str">
-        <v>Campo</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C461" t="str">
-        <v>Campo</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Current value</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B462" t="str">
-        <v>Valor atual</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C462" t="str">
-        <v>Valor atual</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Required: 0</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B463" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C463" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Expected: {value}</v>
+        <v>No validation output</v>
       </c>
       <c r="B464" t="str">
-        <v>Esperado: {value}</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C464" t="str">
-        <v>Esperado: {value}</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Invalid</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B465" t="str">
-        <v>Inválido</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C465" t="str">
-        <v>Inválido</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B466" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C466" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Close</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B467" t="str">
-        <v>Fechar</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C467" t="str">
-        <v>Fechar</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Loading XML editor…</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B468" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C468" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B469" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C469" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B470" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C470" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B471" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C471" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Valid</v>
       </c>
       <c r="B472" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Válido</v>
       </c>
       <c r="C472" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Warning</v>
       </c>
       <c r="B473" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Aviso</v>
       </c>
       <c r="C473" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Error</v>
       </c>
       <c r="B474" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Erro</v>
       </c>
       <c r="C474" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Unknown</v>
       </c>
       <c r="B475" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C475" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>indent</v>
+        <v>Pass</v>
       </c>
       <c r="B476" t="str">
-        <v>indentação</v>
+        <v>Aprovado</v>
       </c>
       <c r="C476" t="str">
-        <v>indentação</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>sort keys</v>
+        <v>Fail</v>
       </c>
       <c r="B477" t="str">
-        <v>ordenar chaves</v>
+        <v>Reprovado</v>
       </c>
       <c r="C477" t="str">
-        <v>ordenar chaves</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B478" t="str">
+        <v>Ver no contexto</v>
+      </c>
+      <c r="C478" t="str">
+        <v>Ver no contexto</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B479" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+      <c r="C479" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B480" t="str">
+        <v>Acionado por</v>
+      </c>
+      <c r="C480" t="str">
+        <v>Acionado por</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B481" t="str">
+        <v>Campo</v>
+      </c>
+      <c r="C481" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B482" t="str">
+        <v>Valor atual</v>
+      </c>
+      <c r="C482" t="str">
+        <v>Valor atual</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B483" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+      <c r="C483" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B484" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+      <c r="C484" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B485" t="str">
+        <v>Inválido</v>
+      </c>
+      <c r="C485" t="str">
+        <v>Inválido</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B486" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+      <c r="C486" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B487" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C487" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B488" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C488" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B489" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C489" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B490" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C490" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B491" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C491" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B492" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C492" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B493" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C493" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B494" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C494" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B495" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C495" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B496" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C496" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B497" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C497" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B478" t="str">
+      <c r="B498" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C478" t="str">
+      <c r="C498" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C478"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C498"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C498"/>
+  <dimension ref="A1:C502"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4606,1294 +4606,1338 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Detecting…</v>
+        <v>Showing the SDR fallback</v>
       </c>
       <c r="B382" t="str">
-        <v>A detetar…</v>
+        <v>A mostrar o recurso SDR</v>
       </c>
       <c r="C382" t="str">
-        <v>Detectando…</v>
+        <v>Mostrando o fallback SDR</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Could not detect environment.</v>
+        <v>HDR Profile in the chain</v>
       </c>
       <c r="B383" t="str">
-        <v>Não foi possível detetar o ambiente.</v>
+        <v>Perfil HDR na cadeia</v>
       </c>
       <c r="C383" t="str">
-        <v>Não foi possível detectar o ambiente.</v>
+        <v>Perfil HDR na cadeia</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>HDR display</v>
+        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B384" t="str">
-        <v>Ecrã HDR</v>
+        <v>As transformações através de um perfil HDR usam o seu AToB0Tag — a renderização SDR fixada exigida pela cláusula 8.10.6 — porque a cláusula 8.10.1 não lhe deixa etiquetas TRC. O resultado é esse recurso, não comportamento HDR.</v>
       </c>
       <c r="C384" t="str">
-        <v>Tela HDR</v>
+        <v>As transformações através de um perfil HDR usam seu AToB0Tag — a renderização SDR fixada exigida pela cláusula 8.10.6 — porque a cláusula 8.10.1 não lhe deixa tags TRC. O resultado é esse fallback, não comportamento HDR.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Wide gamut</v>
+        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B385" t="str">
-        <v>Gamut alargado</v>
+        <v>São perfis HDR, sem etiquetas TRC, pelo que o gamut é construído a partir do AToB0Tag — a renderização SDR fixada que a cláusula 8.10.6 exige a consumidores sem processamento HDR. Não é o gamut HDR do perfil, que não pode ser desenhado num PCS limitado.</v>
       </c>
       <c r="C385" t="str">
-        <v>Gamut amplo</v>
+        <v>São perfis HDR, sem tags TRC, então o gamut é construído a partir do AToB0Tag — a renderização SDR fixada que a cláusula 8.10.6 exige de consumidores sem processamento HDR. Não é o gamut HDR do perfil, que não pode ser desenhado em um PCS limitado.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>HDR canvas path</v>
+        <v>Detecting…</v>
       </c>
       <c r="B386" t="str">
-        <v>Caminho de canvas HDR</v>
+        <v>A detetar…</v>
       </c>
       <c r="C386" t="str">
-        <v>Caminho de canvas HDR</v>
+        <v>Detectando…</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>sRGB</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B387" t="str">
-        <v>sRGB</v>
+        <v>Não foi possível detetar o ambiente.</v>
       </c>
       <c r="C387" t="str">
-        <v>sRGB</v>
+        <v>Não foi possível detectar o ambiente.</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>none</v>
+        <v>HDR display</v>
       </c>
       <c r="B388" t="str">
-        <v>nenhum</v>
+        <v>Ecrã HDR</v>
       </c>
       <c r="C388" t="str">
-        <v>nenhum</v>
+        <v>Tela HDR</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>yes</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B389" t="str">
-        <v>sim</v>
+        <v>Gamut alargado</v>
       </c>
       <c r="C389" t="str">
-        <v>sim</v>
+        <v>Gamut amplo</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>no</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B390" t="str">
-        <v>não</v>
+        <v>Caminho de canvas HDR</v>
       </c>
       <c r="C390" t="str">
-        <v>não</v>
+        <v>Caminho de canvas HDR</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>not reported</v>
+        <v>sRGB</v>
       </c>
       <c r="B391" t="str">
-        <v>não reportado</v>
+        <v>sRGB</v>
       </c>
       <c r="C391" t="str">
-        <v>não informado</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Format</v>
+        <v>none</v>
       </c>
       <c r="B392" t="str">
-        <v>Formato</v>
+        <v>nenhum</v>
       </c>
       <c r="C392" t="str">
-        <v>Formato</v>
+        <v>nenhum</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Inspect</v>
+        <v>yes</v>
       </c>
       <c r="B393" t="str">
-        <v>Inspecionar</v>
+        <v>sim</v>
       </c>
       <c r="C393" t="str">
-        <v>Inspecionar</v>
+        <v>sim</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Display</v>
+        <v>no</v>
       </c>
       <c r="B394" t="str">
-        <v>Mostrar</v>
+        <v>não</v>
       </c>
       <c r="C394" t="str">
-        <v>Exibir</v>
+        <v>não</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>HDR</v>
+        <v>not reported</v>
       </c>
       <c r="B395" t="str">
-        <v>HDR</v>
+        <v>não reportado</v>
       </c>
       <c r="C395" t="str">
-        <v>HDR</v>
+        <v>não informado</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Read the embedded ICC profile — needs no codec</v>
+        <v>Format</v>
       </c>
       <c r="B396" t="str">
-        <v>Ler o perfil ICC incorporado — não precisa de codec</v>
+        <v>Formato</v>
       </c>
       <c r="C396" t="str">
-        <v>Ler o perfil ICC incorporado — não precisa de codec</v>
+        <v>Formato</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Show the pixels</v>
+        <v>Inspect</v>
       </c>
       <c r="B397" t="str">
-        <v>Mostrar os pixels</v>
+        <v>Inspecionar</v>
       </c>
       <c r="C397" t="str">
-        <v>Mostrar os pixels</v>
+        <v>Inspecionar</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Render brighter-than-white</v>
+        <v>Display</v>
       </c>
       <c r="B398" t="str">
-        <v>Representar mais claro do que o branco</v>
+        <v>Mostrar</v>
       </c>
       <c r="C398" t="str">
-        <v>Renderizar mais claro que o branco</v>
+        <v>Exibir</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Decoded by profiletool itself, so browser-independent</v>
+        <v>HDR</v>
       </c>
       <c r="B399" t="str">
-        <v>Descodificado pelo profiletool, logo independente do navegador</v>
+        <v>HDR</v>
       </c>
       <c r="C399" t="str">
-        <v>Decodificado pelo profiletool, portanto independente do navegador</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B400" t="str">
-        <v>Os navegadores não conseguem reportar a margem HDR de um ecrã, apenas se existe um caminho HDR.</v>
+        <v>Ler o perfil ICC incorporado — não precisa de codec</v>
       </c>
       <c r="C400" t="str">
-        <v>Os navegadores não conseguem informar a margem HDR de uma tela, apenas se existe um caminho HDR.</v>
+        <v>Ler o perfil ICC incorporado — não precisa de codec</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Colour primaries</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B401" t="str">
-        <v>Primárias de cor</v>
+        <v>Mostrar os pixels</v>
       </c>
       <c r="C401" t="str">
-        <v>Primárias de cor</v>
+        <v>Mostrar os pixels</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Transfer characteristics</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B402" t="str">
-        <v>Características de transferência</v>
+        <v>Representar mais claro do que o branco</v>
       </c>
       <c r="C402" t="str">
-        <v>Características de transferência</v>
+        <v>Renderizar mais claro que o branco</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Matrix coefficients</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B403" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Descodificado pelo profiletool, logo independente do navegador</v>
       </c>
       <c r="C403" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Decodificado pelo profiletool, portanto independente do navegador</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Video full-range flag</v>
+        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
       </c>
       <c r="B404" t="str">
-        <v>Sinalizador de gama completa de vídeo</v>
+        <v>Os navegadores não conseguem reportar a margem HDR de um ecrã, apenas se existe um caminho HDR.</v>
       </c>
       <c r="C404" t="str">
-        <v>Sinalizador de faixa completa de vídeo</v>
+        <v>Os navegadores não conseguem informar a margem HDR de uma tela, apenas se existe um caminho HDR.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Full range</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B405" t="str">
-        <v>Gama completa</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C405" t="str">
-        <v>Faixa completa</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Narrow range</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B406" t="str">
-        <v>Gama reduzida</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C406" t="str">
-        <v>Faixa reduzida</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B407" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C407" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B408" t="str">
-        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C408" t="str">
-        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Full range</v>
       </c>
       <c r="B409" t="str">
-        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
+        <v>Gama completa</v>
       </c>
       <c r="C409" t="str">
-        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>REPORT</v>
+        <v>Narrow range</v>
       </c>
       <c r="B410" t="str">
-        <v>RELATÓRIO</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C410" t="str">
-        <v>RELATÓRIO</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>FAIL</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B411" t="str">
-        <v>REPROVADO</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C411" t="str">
-        <v>REPROVADO</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>checks</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B412" t="str">
-        <v>verificações</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C412" t="str">
-        <v>verificações</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B413" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C413" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>REPORT</v>
       </c>
       <c r="B414" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C414" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>ICC Profile Tool</v>
+        <v>FAIL</v>
       </c>
       <c r="B415" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C415" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Powered by {lib}</v>
+        <v>checks</v>
       </c>
       <c r="B416" t="str">
-        <v>Com {lib}</v>
+        <v>verificações</v>
       </c>
       <c r="C416" t="str">
-        <v>Com {lib}</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Subscribe</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B417" t="str">
-        <v>Subscrever</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C417" t="str">
-        <v>Inscrever-se</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B418" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C418" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B419" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C419" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Close</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B420" t="str">
-        <v>Fechar</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C420" t="str">
-        <v>Fechar</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B421" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C421" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Email address</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B422" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C422" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B423" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C423" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Close</v>
       </c>
       <c r="B424" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Fechar</v>
       </c>
       <c r="C424" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>(optional)</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B425" t="str">
-        <v>(opcional)</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C425" t="str">
-        <v>(opcional)</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Email address</v>
       </c>
       <c r="B426" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C426" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B427" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C427" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Cancel</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B428" t="str">
-        <v>Cancelar</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C428" t="str">
-        <v>Cancelar</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Subscribe</v>
+        <v>(optional)</v>
       </c>
       <c r="B429" t="str">
-        <v>Subscrever</v>
+        <v>(opcional)</v>
       </c>
       <c r="C429" t="str">
-        <v>Inscrever-se</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B430" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C430" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B431" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C431" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B432" t="str">
-        <v>Fechar</v>
+        <v>Cancelar</v>
       </c>
       <c r="C432" t="str">
-        <v>Fechar</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Privacy notice</v>
+        <v>Subscribe</v>
       </c>
       <c r="B433" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Subscrever</v>
       </c>
       <c r="C433" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B434" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C434" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B435" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C435" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Close</v>
       </c>
       <c r="B436" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Fechar</v>
       </c>
       <c r="C436" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B437" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C437" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B438" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C438" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Error:</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B439" t="str">
-        <v>Erro:</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C439" t="str">
-        <v>Erro:</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Convert to XML</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B440" t="str">
-        <v>Converter para XML</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C440" t="str">
-        <v>Converter para XML</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Convert to JSON</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B441" t="str">
-        <v>Converter para JSON</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C441" t="str">
-        <v>Converter para JSON</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Convert to ICC</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B442" t="str">
-        <v>Converter para ICC</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C442" t="str">
-        <v>Converter para ICC</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Converting to XML…</v>
+        <v>Error:</v>
       </c>
       <c r="B443" t="str">
-        <v>A converter para XML…</v>
+        <v>Erro:</v>
       </c>
       <c r="C443" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B444" t="str">
-        <v>A converter para JSON…</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C444" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B445" t="str">
-        <v>A converter para ICC…</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C445" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B446" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C446" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B447" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C447" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Profile ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B448" t="str">
-        <v>ID do perfil</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C448" t="str">
-        <v>ID do perfil</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>No tags found.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B449" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C449" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Tag Name</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B450" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C450" t="str">
-        <v>Nome da tag</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B451" t="str">
-        <v>ID</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C451" t="str">
-        <v>ID</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Offset</v>
+        <v>Profile ID</v>
       </c>
       <c r="B452" t="str">
-        <v>Deslocamento</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C452" t="str">
-        <v>Deslocamento</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Size</v>
+        <v>No tags found.</v>
       </c>
       <c r="B453" t="str">
-        <v>Tamanho</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C453" t="str">
-        <v>Tamanho</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Pad</v>
+        <v>Tag Name</v>
       </c>
       <c r="B454" t="str">
-        <v>Preenchimento</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C454" t="str">
-        <v>Preenchimento</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Bytes changed since load</v>
+        <v>ID</v>
       </c>
       <c r="B455" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>ID</v>
       </c>
       <c r="C455" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Type</v>
+        <v>Offset</v>
       </c>
       <c r="B456" t="str">
-        <v>Tipo</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C456" t="str">
-        <v>Tipo</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Array of {type}</v>
+        <v>Size</v>
       </c>
       <c r="B457" t="str">
-        <v>Vetor de {type}</v>
+        <v>Tamanho</v>
       </c>
       <c r="C457" t="str">
-        <v>Array de {type}</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>(No content)</v>
+        <v>Pad</v>
       </c>
       <c r="B458" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C458" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>bytes</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B459" t="str">
-        <v>bytes</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C459" t="str">
-        <v>bytes</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Loading full description…</v>
+        <v>Type</v>
       </c>
       <c r="B460" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Tipo</v>
       </c>
       <c r="C460" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Could not load full description:</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B461" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C461" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>(No content)</v>
       </c>
       <c r="B462" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C462" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>bytes</v>
       </c>
       <c r="B463" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>bytes</v>
       </c>
       <c r="C463" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>No validation output</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B464" t="str">
-        <v>Sem saída de validação</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C464" t="str">
-        <v>Sem saída de validação</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Profile is valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B465" t="str">
-        <v>O perfil é válido</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C465" t="str">
-        <v>O perfil é válido</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Profile has warning(s)</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B466" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C466" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B467" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C467" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Critical validation error</v>
+        <v>No validation output</v>
       </c>
       <c r="B468" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C468" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B469" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C469" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B470" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C470" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B471" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C471" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B472" t="str">
-        <v>Válido</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C472" t="str">
-        <v>Válido</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Warning</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B473" t="str">
-        <v>Aviso</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C473" t="str">
-        <v>Aviso</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Error</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B474" t="str">
-        <v>Erro</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C474" t="str">
-        <v>Erro</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Unknown</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B475" t="str">
-        <v>Desconhecido</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C475" t="str">
-        <v>Desconhecido</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Pass</v>
+        <v>Valid</v>
       </c>
       <c r="B476" t="str">
-        <v>Aprovado</v>
+        <v>Válido</v>
       </c>
       <c r="C476" t="str">
-        <v>Aprovado</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Fail</v>
+        <v>Warning</v>
       </c>
       <c r="B477" t="str">
-        <v>Reprovado</v>
+        <v>Aviso</v>
       </c>
       <c r="C477" t="str">
-        <v>Reprovado</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B478" t="str">
-        <v>Ver no contexto</v>
+        <v>Erro</v>
       </c>
       <c r="C478" t="str">
-        <v>Ver no contexto</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B479" t="str">
-        <v>Detalhe de validação</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C479" t="str">
-        <v>Detalhe de validação</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Triggered by</v>
+        <v>Pass</v>
       </c>
       <c r="B480" t="str">
-        <v>Acionado por</v>
+        <v>Aprovado</v>
       </c>
       <c r="C480" t="str">
-        <v>Acionado por</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Field</v>
+        <v>Fail</v>
       </c>
       <c r="B481" t="str">
-        <v>Campo</v>
+        <v>Reprovado</v>
       </c>
       <c r="C481" t="str">
-        <v>Campo</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Current value</v>
+        <v>View in context</v>
       </c>
       <c r="B482" t="str">
-        <v>Valor atual</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C482" t="str">
-        <v>Valor atual</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Required: 0</v>
+        <v>Validation detail</v>
       </c>
       <c r="B483" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C483" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Expected: {value}</v>
+        <v>Triggered by</v>
       </c>
       <c r="B484" t="str">
-        <v>Esperado: {value}</v>
+        <v>Acionado por</v>
       </c>
       <c r="C484" t="str">
-        <v>Esperado: {value}</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Invalid</v>
+        <v>Field</v>
       </c>
       <c r="B485" t="str">
-        <v>Inválido</v>
+        <v>Campo</v>
       </c>
       <c r="C485" t="str">
-        <v>Inválido</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Current value</v>
       </c>
       <c r="B486" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Valor atual</v>
       </c>
       <c r="C486" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Close</v>
+        <v>Required: 0</v>
       </c>
       <c r="B487" t="str">
-        <v>Fechar</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C487" t="str">
-        <v>Fechar</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Loading XML editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B488" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C488" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B489" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Inválido</v>
       </c>
       <c r="C489" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B490" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C490" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B491" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Fechar</v>
       </c>
       <c r="C491" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B492" t="str">
-        <v>● edições XML por guardar</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C492" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B493" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C493" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B494" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C494" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B495" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C495" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>indent</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B496" t="str">
-        <v>indentação</v>
+        <v>● edições XML por guardar</v>
       </c>
       <c r="C496" t="str">
-        <v>indentação</v>
+        <v>● edições XML não salvas</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>sort keys</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B497" t="str">
-        <v>ordenar chaves</v>
+        <v>● edições JSON por guardar</v>
       </c>
       <c r="C497" t="str">
-        <v>ordenar chaves</v>
+        <v>● edições JSON não salvas</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B498" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C498" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B499" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C499" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B500" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C500" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B501" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C501" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B498" t="str">
+      <c r="B502" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C498" t="str">
+      <c r="C502" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C498"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C502"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C502"/>
+  <dimension ref="A1:C512"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4859,1085 +4859,1195 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Colour primaries</v>
+        <v>Browser flags</v>
       </c>
       <c r="B405" t="str">
-        <v>Primárias de cor</v>
+        <v>Flags do navegador</v>
       </c>
       <c r="C405" t="str">
-        <v>Primárias de cor</v>
+        <v>Flags do navegador</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Transfer characteristics</v>
+        <v>on</v>
       </c>
       <c r="B406" t="str">
-        <v>Características de transferência</v>
+        <v>ativa</v>
       </c>
       <c r="C406" t="str">
-        <v>Características de transferência</v>
+        <v>ativada</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Matrix coefficients</v>
+        <v>not enabled</v>
       </c>
       <c r="B407" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>não ativa</v>
       </c>
       <c r="C407" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>não ativada</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Video full-range flag</v>
+        <v>cannot be detected here</v>
       </c>
       <c r="B408" t="str">
-        <v>Sinalizador de gama completa de vídeo</v>
+        <v>não é possível detetar aqui</v>
       </c>
       <c r="C408" t="str">
-        <v>Sinalizador de faixa completa de vídeo</v>
+        <v>não é possível detectar aqui</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Full range</v>
+        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
       </c>
       <c r="B409" t="str">
-        <v>Gama completa</v>
+        <v>Necessário para renderização HDR neste navegador: sem WebGPU, o canvas HDR é a única via. A inspeção de perfis funciona sem isto.</v>
       </c>
       <c r="C409" t="str">
-        <v>Faixa completa</v>
+        <v>Necessário para renderização HDR neste navegador: sem WebGPU, o canvas HDR é a única via. A inspeção de perfis funciona sem isso.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Narrow range</v>
+        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
       </c>
       <c r="B410" t="str">
-        <v>Gama reduzida</v>
+        <v>Opcional: o HDR pode ser renderizado via WebGPU, mas isto acrescenta a via canvas HDR e permite ao profiletool ler a margem HDR real do ecrã.</v>
       </c>
       <c r="C410" t="str">
-        <v>Faixa reduzida</v>
+        <v>Opcional: o HDR pode ser renderizado via WebGPU, mas isto adiciona a via canvas HDR e permite ao profiletool ler a margem HDR real da tela.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
       </c>
       <c r="B411" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>As páginas web não podem abrir páginas de flags. Cole isto na barra de endereço, escolha Enabled e reinicie o navegador.</v>
       </c>
       <c r="C411" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Páginas web não podem abrir páginas de flags. Cole isto na barra de endereço, escolha Enabled e reinicie o navegador.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Copy</v>
       </c>
       <c r="B412" t="str">
-        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
+        <v>Copiar</v>
       </c>
       <c r="C412" t="str">
-        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
+        <v>Copiar</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Copied</v>
       </c>
       <c r="B413" t="str">
-        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
+        <v>Copiado</v>
       </c>
       <c r="C413" t="str">
-        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
+        <v>Copiado</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>REPORT</v>
+        <v>Copy failed — select the address and copy it.</v>
       </c>
       <c r="B414" t="str">
-        <v>RELATÓRIO</v>
+        <v>Falha ao copiar — selecione o endereço e copie-o.</v>
       </c>
       <c r="C414" t="str">
-        <v>RELATÓRIO</v>
+        <v>Falha ao copiar — selecione o endereço e copie.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>FAIL</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B415" t="str">
-        <v>REPROVADO</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C415" t="str">
-        <v>REPROVADO</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>checks</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B416" t="str">
-        <v>verificações</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C416" t="str">
-        <v>verificações</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B417" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C417" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B418" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C418" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Full range</v>
       </c>
       <c r="B419" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Gama completa</v>
       </c>
       <c r="C419" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Powered by {lib}</v>
+        <v>Narrow range</v>
       </c>
       <c r="B420" t="str">
-        <v>Com {lib}</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C420" t="str">
-        <v>Com {lib}</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Subscribe</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B421" t="str">
-        <v>Subscrever</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C421" t="str">
-        <v>Inscrever-se</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B422" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C422" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Get notified about new releases</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B423" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C423" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Close</v>
+        <v>REPORT</v>
       </c>
       <c r="B424" t="str">
-        <v>Fechar</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C424" t="str">
-        <v>Fechar</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>FAIL</v>
       </c>
       <c r="B425" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C425" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Email address</v>
+        <v>checks</v>
       </c>
       <c r="B426" t="str">
-        <v>Endereço de e-mail</v>
+        <v>verificações</v>
       </c>
       <c r="C426" t="str">
-        <v>Endereço de e-mail</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>you@example.com</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B427" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C427" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B428" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C428" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B429" t="str">
-        <v>(opcional)</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C429" t="str">
-        <v>(opcional)</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B430" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C430" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B431" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C431" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B432" t="str">
-        <v>Cancelar</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C432" t="str">
-        <v>Cancelar</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B433" t="str">
-        <v>Subscrever</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C433" t="str">
-        <v>Inscrever-se</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Close</v>
       </c>
       <c r="B434" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Fechar</v>
       </c>
       <c r="C434" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B435" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C435" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B436" t="str">
-        <v>Fechar</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C436" t="str">
-        <v>Fechar</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Privacy notice</v>
+        <v>you@example.com</v>
       </c>
       <c r="B437" t="str">
-        <v>Aviso de privacidade</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C437" t="str">
-        <v>Aviso de privacidade</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B438" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C438" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>(optional)</v>
       </c>
       <c r="B439" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>(opcional)</v>
       </c>
       <c r="C439" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Please check the form and try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B440" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C440" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B441" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C441" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B442" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Cancelar</v>
       </c>
       <c r="C442" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Error:</v>
+        <v>Subscribe</v>
       </c>
       <c r="B443" t="str">
-        <v>Erro:</v>
+        <v>Subscrever</v>
       </c>
       <c r="C443" t="str">
-        <v>Erro:</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Convert to XML</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B444" t="str">
-        <v>Converter para XML</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C444" t="str">
-        <v>Converter para XML</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Convert to JSON</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B445" t="str">
-        <v>Converter para JSON</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C445" t="str">
-        <v>Converter para JSON</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Convert to ICC</v>
+        <v>Close</v>
       </c>
       <c r="B446" t="str">
-        <v>Converter para ICC</v>
+        <v>Fechar</v>
       </c>
       <c r="C446" t="str">
-        <v>Converter para ICC</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Converting to XML…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B447" t="str">
-        <v>A converter para XML…</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C447" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B448" t="str">
-        <v>A converter para JSON…</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C448" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Converting to ICC…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B449" t="str">
-        <v>A converter para ICC…</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C449" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Load ICC profile</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B450" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C450" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B451" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C451" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Profile ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B452" t="str">
-        <v>ID do perfil</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C452" t="str">
-        <v>ID do perfil</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>No tags found.</v>
+        <v>Error:</v>
       </c>
       <c r="B453" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Erro:</v>
       </c>
       <c r="C453" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Tag Name</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B454" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C454" t="str">
-        <v>Nome da tag</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B455" t="str">
-        <v>ID</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C455" t="str">
-        <v>ID</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Offset</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B456" t="str">
-        <v>Deslocamento</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C456" t="str">
-        <v>Deslocamento</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Size</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B457" t="str">
-        <v>Tamanho</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C457" t="str">
-        <v>Tamanho</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Pad</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B458" t="str">
-        <v>Preenchimento</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C458" t="str">
-        <v>Preenchimento</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B459" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C459" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Type</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B460" t="str">
-        <v>Tipo</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C460" t="str">
-        <v>Tipo</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Array of {type}</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B461" t="str">
-        <v>Vetor de {type}</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C461" t="str">
-        <v>Array de {type}</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>(No content)</v>
+        <v>Profile ID</v>
       </c>
       <c r="B462" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C462" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>bytes</v>
+        <v>No tags found.</v>
       </c>
       <c r="B463" t="str">
-        <v>bytes</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C463" t="str">
-        <v>bytes</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Loading full description…</v>
+        <v>Tag Name</v>
       </c>
       <c r="B464" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C464" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Could not load full description:</v>
+        <v>ID</v>
       </c>
       <c r="B465" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>ID</v>
       </c>
       <c r="C465" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Offset</v>
       </c>
       <c r="B466" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C466" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Size</v>
       </c>
       <c r="B467" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Tamanho</v>
       </c>
       <c r="C467" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>No validation output</v>
+        <v>Pad</v>
       </c>
       <c r="B468" t="str">
-        <v>Sem saída de validação</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C468" t="str">
-        <v>Sem saída de validação</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Profile is valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B469" t="str">
-        <v>O perfil é válido</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C469" t="str">
-        <v>O perfil é válido</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Type</v>
       </c>
       <c r="B470" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Tipo</v>
       </c>
       <c r="C470" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B471" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C471" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Critical validation error</v>
+        <v>(No content)</v>
       </c>
       <c r="B472" t="str">
-        <v>Erro de validação crítico</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C472" t="str">
-        <v>Erro de validação crítico</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Unknown validation status</v>
+        <v>bytes</v>
       </c>
       <c r="B473" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>bytes</v>
       </c>
       <c r="C473" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B474" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C474" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B475" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C475" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B476" t="str">
-        <v>Válido</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C476" t="str">
-        <v>Válido</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Warning</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B477" t="str">
-        <v>Aviso</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C477" t="str">
-        <v>Aviso</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Error</v>
+        <v>No validation output</v>
       </c>
       <c r="B478" t="str">
-        <v>Erro</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C478" t="str">
-        <v>Erro</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Unknown</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B479" t="str">
-        <v>Desconhecido</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C479" t="str">
-        <v>Desconhecido</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Pass</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B480" t="str">
-        <v>Aprovado</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C480" t="str">
-        <v>Aprovado</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Fail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B481" t="str">
-        <v>Reprovado</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C481" t="str">
-        <v>Reprovado</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>View in context</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B482" t="str">
-        <v>Ver no contexto</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C482" t="str">
-        <v>Ver no contexto</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Validation detail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B483" t="str">
-        <v>Detalhe de validação</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C483" t="str">
-        <v>Detalhe de validação</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Triggered by</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B484" t="str">
-        <v>Acionado por</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C484" t="str">
-        <v>Acionado por</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Field</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B485" t="str">
-        <v>Campo</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C485" t="str">
-        <v>Campo</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Current value</v>
+        <v>Valid</v>
       </c>
       <c r="B486" t="str">
-        <v>Valor atual</v>
+        <v>Válido</v>
       </c>
       <c r="C486" t="str">
-        <v>Valor atual</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Required: 0</v>
+        <v>Warning</v>
       </c>
       <c r="B487" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Aviso</v>
       </c>
       <c r="C487" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Expected: {value}</v>
+        <v>Error</v>
       </c>
       <c r="B488" t="str">
-        <v>Esperado: {value}</v>
+        <v>Erro</v>
       </c>
       <c r="C488" t="str">
-        <v>Esperado: {value}</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Invalid</v>
+        <v>Unknown</v>
       </c>
       <c r="B489" t="str">
-        <v>Inválido</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C489" t="str">
-        <v>Inválido</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Pass</v>
       </c>
       <c r="B490" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Aprovado</v>
       </c>
       <c r="C490" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Close</v>
+        <v>Fail</v>
       </c>
       <c r="B491" t="str">
-        <v>Fechar</v>
+        <v>Reprovado</v>
       </c>
       <c r="C491" t="str">
-        <v>Fechar</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B492" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C492" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B493" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C493" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B494" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Acionado por</v>
       </c>
       <c r="C494" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B495" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Campo</v>
       </c>
       <c r="C495" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B496" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Valor atual</v>
       </c>
       <c r="C496" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B497" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C497" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B498" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C498" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B499" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Inválido</v>
       </c>
       <c r="C499" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B500" t="str">
-        <v>indentação</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C500" t="str">
-        <v>indentação</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B501" t="str">
-        <v>ordenar chaves</v>
+        <v>Fechar</v>
       </c>
       <c r="C501" t="str">
-        <v>ordenar chaves</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B502" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C502" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B503" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C503" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B504" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C504" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B505" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C505" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B506" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C506" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B507" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C507" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B508" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C508" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B509" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C509" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B510" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C510" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B511" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C511" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B502" t="str">
+      <c r="B512" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C502" t="str">
+      <c r="C512" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C502"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C512"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C512"/>
+  <dimension ref="A1:C529"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4848,13 +4848,13 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
+        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
       </c>
       <c r="B404" t="str">
-        <v>Os navegadores não conseguem reportar a margem HDR de um ecrã, apenas se existe um caminho HDR.</v>
+        <v>Este navegador não indicou a margem HDR do ecrã, apenas se existe um caminho HDR.</v>
       </c>
       <c r="C404" t="str">
-        <v>Os navegadores não conseguem informar a margem HDR de uma tela, apenas se existe um caminho HDR.</v>
+        <v>Este navegador não informou a margem HDR da tela, apenas se existe um caminho HDR.</v>
       </c>
     </row>
     <row r="405">
@@ -4969,1085 +4969,1272 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Colour primaries</v>
+        <v>Pixel ratio</v>
       </c>
       <c r="B415" t="str">
-        <v>Primárias de cor</v>
+        <v>Relação de píxeis</v>
       </c>
       <c r="C415" t="str">
-        <v>Primárias de cor</v>
+        <v>Proporção de pixels</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Transfer characteristics</v>
+        <v>Current monitor</v>
       </c>
       <c r="B416" t="str">
-        <v>Características de transferência</v>
+        <v>Monitor atual</v>
       </c>
       <c r="C416" t="str">
-        <v>Características de transferência</v>
+        <v>Monitor atual</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Matrix coefficients</v>
+        <v>unnamed</v>
       </c>
       <c r="B417" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>sem nome</v>
       </c>
       <c r="C417" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>sem nome</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Video full-range flag</v>
+        <v>primary</v>
       </c>
       <c r="B418" t="str">
-        <v>Sinalizador de gama completa de vídeo</v>
+        <v>principal</v>
       </c>
       <c r="C418" t="str">
-        <v>Sinalizador de faixa completa de vídeo</v>
+        <v>principal</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Full range</v>
+        <v>built-in</v>
       </c>
       <c r="B419" t="str">
-        <v>Gama completa</v>
+        <v>integrado</v>
       </c>
       <c r="C419" t="str">
-        <v>Faixa completa</v>
+        <v>integrado</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Narrow range</v>
+        <v>HDR headroom</v>
       </c>
       <c r="B420" t="str">
-        <v>Gama reduzida</v>
+        <v>Margem HDR</v>
       </c>
       <c r="C420" t="str">
-        <v>Faixa reduzida</v>
+        <v>Margem HDR</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>not exposed by this browser</v>
       </c>
       <c r="B421" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>não exposta por este navegador</v>
       </c>
       <c r="C421" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>não exposta por este navegador</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Shown exactly as the browser reports it. The unit is not standardised yet; an SDR screen has been observed to report 0.</v>
       </c>
       <c r="B422" t="str">
-        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
+        <v>Mostrada tal como o navegador a indica. A unidade ainda não está normalizada; um ecrã SDR indicou 0.</v>
       </c>
       <c r="C422" t="str">
-        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
+        <v>Exibida exatamente como o navegador informa. A unidade ainda não é padronizada; uma tela SDR informou 0.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B423" t="str">
-        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
+        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
       </c>
       <c r="C423" t="str">
-        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
+        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>REPORT</v>
+        <v>Identify displays</v>
       </c>
       <c r="B424" t="str">
-        <v>RELATÓRIO</v>
+        <v>Identificar ecrãs</v>
       </c>
       <c r="C424" t="str">
-        <v>RELATÓRIO</v>
+        <v>Identificar telas</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>FAIL</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B425" t="str">
-        <v>REPROVADO</v>
+        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
       <c r="C425" t="str">
-        <v>REPROVADO</v>
+        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>checks</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B426" t="str">
-        <v>verificações</v>
+        <v>A acompanhar em que monitor está esta janela.</v>
       </c>
       <c r="C426" t="str">
-        <v>verificações</v>
+        <v>Acompanhando em qual monitor esta janela está.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B427" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
       </c>
       <c r="C427" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B428" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
       </c>
       <c r="C428" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B429" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Não foi possível identificar os ecrãs.</v>
       </c>
       <c r="C429" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Não foi possível identificar as telas.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Powered by {lib}</v>
+        <v>Display events</v>
       </c>
       <c r="B430" t="str">
-        <v>Com {lib}</v>
+        <v>Eventos de ecrã</v>
       </c>
       <c r="C430" t="str">
-        <v>Com {lib}</v>
+        <v>Eventos de tela</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Subscribe</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B431" t="str">
-        <v>Subscrever</v>
+        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
       </c>
       <c r="C431" t="str">
-        <v>Inscrever-se</v>
+        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B432" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C432" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Get notified about new releases</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B433" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C433" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Close</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B434" t="str">
-        <v>Fechar</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C434" t="str">
-        <v>Fechar</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B435" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C435" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Email address</v>
+        <v>Full range</v>
       </c>
       <c r="B436" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Gama completa</v>
       </c>
       <c r="C436" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>you@example.com</v>
+        <v>Narrow range</v>
       </c>
       <c r="B437" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C437" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>How will you use profiletool?</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B438" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C438" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>(optional)</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B439" t="str">
-        <v>(opcional)</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C439" t="str">
-        <v>(opcional)</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B440" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C440" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B441" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C441" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B442" t="str">
-        <v>Cancelar</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C442" t="str">
-        <v>Cancelar</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B443" t="str">
-        <v>Subscrever</v>
+        <v>verificações</v>
       </c>
       <c r="C443" t="str">
-        <v>Inscrever-se</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B444" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C444" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B445" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C445" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B446" t="str">
-        <v>Fechar</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C446" t="str">
-        <v>Fechar</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B447" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C447" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B448" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C448" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B449" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C449" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B450" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C450" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B451" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Fechar</v>
       </c>
       <c r="C451" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B452" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C452" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B453" t="str">
-        <v>Erro:</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C453" t="str">
-        <v>Erro:</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B454" t="str">
-        <v>Converter para XML</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C454" t="str">
-        <v>Converter para XML</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B455" t="str">
-        <v>Converter para JSON</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C455" t="str">
-        <v>Converter para JSON</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B456" t="str">
-        <v>Converter para ICC</v>
+        <v>(opcional)</v>
       </c>
       <c r="C456" t="str">
-        <v>Converter para ICC</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B457" t="str">
-        <v>A converter para XML…</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C457" t="str">
-        <v>Convertendo para XML…</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B458" t="str">
-        <v>A converter para JSON…</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C458" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B459" t="str">
-        <v>A converter para ICC…</v>
+        <v>Cancelar</v>
       </c>
       <c r="C459" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B460" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Subscrever</v>
       </c>
       <c r="C460" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B461" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C461" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B462" t="str">
-        <v>ID do perfil</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C462" t="str">
-        <v>ID do perfil</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B463" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Fechar</v>
       </c>
       <c r="C463" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B464" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C464" t="str">
-        <v>Nome da tag</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B465" t="str">
-        <v>ID</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C465" t="str">
-        <v>ID</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B466" t="str">
-        <v>Deslocamento</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C466" t="str">
-        <v>Deslocamento</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B467" t="str">
-        <v>Tamanho</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C467" t="str">
-        <v>Tamanho</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B468" t="str">
-        <v>Preenchimento</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C468" t="str">
-        <v>Preenchimento</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B469" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C469" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B470" t="str">
-        <v>Tipo</v>
+        <v>Erro:</v>
       </c>
       <c r="C470" t="str">
-        <v>Tipo</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B471" t="str">
-        <v>Vetor de {type}</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C471" t="str">
-        <v>Array de {type}</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B472" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C472" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B473" t="str">
-        <v>bytes</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C473" t="str">
-        <v>bytes</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B474" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C474" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B475" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C475" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B476" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C476" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B477" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C477" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B478" t="str">
-        <v>Sem saída de validação</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C478" t="str">
-        <v>Sem saída de validação</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B479" t="str">
-        <v>O perfil é válido</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C479" t="str">
-        <v>O perfil é válido</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B480" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C480" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B481" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C481" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B482" t="str">
-        <v>Erro de validação crítico</v>
+        <v>ID</v>
       </c>
       <c r="C482" t="str">
-        <v>Erro de validação crítico</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B483" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C483" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B484" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Tamanho</v>
       </c>
       <c r="C484" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B485" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C485" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B486" t="str">
-        <v>Válido</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C486" t="str">
-        <v>Válido</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B487" t="str">
-        <v>Aviso</v>
+        <v>Tipo</v>
       </c>
       <c r="C487" t="str">
-        <v>Aviso</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B488" t="str">
-        <v>Erro</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C488" t="str">
-        <v>Erro</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B489" t="str">
-        <v>Desconhecido</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C489" t="str">
-        <v>Desconhecido</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B490" t="str">
-        <v>Aprovado</v>
+        <v>bytes</v>
       </c>
       <c r="C490" t="str">
-        <v>Aprovado</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B491" t="str">
-        <v>Reprovado</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C491" t="str">
-        <v>Reprovado</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B492" t="str">
-        <v>Ver no contexto</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C492" t="str">
-        <v>Ver no contexto</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B493" t="str">
-        <v>Detalhe de validação</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C493" t="str">
-        <v>Detalhe de validação</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B494" t="str">
-        <v>Acionado por</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C494" t="str">
-        <v>Acionado por</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B495" t="str">
-        <v>Campo</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C495" t="str">
-        <v>Campo</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B496" t="str">
-        <v>Valor atual</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C496" t="str">
-        <v>Valor atual</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B497" t="str">
-        <v>Obrigatório: 0</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C497" t="str">
-        <v>Obrigatório: 0</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B498" t="str">
-        <v>Esperado: {value}</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C498" t="str">
-        <v>Esperado: {value}</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B499" t="str">
-        <v>Inválido</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C499" t="str">
-        <v>Inválido</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B500" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C500" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B501" t="str">
-        <v>Fechar</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C501" t="str">
-        <v>Fechar</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B502" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C502" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B503" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Válido</v>
       </c>
       <c r="C503" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B504" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Aviso</v>
       </c>
       <c r="C504" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B505" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Erro</v>
       </c>
       <c r="C505" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B506" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C506" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B507" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Aprovado</v>
       </c>
       <c r="C507" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B508" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Reprovado</v>
       </c>
       <c r="C508" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B509" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C509" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B510" t="str">
-        <v>indentação</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C510" t="str">
-        <v>indentação</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B511" t="str">
-        <v>ordenar chaves</v>
+        <v>Acionado por</v>
       </c>
       <c r="C511" t="str">
-        <v>ordenar chaves</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B512" t="str">
+        <v>Campo</v>
+      </c>
+      <c r="C512" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B513" t="str">
+        <v>Valor atual</v>
+      </c>
+      <c r="C513" t="str">
+        <v>Valor atual</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B514" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+      <c r="C514" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B515" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+      <c r="C515" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B516" t="str">
+        <v>Inválido</v>
+      </c>
+      <c r="C516" t="str">
+        <v>Inválido</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B517" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+      <c r="C517" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B518" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C518" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B519" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C519" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B520" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C520" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B521" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C521" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B522" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C522" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B523" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C523" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B524" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C524" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B525" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C525" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B526" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C526" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B527" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C527" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B528" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C528" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B512" t="str">
+      <c r="B529" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C512" t="str">
+      <c r="C529" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C512"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C529"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C529"/>
+  <dimension ref="A1:C530"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5046,1195 +5046,1206 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Shown exactly as the browser reports it. The unit is not standardised yet; an SDR screen has been observed to report 0.</v>
+        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
       </c>
       <c r="B422" t="str">
-        <v>Mostrada tal como o navegador a indica. A unidade ainda não está normalizada; um ecrã SDR indicou 0.</v>
+        <v>O Chromium indica isto em stops: log₂ da luminância máxima do ecrã ÷ o nível de branco SDR. No Windows só é atualizado quando o Chrome volta a ler o ecrã — janela movida para outro ecrã ou Chrome reativado — e não quando o brilho muda.</v>
       </c>
       <c r="C422" t="str">
-        <v>Exibida exatamente como o navegador informa. A unidade ainda não é padronizada; uma tela SDR informou 0.</v>
+        <v>O Chromium informa isso em stops: log₂ do brilho máximo da tela ÷ o nível de branco SDR. No Windows, só é atualizado quando o Chrome relê a tela — janela movida para outra tela ou Chrome reativado — e não quando o brilho muda.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>{stops} stops (≈{ratio}× SDR white)</v>
       </c>
       <c r="B423" t="str">
-        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
+        <v>{stops} stops (≈{ratio}× o branco SDR)</v>
       </c>
       <c r="C423" t="str">
-        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
+        <v>{stops} stops (≈{ratio}× o branco SDR)</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B424" t="str">
-        <v>Identificar ecrãs</v>
+        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
       </c>
       <c r="C424" t="str">
-        <v>Identificar telas</v>
+        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B425" t="str">
-        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Identificar ecrãs</v>
       </c>
       <c r="C425" t="str">
-        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Identificar telas</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B426" t="str">
-        <v>A acompanhar em que monitor está esta janela.</v>
+        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
       <c r="C426" t="str">
-        <v>Acompanhando em qual monitor esta janela está.</v>
+        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B427" t="str">
-        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
+        <v>A acompanhar em que monitor está esta janela.</v>
       </c>
       <c r="C427" t="str">
-        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
+        <v>Acompanhando em qual monitor esta janela está.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B428" t="str">
-        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
+        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
       </c>
       <c r="C428" t="str">
-        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
+        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B429" t="str">
-        <v>Não foi possível identificar os ecrãs.</v>
+        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
       </c>
       <c r="C429" t="str">
-        <v>Não foi possível identificar as telas.</v>
+        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B430" t="str">
-        <v>Eventos de ecrã</v>
+        <v>Não foi possível identificar os ecrãs.</v>
       </c>
       <c r="C430" t="str">
-        <v>Eventos de tela</v>
+        <v>Não foi possível identificar as telas.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B431" t="str">
-        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
+        <v>Eventos de ecrã</v>
       </c>
       <c r="C431" t="str">
-        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
+        <v>Eventos de tela</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B432" t="str">
-        <v>Primárias de cor</v>
+        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
       </c>
       <c r="C432" t="str">
-        <v>Primárias de cor</v>
+        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B433" t="str">
-        <v>Características de transferência</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C433" t="str">
-        <v>Características de transferência</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B434" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C434" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B435" t="str">
-        <v>Sinalizador de gama completa de vídeo</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C435" t="str">
-        <v>Sinalizador de faixa completa de vídeo</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B436" t="str">
-        <v>Gama completa</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C436" t="str">
-        <v>Faixa completa</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B437" t="str">
-        <v>Gama reduzida</v>
+        <v>Gama completa</v>
       </c>
       <c r="C437" t="str">
-        <v>Faixa reduzida</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B438" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C438" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B439" t="str">
-        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C439" t="str">
-        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B440" t="str">
-        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C440" t="str">
-        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B441" t="str">
-        <v>RELATÓRIO</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C441" t="str">
-        <v>RELATÓRIO</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B442" t="str">
-        <v>REPROVADO</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C442" t="str">
-        <v>REPROVADO</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B443" t="str">
-        <v>verificações</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C443" t="str">
-        <v>verificações</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B444" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>verificações</v>
       </c>
       <c r="C444" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B445" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C445" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B446" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C446" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B447" t="str">
-        <v>Com {lib}</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C447" t="str">
-        <v>Com {lib}</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B448" t="str">
-        <v>Subscrever</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C448" t="str">
-        <v>Inscrever-se</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B449" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Subscrever</v>
       </c>
       <c r="C449" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B450" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C450" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B451" t="str">
-        <v>Fechar</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C451" t="str">
-        <v>Fechar</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B452" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Fechar</v>
       </c>
       <c r="C452" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B453" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C453" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B454" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C454" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B455" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C455" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B456" t="str">
-        <v>(opcional)</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C456" t="str">
-        <v>(opcional)</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B457" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>(opcional)</v>
       </c>
       <c r="C457" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B458" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C458" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B459" t="str">
-        <v>Cancelar</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C459" t="str">
-        <v>Cancelar</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B460" t="str">
-        <v>Subscrever</v>
+        <v>Cancelar</v>
       </c>
       <c r="C460" t="str">
-        <v>Inscrever-se</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B461" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C461" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B462" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C462" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B463" t="str">
-        <v>Fechar</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C463" t="str">
-        <v>Fechar</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B464" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Fechar</v>
       </c>
       <c r="C464" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B465" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C465" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B466" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C466" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B467" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C467" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B468" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C468" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B469" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C469" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B470" t="str">
-        <v>Erro:</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C470" t="str">
-        <v>Erro:</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B471" t="str">
-        <v>Converter para XML</v>
+        <v>Erro:</v>
       </c>
       <c r="C471" t="str">
-        <v>Converter para XML</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B472" t="str">
-        <v>Converter para JSON</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C472" t="str">
-        <v>Converter para JSON</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B473" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C473" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B474" t="str">
-        <v>A converter para XML…</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C474" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B475" t="str">
-        <v>A converter para JSON…</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C475" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B476" t="str">
-        <v>A converter para ICC…</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C476" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B477" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C477" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B478" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C478" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B479" t="str">
-        <v>ID do perfil</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C479" t="str">
-        <v>ID do perfil</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B480" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C480" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B481" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C481" t="str">
-        <v>Nome da tag</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B482" t="str">
-        <v>ID</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C482" t="str">
-        <v>ID</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B483" t="str">
-        <v>Deslocamento</v>
+        <v>ID</v>
       </c>
       <c r="C483" t="str">
-        <v>Deslocamento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B484" t="str">
-        <v>Tamanho</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C484" t="str">
-        <v>Tamanho</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B485" t="str">
-        <v>Preenchimento</v>
+        <v>Tamanho</v>
       </c>
       <c r="C485" t="str">
-        <v>Preenchimento</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B486" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C486" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B487" t="str">
-        <v>Tipo</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C487" t="str">
-        <v>Tipo</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B488" t="str">
-        <v>Vetor de {type}</v>
+        <v>Tipo</v>
       </c>
       <c r="C488" t="str">
-        <v>Array de {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B489" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C489" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B490" t="str">
-        <v>bytes</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C490" t="str">
-        <v>bytes</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B491" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>bytes</v>
       </c>
       <c r="C491" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B492" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C492" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B493" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C493" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B494" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C494" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B495" t="str">
-        <v>Sem saída de validação</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C495" t="str">
-        <v>Sem saída de validação</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B496" t="str">
-        <v>O perfil é válido</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C496" t="str">
-        <v>O perfil é válido</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B497" t="str">
-        <v>O perfil tem avisos</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C497" t="str">
-        <v>O perfil tem avisos</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B498" t="str">
-        <v>O perfil não é conforme</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C498" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B499" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C499" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B500" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C500" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B501" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C501" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B502" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C502" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B503" t="str">
-        <v>Válido</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C503" t="str">
-        <v>Válido</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B504" t="str">
-        <v>Aviso</v>
+        <v>Válido</v>
       </c>
       <c r="C504" t="str">
-        <v>Aviso</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B505" t="str">
-        <v>Erro</v>
+        <v>Aviso</v>
       </c>
       <c r="C505" t="str">
-        <v>Erro</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B506" t="str">
-        <v>Desconhecido</v>
+        <v>Erro</v>
       </c>
       <c r="C506" t="str">
-        <v>Desconhecido</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B507" t="str">
-        <v>Aprovado</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C507" t="str">
-        <v>Aprovado</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B508" t="str">
-        <v>Reprovado</v>
+        <v>Aprovado</v>
       </c>
       <c r="C508" t="str">
-        <v>Reprovado</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B509" t="str">
-        <v>Ver no contexto</v>
+        <v>Reprovado</v>
       </c>
       <c r="C509" t="str">
-        <v>Ver no contexto</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B510" t="str">
-        <v>Detalhe de validação</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C510" t="str">
-        <v>Detalhe de validação</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B511" t="str">
-        <v>Acionado por</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C511" t="str">
-        <v>Acionado por</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B512" t="str">
-        <v>Campo</v>
+        <v>Acionado por</v>
       </c>
       <c r="C512" t="str">
-        <v>Campo</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B513" t="str">
-        <v>Valor atual</v>
+        <v>Campo</v>
       </c>
       <c r="C513" t="str">
-        <v>Valor atual</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B514" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Valor atual</v>
       </c>
       <c r="C514" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B515" t="str">
-        <v>Esperado: {value}</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C515" t="str">
-        <v>Esperado: {value}</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B516" t="str">
-        <v>Inválido</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C516" t="str">
-        <v>Inválido</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B517" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Inválido</v>
       </c>
       <c r="C517" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B518" t="str">
-        <v>Fechar</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C518" t="str">
-        <v>Fechar</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B519" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Fechar</v>
       </c>
       <c r="C519" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B520" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C520" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B521" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C521" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B522" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C522" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B523" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C523" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B524" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>● edições XML por guardar</v>
       </c>
       <c r="C524" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>● edições XML não salvas</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B525" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições JSON por guardar</v>
       </c>
       <c r="C525" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições JSON não salvas</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B526" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
       <c r="C526" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B527" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
       <c r="C527" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B528" t="str">
-        <v>ordenar chaves</v>
+        <v>indentação</v>
       </c>
       <c r="C528" t="str">
-        <v>ordenar chaves</v>
+        <v>indentação</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B529" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C529" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B529" t="str">
+      <c r="B530" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C529" t="str">
+      <c r="C530" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C529"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C530"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C530"/>
+  <dimension ref="A1:C595"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5068,1184 +5068,1899 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>HDR</v>
       </c>
       <c r="B424" t="str">
-        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
+        <v>HDR</v>
       </c>
       <c r="C424" t="str">
-        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Identify displays</v>
+        <v>Gain at a display headroom</v>
       </c>
       <c r="B425" t="str">
-        <v>Identificar ecrãs</v>
+        <v>Ganho para uma margem do ecrã</v>
       </c>
       <c r="C425" t="str">
-        <v>Identificar telas</v>
+        <v>Ganho para uma margem da tela</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR is decoded and rendered by profiletool.</v>
       </c>
       <c r="B426" t="str">
-        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Veja uma imagem HDR neste ecrã. Os ficheiros que o navegador consegue descodificar são mostrados pelo próprio navegador; o OpenEXR é descodificado e apresentado pelo profiletool.</v>
       </c>
       <c r="C426" t="str">
-        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Veja uma imagem HDR nesta tela. Arquivos que o navegador consegue decodificar são exibidos pelo próprio navegador; o OpenEXR é decodificado e renderizado pelo profiletool.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Drop an HDR image here, or click to choose one</v>
       </c>
       <c r="B427" t="str">
-        <v>A acompanhar em que monitor está esta janela.</v>
+        <v>Largue aqui uma imagem HDR ou clique para escolher uma</v>
       </c>
       <c r="C427" t="str">
-        <v>Acompanhando em qual monitor esta janela está.</v>
+        <v>Solte uma imagem HDR aqui ou clique para escolher uma</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>OpenEXR, AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
+        <v>OpenEXR, AVIF, JPEG (incluindo JPEG com gain map), PNG — e HEIC no Safari.</v>
       </c>
       <c r="C428" t="str">
-        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
+        <v>OpenEXR, AVIF, JPEG (incluindo JPEG com gain map), PNG — e HEIC no Safari.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Choose another</v>
       </c>
       <c r="B429" t="str">
-        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
+        <v>Escolher outra</v>
       </c>
       <c r="C429" t="str">
-        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
+        <v>Escolher outra</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Could not identify displays.</v>
+        <v>Clear</v>
       </c>
       <c r="B430" t="str">
-        <v>Não foi possível identificar os ecrãs.</v>
+        <v>Limpar</v>
       </c>
       <c r="C430" t="str">
-        <v>Não foi possível identificar as telas.</v>
+        <v>Limpar</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Display events</v>
+        <v>Embedded ICC profile</v>
       </c>
       <c r="B431" t="str">
-        <v>Eventos de ecrã</v>
+        <v>Perfil ICC incorporado</v>
       </c>
       <c r="C431" t="str">
-        <v>Eventos de tela</v>
+        <v>Perfil ICC incorporado</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>none — OpenEXR states colour through chromaticities</v>
       </c>
       <c r="B432" t="str">
-        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
+        <v>nenhum — o OpenEXR indica a cor através de cromaticidades</v>
       </c>
       <c r="C432" t="str">
-        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
+        <v>nenhum — o OpenEXR informa a cor por cromaticidades</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Colour primaries</v>
+        <v>checking…</v>
       </c>
       <c r="B433" t="str">
-        <v>Primárias de cor</v>
+        <v>a verificar…</v>
       </c>
       <c r="C433" t="str">
-        <v>Primárias de cor</v>
+        <v>verificando…</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Transfer characteristics</v>
+        <v>none</v>
       </c>
       <c r="B434" t="str">
-        <v>Características de transferência</v>
+        <v>nenhum</v>
       </c>
       <c r="C434" t="str">
-        <v>Características de transferência</v>
+        <v>nenhum</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Matrix coefficients</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B435" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Abrir no separador Perfil</v>
       </c>
       <c r="C435" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Abrir na aba Perfil</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Video full-range flag</v>
+        <v>Gain map</v>
       </c>
       <c r="B436" t="str">
-        <v>Sinalizador de gama completa de vídeo</v>
+        <v>Gain map</v>
       </c>
       <c r="C436" t="str">
-        <v>Sinalizador de faixa completa de vídeo</v>
+        <v>Gain map</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Full range</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B437" t="str">
-        <v>Gama completa</v>
+        <v>detetado, não descodificado</v>
       </c>
       <c r="C437" t="str">
-        <v>Faixa completa</v>
+        <v>detectado, não decodificado</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Narrow range</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B438" t="str">
-        <v>Gama reduzida</v>
+        <v>Isso não é uma imagem. Carregue perfis através do painel Perfis.</v>
       </c>
       <c r="C438" t="str">
-        <v>Faixa reduzida</v>
+        <v>Isso não é uma imagem. Carregue perfis pelo painel Perfis.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B439" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Não é um formato de imagem que o profiletool reconheça.</v>
       </c>
       <c r="C439" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Não é um formato de imagem que o profiletool reconheça.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B440" t="str">
-        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
+        <v>Os píxeis TIFF ainda não são mostrados aqui: os navegadores não descodificam TIFF, e a forma de codificar HDR num TIFF de 16 bits ainda não está decidida (fase 4.3). O perfil incorporado pode ser inspecionado.</v>
       </c>
       <c r="C440" t="str">
-        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
+        <v>Os pixels TIFF ainda não são exibidos aqui: os navegadores não decodificam TIFF, e a forma de codificar HDR em um TIFF de 16 bits ainda não foi decidida (fase 4.3). O perfil incorporado pode ser inspecionado.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B441" t="str">
-        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
+        <v>Não é possível mostrar esta imagem aqui:</v>
       </c>
       <c r="C441" t="str">
-        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
+        <v>Não é possível exibir esta imagem aqui:</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>REPORT</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B442" t="str">
-        <v>RELATÓRIO</v>
+        <v>O perfil incorporado pode ainda assim ser inspecionado.</v>
       </c>
       <c r="C442" t="str">
-        <v>RELATÓRIO</v>
+        <v>O perfil incorporado ainda pode ser inspecionado.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>FAIL</v>
+        <v>Shown by</v>
       </c>
       <c r="B443" t="str">
-        <v>REPROVADO</v>
+        <v>Mostrado por</v>
       </c>
       <c r="C443" t="str">
-        <v>REPROVADO</v>
+        <v>Exibido por</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>checks</v>
+        <v>the browser</v>
       </c>
       <c r="B444" t="str">
-        <v>verificações</v>
+        <v>o navegador</v>
       </c>
       <c r="C444" t="str">
-        <v>verificações</v>
+        <v>o navegador</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>profiletool</v>
       </c>
       <c r="B445" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>profiletool</v>
       </c>
       <c r="C445" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>HDR display</v>
       </c>
       <c r="B446" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Ecrã HDR</v>
       </c>
       <c r="C446" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Tela HDR</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B447" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Os navegadores ignoram o HDR indicado apenas por um perfil ICC incorporado, pelo que esta imagem pode parecer baça e plana.</v>
       </c>
       <c r="C447" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Os navegadores ignoram HDR indicado apenas por um perfil ICC incorporado, então esta imagem pode parecer apagada e sem contraste.</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Powered by {lib}</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B448" t="str">
-        <v>Com {lib}</v>
+        <v>Este navegador não consegue alternar uma imagem entre SDR e HDR, pelo que é mostrada tal como o navegador a apresenta.</v>
       </c>
       <c r="C448" t="str">
-        <v>Com {lib}</v>
+        <v>Este navegador não consegue alternar uma imagem entre SDR e HDR, então ela é exibida como o navegador a renderiza.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Subscribe</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B449" t="str">
-        <v>Subscrever</v>
+        <v>O navegador não conseguiu descodificar esta imagem.</v>
       </c>
       <c r="C449" t="str">
-        <v>Inscrever-se</v>
+        <v>O navegador não conseguiu decodificar esta imagem.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Output</v>
       </c>
       <c r="B450" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Saída</v>
       </c>
       <c r="C450" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Get notified about new releases</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B451" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Canvas HDR (float16)</v>
       </c>
       <c r="C451" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Canvas HDR (float16)</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Close</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B452" t="str">
-        <v>Fechar</v>
+        <v>WebGPU (gama alargada)</v>
       </c>
       <c r="C452" t="str">
-        <v>Fechar</v>
+        <v>WebGPU (faixa estendida)</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B453" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Canvas SDR (tone mapping)</v>
       </c>
       <c r="C453" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Canvas SDR (tone mapping)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Email address</v>
+        <v>Size</v>
       </c>
       <c r="B454" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Tamanho</v>
       </c>
       <c r="C454" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>you@example.com</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B455" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Píxel mais brilhante</v>
       </c>
       <c r="C455" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Pixel mais brilhante</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>How will you use profiletool?</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B456" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>{n}× o branco SDR</v>
       </c>
       <c r="C456" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>{n}× o branco SDR</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>(optional)</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B457" t="str">
-        <v>(opcional)</v>
+        <v>Cromaticidades</v>
       </c>
       <c r="C457" t="str">
-        <v>(opcional)</v>
+        <v>Cromaticidades</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B458" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>não indicadas — assume-se Rec. 709</v>
       </c>
       <c r="C458" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>não informadas — assume-se Rec. 709</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B459" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>{from} não está disponível aqui ({why}); é usada a saída seguinte.</v>
       </c>
       <c r="C459" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>{from} não está disponível aqui ({why}); usando a próxima saída.</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Cancel</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B460" t="str">
-        <v>Cancelar</v>
+        <v>Esta saída não consegue transportar valores mais brilhantes do que o branco, pelo que é mostrada a apresentação SDR com tone mapping.</v>
       </c>
       <c r="C460" t="str">
-        <v>Cancelar</v>
+        <v>Esta saída não consegue transportar valores mais brilhantes que o branco, então é exibida a renderização SDR com tone mapping.</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Subscribe</v>
+        <v>Exposure</v>
       </c>
       <c r="B461" t="str">
-        <v>Subscrever</v>
+        <v>Exposição</v>
       </c>
       <c r="C461" t="str">
-        <v>Inscrever-se</v>
+        <v>Exposição</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>{n} stops</v>
       </c>
       <c r="B462" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>{n} stops</v>
       </c>
       <c r="C462" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>{n} stops</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B463" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Não foi possível descodificar:</v>
       </c>
       <c r="C463" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Não foi possível decodificar:</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Close</v>
+        <v>Decoding…</v>
       </c>
       <c r="B464" t="str">
-        <v>Fechar</v>
+        <v>A descodificar…</v>
       </c>
       <c r="C464" t="str">
-        <v>Fechar</v>
+        <v>Decodificando…</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Privacy notice</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B465" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Gama dinâmica</v>
       </c>
       <c r="C465" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Faixa dinâmica</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B466" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Este navegador só oferece os dois extremos, não uma mistura.</v>
       </c>
       <c r="C466" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Este navegador oferece apenas os dois extremos, não uma mistura.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B467" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
       </c>
       <c r="C467" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B468" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Margem do ecrã</v>
       </c>
       <c r="C468" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Margem da tela</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B469" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
       <c r="C469" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Baseline</v>
       </c>
       <c r="B470" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Base</v>
       </c>
       <c r="C470" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Error:</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B471" t="str">
-        <v>Erro:</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
       <c r="C471" t="str">
-        <v>Erro:</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Convert to XML</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B472" t="str">
-        <v>Converter para XML</v>
+        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
       </c>
       <c r="C472" t="str">
-        <v>Converter para XML</v>
+        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Convert to JSON</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B473" t="str">
-        <v>Converter para JSON</v>
+        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
       </c>
       <c r="C473" t="str">
-        <v>Converter para JSON</v>
+        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Convert to ICC</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B474" t="str">
-        <v>Converter para ICC</v>
+        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
       </c>
       <c r="C474" t="str">
-        <v>Converter para ICC</v>
+        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Converting to XML…</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B475" t="str">
-        <v>A converter para XML…</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
       </c>
       <c r="C475" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Converting to JSON…</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B476" t="str">
-        <v>A converter para JSON…</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
       </c>
       <c r="C476" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Converting to ICC…</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B477" t="str">
-        <v>A converter para ICC…</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
       <c r="C477" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Load ICC profile</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B478" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Curva a {h} stops</v>
       </c>
       <c r="C478" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Curva a {h} stops</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B479" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Aplicado a {h} stops</v>
       </c>
       <c r="C479" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Aplicado a {h} stops</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Profile ID</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B480" t="str">
-        <v>ID do perfil</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
       <c r="C480" t="str">
-        <v>ID do perfil</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>No tags found.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B481" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
       <c r="C481" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Tag Name</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B482" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Ganho (stops log2)</v>
       </c>
       <c r="C482" t="str">
-        <v>Nome da tag</v>
+        <v>Ganho (stops log2)</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>ID</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B483" t="str">
-        <v>ID</v>
+        <v>Curva de tons dos cinzentos nesta margem</v>
       </c>
       <c r="C483" t="str">
-        <v>ID</v>
+        <v>Curva de tons de cinza nesta margem</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Offset</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B484" t="str">
-        <v>Deslocamento</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
       <c r="C484" t="str">
-        <v>Deslocamento</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Size</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B485" t="str">
-        <v>Tamanho</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
       <c r="C485" t="str">
-        <v>Tamanho</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Pad</v>
+        <v>No change</v>
       </c>
       <c r="B486" t="str">
-        <v>Preenchimento</v>
+        <v>Sem alteração</v>
       </c>
       <c r="C486" t="str">
-        <v>Preenchimento</v>
+        <v>Sem alteração</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Bytes changed since load</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B487" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Pico do ecrã a {h} stops</v>
       </c>
       <c r="C487" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Pico da tela a {h} stops</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Type</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B488" t="str">
-        <v>Tipo</v>
+        <v>Saída a {h} stops</v>
       </c>
       <c r="C488" t="str">
-        <v>Tipo</v>
+        <v>Saída a {h} stops</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Array of {type}</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B489" t="str">
-        <v>Vetor de {type}</v>
+        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
       </c>
       <c r="C489" t="str">
-        <v>Array de {type}</v>
+        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>(No content)</v>
+        <v>Identify displays</v>
       </c>
       <c r="B490" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Identificar ecrãs</v>
       </c>
       <c r="C490" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Identificar telas</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>bytes</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B491" t="str">
-        <v>bytes</v>
+        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
       <c r="C491" t="str">
-        <v>bytes</v>
+        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Loading full description…</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B492" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>A acompanhar em que monitor está esta janela.</v>
       </c>
       <c r="C492" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Acompanhando em qual monitor esta janela está.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Could not load full description:</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B493" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
       </c>
       <c r="C493" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B494" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
       </c>
       <c r="C494" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B495" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Não foi possível identificar os ecrãs.</v>
       </c>
       <c r="C495" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Não foi possível identificar as telas.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>No validation output</v>
+        <v>Display events</v>
       </c>
       <c r="B496" t="str">
-        <v>Sem saída de validação</v>
+        <v>Eventos de ecrã</v>
       </c>
       <c r="C496" t="str">
-        <v>Sem saída de validação</v>
+        <v>Eventos de tela</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Profile is valid</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B497" t="str">
-        <v>O perfil é válido</v>
+        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
       </c>
       <c r="C497" t="str">
-        <v>O perfil é válido</v>
+        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B498" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C498" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B499" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C499" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Critical validation error</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B500" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C500" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Unknown validation status</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B501" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C501" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Full range</v>
       </c>
       <c r="B502" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Gama completa</v>
       </c>
       <c r="C502" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B503" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C503" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Valid</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B504" t="str">
-        <v>Válido</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C504" t="str">
-        <v>Válido</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Warning</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B505" t="str">
-        <v>Aviso</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C505" t="str">
-        <v>Aviso</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Error</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B506" t="str">
-        <v>Erro</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C506" t="str">
-        <v>Erro</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Unknown</v>
+        <v>REPORT</v>
       </c>
       <c r="B507" t="str">
-        <v>Desconhecido</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C507" t="str">
-        <v>Desconhecido</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Pass</v>
+        <v>FAIL</v>
       </c>
       <c r="B508" t="str">
-        <v>Aprovado</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C508" t="str">
-        <v>Aprovado</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Fail</v>
+        <v>checks</v>
       </c>
       <c r="B509" t="str">
-        <v>Reprovado</v>
+        <v>verificações</v>
       </c>
       <c r="C509" t="str">
-        <v>Reprovado</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>View in context</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B510" t="str">
-        <v>Ver no contexto</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C510" t="str">
-        <v>Ver no contexto</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Validation detail</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B511" t="str">
-        <v>Detalhe de validação</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C511" t="str">
-        <v>Detalhe de validação</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Triggered by</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B512" t="str">
-        <v>Acionado por</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C512" t="str">
-        <v>Acionado por</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Field</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B513" t="str">
-        <v>Campo</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C513" t="str">
-        <v>Campo</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Current value</v>
+        <v>Subscribe</v>
       </c>
       <c r="B514" t="str">
-        <v>Valor atual</v>
+        <v>Subscrever</v>
       </c>
       <c r="C514" t="str">
-        <v>Valor atual</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Required: 0</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B515" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C515" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Expected: {value}</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B516" t="str">
-        <v>Esperado: {value}</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C516" t="str">
-        <v>Esperado: {value}</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Invalid</v>
+        <v>Close</v>
       </c>
       <c r="B517" t="str">
-        <v>Inválido</v>
+        <v>Fechar</v>
       </c>
       <c r="C517" t="str">
-        <v>Inválido</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B518" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C518" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B519" t="str">
-        <v>Fechar</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C519" t="str">
-        <v>Fechar</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Loading XML editor…</v>
+        <v>you@example.com</v>
       </c>
       <c r="B520" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C520" t="str">
-        <v>Carregando editor XML…</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Loading JSON editor…</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B521" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C521" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>(optional)</v>
       </c>
       <c r="B522" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>(opcional)</v>
       </c>
       <c r="C522" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B523" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C523" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>● unsaved XML edits</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B524" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C524" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Cancel</v>
       </c>
       <c r="B525" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Cancelar</v>
       </c>
       <c r="C525" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B526" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C526" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B527" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C527" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>indent</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B528" t="str">
-        <v>indentação</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C528" t="str">
-        <v>indentação</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B529" t="str">
-        <v>ordenar chaves</v>
+        <v>Fechar</v>
       </c>
       <c r="C529" t="str">
-        <v>ordenar chaves</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B530" t="str">
+        <v>Aviso de privacidade</v>
+      </c>
+      <c r="C530" t="str">
+        <v>Aviso de privacidade</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B531" t="str">
+        <v>Introduza um endereço de e-mail válido.</v>
+      </c>
+      <c r="C531" t="str">
+        <v>Insira um endereço de e-mail válido.</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B532" t="str">
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+      </c>
+      <c r="C532" t="str">
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B533" t="str">
+        <v>Verifique o formulário e tente novamente.</v>
+      </c>
+      <c r="C533" t="str">
+        <v>Verifique o formulário e tente novamente.</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B534" t="str">
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+      </c>
+      <c r="C534" t="str">
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B535" t="str">
+        <v>Erro de rede. Tente novamente.</v>
+      </c>
+      <c r="C535" t="str">
+        <v>Erro de rede. Tente novamente.</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B536" t="str">
+        <v>Erro:</v>
+      </c>
+      <c r="C536" t="str">
+        <v>Erro:</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B537" t="str">
+        <v>Converter para XML</v>
+      </c>
+      <c r="C537" t="str">
+        <v>Converter para XML</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B538" t="str">
+        <v>Converter para JSON</v>
+      </c>
+      <c r="C538" t="str">
+        <v>Converter para JSON</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B539" t="str">
+        <v>Converter para ICC</v>
+      </c>
+      <c r="C539" t="str">
+        <v>Converter para ICC</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B540" t="str">
+        <v>A converter para XML…</v>
+      </c>
+      <c r="C540" t="str">
+        <v>Convertendo para XML…</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B541" t="str">
+        <v>A converter para JSON…</v>
+      </c>
+      <c r="C541" t="str">
+        <v>Convertendo para JSON…</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B542" t="str">
+        <v>A converter para ICC…</v>
+      </c>
+      <c r="C542" t="str">
+        <v>Convertendo para ICC…</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B543" t="str">
+        <v>Carregar perfil ICC</v>
+      </c>
+      <c r="C543" t="str">
+        <v>Carregar perfil ICC</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B544" t="str">
+        <v>Zona de largada para ficheiros de perfil ICC</v>
+      </c>
+      <c r="C544" t="str">
+        <v>Área de soltar para arquivos de perfil ICC</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B545" t="str">
+        <v>ID do perfil</v>
+      </c>
+      <c r="C545" t="str">
+        <v>ID do perfil</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B546" t="str">
+        <v>Nenhuma etiqueta encontrada.</v>
+      </c>
+      <c r="C546" t="str">
+        <v>Nenhuma tag encontrada.</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B547" t="str">
+        <v>Nome da etiqueta</v>
+      </c>
+      <c r="C547" t="str">
+        <v>Nome da tag</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B548" t="str">
+        <v>ID</v>
+      </c>
+      <c r="C548" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B549" t="str">
+        <v>Deslocamento</v>
+      </c>
+      <c r="C549" t="str">
+        <v>Deslocamento</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B550" t="str">
+        <v>Tamanho</v>
+      </c>
+      <c r="C550" t="str">
+        <v>Tamanho</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B551" t="str">
+        <v>Preenchimento</v>
+      </c>
+      <c r="C551" t="str">
+        <v>Preenchimento</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B552" t="str">
+        <v>Bytes alterados desde o carregamento</v>
+      </c>
+      <c r="C552" t="str">
+        <v>Bytes alterados desde o carregamento</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B553" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="C553" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B554" t="str">
+        <v>Vetor de {type}</v>
+      </c>
+      <c r="C554" t="str">
+        <v>Array de {type}</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B555" t="str">
+        <v>(Sem conteúdo)</v>
+      </c>
+      <c r="C555" t="str">
+        <v>(Sem conteúdo)</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B556" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="C556" t="str">
+        <v>bytes</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B557" t="str">
+        <v>A carregar descrição completa…</v>
+      </c>
+      <c r="C557" t="str">
+        <v>Carregando descrição completa…</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B558" t="str">
+        <v>Não foi possível carregar a descrição completa:</v>
+      </c>
+      <c r="C558" t="str">
+        <v>Não foi possível carregar a descrição completa:</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B559" t="str">
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+      </c>
+      <c r="C559" t="str">
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B560" t="str">
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+      </c>
+      <c r="C560" t="str">
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B561" t="str">
+        <v>Sem saída de validação</v>
+      </c>
+      <c r="C561" t="str">
+        <v>Sem saída de validação</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B562" t="str">
+        <v>O perfil é válido</v>
+      </c>
+      <c r="C562" t="str">
+        <v>O perfil é válido</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B563" t="str">
+        <v>O perfil tem avisos</v>
+      </c>
+      <c r="C563" t="str">
+        <v>O perfil tem avisos</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B564" t="str">
+        <v>O perfil não é conforme</v>
+      </c>
+      <c r="C564" t="str">
+        <v>O perfil não está em conformidade</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B565" t="str">
+        <v>Erro de validação crítico</v>
+      </c>
+      <c r="C565" t="str">
+        <v>Erro de validação crítico</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B566" t="str">
+        <v>Estado de validação desconhecido</v>
+      </c>
+      <c r="C566" t="str">
+        <v>Status de validação desconhecido</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B567" t="str">
+        <v>Crítico — apresentado apenas para inspeção</v>
+      </c>
+      <c r="C567" t="str">
+        <v>Crítico — exibido apenas para inspeção</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B568" t="str">
+        <v>Sem avisos nem erros encontrados.</v>
+      </c>
+      <c r="C568" t="str">
+        <v>Nenhum aviso ou erro encontrado.</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B569" t="str">
+        <v>Válido</v>
+      </c>
+      <c r="C569" t="str">
+        <v>Válido</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B570" t="str">
+        <v>Aviso</v>
+      </c>
+      <c r="C570" t="str">
+        <v>Aviso</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B571" t="str">
+        <v>Erro</v>
+      </c>
+      <c r="C571" t="str">
+        <v>Erro</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B572" t="str">
+        <v>Desconhecido</v>
+      </c>
+      <c r="C572" t="str">
+        <v>Desconhecido</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B573" t="str">
+        <v>Aprovado</v>
+      </c>
+      <c r="C573" t="str">
+        <v>Aprovado</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B574" t="str">
+        <v>Reprovado</v>
+      </c>
+      <c r="C574" t="str">
+        <v>Reprovado</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B575" t="str">
+        <v>Ver no contexto</v>
+      </c>
+      <c r="C575" t="str">
+        <v>Ver no contexto</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B576" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+      <c r="C576" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B577" t="str">
+        <v>Acionado por</v>
+      </c>
+      <c r="C577" t="str">
+        <v>Acionado por</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B578" t="str">
+        <v>Campo</v>
+      </c>
+      <c r="C578" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B579" t="str">
+        <v>Valor atual</v>
+      </c>
+      <c r="C579" t="str">
+        <v>Valor atual</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B580" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+      <c r="C580" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B581" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+      <c r="C581" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B582" t="str">
+        <v>Inválido</v>
+      </c>
+      <c r="C582" t="str">
+        <v>Inválido</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B583" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+      <c r="C583" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B584" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C584" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B585" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C585" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B586" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C586" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B587" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C587" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B588" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C588" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B589" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C589" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B590" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C590" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B591" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C591" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B592" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C592" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B593" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C593" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B594" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C594" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B530" t="str">
+      <c r="B595" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C530" t="str">
+      <c r="C595" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C530"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C595"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C595"/>
+  <dimension ref="A1:C612"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5203,10 +5203,10 @@
         <v>Gain map</v>
       </c>
       <c r="B436" t="str">
-        <v>Gain map</v>
+        <v>Mapa de ganho</v>
       </c>
       <c r="C436" t="str">
-        <v>Gain map</v>
+        <v>Mapa de ganho</v>
       </c>
     </row>
     <row r="437">
@@ -5541,1426 +5541,1613 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B467" t="str">
-        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
+        <v>descodificado pelo próprio profiletool, portanto independente do navegador</v>
       </c>
       <c r="C467" t="str">
-        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
+        <v>decodificado pelo próprio profiletool, portanto independente do navegador</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Display headroom</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B468" t="str">
-        <v>Margem do ecrã</v>
+        <v>este navegador descodifica-o</v>
       </c>
       <c r="C468" t="str">
-        <v>Margem da tela</v>
+        <v>este navegador o decodifica</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B469" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>este navegador não o descodifica</v>
       </c>
       <c r="C469" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>este navegador não o decodifica</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Baseline</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B470" t="str">
-        <v>Base</v>
+        <v>mostrar HEIC requer o Safari ou outro navegador WebKit — o Chrome e o Firefox não descodificam HEIC em nenhuma plataforma, incluindo o macOS</v>
       </c>
       <c r="C470" t="str">
-        <v>Base</v>
+        <v>exibir HEIC requer o Safari ou outro navegador WebKit — Chrome e Firefox não decodificam HEIC em nenhuma plataforma, inclusive no macOS</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B471" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>mostrar JPEG XL requer o Safari; os outros navegadores ainda não o suportam</v>
       </c>
       <c r="C471" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>exibir JPEG XL requer o Safari; outros navegadores ainda não o suportam</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B472" t="str">
-        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
+        <v>adiado para uma versão posterior</v>
       </c>
       <c r="C472" t="str">
-        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
+        <v>adiado para uma versão futura</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B473" t="str">
-        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
+        <v>este ecrã não indica nenhum caminho HDR, pelo que o HDR é apresentado em SDR com tone mapping</v>
       </c>
       <c r="C473" t="str">
-        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
+        <v>esta tela não informa nenhum caminho HDR, então o HDR é exibido em SDR com tone mapping</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B474" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
+        <v>este navegador não oferece um canvas HDR (requer canvas float16 ou WebGPU)</v>
       </c>
       <c r="C474" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
+        <v>este navegador não oferece um canvas HDR (requer canvas float16 ou WebGPU)</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B475" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
+        <v>o Firefox não mostra imagens HDR nem lê gain maps; o conteúdo HDR é mostrado em SDR</v>
       </c>
       <c r="C475" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
+        <v>o Firefox não exibe imagens HDR nem lê gain maps; o conteúdo HDR é exibido em SDR</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B476" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
+        <v>a inspeção só precisa de analisar o contentor, não de um codec</v>
       </c>
       <c r="C476" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
+        <v>a inspeção só precisa analisar o contêiner, não de um codec</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B477" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>ecrã HDR e canvas HDR estão ambos disponíveis</v>
       </c>
       <c r="C477" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>tela HDR e canvas HDR estão disponíveis</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Curve at {h} stops</v>
+        <v>unknown format</v>
       </c>
       <c r="B478" t="str">
-        <v>Curva a {h} stops</v>
+        <v>formato desconhecido</v>
       </c>
       <c r="C478" t="str">
-        <v>Curva a {h} stops</v>
+        <v>formato desconhecido</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Applied at {h} stops</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B479" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>{browser} em {os}</v>
       </c>
       <c r="C479" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>{browser} no {os}</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B480" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>{name} · ecrã HDR detetado</v>
       </c>
       <c r="C480" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>{name} · tela HDR detectada</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B481" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>{name} · ecrã SDR</v>
       </c>
       <c r="C481" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>{name} · tela SDR</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B482" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>O WebGPU aplicou o tone mapping «{mode}», pelo que a saída fica limitada a SDR</v>
       </c>
       <c r="C482" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>O WebGPU aplicou o tone mapping “{mode}”, então a saída fica limitada a SDR</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B483" t="str">
-        <v>Curva de tons dos cinzentos nesta margem</v>
+        <v>Este navegador não indica o tone mapping WebGPU aplicado, pelo que a saída HDR não está confirmada</v>
       </c>
       <c r="C483" t="str">
-        <v>Curva de tons de cinza nesta margem</v>
+        <v>Este navegador não informa o tone mapping WebGPU aplicado, então a saída HDR não está confirmada</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B484" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
       </c>
       <c r="C484" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B485" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Margem do ecrã</v>
       </c>
       <c r="C485" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Margem da tela</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>No change</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B486" t="str">
-        <v>Sem alteração</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
       <c r="C486" t="str">
-        <v>Sem alteração</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Baseline</v>
       </c>
       <c r="B487" t="str">
-        <v>Pico do ecrã a {h} stops</v>
+        <v>Base</v>
       </c>
       <c r="C487" t="str">
-        <v>Pico da tela a {h} stops</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Output at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B488" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
       <c r="C488" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B489" t="str">
-        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
+        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
       </c>
       <c r="C489" t="str">
-        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
+        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Identify displays</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B490" t="str">
-        <v>Identificar ecrãs</v>
+        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
       </c>
       <c r="C490" t="str">
-        <v>Identificar telas</v>
+        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B491" t="str">
-        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
       </c>
       <c r="C491" t="str">
-        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B492" t="str">
-        <v>A acompanhar em que monitor está esta janela.</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
       </c>
       <c r="C492" t="str">
-        <v>Acompanhando em qual monitor esta janela está.</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B493" t="str">
-        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
       </c>
       <c r="C493" t="str">
-        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B494" t="str">
-        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
       <c r="C494" t="str">
-        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Could not identify displays.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B495" t="str">
-        <v>Não foi possível identificar os ecrãs.</v>
+        <v>Curva a {h} stops</v>
       </c>
       <c r="C495" t="str">
-        <v>Não foi possível identificar as telas.</v>
+        <v>Curva a {h} stops</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Display events</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B496" t="str">
-        <v>Eventos de ecrã</v>
+        <v>Aplicado a {h} stops</v>
       </c>
       <c r="C496" t="str">
-        <v>Eventos de tela</v>
+        <v>Aplicado a {h} stops</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B497" t="str">
-        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
       <c r="C497" t="str">
-        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Colour primaries</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B498" t="str">
-        <v>Primárias de cor</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
       <c r="C498" t="str">
-        <v>Primárias de cor</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Transfer characteristics</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B499" t="str">
-        <v>Características de transferência</v>
+        <v>Ganho (stops log2)</v>
       </c>
       <c r="C499" t="str">
-        <v>Características de transferência</v>
+        <v>Ganho (stops log2)</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Matrix coefficients</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B500" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Curva de tons dos cinzentos nesta margem</v>
       </c>
       <c r="C500" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Curva de tons de cinza nesta margem</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Video full-range flag</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B501" t="str">
-        <v>Sinalizador de gama completa de vídeo</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
       <c r="C501" t="str">
-        <v>Sinalizador de faixa completa de vídeo</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Full range</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B502" t="str">
-        <v>Gama completa</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
       <c r="C502" t="str">
-        <v>Faixa completa</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Narrow range</v>
+        <v>No change</v>
       </c>
       <c r="B503" t="str">
-        <v>Gama reduzida</v>
+        <v>Sem alteração</v>
       </c>
       <c r="C503" t="str">
-        <v>Faixa reduzida</v>
+        <v>Sem alteração</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B504" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Pico do ecrã a {h} stops</v>
       </c>
       <c r="C504" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Pico da tela a {h} stops</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B505" t="str">
-        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
+        <v>Saída a {h} stops</v>
       </c>
       <c r="C505" t="str">
-        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
+        <v>Saída a {h} stops</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B506" t="str">
-        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
+        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
       </c>
       <c r="C506" t="str">
-        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
+        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>REPORT</v>
+        <v>Identify displays</v>
       </c>
       <c r="B507" t="str">
-        <v>RELATÓRIO</v>
+        <v>Identificar ecrãs</v>
       </c>
       <c r="C507" t="str">
-        <v>RELATÓRIO</v>
+        <v>Identificar telas</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>FAIL</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B508" t="str">
-        <v>REPROVADO</v>
+        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
       <c r="C508" t="str">
-        <v>REPROVADO</v>
+        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>checks</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B509" t="str">
-        <v>verificações</v>
+        <v>A acompanhar em que monitor está esta janela.</v>
       </c>
       <c r="C509" t="str">
-        <v>verificações</v>
+        <v>Acompanhando em qual monitor esta janela está.</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B510" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
       </c>
       <c r="C510" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B511" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
       </c>
       <c r="C511" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B512" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Não foi possível identificar os ecrãs.</v>
       </c>
       <c r="C512" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Não foi possível identificar as telas.</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Powered by {lib}</v>
+        <v>Display events</v>
       </c>
       <c r="B513" t="str">
-        <v>Com {lib}</v>
+        <v>Eventos de ecrã</v>
       </c>
       <c r="C513" t="str">
-        <v>Com {lib}</v>
+        <v>Eventos de tela</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Subscribe</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B514" t="str">
-        <v>Subscrever</v>
+        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
       </c>
       <c r="C514" t="str">
-        <v>Inscrever-se</v>
+        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B515" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C515" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Get notified about new releases</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B516" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C516" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Close</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B517" t="str">
-        <v>Fechar</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C517" t="str">
-        <v>Fechar</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B518" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C518" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Email address</v>
+        <v>Full range</v>
       </c>
       <c r="B519" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Gama completa</v>
       </c>
       <c r="C519" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>you@example.com</v>
+        <v>Narrow range</v>
       </c>
       <c r="B520" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C520" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>How will you use profiletool?</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B521" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C521" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>(optional)</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B522" t="str">
-        <v>(opcional)</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C522" t="str">
-        <v>(opcional)</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B523" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C523" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B524" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C524" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B525" t="str">
-        <v>Cancelar</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C525" t="str">
-        <v>Cancelar</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B526" t="str">
-        <v>Subscrever</v>
+        <v>verificações</v>
       </c>
       <c r="C526" t="str">
-        <v>Inscrever-se</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B527" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C527" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B528" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C528" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B529" t="str">
-        <v>Fechar</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C529" t="str">
-        <v>Fechar</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B530" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C530" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B531" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C531" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B532" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C532" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B533" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C533" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B534" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Fechar</v>
       </c>
       <c r="C534" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B535" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C535" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B536" t="str">
-        <v>Erro:</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C536" t="str">
-        <v>Erro:</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B537" t="str">
-        <v>Converter para XML</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C537" t="str">
-        <v>Converter para XML</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B538" t="str">
-        <v>Converter para JSON</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C538" t="str">
-        <v>Converter para JSON</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B539" t="str">
-        <v>Converter para ICC</v>
+        <v>(opcional)</v>
       </c>
       <c r="C539" t="str">
-        <v>Converter para ICC</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B540" t="str">
-        <v>A converter para XML…</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C540" t="str">
-        <v>Convertendo para XML…</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B541" t="str">
-        <v>A converter para JSON…</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C541" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B542" t="str">
-        <v>A converter para ICC…</v>
+        <v>Cancelar</v>
       </c>
       <c r="C542" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B543" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Subscrever</v>
       </c>
       <c r="C543" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B544" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C544" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B545" t="str">
-        <v>ID do perfil</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C545" t="str">
-        <v>ID do perfil</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B546" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Fechar</v>
       </c>
       <c r="C546" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B547" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C547" t="str">
-        <v>Nome da tag</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B548" t="str">
-        <v>ID</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C548" t="str">
-        <v>ID</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B549" t="str">
-        <v>Deslocamento</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C549" t="str">
-        <v>Deslocamento</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B550" t="str">
-        <v>Tamanho</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C550" t="str">
-        <v>Tamanho</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B551" t="str">
-        <v>Preenchimento</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C551" t="str">
-        <v>Preenchimento</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B552" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C552" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B553" t="str">
-        <v>Tipo</v>
+        <v>Erro:</v>
       </c>
       <c r="C553" t="str">
-        <v>Tipo</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B554" t="str">
-        <v>Vetor de {type}</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C554" t="str">
-        <v>Array de {type}</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B555" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C555" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B556" t="str">
-        <v>bytes</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C556" t="str">
-        <v>bytes</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B557" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C557" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B558" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C558" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B559" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C559" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B560" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C560" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B561" t="str">
-        <v>Sem saída de validação</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C561" t="str">
-        <v>Sem saída de validação</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B562" t="str">
-        <v>O perfil é válido</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C562" t="str">
-        <v>O perfil é válido</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B563" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C563" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B564" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C564" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B565" t="str">
-        <v>Erro de validação crítico</v>
+        <v>ID</v>
       </c>
       <c r="C565" t="str">
-        <v>Erro de validação crítico</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B566" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C566" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B567" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Tamanho</v>
       </c>
       <c r="C567" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B568" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C568" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B569" t="str">
-        <v>Válido</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C569" t="str">
-        <v>Válido</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B570" t="str">
-        <v>Aviso</v>
+        <v>Tipo</v>
       </c>
       <c r="C570" t="str">
-        <v>Aviso</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B571" t="str">
-        <v>Erro</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C571" t="str">
-        <v>Erro</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B572" t="str">
-        <v>Desconhecido</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C572" t="str">
-        <v>Desconhecido</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B573" t="str">
-        <v>Aprovado</v>
+        <v>bytes</v>
       </c>
       <c r="C573" t="str">
-        <v>Aprovado</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B574" t="str">
-        <v>Reprovado</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C574" t="str">
-        <v>Reprovado</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B575" t="str">
-        <v>Ver no contexto</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C575" t="str">
-        <v>Ver no contexto</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B576" t="str">
-        <v>Detalhe de validação</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C576" t="str">
-        <v>Detalhe de validação</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B577" t="str">
-        <v>Acionado por</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C577" t="str">
-        <v>Acionado por</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B578" t="str">
-        <v>Campo</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C578" t="str">
-        <v>Campo</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B579" t="str">
-        <v>Valor atual</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C579" t="str">
-        <v>Valor atual</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B580" t="str">
-        <v>Obrigatório: 0</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C580" t="str">
-        <v>Obrigatório: 0</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B581" t="str">
-        <v>Esperado: {value}</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C581" t="str">
-        <v>Esperado: {value}</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B582" t="str">
-        <v>Inválido</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C582" t="str">
-        <v>Inválido</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B583" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C583" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B584" t="str">
-        <v>Fechar</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C584" t="str">
-        <v>Fechar</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B585" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C585" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B586" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Válido</v>
       </c>
       <c r="C586" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B587" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Aviso</v>
       </c>
       <c r="C587" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B588" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Erro</v>
       </c>
       <c r="C588" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B589" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C589" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B590" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Aprovado</v>
       </c>
       <c r="C590" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B591" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Reprovado</v>
       </c>
       <c r="C591" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B592" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C592" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B593" t="str">
-        <v>indentação</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C593" t="str">
-        <v>indentação</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B594" t="str">
-        <v>ordenar chaves</v>
+        <v>Acionado por</v>
       </c>
       <c r="C594" t="str">
-        <v>ordenar chaves</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B595" t="str">
+        <v>Campo</v>
+      </c>
+      <c r="C595" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B596" t="str">
+        <v>Valor atual</v>
+      </c>
+      <c r="C596" t="str">
+        <v>Valor atual</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B597" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+      <c r="C597" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B598" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+      <c r="C598" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B599" t="str">
+        <v>Inválido</v>
+      </c>
+      <c r="C599" t="str">
+        <v>Inválido</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B600" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+      <c r="C600" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B601" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C601" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B602" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C602" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B603" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C603" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B604" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C604" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B605" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C605" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B606" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C606" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B607" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C607" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B608" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C608" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B609" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C609" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B610" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C610" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B611" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C611" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B595" t="str">
+      <c r="B612" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C595" t="str">
+      <c r="C612" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C595"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C612"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C612"/>
+  <dimension ref="A1:C625"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5728,1426 +5728,1569 @@
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Display peak</v>
       </c>
       <c r="B484" t="str">
-        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
+        <v>Pico do ecrã</v>
       </c>
       <c r="C484" t="str">
-        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
+        <v>Pico da tela</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Display headroom</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B485" t="str">
-        <v>Margem do ecrã</v>
+        <v>{r}× o branco SDR ({n} stops)</v>
       </c>
       <c r="C485" t="str">
-        <v>Margem da tela</v>
+        <v>{r}× o branco SDR ({n} stops)</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B486" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>1× — ecrã SDR</v>
       </c>
       <c r="C486" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>1× — tela SDR</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Baseline</v>
+        <v>not known</v>
       </c>
       <c r="B487" t="str">
-        <v>Base</v>
+        <v>desconhecido</v>
       </c>
       <c r="C487" t="str">
-        <v>Base</v>
+        <v>desconhecido</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B488" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>Este ecrã não indica HDR, pelo que o navegador mostra a imagem em SDR em ambos os extremos.</v>
       </c>
       <c r="C488" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>Esta tela não informa HDR, então o navegador exibe a imagem em SDR nos dois extremos.</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B489" t="str">
-        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
+        <v>Este ecrã não indica HDR, pelo que tudo o que for mais brilhante do que o branco SDR é cortado. «Ajustar ao ecrã» mostra antes a apresentação com tone mapping.</v>
       </c>
       <c r="C489" t="str">
-        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
+        <v>Esta tela não informa HDR, então tudo que for mais brilhante que o branco SDR é cortado. “Ajustar à tela” exibe a renderização com tone mapping.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B490" t="str">
-        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
+        <v>Esta imagem pede {img}× o branco SDR, mas este ecrã só chega a {disp}×, pelo que os valores mais brilhantes são cortados. «Ajustar ao ecrã» suaviza-os até ao pico do ecrã.</v>
       </c>
       <c r="C490" t="str">
-        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
+        <v>Esta imagem pede {img}× o branco SDR, mas esta tela só chega a {disp}×, então valores mais brilhantes são cortados. “Ajustar à tela” os suaviza até o pico da tela.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Fit to display</v>
       </c>
       <c r="B491" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
+        <v>Ajustar ao ecrã</v>
       </c>
       <c r="C491" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
+        <v>Ajustar à tela</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B492" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
+        <v>Limita o brilho ao pico que este ecrã indica. No Windows esse valor pode atrasar-se face às mudanças de brilho.</v>
       </c>
       <c r="C492" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
+        <v>Limita o brilho ao pico que esta tela informa. No Windows esse valor pode ficar atrasado em relação às mudanças de brilho.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>no limit</v>
       </c>
       <c r="B493" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
+        <v>sem limite</v>
       </c>
       <c r="C493" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
+        <v>sem limite</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B494" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>limite {n} stops ({r}×)</v>
       </c>
       <c r="C494" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>limite {n} stops ({r}×)</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Curve at {h} stops</v>
+        <v>SDR white</v>
       </c>
       <c r="B495" t="str">
-        <v>Curva a {h} stops</v>
+        <v>Branco SDR</v>
       </c>
       <c r="C495" t="str">
-        <v>Curva a {h} stops</v>
+        <v>Branco SDR</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B496" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Branco SDR simples, para comparação. Num ecrã HDR, as altas luzes HDR parecem mais brilhantes do que este.</v>
       </c>
       <c r="C496" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Branco SDR simples, para comparação. Em uma tela HDR, os realces HDR parecem mais brilhantes que este.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B497" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
       </c>
       <c r="C497" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B498" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>Margem do ecrã</v>
       </c>
       <c r="C498" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>Margem da tela</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B499" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
       <c r="C499" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Baseline</v>
       </c>
       <c r="B500" t="str">
-        <v>Curva de tons dos cinzentos nesta margem</v>
+        <v>Base</v>
       </c>
       <c r="C500" t="str">
-        <v>Curva de tons de cinza nesta margem</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B501" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
       <c r="C501" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B502" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
       </c>
       <c r="C502" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>No change</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B503" t="str">
-        <v>Sem alteração</v>
+        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
       </c>
       <c r="C503" t="str">
-        <v>Sem alteração</v>
+        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B504" t="str">
-        <v>Pico do ecrã a {h} stops</v>
+        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
       </c>
       <c r="C504" t="str">
-        <v>Pico da tela a {h} stops</v>
+        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Output at {h} stops</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B505" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
       </c>
       <c r="C505" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B506" t="str">
-        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
       </c>
       <c r="C506" t="str">
-        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Identify displays</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B507" t="str">
-        <v>Identificar ecrãs</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
       <c r="C507" t="str">
-        <v>Identificar telas</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B508" t="str">
-        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Curva a {h} stops</v>
       </c>
       <c r="C508" t="str">
-        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Curva a {h} stops</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B509" t="str">
-        <v>A acompanhar em que monitor está esta janela.</v>
+        <v>Aplicado a {h} stops</v>
       </c>
       <c r="C509" t="str">
-        <v>Acompanhando em qual monitor esta janela está.</v>
+        <v>Aplicado a {h} stops</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B510" t="str">
-        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
       <c r="C510" t="str">
-        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B511" t="str">
-        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
       <c r="C511" t="str">
-        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Could not identify displays.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B512" t="str">
-        <v>Não foi possível identificar os ecrãs.</v>
+        <v>Ganho (stops log2)</v>
       </c>
       <c r="C512" t="str">
-        <v>Não foi possível identificar as telas.</v>
+        <v>Ganho (stops log2)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Display events</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B513" t="str">
-        <v>Eventos de ecrã</v>
+        <v>Curva de tons dos cinzentos nesta margem</v>
       </c>
       <c r="C513" t="str">
-        <v>Eventos de tela</v>
+        <v>Curva de tons de cinza nesta margem</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B514" t="str">
-        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
       <c r="C514" t="str">
-        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Colour primaries</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B515" t="str">
-        <v>Primárias de cor</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
       <c r="C515" t="str">
-        <v>Primárias de cor</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Transfer characteristics</v>
+        <v>No change</v>
       </c>
       <c r="B516" t="str">
-        <v>Características de transferência</v>
+        <v>Sem alteração</v>
       </c>
       <c r="C516" t="str">
-        <v>Características de transferência</v>
+        <v>Sem alteração</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Matrix coefficients</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B517" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Pico do ecrã a {h} stops</v>
       </c>
       <c r="C517" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Pico da tela a {h} stops</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Video full-range flag</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B518" t="str">
-        <v>Sinalizador de gama completa de vídeo</v>
+        <v>Saída a {h} stops</v>
       </c>
       <c r="C518" t="str">
-        <v>Sinalizador de faixa completa de vídeo</v>
+        <v>Saída a {h} stops</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Full range</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B519" t="str">
-        <v>Gama completa</v>
+        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
       </c>
       <c r="C519" t="str">
-        <v>Faixa completa</v>
+        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Narrow range</v>
+        <v>Identify displays</v>
       </c>
       <c r="B520" t="str">
-        <v>Gama reduzida</v>
+        <v>Identificar ecrãs</v>
       </c>
       <c r="C520" t="str">
-        <v>Faixa reduzida</v>
+        <v>Identificar telas</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B521" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
       <c r="C521" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B522" t="str">
-        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
+        <v>A acompanhar em que monitor está esta janela.</v>
       </c>
       <c r="C522" t="str">
-        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
+        <v>Acompanhando em qual monitor esta janela está.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B523" t="str">
-        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
+        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
       </c>
       <c r="C523" t="str">
-        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
+        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>REPORT</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B524" t="str">
-        <v>RELATÓRIO</v>
+        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
       </c>
       <c r="C524" t="str">
-        <v>RELATÓRIO</v>
+        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>FAIL</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B525" t="str">
-        <v>REPROVADO</v>
+        <v>Não foi possível identificar os ecrãs.</v>
       </c>
       <c r="C525" t="str">
-        <v>REPROVADO</v>
+        <v>Não foi possível identificar as telas.</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>checks</v>
+        <v>Display events</v>
       </c>
       <c r="B526" t="str">
-        <v>verificações</v>
+        <v>Eventos de ecrã</v>
       </c>
       <c r="C526" t="str">
-        <v>verificações</v>
+        <v>Eventos de tela</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B527" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
       </c>
       <c r="C527" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B528" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C528" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B529" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C529" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Powered by {lib}</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B530" t="str">
-        <v>Com {lib}</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C530" t="str">
-        <v>Com {lib}</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Subscribe</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B531" t="str">
-        <v>Subscrever</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C531" t="str">
-        <v>Inscrever-se</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Full range</v>
       </c>
       <c r="B532" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Gama completa</v>
       </c>
       <c r="C532" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Get notified about new releases</v>
+        <v>Narrow range</v>
       </c>
       <c r="B533" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C533" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Close</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B534" t="str">
-        <v>Fechar</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C534" t="str">
-        <v>Fechar</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B535" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C535" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Email address</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B536" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C536" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>you@example.com</v>
+        <v>REPORT</v>
       </c>
       <c r="B537" t="str">
-        <v>voce@exemplo.com</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C537" t="str">
-        <v>voce@exemplo.com</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>How will you use profiletool?</v>
+        <v>FAIL</v>
       </c>
       <c r="B538" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C538" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>(optional)</v>
+        <v>checks</v>
       </c>
       <c r="B539" t="str">
-        <v>(opcional)</v>
+        <v>verificações</v>
       </c>
       <c r="C539" t="str">
-        <v>(opcional)</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B540" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C540" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B541" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C541" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Cancel</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B542" t="str">
-        <v>Cancelar</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C542" t="str">
-        <v>Cancelar</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B543" t="str">
-        <v>Subscrever</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C543" t="str">
-        <v>Inscrever-se</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B544" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C544" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B545" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C545" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B546" t="str">
-        <v>Fechar</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C546" t="str">
-        <v>Fechar</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B547" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Fechar</v>
       </c>
       <c r="C547" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B548" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C548" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Email address</v>
       </c>
       <c r="B549" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C549" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Please check the form and try again.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B550" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C550" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B551" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C551" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Network error. Please try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B552" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>(opcional)</v>
       </c>
       <c r="C552" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Error:</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B553" t="str">
-        <v>Erro:</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C553" t="str">
-        <v>Erro:</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Convert to XML</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B554" t="str">
-        <v>Converter para XML</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C554" t="str">
-        <v>Converter para XML</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Convert to JSON</v>
+        <v>Cancel</v>
       </c>
       <c r="B555" t="str">
-        <v>Converter para JSON</v>
+        <v>Cancelar</v>
       </c>
       <c r="C555" t="str">
-        <v>Converter para JSON</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Convert to ICC</v>
+        <v>Subscribe</v>
       </c>
       <c r="B556" t="str">
-        <v>Converter para ICC</v>
+        <v>Subscrever</v>
       </c>
       <c r="C556" t="str">
-        <v>Converter para ICC</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Converting to XML…</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B557" t="str">
-        <v>A converter para XML…</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C557" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Converting to JSON…</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B558" t="str">
-        <v>A converter para JSON…</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C558" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Converting to ICC…</v>
+        <v>Close</v>
       </c>
       <c r="B559" t="str">
-        <v>A converter para ICC…</v>
+        <v>Fechar</v>
       </c>
       <c r="C559" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Load ICC profile</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B560" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C560" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B561" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C561" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Profile ID</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B562" t="str">
-        <v>ID do perfil</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C562" t="str">
-        <v>ID do perfil</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>No tags found.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B563" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C563" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Tag Name</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B564" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C564" t="str">
-        <v>Nome da tag</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B565" t="str">
-        <v>ID</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C565" t="str">
-        <v>ID</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Offset</v>
+        <v>Error:</v>
       </c>
       <c r="B566" t="str">
-        <v>Deslocamento</v>
+        <v>Erro:</v>
       </c>
       <c r="C566" t="str">
-        <v>Deslocamento</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Size</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B567" t="str">
-        <v>Tamanho</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C567" t="str">
-        <v>Tamanho</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Pad</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B568" t="str">
-        <v>Preenchimento</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C568" t="str">
-        <v>Preenchimento</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Bytes changed since load</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B569" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C569" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Type</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B570" t="str">
-        <v>Tipo</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C570" t="str">
-        <v>Tipo</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Array of {type}</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B571" t="str">
-        <v>Vetor de {type}</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C571" t="str">
-        <v>Array de {type}</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>(No content)</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B572" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C572" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>bytes</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B573" t="str">
-        <v>bytes</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C573" t="str">
-        <v>bytes</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Loading full description…</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B574" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C574" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Could not load full description:</v>
+        <v>Profile ID</v>
       </c>
       <c r="B575" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C575" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>No tags found.</v>
       </c>
       <c r="B576" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C576" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B577" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C577" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>No validation output</v>
+        <v>ID</v>
       </c>
       <c r="B578" t="str">
-        <v>Sem saída de validação</v>
+        <v>ID</v>
       </c>
       <c r="C578" t="str">
-        <v>Sem saída de validação</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Profile is valid</v>
+        <v>Offset</v>
       </c>
       <c r="B579" t="str">
-        <v>O perfil é válido</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C579" t="str">
-        <v>O perfil é válido</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Size</v>
       </c>
       <c r="B580" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Tamanho</v>
       </c>
       <c r="C580" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Pad</v>
       </c>
       <c r="B581" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C581" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Critical validation error</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B582" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C582" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Unknown validation status</v>
+        <v>Type</v>
       </c>
       <c r="B583" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Tipo</v>
       </c>
       <c r="C583" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B584" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C584" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>No warnings or errors found.</v>
+        <v>(No content)</v>
       </c>
       <c r="B585" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C585" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Valid</v>
+        <v>bytes</v>
       </c>
       <c r="B586" t="str">
-        <v>Válido</v>
+        <v>bytes</v>
       </c>
       <c r="C586" t="str">
-        <v>Válido</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Warning</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B587" t="str">
-        <v>Aviso</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C587" t="str">
-        <v>Aviso</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Error</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B588" t="str">
-        <v>Erro</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C588" t="str">
-        <v>Erro</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Unknown</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B589" t="str">
-        <v>Desconhecido</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C589" t="str">
-        <v>Desconhecido</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Pass</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B590" t="str">
-        <v>Aprovado</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C590" t="str">
-        <v>Aprovado</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Fail</v>
+        <v>No validation output</v>
       </c>
       <c r="B591" t="str">
-        <v>Reprovado</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C591" t="str">
-        <v>Reprovado</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>View in context</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B592" t="str">
-        <v>Ver no contexto</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C592" t="str">
-        <v>Ver no contexto</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Validation detail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B593" t="str">
-        <v>Detalhe de validação</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C593" t="str">
-        <v>Detalhe de validação</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Triggered by</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B594" t="str">
-        <v>Acionado por</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C594" t="str">
-        <v>Acionado por</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Field</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B595" t="str">
-        <v>Campo</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C595" t="str">
-        <v>Campo</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Current value</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B596" t="str">
-        <v>Valor atual</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C596" t="str">
-        <v>Valor atual</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Required: 0</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B597" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C597" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Expected: {value}</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B598" t="str">
-        <v>Esperado: {value}</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C598" t="str">
-        <v>Esperado: {value}</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Invalid</v>
+        <v>Valid</v>
       </c>
       <c r="B599" t="str">
-        <v>Inválido</v>
+        <v>Válido</v>
       </c>
       <c r="C599" t="str">
-        <v>Inválido</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Warning</v>
       </c>
       <c r="B600" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Aviso</v>
       </c>
       <c r="C600" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Close</v>
+        <v>Error</v>
       </c>
       <c r="B601" t="str">
-        <v>Fechar</v>
+        <v>Erro</v>
       </c>
       <c r="C601" t="str">
-        <v>Fechar</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Loading XML editor…</v>
+        <v>Unknown</v>
       </c>
       <c r="B602" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C602" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Pass</v>
       </c>
       <c r="B603" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Aprovado</v>
       </c>
       <c r="C603" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Fail</v>
       </c>
       <c r="B604" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Reprovado</v>
       </c>
       <c r="C604" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>View in context</v>
       </c>
       <c r="B605" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C605" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Validation detail</v>
       </c>
       <c r="B606" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C606" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Triggered by</v>
       </c>
       <c r="B607" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Acionado por</v>
       </c>
       <c r="C607" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Field</v>
       </c>
       <c r="B608" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Campo</v>
       </c>
       <c r="C608" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Current value</v>
       </c>
       <c r="B609" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Valor atual</v>
       </c>
       <c r="C609" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>indent</v>
+        <v>Required: 0</v>
       </c>
       <c r="B610" t="str">
-        <v>indentação</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C610" t="str">
-        <v>indentação</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>sort keys</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B611" t="str">
-        <v>ordenar chaves</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C611" t="str">
-        <v>ordenar chaves</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B612" t="str">
+        <v>Inválido</v>
+      </c>
+      <c r="C612" t="str">
+        <v>Inválido</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B613" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+      <c r="C613" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B614" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C614" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B615" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C615" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B616" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C616" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B617" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C617" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B618" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C618" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B619" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C619" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B620" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C620" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B621" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C621" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B622" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C622" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B623" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C623" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B624" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C624" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B612" t="str">
+      <c r="B625" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C612" t="str">
+      <c r="C625" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C612"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C625"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C625"/>
+  <dimension ref="A1:C627"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5871,1426 +5871,1448 @@
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B497" t="str">
-        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
+        <v>Amostra de branco SDR</v>
       </c>
       <c r="C497" t="str">
-        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
+        <v>Amostra de branco SDR</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Display headroom</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B498" t="str">
-        <v>Margem do ecrã</v>
+        <v>Arraste para a mover; faça duplo clique para a repor junto à imagem.</v>
       </c>
       <c r="C498" t="str">
-        <v>Margem da tela</v>
+        <v>Arraste para movê-la; clique duas vezes para colocá-la de volta ao lado da imagem.</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B499" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
       </c>
       <c r="C499" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Baseline</v>
+        <v>Display headroom</v>
       </c>
       <c r="B500" t="str">
-        <v>Base</v>
+        <v>Margem do ecrã</v>
       </c>
       <c r="C500" t="str">
-        <v>Base</v>
+        <v>Margem da tela</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B501" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
       <c r="C501" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Baseline</v>
       </c>
       <c r="B502" t="str">
-        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
+        <v>Base</v>
       </c>
       <c r="C502" t="str">
-        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B503" t="str">
-        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
       <c r="C503" t="str">
-        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B504" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
+        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
       </c>
       <c r="C504" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
+        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B505" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
+        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
       </c>
       <c r="C505" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
+        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B506" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
+        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
       </c>
       <c r="C506" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
+        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B507" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
       </c>
       <c r="C507" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Curve at {h} stops</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B508" t="str">
-        <v>Curva a {h} stops</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
       </c>
       <c r="C508" t="str">
-        <v>Curva a {h} stops</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B509" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
       <c r="C509" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B510" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>Curva a {h} stops</v>
       </c>
       <c r="C510" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>Curva a {h} stops</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B511" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>Aplicado a {h} stops</v>
       </c>
       <c r="C511" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>Aplicado a {h} stops</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B512" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
       <c r="C512" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B513" t="str">
-        <v>Curva de tons dos cinzentos nesta margem</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
       <c r="C513" t="str">
-        <v>Curva de tons de cinza nesta margem</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B514" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Ganho (stops log2)</v>
       </c>
       <c r="C514" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Ganho (stops log2)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B515" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Curva de tons dos cinzentos nesta margem</v>
       </c>
       <c r="C515" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Curva de tons de cinza nesta margem</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>No change</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B516" t="str">
-        <v>Sem alteração</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
       <c r="C516" t="str">
-        <v>Sem alteração</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B517" t="str">
-        <v>Pico do ecrã a {h} stops</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
       <c r="C517" t="str">
-        <v>Pico da tela a {h} stops</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Output at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B518" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Sem alteração</v>
       </c>
       <c r="C518" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Sem alteração</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B519" t="str">
-        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
+        <v>Pico do ecrã a {h} stops</v>
       </c>
       <c r="C519" t="str">
-        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
+        <v>Pico da tela a {h} stops</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Identify displays</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B520" t="str">
-        <v>Identificar ecrãs</v>
+        <v>Saída a {h} stops</v>
       </c>
       <c r="C520" t="str">
-        <v>Identificar telas</v>
+        <v>Saída a {h} stops</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B521" t="str">
-        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
       </c>
       <c r="C521" t="str">
-        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B522" t="str">
-        <v>A acompanhar em que monitor está esta janela.</v>
+        <v>Identificar ecrãs</v>
       </c>
       <c r="C522" t="str">
-        <v>Acompanhando em qual monitor esta janela está.</v>
+        <v>Identificar telas</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B523" t="str">
-        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
+        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
       <c r="C523" t="str">
-        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
+        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B524" t="str">
-        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
+        <v>A acompanhar em que monitor está esta janela.</v>
       </c>
       <c r="C524" t="str">
-        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
+        <v>Acompanhando em qual monitor esta janela está.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Could not identify displays.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B525" t="str">
-        <v>Não foi possível identificar os ecrãs.</v>
+        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
       </c>
       <c r="C525" t="str">
-        <v>Não foi possível identificar as telas.</v>
+        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Display events</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B526" t="str">
-        <v>Eventos de ecrã</v>
+        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
       </c>
       <c r="C526" t="str">
-        <v>Eventos de tela</v>
+        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B527" t="str">
-        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
+        <v>Não foi possível identificar os ecrãs.</v>
       </c>
       <c r="C527" t="str">
-        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
+        <v>Não foi possível identificar as telas.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Colour primaries</v>
+        <v>Display events</v>
       </c>
       <c r="B528" t="str">
-        <v>Primárias de cor</v>
+        <v>Eventos de ecrã</v>
       </c>
       <c r="C528" t="str">
-        <v>Primárias de cor</v>
+        <v>Eventos de tela</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Transfer characteristics</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B529" t="str">
-        <v>Características de transferência</v>
+        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
       </c>
       <c r="C529" t="str">
-        <v>Características de transferência</v>
+        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Matrix coefficients</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B530" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C530" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Video full-range flag</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B531" t="str">
-        <v>Sinalizador de gama completa de vídeo</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C531" t="str">
-        <v>Sinalizador de faixa completa de vídeo</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Full range</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B532" t="str">
-        <v>Gama completa</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C532" t="str">
-        <v>Faixa completa</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Narrow range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B533" t="str">
-        <v>Gama reduzida</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C533" t="str">
-        <v>Faixa reduzida</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Full range</v>
       </c>
       <c r="B534" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Gama completa</v>
       </c>
       <c r="C534" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B535" t="str">
-        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C535" t="str">
-        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B536" t="str">
-        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C536" t="str">
-        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>REPORT</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B537" t="str">
-        <v>RELATÓRIO</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C537" t="str">
-        <v>RELATÓRIO</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>FAIL</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B538" t="str">
-        <v>REPROVADO</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C538" t="str">
-        <v>REPROVADO</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>checks</v>
+        <v>REPORT</v>
       </c>
       <c r="B539" t="str">
-        <v>verificações</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C539" t="str">
-        <v>verificações</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>FAIL</v>
       </c>
       <c r="B540" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C540" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>checks</v>
       </c>
       <c r="B541" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>verificações</v>
       </c>
       <c r="C541" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B542" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C542" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B543" t="str">
-        <v>Com {lib}</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C543" t="str">
-        <v>Com {lib}</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Subscribe</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B544" t="str">
-        <v>Subscrever</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C544" t="str">
-        <v>Inscrever-se</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B545" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C545" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Get notified about new releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B546" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Subscrever</v>
       </c>
       <c r="C546" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Close</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B547" t="str">
-        <v>Fechar</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C547" t="str">
-        <v>Fechar</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B548" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C548" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Email address</v>
+        <v>Close</v>
       </c>
       <c r="B549" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Fechar</v>
       </c>
       <c r="C549" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>you@example.com</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B550" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C550" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Email address</v>
       </c>
       <c r="B551" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C551" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>(optional)</v>
+        <v>you@example.com</v>
       </c>
       <c r="B552" t="str">
-        <v>(opcional)</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C552" t="str">
-        <v>(opcional)</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B553" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C553" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>(optional)</v>
       </c>
       <c r="B554" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>(opcional)</v>
       </c>
       <c r="C554" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Cancel</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B555" t="str">
-        <v>Cancelar</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C555" t="str">
-        <v>Cancelar</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Subscribe</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B556" t="str">
-        <v>Subscrever</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C556" t="str">
-        <v>Inscrever-se</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Cancel</v>
       </c>
       <c r="B557" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Cancelar</v>
       </c>
       <c r="C557" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B558" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C558" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Close</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B559" t="str">
-        <v>Fechar</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C559" t="str">
-        <v>Fechar</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Privacy notice</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B560" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C560" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Close</v>
       </c>
       <c r="B561" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Fechar</v>
       </c>
       <c r="C561" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B562" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C562" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B563" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C563" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B564" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C564" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B565" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C565" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Error:</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B566" t="str">
-        <v>Erro:</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C566" t="str">
-        <v>Erro:</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Convert to XML</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B567" t="str">
-        <v>Converter para XML</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C567" t="str">
-        <v>Converter para XML</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Convert to JSON</v>
+        <v>Error:</v>
       </c>
       <c r="B568" t="str">
-        <v>Converter para JSON</v>
+        <v>Erro:</v>
       </c>
       <c r="C568" t="str">
-        <v>Converter para JSON</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B569" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C569" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B570" t="str">
-        <v>A converter para XML…</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C570" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B571" t="str">
-        <v>A converter para JSON…</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C571" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B572" t="str">
-        <v>A converter para ICC…</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C572" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B573" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C573" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B574" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C574" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Profile ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B575" t="str">
-        <v>ID do perfil</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C575" t="str">
-        <v>ID do perfil</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>No tags found.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B576" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C576" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Tag Name</v>
+        <v>Profile ID</v>
       </c>
       <c r="B577" t="str">
-        <v>Nome da etiqueta</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C577" t="str">
-        <v>Nome da tag</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B578" t="str">
-        <v>ID</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C578" t="str">
-        <v>ID</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Offset</v>
+        <v>Tag Name</v>
       </c>
       <c r="B579" t="str">
-        <v>Deslocamento</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C579" t="str">
-        <v>Deslocamento</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Size</v>
+        <v>ID</v>
       </c>
       <c r="B580" t="str">
-        <v>Tamanho</v>
+        <v>ID</v>
       </c>
       <c r="C580" t="str">
-        <v>Tamanho</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Pad</v>
+        <v>Offset</v>
       </c>
       <c r="B581" t="str">
-        <v>Preenchimento</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C581" t="str">
-        <v>Preenchimento</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Bytes changed since load</v>
+        <v>Size</v>
       </c>
       <c r="B582" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Tamanho</v>
       </c>
       <c r="C582" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Type</v>
+        <v>Pad</v>
       </c>
       <c r="B583" t="str">
-        <v>Tipo</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C583" t="str">
-        <v>Tipo</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Array of {type}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B584" t="str">
-        <v>Vetor de {type}</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C584" t="str">
-        <v>Array de {type}</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>(No content)</v>
+        <v>Type</v>
       </c>
       <c r="B585" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Tipo</v>
       </c>
       <c r="C585" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>bytes</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B586" t="str">
-        <v>bytes</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C586" t="str">
-        <v>bytes</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Loading full description…</v>
+        <v>(No content)</v>
       </c>
       <c r="B587" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C587" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Could not load full description:</v>
+        <v>bytes</v>
       </c>
       <c r="B588" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>bytes</v>
       </c>
       <c r="C588" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B589" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C589" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B590" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C590" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B591" t="str">
-        <v>Sem saída de validação</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C591" t="str">
-        <v>Sem saída de validação</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Profile is valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B592" t="str">
-        <v>O perfil é válido</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C592" t="str">
-        <v>O perfil é válido</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No validation output</v>
       </c>
       <c r="B593" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C593" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B594" t="str">
-        <v>O perfil não é conforme</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C594" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Critical validation error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B595" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C595" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B596" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C596" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B597" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C597" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B598" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C598" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Valid</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B599" t="str">
-        <v>Válido</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C599" t="str">
-        <v>Válido</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B600" t="str">
-        <v>Aviso</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C600" t="str">
-        <v>Aviso</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B601" t="str">
-        <v>Erro</v>
+        <v>Válido</v>
       </c>
       <c r="C601" t="str">
-        <v>Erro</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B602" t="str">
-        <v>Desconhecido</v>
+        <v>Aviso</v>
       </c>
       <c r="C602" t="str">
-        <v>Desconhecido</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Pass</v>
+        <v>Error</v>
       </c>
       <c r="B603" t="str">
-        <v>Aprovado</v>
+        <v>Erro</v>
       </c>
       <c r="C603" t="str">
-        <v>Aprovado</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Fail</v>
+        <v>Unknown</v>
       </c>
       <c r="B604" t="str">
-        <v>Reprovado</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C604" t="str">
-        <v>Reprovado</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>View in context</v>
+        <v>Pass</v>
       </c>
       <c r="B605" t="str">
-        <v>Ver no contexto</v>
+        <v>Aprovado</v>
       </c>
       <c r="C605" t="str">
-        <v>Ver no contexto</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Validation detail</v>
+        <v>Fail</v>
       </c>
       <c r="B606" t="str">
-        <v>Detalhe de validação</v>
+        <v>Reprovado</v>
       </c>
       <c r="C606" t="str">
-        <v>Detalhe de validação</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B607" t="str">
-        <v>Acionado por</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C607" t="str">
-        <v>Acionado por</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B608" t="str">
-        <v>Campo</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C608" t="str">
-        <v>Campo</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B609" t="str">
-        <v>Valor atual</v>
+        <v>Acionado por</v>
       </c>
       <c r="C609" t="str">
-        <v>Valor atual</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B610" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Campo</v>
       </c>
       <c r="C610" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B611" t="str">
-        <v>Esperado: {value}</v>
+        <v>Valor atual</v>
       </c>
       <c r="C611" t="str">
-        <v>Esperado: {value}</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B612" t="str">
-        <v>Inválido</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C612" t="str">
-        <v>Inválido</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B613" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C613" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B614" t="str">
-        <v>Fechar</v>
+        <v>Inválido</v>
       </c>
       <c r="C614" t="str">
-        <v>Fechar</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B615" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C615" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B616" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Fechar</v>
       </c>
       <c r="C616" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B617" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C617" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B618" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C618" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B619" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C619" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B620" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C620" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B621" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições XML por guardar</v>
       </c>
       <c r="C621" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições XML não salvas</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B622" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● edições JSON por guardar</v>
       </c>
       <c r="C622" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● edições JSON não salvas</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B623" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
       <c r="C623" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B624" t="str">
-        <v>ordenar chaves</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
       <c r="C624" t="str">
-        <v>ordenar chaves</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B625" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C625" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B626" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C626" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B625" t="str">
+      <c r="B627" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C625" t="str">
+      <c r="C627" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C625"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C627"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C627"/>
+  <dimension ref="A1:C650"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5893,1426 +5893,1679 @@
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Assign profile</v>
       </c>
       <c r="B499" t="str">
-        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
+        <v>Atribuir perfil</v>
       </c>
       <c r="C499" t="str">
-        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
+        <v>Atribuir perfil</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Display headroom</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B500" t="str">
-        <v>Margem do ecrã</v>
+        <v>Nenhum — o que o ficheiro indica</v>
       </c>
       <c r="C500" t="str">
-        <v>Margem da tela</v>
+        <v>Nenhum — o que o arquivo indica</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B501" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>Perfil incorporado ({n} B)</v>
       </c>
       <c r="C501" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>Perfil incorporado ({n} B)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B502" t="str">
-        <v>Base</v>
+        <v>Perfis HDR no pool</v>
       </c>
       <c r="C502" t="str">
-        <v>Base</v>
+        <v>Perfis HDR no pool</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Profile</v>
       </c>
       <c r="B503" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>Perfil</v>
       </c>
       <c r="C503" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>embedded profile</v>
       </c>
       <c r="B504" t="str">
-        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
+        <v>perfil incorporado</v>
       </c>
       <c r="C504" t="str">
-        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
+        <v>perfil incorporado</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B505" t="str">
-        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
+        <v>Caminho do motor de cor</v>
       </c>
       <c r="C505" t="str">
-        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
+        <v>Caminho do mecanismo de cor</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B506" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
+        <v>Caminho HDR, curva de ganho aplicada</v>
       </c>
       <c r="C506" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
+        <v>Caminho HDR, curva de ganho aplicada</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B507" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
+        <v>Caminho HDR, sem curva de ganho</v>
       </c>
       <c r="C507" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
+        <v>Caminho HDR, sem curva de ganho</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B508" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
+        <v>AToB0 pré-calculado — não é o caminho HDR</v>
       </c>
       <c r="C508" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
+        <v>AToB0 pré-calculado — não é o caminho HDR</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>Transfer</v>
       </c>
       <c r="B509" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>Transferência</v>
       </c>
       <c r="C509" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>Transferência</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Curve at {h} stops</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B510" t="str">
-        <v>Curva a {h} stops</v>
+        <v>Branco de referência HDR</v>
       </c>
       <c r="C510" t="str">
-        <v>Curva a {h} stops</v>
+        <v>Branco de referência HDR</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Target headroom</v>
       </c>
       <c r="B511" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Margem alvo</v>
       </c>
       <c r="C511" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Margem alvo</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B512" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>{r}× o branco de referência ({n} stops)</v>
       </c>
       <c r="C512" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>{r}× o branco de referência ({n} stops)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B513" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="C513" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>Tone mapping</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B514" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>Auto (ordem da cláusula 8.10.3)</v>
       </c>
       <c r="C514" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>Auto (ordem da cláusula 8.10.3)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B515" t="str">
-        <v>Curva de tons dos cinzentos nesta margem</v>
+        <v>Curva de ganho (HAGC)</v>
       </c>
       <c r="C515" t="str">
-        <v>Curva de tons de cinza nesta margem</v>
+        <v>Curva de ganho (HAGC)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B516" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Alternativa SDR pré-calculada (AToB0)</v>
       </c>
       <c r="C516" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Alternativa SDR pré-calculada (AToB0)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B517" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Desligado — como um CMM anterior à emenda</v>
       </c>
       <c r="C517" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Desligado — como um CMM anterior à emenda</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>No change</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B518" t="str">
-        <v>Sem alteração</v>
+        <v>A aplicar o perfil…</v>
       </c>
       <c r="C518" t="str">
-        <v>Sem alteração</v>
+        <v>Aplicando o perfil…</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>OpenEXR holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B519" t="str">
-        <v>Pico do ecrã a {h} stops</v>
+        <v>O OpenEXR contém luz linear, pelo que precisa de um perfil com transferência Linear (8).</v>
       </c>
       <c r="C519" t="str">
-        <v>Pico da tela a {h} stops</v>
+        <v>O OpenEXR contém luz linear, então precisa de um perfil com transferência Linear (8).</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Output at {h} stops</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B520" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
       </c>
       <c r="C520" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B521" t="str">
-        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
+        <v>Para interpretar os seus valores, atribua um perfil acima.</v>
       </c>
       <c r="C521" t="str">
-        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
+        <v>Para interpretar seus valores, atribua um perfil acima.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Identify displays</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B522" t="str">
-        <v>Identificar ecrãs</v>
+        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
       </c>
       <c r="C522" t="str">
-        <v>Identificar telas</v>
+        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B523" t="str">
-        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Margem do ecrã</v>
       </c>
       <c r="C523" t="str">
-        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Margem da tela</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B524" t="str">
-        <v>A acompanhar em que monitor está esta janela.</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
       <c r="C524" t="str">
-        <v>Acompanhando em qual monitor esta janela está.</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Baseline</v>
       </c>
       <c r="B525" t="str">
-        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
+        <v>Base</v>
       </c>
       <c r="C525" t="str">
-        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B526" t="str">
-        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
       <c r="C526" t="str">
-        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Could not identify displays.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B527" t="str">
-        <v>Não foi possível identificar os ecrãs.</v>
+        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
       </c>
       <c r="C527" t="str">
-        <v>Não foi possível identificar as telas.</v>
+        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Display events</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B528" t="str">
-        <v>Eventos de ecrã</v>
+        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
       </c>
       <c r="C528" t="str">
-        <v>Eventos de tela</v>
+        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B529" t="str">
-        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
+        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
       </c>
       <c r="C529" t="str">
-        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
+        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Colour primaries</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B530" t="str">
-        <v>Primárias de cor</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
       </c>
       <c r="C530" t="str">
-        <v>Primárias de cor</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Transfer characteristics</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B531" t="str">
-        <v>Características de transferência</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
       </c>
       <c r="C531" t="str">
-        <v>Características de transferência</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Matrix coefficients</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B532" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
       <c r="C532" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Video full-range flag</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B533" t="str">
-        <v>Sinalizador de gama completa de vídeo</v>
+        <v>Curva a {h} stops</v>
       </c>
       <c r="C533" t="str">
-        <v>Sinalizador de faixa completa de vídeo</v>
+        <v>Curva a {h} stops</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Full range</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B534" t="str">
-        <v>Gama completa</v>
+        <v>Aplicado a {h} stops</v>
       </c>
       <c r="C534" t="str">
-        <v>Faixa completa</v>
+        <v>Aplicado a {h} stops</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Narrow range</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B535" t="str">
-        <v>Gama reduzida</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
       <c r="C535" t="str">
-        <v>Faixa reduzida</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B536" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
       <c r="C536" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B537" t="str">
-        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
+        <v>Ganho (stops log2)</v>
       </c>
       <c r="C537" t="str">
-        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
+        <v>Ganho (stops log2)</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B538" t="str">
-        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
+        <v>Curva de tons dos cinzentos nesta margem</v>
       </c>
       <c r="C538" t="str">
-        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
+        <v>Curva de tons de cinza nesta margem</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>REPORT</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B539" t="str">
-        <v>RELATÓRIO</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
       <c r="C539" t="str">
-        <v>RELATÓRIO</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>FAIL</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B540" t="str">
-        <v>REPROVADO</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
       <c r="C540" t="str">
-        <v>REPROVADO</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>checks</v>
+        <v>No change</v>
       </c>
       <c r="B541" t="str">
-        <v>verificações</v>
+        <v>Sem alteração</v>
       </c>
       <c r="C541" t="str">
-        <v>verificações</v>
+        <v>Sem alteração</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Pico do ecrã a {h} stops</v>
       </c>
       <c r="C542" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Pico da tela a {h} stops</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B543" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Saída a {h} stops</v>
       </c>
       <c r="C543" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Saída a {h} stops</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B544" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
       </c>
       <c r="C544" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Powered by {lib}</v>
+        <v>Identify displays</v>
       </c>
       <c r="B545" t="str">
-        <v>Com {lib}</v>
+        <v>Identificar ecrãs</v>
       </c>
       <c r="C545" t="str">
-        <v>Com {lib}</v>
+        <v>Identificar telas</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Subscribe</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B546" t="str">
-        <v>Subscrever</v>
+        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
       <c r="C546" t="str">
-        <v>Inscrever-se</v>
+        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B547" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>A acompanhar em que monitor está esta janela.</v>
       </c>
       <c r="C547" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Acompanhando em qual monitor esta janela está.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Get notified about new releases</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B548" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
       </c>
       <c r="C548" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Close</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B549" t="str">
-        <v>Fechar</v>
+        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
       </c>
       <c r="C549" t="str">
-        <v>Fechar</v>
+        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B550" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Não foi possível identificar os ecrãs.</v>
       </c>
       <c r="C550" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Não foi possível identificar as telas.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Email address</v>
+        <v>Display events</v>
       </c>
       <c r="B551" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Eventos de ecrã</v>
       </c>
       <c r="C551" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Eventos de tela</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>you@example.com</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B552" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
       </c>
       <c r="C552" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B553" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C553" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>(optional)</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B554" t="str">
-        <v>(opcional)</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C554" t="str">
-        <v>(opcional)</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B555" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C555" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B556" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C556" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Cancel</v>
+        <v>Full range</v>
       </c>
       <c r="B557" t="str">
-        <v>Cancelar</v>
+        <v>Gama completa</v>
       </c>
       <c r="C557" t="str">
-        <v>Cancelar</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B558" t="str">
-        <v>Subscrever</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C558" t="str">
-        <v>Inscrever-se</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B559" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C559" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B560" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C560" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B561" t="str">
-        <v>Fechar</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C561" t="str">
-        <v>Fechar</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Privacy notice</v>
+        <v>REPORT</v>
       </c>
       <c r="B562" t="str">
-        <v>Aviso de privacidade</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C562" t="str">
-        <v>Aviso de privacidade</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>FAIL</v>
       </c>
       <c r="B563" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C563" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>checks</v>
       </c>
       <c r="B564" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>verificações</v>
       </c>
       <c r="C564" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B565" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C565" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B566" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C566" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Network error. Please try again.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B567" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C567" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Error:</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B568" t="str">
-        <v>Erro:</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C568" t="str">
-        <v>Erro:</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B569" t="str">
-        <v>Converter para XML</v>
+        <v>Subscrever</v>
       </c>
       <c r="C569" t="str">
-        <v>Converter para XML</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Convert to JSON</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B570" t="str">
-        <v>Converter para JSON</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C570" t="str">
-        <v>Converter para JSON</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Convert to ICC</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B571" t="str">
-        <v>Converter para ICC</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C571" t="str">
-        <v>Converter para ICC</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B572" t="str">
-        <v>A converter para XML…</v>
+        <v>Fechar</v>
       </c>
       <c r="C572" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Converting to JSON…</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B573" t="str">
-        <v>A converter para JSON…</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C573" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Converting to ICC…</v>
+        <v>Email address</v>
       </c>
       <c r="B574" t="str">
-        <v>A converter para ICC…</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C574" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Load ICC profile</v>
+        <v>you@example.com</v>
       </c>
       <c r="B575" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C575" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B576" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C576" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Profile ID</v>
+        <v>(optional)</v>
       </c>
       <c r="B577" t="str">
-        <v>ID do perfil</v>
+        <v>(opcional)</v>
       </c>
       <c r="C577" t="str">
-        <v>ID do perfil</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>No tags found.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B578" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C578" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Tag Name</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B579" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C579" t="str">
-        <v>Nome da tag</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B580" t="str">
-        <v>ID</v>
+        <v>Cancelar</v>
       </c>
       <c r="C580" t="str">
-        <v>ID</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Offset</v>
+        <v>Subscribe</v>
       </c>
       <c r="B581" t="str">
-        <v>Deslocamento</v>
+        <v>Subscrever</v>
       </c>
       <c r="C581" t="str">
-        <v>Deslocamento</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Size</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B582" t="str">
-        <v>Tamanho</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C582" t="str">
-        <v>Tamanho</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Pad</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B583" t="str">
-        <v>Preenchimento</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C583" t="str">
-        <v>Preenchimento</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Bytes changed since load</v>
+        <v>Close</v>
       </c>
       <c r="B584" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Fechar</v>
       </c>
       <c r="C584" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Type</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B585" t="str">
-        <v>Tipo</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C585" t="str">
-        <v>Tipo</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Array of {type}</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B586" t="str">
-        <v>Vetor de {type}</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C586" t="str">
-        <v>Array de {type}</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>(No content)</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B587" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C587" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>bytes</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B588" t="str">
-        <v>bytes</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C588" t="str">
-        <v>bytes</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Loading full description…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B589" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C589" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Could not load full description:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B590" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C590" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error:</v>
       </c>
       <c r="B591" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Erro:</v>
       </c>
       <c r="C591" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B592" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C592" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>No validation output</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B593" t="str">
-        <v>Sem saída de validação</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C593" t="str">
-        <v>Sem saída de validação</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Profile is valid</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B594" t="str">
-        <v>O perfil é válido</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C594" t="str">
-        <v>O perfil é válido</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B595" t="str">
-        <v>O perfil tem avisos</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C595" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B596" t="str">
-        <v>O perfil não é conforme</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C596" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Critical validation error</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B597" t="str">
-        <v>Erro de validação crítico</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C597" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Unknown validation status</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B598" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C598" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B599" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C599" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B600" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C600" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Valid</v>
+        <v>No tags found.</v>
       </c>
       <c r="B601" t="str">
-        <v>Válido</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C601" t="str">
-        <v>Válido</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Warning</v>
+        <v>Tag Name</v>
       </c>
       <c r="B602" t="str">
-        <v>Aviso</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C602" t="str">
-        <v>Aviso</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
       <c r="B603" t="str">
-        <v>Erro</v>
+        <v>ID</v>
       </c>
       <c r="C603" t="str">
-        <v>Erro</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Unknown</v>
+        <v>Offset</v>
       </c>
       <c r="B604" t="str">
-        <v>Desconhecido</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C604" t="str">
-        <v>Desconhecido</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Pass</v>
+        <v>Size</v>
       </c>
       <c r="B605" t="str">
-        <v>Aprovado</v>
+        <v>Tamanho</v>
       </c>
       <c r="C605" t="str">
-        <v>Aprovado</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Fail</v>
+        <v>Pad</v>
       </c>
       <c r="B606" t="str">
-        <v>Reprovado</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C606" t="str">
-        <v>Reprovado</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>View in context</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B607" t="str">
-        <v>Ver no contexto</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C607" t="str">
-        <v>Ver no contexto</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Validation detail</v>
+        <v>Type</v>
       </c>
       <c r="B608" t="str">
-        <v>Detalhe de validação</v>
+        <v>Tipo</v>
       </c>
       <c r="C608" t="str">
-        <v>Detalhe de validação</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Triggered by</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B609" t="str">
-        <v>Acionado por</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C609" t="str">
-        <v>Acionado por</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Field</v>
+        <v>(No content)</v>
       </c>
       <c r="B610" t="str">
-        <v>Campo</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C610" t="str">
-        <v>Campo</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Current value</v>
+        <v>bytes</v>
       </c>
       <c r="B611" t="str">
-        <v>Valor atual</v>
+        <v>bytes</v>
       </c>
       <c r="C611" t="str">
-        <v>Valor atual</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Required: 0</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B612" t="str">
-        <v>Obrigatório: 0</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C612" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B613" t="str">
-        <v>Esperado: {value}</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C613" t="str">
-        <v>Esperado: {value}</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Invalid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B614" t="str">
-        <v>Inválido</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C614" t="str">
-        <v>Inválido</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B615" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C615" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Close</v>
+        <v>No validation output</v>
       </c>
       <c r="B616" t="str">
-        <v>Fechar</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C616" t="str">
-        <v>Fechar</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Loading XML editor…</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B617" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C617" t="str">
-        <v>Carregando editor XML…</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B618" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C618" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B619" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C619" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B620" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C620" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B621" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C621" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B622" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C622" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B623" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C623" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Valid</v>
       </c>
       <c r="B624" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Válido</v>
       </c>
       <c r="C624" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>indent</v>
+        <v>Warning</v>
       </c>
       <c r="B625" t="str">
-        <v>indentação</v>
+        <v>Aviso</v>
       </c>
       <c r="C625" t="str">
-        <v>indentação</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>sort keys</v>
+        <v>Error</v>
       </c>
       <c r="B626" t="str">
-        <v>ordenar chaves</v>
+        <v>Erro</v>
       </c>
       <c r="C626" t="str">
-        <v>ordenar chaves</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B627" t="str">
+        <v>Desconhecido</v>
+      </c>
+      <c r="C627" t="str">
+        <v>Desconhecido</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B628" t="str">
+        <v>Aprovado</v>
+      </c>
+      <c r="C628" t="str">
+        <v>Aprovado</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B629" t="str">
+        <v>Reprovado</v>
+      </c>
+      <c r="C629" t="str">
+        <v>Reprovado</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B630" t="str">
+        <v>Ver no contexto</v>
+      </c>
+      <c r="C630" t="str">
+        <v>Ver no contexto</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B631" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+      <c r="C631" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B632" t="str">
+        <v>Acionado por</v>
+      </c>
+      <c r="C632" t="str">
+        <v>Acionado por</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B633" t="str">
+        <v>Campo</v>
+      </c>
+      <c r="C633" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B634" t="str">
+        <v>Valor atual</v>
+      </c>
+      <c r="C634" t="str">
+        <v>Valor atual</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B635" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+      <c r="C635" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B636" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+      <c r="C636" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B637" t="str">
+        <v>Inválido</v>
+      </c>
+      <c r="C637" t="str">
+        <v>Inválido</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B638" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+      <c r="C638" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B639" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C639" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B640" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C640" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B641" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C641" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B642" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C642" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B643" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C643" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B644" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C644" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B645" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C645" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B646" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C646" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B647" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C647" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B648" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C648" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B649" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C649" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B627" t="str">
+      <c r="B650" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C627" t="str">
+      <c r="C650" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C627"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C650"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C650"/>
+  <dimension ref="A1:C658"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -6146,1426 +6146,1514 @@
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B522" t="str">
-        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
+        <v>Perfis HDR</v>
       </c>
       <c r="C522" t="str">
-        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
+        <v>Perfis HDR</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Display headroom</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B523" t="str">
-        <v>Margem do ecrã</v>
+        <v>Transferência linear</v>
       </c>
       <c r="C523" t="str">
-        <v>Margem da tela</v>
+        <v>Transferência linear</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B524" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>Transferência não linear (PQ, HLG)</v>
       </c>
       <c r="C524" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>Transferência não linear (PQ, HLG)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B525" t="str">
-        <v>Base</v>
+        <v>Perfis HDR — transferência linear</v>
       </c>
       <c r="C525" t="str">
-        <v>Base</v>
+        <v>Perfis HDR — transferência linear</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>Perfis HDR — transferência PQ / HLG</v>
       </c>
       <c r="C526" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>Perfis HDR — transferência PQ / HLG</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>OpenEXR holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B527" t="str">
-        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
+        <v>O OpenEXR contém luz linear, pelo que só podem ser atribuídos perfis HDR com transferência linear.</v>
       </c>
       <c r="C527" t="str">
-        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
+        <v>O OpenEXR contém luz linear, então só podem ser atribuídos perfis HDR com transferência linear.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B528" t="str">
-        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
+        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis lista-os em Perfis HDR › Transferência não linear.</v>
       </c>
       <c r="C528" t="str">
-        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
+        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis os lista em Perfis HDR › Transferência não linear.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B529" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
+        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
       </c>
       <c r="C529" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
+        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B530" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
+        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
       </c>
       <c r="C530" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
+        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B531" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
+        <v>Margem do ecrã</v>
       </c>
       <c r="C531" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
+        <v>Margem da tela</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B532" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
       <c r="C532" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Baseline</v>
       </c>
       <c r="B533" t="str">
-        <v>Curva a {h} stops</v>
+        <v>Base</v>
       </c>
       <c r="C533" t="str">
-        <v>Curva a {h} stops</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B534" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
       <c r="C534" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B535" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
       </c>
       <c r="C535" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B536" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
       </c>
       <c r="C536" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B537" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
       </c>
       <c r="C537" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B538" t="str">
-        <v>Curva de tons dos cinzentos nesta margem</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
       </c>
       <c r="C538" t="str">
-        <v>Curva de tons de cinza nesta margem</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B539" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
       </c>
       <c r="C539" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B540" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
       <c r="C540" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>No change</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B541" t="str">
-        <v>Sem alteração</v>
+        <v>Curva a {h} stops</v>
       </c>
       <c r="C541" t="str">
-        <v>Sem alteração</v>
+        <v>Curva a {h} stops</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>Pico do ecrã a {h} stops</v>
+        <v>Aplicado a {h} stops</v>
       </c>
       <c r="C542" t="str">
-        <v>Pico da tela a {h} stops</v>
+        <v>Aplicado a {h} stops</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Output at {h} stops</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B543" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
       <c r="C543" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B544" t="str">
-        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
       <c r="C544" t="str">
-        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Identify displays</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B545" t="str">
-        <v>Identificar ecrãs</v>
+        <v>Ganho (stops log2)</v>
       </c>
       <c r="C545" t="str">
-        <v>Identificar telas</v>
+        <v>Ganho (stops log2)</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B546" t="str">
-        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Curva de tons dos cinzentos nesta margem</v>
       </c>
       <c r="C546" t="str">
-        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Curva de tons de cinza nesta margem</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B547" t="str">
-        <v>A acompanhar em que monitor está esta janela.</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
       <c r="C547" t="str">
-        <v>Acompanhando em qual monitor esta janela está.</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B548" t="str">
-        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
       <c r="C548" t="str">
-        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>No change</v>
       </c>
       <c r="B549" t="str">
-        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
+        <v>Sem alteração</v>
       </c>
       <c r="C549" t="str">
-        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
+        <v>Sem alteração</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Could not identify displays.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B550" t="str">
-        <v>Não foi possível identificar os ecrãs.</v>
+        <v>Pico do ecrã a {h} stops</v>
       </c>
       <c r="C550" t="str">
-        <v>Não foi possível identificar as telas.</v>
+        <v>Pico da tela a {h} stops</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Display events</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B551" t="str">
-        <v>Eventos de ecrã</v>
+        <v>Saída a {h} stops</v>
       </c>
       <c r="C551" t="str">
-        <v>Eventos de tela</v>
+        <v>Saída a {h} stops</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B552" t="str">
-        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
+        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
       </c>
       <c r="C552" t="str">
-        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
+        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Colour primaries</v>
+        <v>Identify displays</v>
       </c>
       <c r="B553" t="str">
-        <v>Primárias de cor</v>
+        <v>Identificar ecrãs</v>
       </c>
       <c r="C553" t="str">
-        <v>Primárias de cor</v>
+        <v>Identificar telas</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Transfer characteristics</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B554" t="str">
-        <v>Características de transferência</v>
+        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
       <c r="C554" t="str">
-        <v>Características de transferência</v>
+        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Matrix coefficients</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B555" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>A acompanhar em que monitor está esta janela.</v>
       </c>
       <c r="C555" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Acompanhando em qual monitor esta janela está.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Video full-range flag</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B556" t="str">
-        <v>Sinalizador de gama completa de vídeo</v>
+        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
       </c>
       <c r="C556" t="str">
-        <v>Sinalizador de faixa completa de vídeo</v>
+        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Full range</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B557" t="str">
-        <v>Gama completa</v>
+        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
       </c>
       <c r="C557" t="str">
-        <v>Faixa completa</v>
+        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Narrow range</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B558" t="str">
-        <v>Gama reduzida</v>
+        <v>Não foi possível identificar os ecrãs.</v>
       </c>
       <c r="C558" t="str">
-        <v>Faixa reduzida</v>
+        <v>Não foi possível identificar as telas.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Display events</v>
       </c>
       <c r="B559" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Eventos de ecrã</v>
       </c>
       <c r="C559" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Eventos de tela</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B560" t="str">
-        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
+        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
       </c>
       <c r="C560" t="str">
-        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
+        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B561" t="str">
-        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C561" t="str">
-        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>REPORT</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B562" t="str">
-        <v>RELATÓRIO</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C562" t="str">
-        <v>RELATÓRIO</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>FAIL</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B563" t="str">
-        <v>REPROVADO</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C563" t="str">
-        <v>REPROVADO</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>checks</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B564" t="str">
-        <v>verificações</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C564" t="str">
-        <v>verificações</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Full range</v>
       </c>
       <c r="B565" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Gama completa</v>
       </c>
       <c r="C565" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Narrow range</v>
       </c>
       <c r="B566" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C566" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>ICC Profile Tool</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B567" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C567" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Powered by {lib}</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B568" t="str">
-        <v>Com {lib}</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C568" t="str">
-        <v>Com {lib}</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Subscribe</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B569" t="str">
-        <v>Subscrever</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C569" t="str">
-        <v>Inscrever-se</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>REPORT</v>
       </c>
       <c r="B570" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C570" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Get notified about new releases</v>
+        <v>FAIL</v>
       </c>
       <c r="B571" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C571" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Close</v>
+        <v>checks</v>
       </c>
       <c r="B572" t="str">
-        <v>Fechar</v>
+        <v>verificações</v>
       </c>
       <c r="C572" t="str">
-        <v>Fechar</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B573" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C573" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Email address</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B574" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C574" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>you@example.com</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B575" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C575" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B576" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C576" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>(optional)</v>
+        <v>Subscribe</v>
       </c>
       <c r="B577" t="str">
-        <v>(opcional)</v>
+        <v>Subscrever</v>
       </c>
       <c r="C577" t="str">
-        <v>(opcional)</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B578" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C578" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B579" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C579" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Cancel</v>
+        <v>Close</v>
       </c>
       <c r="B580" t="str">
-        <v>Cancelar</v>
+        <v>Fechar</v>
       </c>
       <c r="C580" t="str">
-        <v>Cancelar</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Subscribe</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B581" t="str">
-        <v>Subscrever</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C581" t="str">
-        <v>Inscrever-se</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Email address</v>
       </c>
       <c r="B582" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C582" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B583" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C583" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Close</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B584" t="str">
-        <v>Fechar</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C584" t="str">
-        <v>Fechar</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Privacy notice</v>
+        <v>(optional)</v>
       </c>
       <c r="B585" t="str">
-        <v>Aviso de privacidade</v>
+        <v>(opcional)</v>
       </c>
       <c r="C585" t="str">
-        <v>Aviso de privacidade</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B586" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C586" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B587" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C587" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B588" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Cancelar</v>
       </c>
       <c r="C588" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B589" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C589" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B590" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C590" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Error:</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B591" t="str">
-        <v>Erro:</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C591" t="str">
-        <v>Erro:</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Convert to XML</v>
+        <v>Close</v>
       </c>
       <c r="B592" t="str">
-        <v>Converter para XML</v>
+        <v>Fechar</v>
       </c>
       <c r="C592" t="str">
-        <v>Converter para XML</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Convert to JSON</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B593" t="str">
-        <v>Converter para JSON</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C593" t="str">
-        <v>Converter para JSON</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Convert to ICC</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B594" t="str">
-        <v>Converter para ICC</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C594" t="str">
-        <v>Converter para ICC</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Converting to XML…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B595" t="str">
-        <v>A converter para XML…</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C595" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B596" t="str">
-        <v>A converter para JSON…</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C596" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Converting to ICC…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B597" t="str">
-        <v>A converter para ICC…</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C597" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Load ICC profile</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B598" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C598" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Error:</v>
       </c>
       <c r="B599" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Erro:</v>
       </c>
       <c r="C599" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Profile ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B600" t="str">
-        <v>ID do perfil</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C600" t="str">
-        <v>ID do perfil</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>No tags found.</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B601" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C601" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Tag Name</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B602" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C602" t="str">
-        <v>Nome da tag</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>ID</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B603" t="str">
-        <v>ID</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C603" t="str">
-        <v>ID</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Offset</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B604" t="str">
-        <v>Deslocamento</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C604" t="str">
-        <v>Deslocamento</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Size</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B605" t="str">
-        <v>Tamanho</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C605" t="str">
-        <v>Tamanho</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Pad</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B606" t="str">
-        <v>Preenchimento</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C606" t="str">
-        <v>Preenchimento</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Bytes changed since load</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B607" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C607" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Type</v>
+        <v>Profile ID</v>
       </c>
       <c r="B608" t="str">
-        <v>Tipo</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C608" t="str">
-        <v>Tipo</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Array of {type}</v>
+        <v>No tags found.</v>
       </c>
       <c r="B609" t="str">
-        <v>Vetor de {type}</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C609" t="str">
-        <v>Array de {type}</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>(No content)</v>
+        <v>Tag Name</v>
       </c>
       <c r="B610" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C610" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>bytes</v>
+        <v>ID</v>
       </c>
       <c r="B611" t="str">
-        <v>bytes</v>
+        <v>ID</v>
       </c>
       <c r="C611" t="str">
-        <v>bytes</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Loading full description…</v>
+        <v>Offset</v>
       </c>
       <c r="B612" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C612" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Could not load full description:</v>
+        <v>Size</v>
       </c>
       <c r="B613" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Tamanho</v>
       </c>
       <c r="C613" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Pad</v>
       </c>
       <c r="B614" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C614" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B615" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C615" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>No validation output</v>
+        <v>Type</v>
       </c>
       <c r="B616" t="str">
-        <v>Sem saída de validação</v>
+        <v>Tipo</v>
       </c>
       <c r="C616" t="str">
-        <v>Sem saída de validação</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Profile is valid</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B617" t="str">
-        <v>O perfil é válido</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C617" t="str">
-        <v>O perfil é válido</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Profile has warning(s)</v>
+        <v>(No content)</v>
       </c>
       <c r="B618" t="str">
-        <v>O perfil tem avisos</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C618" t="str">
-        <v>O perfil tem avisos</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Profile is non-compliant</v>
+        <v>bytes</v>
       </c>
       <c r="B619" t="str">
-        <v>O perfil não é conforme</v>
+        <v>bytes</v>
       </c>
       <c r="C619" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Critical validation error</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B620" t="str">
-        <v>Erro de validação crítico</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C620" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Unknown validation status</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B621" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C621" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B622" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C622" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B623" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C623" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B624" t="str">
-        <v>Válido</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C624" t="str">
-        <v>Válido</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Warning</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B625" t="str">
-        <v>Aviso</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C625" t="str">
-        <v>Aviso</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B626" t="str">
-        <v>Erro</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C626" t="str">
-        <v>Erro</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Unknown</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B627" t="str">
-        <v>Desconhecido</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C627" t="str">
-        <v>Desconhecido</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Pass</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B628" t="str">
-        <v>Aprovado</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C628" t="str">
-        <v>Aprovado</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Fail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B629" t="str">
-        <v>Reprovado</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C629" t="str">
-        <v>Reprovado</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>View in context</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B630" t="str">
-        <v>Ver no contexto</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C630" t="str">
-        <v>Ver no contexto</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Validation detail</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B631" t="str">
-        <v>Detalhe de validação</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C631" t="str">
-        <v>Detalhe de validação</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Triggered by</v>
+        <v>Valid</v>
       </c>
       <c r="B632" t="str">
-        <v>Acionado por</v>
+        <v>Válido</v>
       </c>
       <c r="C632" t="str">
-        <v>Acionado por</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Field</v>
+        <v>Warning</v>
       </c>
       <c r="B633" t="str">
-        <v>Campo</v>
+        <v>Aviso</v>
       </c>
       <c r="C633" t="str">
-        <v>Campo</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Current value</v>
+        <v>Error</v>
       </c>
       <c r="B634" t="str">
-        <v>Valor atual</v>
+        <v>Erro</v>
       </c>
       <c r="C634" t="str">
-        <v>Valor atual</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Required: 0</v>
+        <v>Unknown</v>
       </c>
       <c r="B635" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C635" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Expected: {value}</v>
+        <v>Pass</v>
       </c>
       <c r="B636" t="str">
-        <v>Esperado: {value}</v>
+        <v>Aprovado</v>
       </c>
       <c r="C636" t="str">
-        <v>Esperado: {value}</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Invalid</v>
+        <v>Fail</v>
       </c>
       <c r="B637" t="str">
-        <v>Inválido</v>
+        <v>Reprovado</v>
       </c>
       <c r="C637" t="str">
-        <v>Inválido</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>View in context</v>
       </c>
       <c r="B638" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C638" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Close</v>
+        <v>Validation detail</v>
       </c>
       <c r="B639" t="str">
-        <v>Fechar</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C639" t="str">
-        <v>Fechar</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Loading XML editor…</v>
+        <v>Triggered by</v>
       </c>
       <c r="B640" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Acionado por</v>
       </c>
       <c r="C640" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Field</v>
       </c>
       <c r="B641" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Campo</v>
       </c>
       <c r="C641" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Current value</v>
       </c>
       <c r="B642" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Valor atual</v>
       </c>
       <c r="C642" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Required: 0</v>
       </c>
       <c r="B643" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C643" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B644" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C644" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Invalid</v>
       </c>
       <c r="B645" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Inválido</v>
       </c>
       <c r="C645" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B646" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C646" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Close</v>
       </c>
       <c r="B647" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Fechar</v>
       </c>
       <c r="C647" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>indent</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B648" t="str">
-        <v>indentação</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C648" t="str">
-        <v>indentação</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>sort keys</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B649" t="str">
-        <v>ordenar chaves</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C649" t="str">
-        <v>ordenar chaves</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B650" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C650" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B651" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C651" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B652" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C652" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B653" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C653" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B654" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C654" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B655" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C655" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B656" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C656" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B657" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C657" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B650" t="str">
+      <c r="B658" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C650" t="str">
+      <c r="C658" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C650"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C658"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C658"/>
+  <dimension ref="A1:C659"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5090,13 +5090,13 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR is decoded and rendered by profiletool.</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
       </c>
       <c r="B426" t="str">
-        <v>Veja uma imagem HDR neste ecrã. Os ficheiros que o navegador consegue descodificar são mostrados pelo próprio navegador; o OpenEXR é descodificado e apresentado pelo profiletool.</v>
+        <v>Veja uma imagem HDR neste ecrã. Os ficheiros que o navegador consegue descodificar são mostrados pelo próprio navegador; o OpenEXR e o Radiance HDR são descodificados e apresentados pelo profiletool.</v>
       </c>
       <c r="C426" t="str">
-        <v>Veja uma imagem HDR nesta tela. Arquivos que o navegador consegue decodificar são exibidos pelo próprio navegador; o OpenEXR é decodificado e renderizado pelo profiletool.</v>
+        <v>Veja uma imagem HDR nesta tela. Arquivos que o navegador consegue decodificar são exibidos pelo próprio navegador; o OpenEXR e o Radiance HDR são decodificados e renderizados pelo profiletool.</v>
       </c>
     </row>
     <row r="427">
@@ -5112,13 +5112,13 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, AVIF, JPEG (incluindo JPEG com gain map), PNG — e HEIC no Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (incluindo JPEG com gain map), PNG — e HEIC no Safari.</v>
       </c>
       <c r="C428" t="str">
-        <v>OpenEXR, AVIF, JPEG (incluindo JPEG com gain map), PNG — e HEIC no Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (incluindo JPEG com gain map), PNG — e HEIC no Safari.</v>
       </c>
     </row>
     <row r="429">
@@ -5167,2493 +5167,2504 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>checking…</v>
+        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
       </c>
       <c r="B433" t="str">
-        <v>a verificar…</v>
+        <v>nenhum — o Radiance HDR indica a cor através do cabeçalho PRIMARIES</v>
       </c>
       <c r="C433" t="str">
-        <v>verificando…</v>
+        <v>nenhum — o Radiance HDR informa a cor pelo cabeçalho PRIMARIES</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>none</v>
+        <v>checking…</v>
       </c>
       <c r="B434" t="str">
-        <v>nenhum</v>
+        <v>a verificar…</v>
       </c>
       <c r="C434" t="str">
-        <v>nenhum</v>
+        <v>verificando…</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Open in Profile tab</v>
+        <v>none</v>
       </c>
       <c r="B435" t="str">
-        <v>Abrir no separador Perfil</v>
+        <v>nenhum</v>
       </c>
       <c r="C435" t="str">
-        <v>Abrir na aba Perfil</v>
+        <v>nenhum</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Gain map</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B436" t="str">
-        <v>Mapa de ganho</v>
+        <v>Abrir no separador Perfil</v>
       </c>
       <c r="C436" t="str">
-        <v>Mapa de ganho</v>
+        <v>Abrir na aba Perfil</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>detected, not decoded</v>
+        <v>Gain map</v>
       </c>
       <c r="B437" t="str">
-        <v>detetado, não descodificado</v>
+        <v>Mapa de ganho</v>
       </c>
       <c r="C437" t="str">
-        <v>detectado, não decodificado</v>
+        <v>Mapa de ganho</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>That is not an image. Load profiles through the Profiles pane.</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B438" t="str">
-        <v>Isso não é uma imagem. Carregue perfis através do painel Perfis.</v>
+        <v>detetado, não descodificado</v>
       </c>
       <c r="C438" t="str">
-        <v>Isso não é uma imagem. Carregue perfis pelo painel Perfis.</v>
+        <v>detectado, não decodificado</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Not an image format profiletool recognises.</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B439" t="str">
-        <v>Não é um formato de imagem que o profiletool reconheça.</v>
+        <v>Isso não é uma imagem. Carregue perfis através do painel Perfis.</v>
       </c>
       <c r="C439" t="str">
-        <v>Não é um formato de imagem que o profiletool reconheça.</v>
+        <v>Isso não é uma imagem. Carregue perfis pelo painel Perfis.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B440" t="str">
-        <v>Os píxeis TIFF ainda não são mostrados aqui: os navegadores não descodificam TIFF, e a forma de codificar HDR num TIFF de 16 bits ainda não está decidida (fase 4.3). O perfil incorporado pode ser inspecionado.</v>
+        <v>Não é um formato de imagem que o profiletool reconheça.</v>
       </c>
       <c r="C440" t="str">
-        <v>Os pixels TIFF ainda não são exibidos aqui: os navegadores não decodificam TIFF, e a forma de codificar HDR em um TIFF de 16 bits ainda não foi decidida (fase 4.3). O perfil incorporado pode ser inspecionado.</v>
+        <v>Não é um formato de imagem que o profiletool reconheça.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Cannot display this image here:</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B441" t="str">
-        <v>Não é possível mostrar esta imagem aqui:</v>
+        <v>Os píxeis TIFF ainda não são mostrados aqui: os navegadores não descodificam TIFF, e a forma de codificar HDR num TIFF de 16 bits ainda não está decidida (fase 4.3). O perfil incorporado pode ser inspecionado.</v>
       </c>
       <c r="C441" t="str">
-        <v>Não é possível exibir esta imagem aqui:</v>
+        <v>Os pixels TIFF ainda não são exibidos aqui: os navegadores não decodificam TIFF, e a forma de codificar HDR em um TIFF de 16 bits ainda não foi decidida (fase 4.3). O perfil incorporado pode ser inspecionado.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Its embedded profile can still be inspected.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B442" t="str">
-        <v>O perfil incorporado pode ainda assim ser inspecionado.</v>
+        <v>Não é possível mostrar esta imagem aqui:</v>
       </c>
       <c r="C442" t="str">
-        <v>O perfil incorporado ainda pode ser inspecionado.</v>
+        <v>Não é possível exibir esta imagem aqui:</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Shown by</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B443" t="str">
-        <v>Mostrado por</v>
+        <v>O perfil incorporado pode ainda assim ser inspecionado.</v>
       </c>
       <c r="C443" t="str">
-        <v>Exibido por</v>
+        <v>O perfil incorporado ainda pode ser inspecionado.</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>the browser</v>
+        <v>Shown by</v>
       </c>
       <c r="B444" t="str">
-        <v>o navegador</v>
+        <v>Mostrado por</v>
       </c>
       <c r="C444" t="str">
-        <v>o navegador</v>
+        <v>Exibido por</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>profiletool</v>
+        <v>the browser</v>
       </c>
       <c r="B445" t="str">
-        <v>profiletool</v>
+        <v>o navegador</v>
       </c>
       <c r="C445" t="str">
-        <v>profiletool</v>
+        <v>o navegador</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>HDR display</v>
+        <v>profiletool</v>
       </c>
       <c r="B446" t="str">
-        <v>Ecrã HDR</v>
+        <v>profiletool</v>
       </c>
       <c r="C446" t="str">
-        <v>Tela HDR</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
+        <v>HDR display</v>
       </c>
       <c r="B447" t="str">
-        <v>Os navegadores ignoram o HDR indicado apenas por um perfil ICC incorporado, pelo que esta imagem pode parecer baça e plana.</v>
+        <v>Ecrã HDR</v>
       </c>
       <c r="C447" t="str">
-        <v>Os navegadores ignoram HDR indicado apenas por um perfil ICC incorporado, então esta imagem pode parecer apagada e sem contraste.</v>
+        <v>Tela HDR</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B448" t="str">
-        <v>Este navegador não consegue alternar uma imagem entre SDR e HDR, pelo que é mostrada tal como o navegador a apresenta.</v>
+        <v>Os navegadores ignoram o HDR indicado apenas por um perfil ICC incorporado, pelo que esta imagem pode parecer baça e plana.</v>
       </c>
       <c r="C448" t="str">
-        <v>Este navegador não consegue alternar uma imagem entre SDR e HDR, então ela é exibida como o navegador a renderiza.</v>
+        <v>Os navegadores ignoram HDR indicado apenas por um perfil ICC incorporado, então esta imagem pode parecer apagada e sem contraste.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>The browser could not decode this image.</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B449" t="str">
-        <v>O navegador não conseguiu descodificar esta imagem.</v>
+        <v>Este navegador não consegue alternar uma imagem entre SDR e HDR, pelo que é mostrada tal como o navegador a apresenta.</v>
       </c>
       <c r="C449" t="str">
-        <v>O navegador não conseguiu decodificar esta imagem.</v>
+        <v>Este navegador não consegue alternar uma imagem entre SDR e HDR, então ela é exibida como o navegador a renderiza.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Output</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B450" t="str">
-        <v>Saída</v>
+        <v>O navegador não conseguiu descodificar esta imagem.</v>
       </c>
       <c r="C450" t="str">
-        <v>Saída</v>
+        <v>O navegador não conseguiu decodificar esta imagem.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>HDR canvas (float16)</v>
+        <v>Output</v>
       </c>
       <c r="B451" t="str">
-        <v>Canvas HDR (float16)</v>
+        <v>Saída</v>
       </c>
       <c r="C451" t="str">
-        <v>Canvas HDR (float16)</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>WebGPU (extended range)</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B452" t="str">
-        <v>WebGPU (gama alargada)</v>
+        <v>Canvas HDR (float16)</v>
       </c>
       <c r="C452" t="str">
-        <v>WebGPU (faixa estendida)</v>
+        <v>Canvas HDR (float16)</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>SDR canvas (tone-mapped)</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B453" t="str">
-        <v>Canvas SDR (tone mapping)</v>
+        <v>WebGPU (gama alargada)</v>
       </c>
       <c r="C453" t="str">
-        <v>Canvas SDR (tone mapping)</v>
+        <v>WebGPU (faixa estendida)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Size</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B454" t="str">
-        <v>Tamanho</v>
+        <v>Canvas SDR (tone mapping)</v>
       </c>
       <c r="C454" t="str">
-        <v>Tamanho</v>
+        <v>Canvas SDR (tone mapping)</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Brightest pixel</v>
+        <v>Size</v>
       </c>
       <c r="B455" t="str">
-        <v>Píxel mais brilhante</v>
+        <v>Tamanho</v>
       </c>
       <c r="C455" t="str">
-        <v>Pixel mais brilhante</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>{n}× SDR white</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B456" t="str">
-        <v>{n}× o branco SDR</v>
+        <v>Píxel mais brilhante</v>
       </c>
       <c r="C456" t="str">
-        <v>{n}× o branco SDR</v>
+        <v>Pixel mais brilhante</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Chromaticities</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B457" t="str">
-        <v>Cromaticidades</v>
+        <v>{n}× o branco SDR</v>
       </c>
       <c r="C457" t="str">
-        <v>Cromaticidades</v>
+        <v>{n}× o branco SDR</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>not stated — Rec. 709 assumed</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B458" t="str">
-        <v>não indicadas — assume-se Rec. 709</v>
+        <v>Cromaticidades</v>
       </c>
       <c r="C458" t="str">
-        <v>não informadas — assume-se Rec. 709</v>
+        <v>Cromaticidades</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>{from} was not available here ({why}); using the next output.</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B459" t="str">
-        <v>{from} não está disponível aqui ({why}); é usada a saída seguinte.</v>
+        <v>não indicadas — assume-se Rec. 709</v>
       </c>
       <c r="C459" t="str">
-        <v>{from} não está disponível aqui ({why}); usando a próxima saída.</v>
+        <v>não informadas — assume-se Rec. 709</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B460" t="str">
-        <v>Esta saída não consegue transportar valores mais brilhantes do que o branco, pelo que é mostrada a apresentação SDR com tone mapping.</v>
+        <v>{from} não está disponível aqui ({why}); é usada a saída seguinte.</v>
       </c>
       <c r="C460" t="str">
-        <v>Esta saída não consegue transportar valores mais brilhantes que o branco, então é exibida a renderização SDR com tone mapping.</v>
+        <v>{from} não está disponível aqui ({why}); usando a próxima saída.</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Exposure</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B461" t="str">
-        <v>Exposição</v>
+        <v>Esta saída não consegue transportar valores mais brilhantes do que o branco, pelo que é mostrada a apresentação SDR com tone mapping.</v>
       </c>
       <c r="C461" t="str">
-        <v>Exposição</v>
+        <v>Esta saída não consegue transportar valores mais brilhantes que o branco, então é exibida a renderização SDR com tone mapping.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>{n} stops</v>
+        <v>Exposure</v>
       </c>
       <c r="B462" t="str">
-        <v>{n} stops</v>
+        <v>Exposição</v>
       </c>
       <c r="C462" t="str">
-        <v>{n} stops</v>
+        <v>Exposição</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Could not decode:</v>
+        <v>{n} stops</v>
       </c>
       <c r="B463" t="str">
-        <v>Não foi possível descodificar:</v>
+        <v>{n} stops</v>
       </c>
       <c r="C463" t="str">
-        <v>Não foi possível decodificar:</v>
+        <v>{n} stops</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Decoding…</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B464" t="str">
-        <v>A descodificar…</v>
+        <v>Não foi possível descodificar:</v>
       </c>
       <c r="C464" t="str">
-        <v>Decodificando…</v>
+        <v>Não foi possível decodificar:</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Dynamic range</v>
+        <v>Decoding…</v>
       </c>
       <c r="B465" t="str">
-        <v>Gama dinâmica</v>
+        <v>A descodificar…</v>
       </c>
       <c r="C465" t="str">
-        <v>Faixa dinâmica</v>
+        <v>Decodificando…</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B466" t="str">
-        <v>Este navegador só oferece os dois extremos, não uma mistura.</v>
+        <v>Gama dinâmica</v>
       </c>
       <c r="C466" t="str">
-        <v>Este navegador oferece apenas os dois extremos, não uma mistura.</v>
+        <v>Faixa dinâmica</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B467" t="str">
-        <v>descodificado pelo próprio profiletool, portanto independente do navegador</v>
+        <v>Este navegador só oferece os dois extremos, não uma mistura.</v>
       </c>
       <c r="C467" t="str">
-        <v>decodificado pelo próprio profiletool, portanto independente do navegador</v>
+        <v>Este navegador oferece apenas os dois extremos, não uma mistura.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>this browser decodes it</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B468" t="str">
-        <v>este navegador descodifica-o</v>
+        <v>descodificado pelo próprio profiletool, portanto independente do navegador</v>
       </c>
       <c r="C468" t="str">
-        <v>este navegador o decodifica</v>
+        <v>decodificado pelo próprio profiletool, portanto independente do navegador</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>this browser does not decode it</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B469" t="str">
-        <v>este navegador não o descodifica</v>
+        <v>este navegador descodifica-o</v>
       </c>
       <c r="C469" t="str">
-        <v>este navegador não o decodifica</v>
+        <v>este navegador o decodifica</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B470" t="str">
-        <v>mostrar HEIC requer o Safari ou outro navegador WebKit — o Chrome e o Firefox não descodificam HEIC em nenhuma plataforma, incluindo o macOS</v>
+        <v>este navegador não o descodifica</v>
       </c>
       <c r="C470" t="str">
-        <v>exibir HEIC requer o Safari ou outro navegador WebKit — Chrome e Firefox não decodificam HEIC em nenhuma plataforma, inclusive no macOS</v>
+        <v>este navegador não o decodifica</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B471" t="str">
-        <v>mostrar JPEG XL requer o Safari; os outros navegadores ainda não o suportam</v>
+        <v>mostrar HEIC requer o Safari ou outro navegador WebKit — o Chrome e o Firefox não descodificam HEIC em nenhuma plataforma, incluindo o macOS</v>
       </c>
       <c r="C471" t="str">
-        <v>exibir JPEG XL requer o Safari; outros navegadores ainda não o suportam</v>
+        <v>exibir HEIC requer o Safari ou outro navegador WebKit — Chrome e Firefox não decodificam HEIC em nenhuma plataforma, inclusive no macOS</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>deferred to a later release</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B472" t="str">
-        <v>adiado para uma versão posterior</v>
+        <v>mostrar JPEG XL requer o Safari; os outros navegadores ainda não o suportam</v>
       </c>
       <c r="C472" t="str">
-        <v>adiado para uma versão futura</v>
+        <v>exibir JPEG XL requer o Safari; outros navegadores ainda não o suportam</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B473" t="str">
-        <v>este ecrã não indica nenhum caminho HDR, pelo que o HDR é apresentado em SDR com tone mapping</v>
+        <v>adiado para uma versão posterior</v>
       </c>
       <c r="C473" t="str">
-        <v>esta tela não informa nenhum caminho HDR, então o HDR é exibido em SDR com tone mapping</v>
+        <v>adiado para uma versão futura</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B474" t="str">
-        <v>este navegador não oferece um canvas HDR (requer canvas float16 ou WebGPU)</v>
+        <v>este ecrã não indica nenhum caminho HDR, pelo que o HDR é apresentado em SDR com tone mapping</v>
       </c>
       <c r="C474" t="str">
-        <v>este navegador não oferece um canvas HDR (requer canvas float16 ou WebGPU)</v>
+        <v>esta tela não informa nenhum caminho HDR, então o HDR é exibido em SDR com tone mapping</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B475" t="str">
-        <v>o Firefox não mostra imagens HDR nem lê gain maps; o conteúdo HDR é mostrado em SDR</v>
+        <v>este navegador não oferece um canvas HDR (requer canvas float16 ou WebGPU)</v>
       </c>
       <c r="C475" t="str">
-        <v>o Firefox não exibe imagens HDR nem lê gain maps; o conteúdo HDR é exibido em SDR</v>
+        <v>este navegador não oferece um canvas HDR (requer canvas float16 ou WebGPU)</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B476" t="str">
-        <v>a inspeção só precisa de analisar o contentor, não de um codec</v>
+        <v>o Firefox não mostra imagens HDR nem lê gain maps; o conteúdo HDR é mostrado em SDR</v>
       </c>
       <c r="C476" t="str">
-        <v>a inspeção só precisa analisar o contêiner, não de um codec</v>
+        <v>o Firefox não exibe imagens HDR nem lê gain maps; o conteúdo HDR é exibido em SDR</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B477" t="str">
-        <v>ecrã HDR e canvas HDR estão ambos disponíveis</v>
+        <v>a inspeção só precisa de analisar o contentor, não de um codec</v>
       </c>
       <c r="C477" t="str">
-        <v>tela HDR e canvas HDR estão disponíveis</v>
+        <v>a inspeção só precisa analisar o contêiner, não de um codec</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>unknown format</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B478" t="str">
-        <v>formato desconhecido</v>
+        <v>ecrã HDR e canvas HDR estão ambos disponíveis</v>
       </c>
       <c r="C478" t="str">
-        <v>formato desconhecido</v>
+        <v>tela HDR e canvas HDR estão disponíveis</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>{browser} on {os}</v>
+        <v>unknown format</v>
       </c>
       <c r="B479" t="str">
-        <v>{browser} em {os}</v>
+        <v>formato desconhecido</v>
       </c>
       <c r="C479" t="str">
-        <v>{browser} no {os}</v>
+        <v>formato desconhecido</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B480" t="str">
-        <v>{name} · ecrã HDR detetado</v>
+        <v>{browser} em {os}</v>
       </c>
       <c r="C480" t="str">
-        <v>{name} · tela HDR detectada</v>
+        <v>{browser} no {os}</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>{name} · SDR display</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B481" t="str">
-        <v>{name} · ecrã SDR</v>
+        <v>{name} · ecrã HDR detetado</v>
       </c>
       <c r="C481" t="str">
-        <v>{name} · tela SDR</v>
+        <v>{name} · tela HDR detectada</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B482" t="str">
-        <v>O WebGPU aplicou o tone mapping «{mode}», pelo que a saída fica limitada a SDR</v>
+        <v>{name} · ecrã SDR</v>
       </c>
       <c r="C482" t="str">
-        <v>O WebGPU aplicou o tone mapping “{mode}”, então a saída fica limitada a SDR</v>
+        <v>{name} · tela SDR</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B483" t="str">
-        <v>Este navegador não indica o tone mapping WebGPU aplicado, pelo que a saída HDR não está confirmada</v>
+        <v>O WebGPU aplicou o tone mapping «{mode}», pelo que a saída fica limitada a SDR</v>
       </c>
       <c r="C483" t="str">
-        <v>Este navegador não informa o tone mapping WebGPU aplicado, então a saída HDR não está confirmada</v>
+        <v>O WebGPU aplicou o tone mapping “{mode}”, então a saída fica limitada a SDR</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Display peak</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B484" t="str">
-        <v>Pico do ecrã</v>
+        <v>Este navegador não indica o tone mapping WebGPU aplicado, pelo que a saída HDR não está confirmada</v>
       </c>
       <c r="C484" t="str">
-        <v>Pico da tela</v>
+        <v>Este navegador não informa o tone mapping WebGPU aplicado, então a saída HDR não está confirmada</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>Display peak</v>
       </c>
       <c r="B485" t="str">
-        <v>{r}× o branco SDR ({n} stops)</v>
+        <v>Pico do ecrã</v>
       </c>
       <c r="C485" t="str">
-        <v>{r}× o branco SDR ({n} stops)</v>
+        <v>Pico da tela</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>1× — SDR display</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B486" t="str">
-        <v>1× — ecrã SDR</v>
+        <v>{r}× o branco SDR ({n} stops)</v>
       </c>
       <c r="C486" t="str">
-        <v>1× — tela SDR</v>
+        <v>{r}× o branco SDR ({n} stops)</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>not known</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B487" t="str">
-        <v>desconhecido</v>
+        <v>1× — ecrã SDR</v>
       </c>
       <c r="C487" t="str">
-        <v>desconhecido</v>
+        <v>1× — tela SDR</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>not known</v>
       </c>
       <c r="B488" t="str">
-        <v>Este ecrã não indica HDR, pelo que o navegador mostra a imagem em SDR em ambos os extremos.</v>
+        <v>desconhecido</v>
       </c>
       <c r="C488" t="str">
-        <v>Esta tela não informa HDR, então o navegador exibe a imagem em SDR nos dois extremos.</v>
+        <v>desconhecido</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B489" t="str">
-        <v>Este ecrã não indica HDR, pelo que tudo o que for mais brilhante do que o branco SDR é cortado. «Ajustar ao ecrã» mostra antes a apresentação com tone mapping.</v>
+        <v>Este ecrã não indica HDR, pelo que o navegador mostra a imagem em SDR em ambos os extremos.</v>
       </c>
       <c r="C489" t="str">
-        <v>Esta tela não informa HDR, então tudo que for mais brilhante que o branco SDR é cortado. “Ajustar à tela” exibe a renderização com tone mapping.</v>
+        <v>Esta tela não informa HDR, então o navegador exibe a imagem em SDR nos dois extremos.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B490" t="str">
-        <v>Esta imagem pede {img}× o branco SDR, mas este ecrã só chega a {disp}×, pelo que os valores mais brilhantes são cortados. «Ajustar ao ecrã» suaviza-os até ao pico do ecrã.</v>
+        <v>Este ecrã não indica HDR, pelo que tudo o que for mais brilhante do que o branco SDR é cortado. «Ajustar ao ecrã» mostra antes a apresentação com tone mapping.</v>
       </c>
       <c r="C490" t="str">
-        <v>Esta imagem pede {img}× o branco SDR, mas esta tela só chega a {disp}×, então valores mais brilhantes são cortados. “Ajustar à tela” os suaviza até o pico da tela.</v>
+        <v>Esta tela não informa HDR, então tudo que for mais brilhante que o branco SDR é cortado. “Ajustar à tela” exibe a renderização com tone mapping.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Fit to display</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B491" t="str">
-        <v>Ajustar ao ecrã</v>
+        <v>Esta imagem pede {img}× o branco SDR, mas este ecrã só chega a {disp}×, pelo que os valores mais brilhantes são cortados. «Ajustar ao ecrã» suaviza-os até ao pico do ecrã.</v>
       </c>
       <c r="C491" t="str">
-        <v>Ajustar à tela</v>
+        <v>Esta imagem pede {img}× o branco SDR, mas esta tela só chega a {disp}×, então valores mais brilhantes são cortados. “Ajustar à tela” os suaviza até o pico da tela.</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Fit to display</v>
       </c>
       <c r="B492" t="str">
-        <v>Limita o brilho ao pico que este ecrã indica. No Windows esse valor pode atrasar-se face às mudanças de brilho.</v>
+        <v>Ajustar ao ecrã</v>
       </c>
       <c r="C492" t="str">
-        <v>Limita o brilho ao pico que esta tela informa. No Windows esse valor pode ficar atrasado em relação às mudanças de brilho.</v>
+        <v>Ajustar à tela</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>no limit</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B493" t="str">
-        <v>sem limite</v>
+        <v>Limita o brilho ao pico que este ecrã indica. No Windows esse valor pode atrasar-se face às mudanças de brilho.</v>
       </c>
       <c r="C493" t="str">
-        <v>sem limite</v>
+        <v>Limita o brilho ao pico que esta tela informa. No Windows esse valor pode ficar atrasado em relação às mudanças de brilho.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>no limit</v>
       </c>
       <c r="B494" t="str">
-        <v>limite {n} stops ({r}×)</v>
+        <v>sem limite</v>
       </c>
       <c r="C494" t="str">
-        <v>limite {n} stops ({r}×)</v>
+        <v>sem limite</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>SDR white</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B495" t="str">
-        <v>Branco SDR</v>
+        <v>limite {n} stops ({r}×)</v>
       </c>
       <c r="C495" t="str">
-        <v>Branco SDR</v>
+        <v>limite {n} stops ({r}×)</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>SDR white</v>
       </c>
       <c r="B496" t="str">
-        <v>Branco SDR simples, para comparação. Num ecrã HDR, as altas luzes HDR parecem mais brilhantes do que este.</v>
+        <v>Branco SDR</v>
       </c>
       <c r="C496" t="str">
-        <v>Branco SDR simples, para comparação. Em uma tela HDR, os realces HDR parecem mais brilhantes que este.</v>
+        <v>Branco SDR</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>SDR white patch</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B497" t="str">
-        <v>Amostra de branco SDR</v>
+        <v>Branco SDR simples, para comparação. Num ecrã HDR, as altas luzes HDR parecem mais brilhantes do que este.</v>
       </c>
       <c r="C497" t="str">
-        <v>Amostra de branco SDR</v>
+        <v>Branco SDR simples, para comparação. Em uma tela HDR, os realces HDR parecem mais brilhantes que este.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B498" t="str">
-        <v>Arraste para a mover; faça duplo clique para a repor junto à imagem.</v>
+        <v>Amostra de branco SDR</v>
       </c>
       <c r="C498" t="str">
-        <v>Arraste para movê-la; clique duas vezes para colocá-la de volta ao lado da imagem.</v>
+        <v>Amostra de branco SDR</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Assign profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B499" t="str">
-        <v>Atribuir perfil</v>
+        <v>Arraste para a mover; faça duplo clique para a repor junto à imagem.</v>
       </c>
       <c r="C499" t="str">
-        <v>Atribuir perfil</v>
+        <v>Arraste para movê-la; clique duas vezes para colocá-la de volta ao lado da imagem.</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>None — use what the file signals</v>
+        <v>Assign profile</v>
       </c>
       <c r="B500" t="str">
-        <v>Nenhum — o que o ficheiro indica</v>
+        <v>Atribuir perfil</v>
       </c>
       <c r="C500" t="str">
-        <v>Nenhum — o que o arquivo indica</v>
+        <v>Atribuir perfil</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B501" t="str">
-        <v>Perfil incorporado ({n} B)</v>
+        <v>Nenhum — o que o ficheiro indica</v>
       </c>
       <c r="C501" t="str">
-        <v>Perfil incorporado ({n} B)</v>
+        <v>Nenhum — o que o arquivo indica</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B502" t="str">
-        <v>Perfis HDR no pool</v>
+        <v>Perfil incorporado ({n} B)</v>
       </c>
       <c r="C502" t="str">
-        <v>Perfis HDR no pool</v>
+        <v>Perfil incorporado ({n} B)</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Profile</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B503" t="str">
-        <v>Perfil</v>
+        <v>Perfis HDR no pool</v>
       </c>
       <c r="C503" t="str">
-        <v>Perfil</v>
+        <v>Perfis HDR no pool</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>embedded profile</v>
+        <v>Profile</v>
       </c>
       <c r="B504" t="str">
-        <v>perfil incorporado</v>
+        <v>Perfil</v>
       </c>
       <c r="C504" t="str">
-        <v>perfil incorporado</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Colour engine path</v>
+        <v>embedded profile</v>
       </c>
       <c r="B505" t="str">
-        <v>Caminho do motor de cor</v>
+        <v>perfil incorporado</v>
       </c>
       <c r="C505" t="str">
-        <v>Caminho do mecanismo de cor</v>
+        <v>perfil incorporado</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B506" t="str">
-        <v>Caminho HDR, curva de ganho aplicada</v>
+        <v>Caminho do motor de cor</v>
       </c>
       <c r="C506" t="str">
-        <v>Caminho HDR, curva de ganho aplicada</v>
+        <v>Caminho do mecanismo de cor</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B507" t="str">
-        <v>Caminho HDR, sem curva de ganho</v>
+        <v>Caminho HDR, curva de ganho aplicada</v>
       </c>
       <c r="C507" t="str">
-        <v>Caminho HDR, sem curva de ganho</v>
+        <v>Caminho HDR, curva de ganho aplicada</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B508" t="str">
-        <v>AToB0 pré-calculado — não é o caminho HDR</v>
+        <v>Caminho HDR, sem curva de ganho</v>
       </c>
       <c r="C508" t="str">
-        <v>AToB0 pré-calculado — não é o caminho HDR</v>
+        <v>Caminho HDR, sem curva de ganho</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Transfer</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B509" t="str">
-        <v>Transferência</v>
+        <v>AToB0 pré-calculado — não é o caminho HDR</v>
       </c>
       <c r="C509" t="str">
-        <v>Transferência</v>
+        <v>AToB0 pré-calculado — não é o caminho HDR</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>HDR reference white</v>
+        <v>Transfer</v>
       </c>
       <c r="B510" t="str">
-        <v>Branco de referência HDR</v>
+        <v>Transferência</v>
       </c>
       <c r="C510" t="str">
-        <v>Branco de referência HDR</v>
+        <v>Transferência</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Target headroom</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B511" t="str">
-        <v>Margem alvo</v>
+        <v>Branco de referência HDR</v>
       </c>
       <c r="C511" t="str">
-        <v>Margem alvo</v>
+        <v>Branco de referência HDR</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B512" t="str">
-        <v>{r}× o branco de referência ({n} stops)</v>
+        <v>Margem alvo</v>
       </c>
       <c r="C512" t="str">
-        <v>{r}× o branco de referência ({n} stops)</v>
+        <v>Margem alvo</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B513" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× o branco de referência ({n} stops)</v>
       </c>
       <c r="C513" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× o branco de referência ({n} stops)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B514" t="str">
-        <v>Auto (ordem da cláusula 8.10.3)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="C514" t="str">
-        <v>Auto (ordem da cláusula 8.10.3)</v>
+        <v>Tone mapping</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B515" t="str">
-        <v>Curva de ganho (HAGC)</v>
+        <v>Auto (ordem da cláusula 8.10.3)</v>
       </c>
       <c r="C515" t="str">
-        <v>Curva de ganho (HAGC)</v>
+        <v>Auto (ordem da cláusula 8.10.3)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B516" t="str">
-        <v>Alternativa SDR pré-calculada (AToB0)</v>
+        <v>Curva de ganho (HAGC)</v>
       </c>
       <c r="C516" t="str">
-        <v>Alternativa SDR pré-calculada (AToB0)</v>
+        <v>Curva de ganho (HAGC)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B517" t="str">
-        <v>Desligado — como um CMM anterior à emenda</v>
+        <v>Alternativa SDR pré-calculada (AToB0)</v>
       </c>
       <c r="C517" t="str">
-        <v>Desligado — como um CMM anterior à emenda</v>
+        <v>Alternativa SDR pré-calculada (AToB0)</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Applying the profile…</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B518" t="str">
-        <v>A aplicar o perfil…</v>
+        <v>Desligado — como um CMM anterior à emenda</v>
       </c>
       <c r="C518" t="str">
-        <v>Aplicando o perfil…</v>
+        <v>Desligado — como um CMM anterior à emenda</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>OpenEXR holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B519" t="str">
-        <v>O OpenEXR contém luz linear, pelo que precisa de um perfil com transferência Linear (8).</v>
+        <v>A aplicar o perfil…</v>
       </c>
       <c r="C519" t="str">
-        <v>O OpenEXR contém luz linear, então precisa de um perfil com transferência Linear (8).</v>
+        <v>Aplicando o perfil…</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B520" t="str">
-        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
+        <v>O {format} contém luz linear, pelo que precisa de um perfil com transferência Linear (8).</v>
       </c>
       <c r="C520" t="str">
-        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
+        <v>O {format} contém luz linear, então precisa de um perfil com transferência Linear (8).</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B521" t="str">
-        <v>Para interpretar os seus valores, atribua um perfil acima.</v>
+        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
       </c>
       <c r="C521" t="str">
-        <v>Para interpretar seus valores, atribua um perfil acima.</v>
+        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>HDR Profiles</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B522" t="str">
-        <v>Perfis HDR</v>
+        <v>Para interpretar os seus valores, atribua um perfil acima.</v>
       </c>
       <c r="C522" t="str">
-        <v>Perfis HDR</v>
+        <v>Para interpretar seus valores, atribua um perfil acima.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Linear transfer</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B523" t="str">
-        <v>Transferência linear</v>
+        <v>Perfis HDR</v>
       </c>
       <c r="C523" t="str">
-        <v>Transferência linear</v>
+        <v>Perfis HDR</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B524" t="str">
-        <v>Transferência não linear (PQ, HLG)</v>
+        <v>Transferência linear</v>
       </c>
       <c r="C524" t="str">
-        <v>Transferência não linear (PQ, HLG)</v>
+        <v>Transferência linear</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B525" t="str">
-        <v>Perfis HDR — transferência linear</v>
+        <v>Transferência não linear (PQ, HLG)</v>
       </c>
       <c r="C525" t="str">
-        <v>Perfis HDR — transferência linear</v>
+        <v>Transferência não linear (PQ, HLG)</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>Perfis HDR — transferência PQ / HLG</v>
+        <v>Perfis HDR — transferência linear</v>
       </c>
       <c r="C526" t="str">
-        <v>Perfis HDR — transferência PQ / HLG</v>
+        <v>Perfis HDR — transferência linear</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>OpenEXR holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B527" t="str">
-        <v>O OpenEXR contém luz linear, pelo que só podem ser atribuídos perfis HDR com transferência linear.</v>
+        <v>Perfis HDR — transferência PQ / HLG</v>
       </c>
       <c r="C527" t="str">
-        <v>O OpenEXR contém luz linear, então só podem ser atribuídos perfis HDR com transferência linear.</v>
+        <v>Perfis HDR — transferência PQ / HLG</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B528" t="str">
-        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis lista-os em Perfis HDR › Transferência não linear.</v>
+        <v>O {format} contém luz linear, pelo que só podem ser atribuídos perfis HDR com transferência linear.</v>
       </c>
       <c r="C528" t="str">
-        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis os lista em Perfis HDR › Transferência não linear.</v>
+        <v>O {format} contém luz linear, então só podem ser atribuídos perfis HDR com transferência linear.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B529" t="str">
-        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
+        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis lista-os em Perfis HDR › Transferência não linear.</v>
       </c>
       <c r="C529" t="str">
-        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
+        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis os lista em Perfis HDR › Transferência não linear.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B530" t="str">
-        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
+        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
       </c>
       <c r="C530" t="str">
-        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
+        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B531" t="str">
-        <v>Margem do ecrã</v>
+        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
       </c>
       <c r="C531" t="str">
-        <v>Margem da tela</v>
+        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B532" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>Margem do ecrã</v>
       </c>
       <c r="C532" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>Margem da tela</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B533" t="str">
-        <v>Base</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
       <c r="C533" t="str">
-        <v>Base</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Baseline</v>
       </c>
       <c r="B534" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>Base</v>
       </c>
       <c r="C534" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B535" t="str">
-        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
       <c r="C535" t="str">
-        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B536" t="str">
-        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
+        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
       </c>
       <c r="C536" t="str">
-        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
+        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B537" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
+        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
       </c>
       <c r="C537" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
+        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B538" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
+        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
       </c>
       <c r="C538" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
+        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B539" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
       </c>
       <c r="C539" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B540" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
       </c>
       <c r="C540" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B541" t="str">
-        <v>Curva a {h} stops</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
       <c r="C541" t="str">
-        <v>Curva a {h} stops</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Curva a {h} stops</v>
       </c>
       <c r="C542" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Curva a {h} stops</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B543" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>Aplicado a {h} stops</v>
       </c>
       <c r="C543" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>Aplicado a {h} stops</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B544" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
       <c r="C544" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B545" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
       <c r="C545" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B546" t="str">
-        <v>Curva de tons dos cinzentos nesta margem</v>
+        <v>Ganho (stops log2)</v>
       </c>
       <c r="C546" t="str">
-        <v>Curva de tons de cinza nesta margem</v>
+        <v>Ganho (stops log2)</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B547" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Curva de tons dos cinzentos nesta margem</v>
       </c>
       <c r="C547" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Curva de tons de cinza nesta margem</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B548" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
       <c r="C548" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B549" t="str">
-        <v>Sem alteração</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
       <c r="C549" t="str">
-        <v>Sem alteração</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B550" t="str">
-        <v>Pico do ecrã a {h} stops</v>
+        <v>Sem alteração</v>
       </c>
       <c r="C550" t="str">
-        <v>Pico da tela a {h} stops</v>
+        <v>Sem alteração</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B551" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Pico do ecrã a {h} stops</v>
       </c>
       <c r="C551" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Pico da tela a {h} stops</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B552" t="str">
-        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
+        <v>Saída a {h} stops</v>
       </c>
       <c r="C552" t="str">
-        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
+        <v>Saída a {h} stops</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B553" t="str">
-        <v>Identificar ecrãs</v>
+        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
       </c>
       <c r="C553" t="str">
-        <v>Identificar telas</v>
+        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B554" t="str">
-        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Identificar ecrãs</v>
       </c>
       <c r="C554" t="str">
-        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Identificar telas</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B555" t="str">
-        <v>A acompanhar em que monitor está esta janela.</v>
+        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
       <c r="C555" t="str">
-        <v>Acompanhando em qual monitor esta janela está.</v>
+        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B556" t="str">
-        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
+        <v>A acompanhar em que monitor está esta janela.</v>
       </c>
       <c r="C556" t="str">
-        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
+        <v>Acompanhando em qual monitor esta janela está.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B557" t="str">
-        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
+        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
       </c>
       <c r="C557" t="str">
-        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
+        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B558" t="str">
-        <v>Não foi possível identificar os ecrãs.</v>
+        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
       </c>
       <c r="C558" t="str">
-        <v>Não foi possível identificar as telas.</v>
+        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B559" t="str">
-        <v>Eventos de ecrã</v>
+        <v>Não foi possível identificar os ecrãs.</v>
       </c>
       <c r="C559" t="str">
-        <v>Eventos de tela</v>
+        <v>Não foi possível identificar as telas.</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B560" t="str">
-        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
+        <v>Eventos de ecrã</v>
       </c>
       <c r="C560" t="str">
-        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
+        <v>Eventos de tela</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B561" t="str">
-        <v>Primárias de cor</v>
+        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
       </c>
       <c r="C561" t="str">
-        <v>Primárias de cor</v>
+        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B562" t="str">
-        <v>Características de transferência</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C562" t="str">
-        <v>Características de transferência</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B563" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C563" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B564" t="str">
-        <v>Sinalizador de gama completa de vídeo</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C564" t="str">
-        <v>Sinalizador de faixa completa de vídeo</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B565" t="str">
-        <v>Gama completa</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C565" t="str">
-        <v>Faixa completa</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B566" t="str">
-        <v>Gama reduzida</v>
+        <v>Gama completa</v>
       </c>
       <c r="C566" t="str">
-        <v>Faixa reduzida</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B567" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C567" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B568" t="str">
-        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C568" t="str">
-        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B569" t="str">
-        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C569" t="str">
-        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B570" t="str">
-        <v>RELATÓRIO</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C570" t="str">
-        <v>RELATÓRIO</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B571" t="str">
-        <v>REPROVADO</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C571" t="str">
-        <v>REPROVADO</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B572" t="str">
-        <v>verificações</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C572" t="str">
-        <v>verificações</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B573" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>verificações</v>
       </c>
       <c r="C573" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B574" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C574" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B575" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C575" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B576" t="str">
-        <v>Com {lib}</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C576" t="str">
-        <v>Com {lib}</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B577" t="str">
-        <v>Subscrever</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C577" t="str">
-        <v>Inscrever-se</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B578" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Subscrever</v>
       </c>
       <c r="C578" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B579" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C579" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B580" t="str">
-        <v>Fechar</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C580" t="str">
-        <v>Fechar</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B581" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Fechar</v>
       </c>
       <c r="C581" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B582" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C582" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B583" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C583" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B584" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C584" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B585" t="str">
-        <v>(opcional)</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C585" t="str">
-        <v>(opcional)</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B586" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>(opcional)</v>
       </c>
       <c r="C586" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B587" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C587" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B588" t="str">
-        <v>Cancelar</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C588" t="str">
-        <v>Cancelar</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B589" t="str">
-        <v>Subscrever</v>
+        <v>Cancelar</v>
       </c>
       <c r="C589" t="str">
-        <v>Inscrever-se</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B590" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C590" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B591" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C591" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B592" t="str">
-        <v>Fechar</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C592" t="str">
-        <v>Fechar</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B593" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Fechar</v>
       </c>
       <c r="C593" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B594" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C594" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B595" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C595" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B596" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C596" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B597" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C597" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B598" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C598" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B599" t="str">
-        <v>Erro:</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C599" t="str">
-        <v>Erro:</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B600" t="str">
-        <v>Converter para XML</v>
+        <v>Erro:</v>
       </c>
       <c r="C600" t="str">
-        <v>Converter para XML</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B601" t="str">
-        <v>Converter para JSON</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C601" t="str">
-        <v>Converter para JSON</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B602" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C602" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B603" t="str">
-        <v>A converter para XML…</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C603" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B604" t="str">
-        <v>A converter para JSON…</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C604" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B605" t="str">
-        <v>A converter para ICC…</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C605" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B606" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C606" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B607" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C607" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B608" t="str">
-        <v>ID do perfil</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C608" t="str">
-        <v>ID do perfil</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B609" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C609" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B610" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C610" t="str">
-        <v>Nome da tag</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B611" t="str">
-        <v>ID</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C611" t="str">
-        <v>ID</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B612" t="str">
-        <v>Deslocamento</v>
+        <v>ID</v>
       </c>
       <c r="C612" t="str">
-        <v>Deslocamento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B613" t="str">
-        <v>Tamanho</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C613" t="str">
-        <v>Tamanho</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B614" t="str">
-        <v>Preenchimento</v>
+        <v>Tamanho</v>
       </c>
       <c r="C614" t="str">
-        <v>Preenchimento</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B615" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C615" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B616" t="str">
-        <v>Tipo</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C616" t="str">
-        <v>Tipo</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B617" t="str">
-        <v>Vetor de {type}</v>
+        <v>Tipo</v>
       </c>
       <c r="C617" t="str">
-        <v>Array de {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B618" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C618" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B619" t="str">
-        <v>bytes</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C619" t="str">
-        <v>bytes</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B620" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>bytes</v>
       </c>
       <c r="C620" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B621" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C621" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B622" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C622" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B623" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C623" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B624" t="str">
-        <v>Sem saída de validação</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C624" t="str">
-        <v>Sem saída de validação</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B625" t="str">
-        <v>O perfil é válido</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C625" t="str">
-        <v>O perfil é válido</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B626" t="str">
-        <v>O perfil tem avisos</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C626" t="str">
-        <v>O perfil tem avisos</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B627" t="str">
-        <v>O perfil não é conforme</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C627" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B628" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C628" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B629" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C629" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B630" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C630" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B631" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C631" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B632" t="str">
-        <v>Válido</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C632" t="str">
-        <v>Válido</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B633" t="str">
-        <v>Aviso</v>
+        <v>Válido</v>
       </c>
       <c r="C633" t="str">
-        <v>Aviso</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B634" t="str">
-        <v>Erro</v>
+        <v>Aviso</v>
       </c>
       <c r="C634" t="str">
-        <v>Erro</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B635" t="str">
-        <v>Desconhecido</v>
+        <v>Erro</v>
       </c>
       <c r="C635" t="str">
-        <v>Desconhecido</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B636" t="str">
-        <v>Aprovado</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C636" t="str">
-        <v>Aprovado</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B637" t="str">
-        <v>Reprovado</v>
+        <v>Aprovado</v>
       </c>
       <c r="C637" t="str">
-        <v>Reprovado</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B638" t="str">
-        <v>Ver no contexto</v>
+        <v>Reprovado</v>
       </c>
       <c r="C638" t="str">
-        <v>Ver no contexto</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B639" t="str">
-        <v>Detalhe de validação</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C639" t="str">
-        <v>Detalhe de validação</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B640" t="str">
-        <v>Acionado por</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C640" t="str">
-        <v>Acionado por</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B641" t="str">
-        <v>Campo</v>
+        <v>Acionado por</v>
       </c>
       <c r="C641" t="str">
-        <v>Campo</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B642" t="str">
-        <v>Valor atual</v>
+        <v>Campo</v>
       </c>
       <c r="C642" t="str">
-        <v>Valor atual</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B643" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Valor atual</v>
       </c>
       <c r="C643" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B644" t="str">
-        <v>Esperado: {value}</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C644" t="str">
-        <v>Esperado: {value}</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B645" t="str">
-        <v>Inválido</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C645" t="str">
-        <v>Inválido</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B646" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Inválido</v>
       </c>
       <c r="C646" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B647" t="str">
-        <v>Fechar</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C647" t="str">
-        <v>Fechar</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B648" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Fechar</v>
       </c>
       <c r="C648" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B649" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C649" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B650" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C650" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B651" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C651" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B652" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C652" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B653" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>● edições XML por guardar</v>
       </c>
       <c r="C653" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>● edições XML não salvas</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B654" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições JSON por guardar</v>
       </c>
       <c r="C654" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições JSON não salvas</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B655" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
       <c r="C655" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B656" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
       <c r="C656" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B657" t="str">
-        <v>ordenar chaves</v>
+        <v>indentação</v>
       </c>
       <c r="C657" t="str">
-        <v>ordenar chaves</v>
+        <v>indentação</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B658" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C658" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B658" t="str">
+      <c r="B659" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C658" t="str">
+      <c r="C659" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C658"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C659"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C659"/>
+  <dimension ref="A1:C670"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5827,1844 +5827,1965 @@
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Image details</v>
       </c>
       <c r="B493" t="str">
-        <v>Limita o brilho ao pico que este ecrã indica. No Windows esse valor pode atrasar-se face às mudanças de brilho.</v>
+        <v>Detalhes da imagem</v>
       </c>
       <c r="C493" t="str">
-        <v>Limita o brilho ao pico que esta tela informa. No Windows esse valor pode ficar atrasado em relação às mudanças de brilho.</v>
+        <v>Detalhes da imagem</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>no limit</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B494" t="str">
-        <v>sem limite</v>
+        <v>indisponível — o navegador apresenta esta imagem e não a consegue limitar a um pico definido</v>
       </c>
       <c r="C494" t="str">
-        <v>sem limite</v>
+        <v>indisponível — o navegador renderiza esta imagem e não consegue limitá-la a um pico definido</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B495" t="str">
-        <v>limite {n} stops ({r}×)</v>
+        <v>indisponível — esta saída não mostra nada acima do branco SDR</v>
       </c>
       <c r="C495" t="str">
-        <v>limite {n} stops ({r}×)</v>
+        <v>indisponível — esta saída não mostra nada acima do branco SDR</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>SDR white</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B496" t="str">
-        <v>Branco SDR</v>
+        <v>indisponível — o pico deste ecrã não é conhecido</v>
       </c>
       <c r="C496" t="str">
-        <v>Branco SDR</v>
+        <v>indisponível — o pico desta tela não é conhecido</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>Zoom in</v>
       </c>
       <c r="B497" t="str">
-        <v>Branco SDR simples, para comparação. Num ecrã HDR, as altas luzes HDR parecem mais brilhantes do que este.</v>
+        <v>Aproximar</v>
       </c>
       <c r="C497" t="str">
-        <v>Branco SDR simples, para comparação. Em uma tela HDR, os realces HDR parecem mais brilhantes que este.</v>
+        <v>Aproximar</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>SDR white patch</v>
+        <v>Zoom out</v>
       </c>
       <c r="B498" t="str">
-        <v>Amostra de branco SDR</v>
+        <v>Afastar</v>
       </c>
       <c r="C498" t="str">
-        <v>Amostra de branco SDR</v>
+        <v>Afastar</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>Fit image</v>
       </c>
       <c r="B499" t="str">
-        <v>Arraste para a mover; faça duplo clique para a repor junto à imagem.</v>
+        <v>Ajustar imagem</v>
       </c>
       <c r="C499" t="str">
-        <v>Arraste para movê-la; clique duas vezes para colocá-la de volta ao lado da imagem.</v>
+        <v>Ajustar imagem</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Assign profile</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B500" t="str">
-        <v>Atribuir perfil</v>
+        <v>Píxeis reais (1:1)</v>
       </c>
       <c r="C500" t="str">
-        <v>Atribuir perfil</v>
+        <v>Pixels reais (1:1)</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>None — use what the file signals</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B501" t="str">
-        <v>Nenhum — o que o ficheiro indica</v>
+        <v>Arraste para deslocar · Ctrl+roda para zoom · duplo clique para repor</v>
       </c>
       <c r="C501" t="str">
-        <v>Nenhum — o que o arquivo indica</v>
+        <v>Arraste para mover · Ctrl+roda para zoom · clique duplo para redefinir</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B502" t="str">
-        <v>Perfil incorporado ({n} B)</v>
+        <v>Arraste para redimensionar a área da imagem; duplo clique para repor o tamanho predefinido</v>
       </c>
       <c r="C502" t="str">
-        <v>Perfil incorporado ({n} B)</v>
+        <v>Arraste para redimensionar a área da imagem; clique duplo para voltar ao tamanho padrão</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Image view</v>
       </c>
       <c r="B503" t="str">
-        <v>Perfis HDR no pool</v>
+        <v>Vista da imagem</v>
       </c>
       <c r="C503" t="str">
-        <v>Perfis HDR no pool</v>
+        <v>Visualização da imagem</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Profile</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B504" t="str">
-        <v>Perfil</v>
+        <v>Limita o brilho ao pico que este ecrã indica. No Windows esse valor pode atrasar-se face às mudanças de brilho.</v>
       </c>
       <c r="C504" t="str">
-        <v>Perfil</v>
+        <v>Limita o brilho ao pico que esta tela informa. No Windows esse valor pode ficar atrasado em relação às mudanças de brilho.</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>embedded profile</v>
+        <v>no limit</v>
       </c>
       <c r="B505" t="str">
-        <v>perfil incorporado</v>
+        <v>sem limite</v>
       </c>
       <c r="C505" t="str">
-        <v>perfil incorporado</v>
+        <v>sem limite</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Colour engine path</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B506" t="str">
-        <v>Caminho do motor de cor</v>
+        <v>limite {n} stops ({r}×)</v>
       </c>
       <c r="C506" t="str">
-        <v>Caminho do mecanismo de cor</v>
+        <v>limite {n} stops ({r}×)</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>SDR white</v>
       </c>
       <c r="B507" t="str">
-        <v>Caminho HDR, curva de ganho aplicada</v>
+        <v>Branco SDR</v>
       </c>
       <c r="C507" t="str">
-        <v>Caminho HDR, curva de ganho aplicada</v>
+        <v>Branco SDR</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B508" t="str">
-        <v>Caminho HDR, sem curva de ganho</v>
+        <v>Branco SDR simples, para comparação. Num ecrã HDR, as altas luzes HDR parecem mais brilhantes do que este.</v>
       </c>
       <c r="C508" t="str">
-        <v>Caminho HDR, sem curva de ganho</v>
+        <v>Branco SDR simples, para comparação. Em uma tela HDR, os realces HDR parecem mais brilhantes que este.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B509" t="str">
-        <v>AToB0 pré-calculado — não é o caminho HDR</v>
+        <v>Amostra de branco SDR</v>
       </c>
       <c r="C509" t="str">
-        <v>AToB0 pré-calculado — não é o caminho HDR</v>
+        <v>Amostra de branco SDR</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Transfer</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B510" t="str">
-        <v>Transferência</v>
+        <v>Arraste para a mover; faça duplo clique para a repor junto à imagem.</v>
       </c>
       <c r="C510" t="str">
-        <v>Transferência</v>
+        <v>Arraste para movê-la; clique duas vezes para colocá-la de volta ao lado da imagem.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>HDR reference white</v>
+        <v>Assign profile</v>
       </c>
       <c r="B511" t="str">
-        <v>Branco de referência HDR</v>
+        <v>Atribuir perfil</v>
       </c>
       <c r="C511" t="str">
-        <v>Branco de referência HDR</v>
+        <v>Atribuir perfil</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Target headroom</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B512" t="str">
-        <v>Margem alvo</v>
+        <v>Nenhum — o que o ficheiro indica</v>
       </c>
       <c r="C512" t="str">
-        <v>Margem alvo</v>
+        <v>Nenhum — o que o arquivo indica</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B513" t="str">
-        <v>{r}× o branco de referência ({n} stops)</v>
+        <v>Perfil incorporado ({n} B)</v>
       </c>
       <c r="C513" t="str">
-        <v>{r}× o branco de referência ({n} stops)</v>
+        <v>Perfil incorporado ({n} B)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Tone mapping</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B514" t="str">
-        <v>Tone mapping</v>
+        <v>Perfis HDR no pool</v>
       </c>
       <c r="C514" t="str">
-        <v>Tone mapping</v>
+        <v>Perfis HDR no pool</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Profile</v>
       </c>
       <c r="B515" t="str">
-        <v>Auto (ordem da cláusula 8.10.3)</v>
+        <v>Perfil</v>
       </c>
       <c r="C515" t="str">
-        <v>Auto (ordem da cláusula 8.10.3)</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>embedded profile</v>
       </c>
       <c r="B516" t="str">
-        <v>Curva de ganho (HAGC)</v>
+        <v>perfil incorporado</v>
       </c>
       <c r="C516" t="str">
-        <v>Curva de ganho (HAGC)</v>
+        <v>perfil incorporado</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B517" t="str">
-        <v>Alternativa SDR pré-calculada (AToB0)</v>
+        <v>Caminho do motor de cor</v>
       </c>
       <c r="C517" t="str">
-        <v>Alternativa SDR pré-calculada (AToB0)</v>
+        <v>Caminho do mecanismo de cor</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B518" t="str">
-        <v>Desligado — como um CMM anterior à emenda</v>
+        <v>Caminho HDR, curva de ganho aplicada</v>
       </c>
       <c r="C518" t="str">
-        <v>Desligado — como um CMM anterior à emenda</v>
+        <v>Caminho HDR, curva de ganho aplicada</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Applying the profile…</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B519" t="str">
-        <v>A aplicar o perfil…</v>
+        <v>Caminho HDR, sem curva de ganho</v>
       </c>
       <c r="C519" t="str">
-        <v>Aplicando o perfil…</v>
+        <v>Caminho HDR, sem curva de ganho</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B520" t="str">
-        <v>O {format} contém luz linear, pelo que precisa de um perfil com transferência Linear (8).</v>
+        <v>AToB0 pré-calculado — não é o caminho HDR</v>
       </c>
       <c r="C520" t="str">
-        <v>O {format} contém luz linear, então precisa de um perfil com transferência Linear (8).</v>
+        <v>AToB0 pré-calculado — não é o caminho HDR</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Transfer</v>
       </c>
       <c r="B521" t="str">
-        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
+        <v>Transferência</v>
       </c>
       <c r="C521" t="str">
-        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
+        <v>Transferência</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B522" t="str">
-        <v>Para interpretar os seus valores, atribua um perfil acima.</v>
+        <v>Branco de referência HDR</v>
       </c>
       <c r="C522" t="str">
-        <v>Para interpretar seus valores, atribua um perfil acima.</v>
+        <v>Branco de referência HDR</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>HDR Profiles</v>
+        <v>Target headroom</v>
       </c>
       <c r="B523" t="str">
-        <v>Perfis HDR</v>
+        <v>Margem alvo</v>
       </c>
       <c r="C523" t="str">
-        <v>Perfis HDR</v>
+        <v>Margem alvo</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Linear transfer</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B524" t="str">
-        <v>Transferência linear</v>
+        <v>{r}× o branco de referência ({n} stops)</v>
       </c>
       <c r="C524" t="str">
-        <v>Transferência linear</v>
+        <v>{r}× o branco de referência ({n} stops)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B525" t="str">
-        <v>Transferência não linear (PQ, HLG)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="C525" t="str">
-        <v>Transferência não linear (PQ, HLG)</v>
+        <v>Tone mapping</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B526" t="str">
-        <v>Perfis HDR — transferência linear</v>
+        <v>Auto (ordem da cláusula 8.10.3)</v>
       </c>
       <c r="C526" t="str">
-        <v>Perfis HDR — transferência linear</v>
+        <v>Auto (ordem da cláusula 8.10.3)</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B527" t="str">
-        <v>Perfis HDR — transferência PQ / HLG</v>
+        <v>Curva de ganho (HAGC)</v>
       </c>
       <c r="C527" t="str">
-        <v>Perfis HDR — transferência PQ / HLG</v>
+        <v>Curva de ganho (HAGC)</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B528" t="str">
-        <v>O {format} contém luz linear, pelo que só podem ser atribuídos perfis HDR com transferência linear.</v>
+        <v>Alternativa SDR pré-calculada (AToB0)</v>
       </c>
       <c r="C528" t="str">
-        <v>O {format} contém luz linear, então só podem ser atribuídos perfis HDR com transferência linear.</v>
+        <v>Alternativa SDR pré-calculada (AToB0)</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B529" t="str">
-        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis lista-os em Perfis HDR › Transferência não linear.</v>
+        <v>Desligado — como um CMM anterior à emenda</v>
       </c>
       <c r="C529" t="str">
-        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis os lista em Perfis HDR › Transferência não linear.</v>
+        <v>Desligado — como um CMM anterior à emenda</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B530" t="str">
-        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
+        <v>A aplicar o perfil…</v>
       </c>
       <c r="C530" t="str">
-        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
+        <v>Aplicando o perfil…</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B531" t="str">
-        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
+        <v>O {format} contém luz linear, pelo que precisa de um perfil com transferência Linear (8).</v>
       </c>
       <c r="C531" t="str">
-        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
+        <v>O {format} contém luz linear, então precisa de um perfil com transferência Linear (8).</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Display headroom</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B532" t="str">
-        <v>Margem do ecrã</v>
+        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
       </c>
       <c r="C532" t="str">
-        <v>Margem da tela</v>
+        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B533" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>Para interpretar os seus valores, atribua um perfil acima.</v>
       </c>
       <c r="C533" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>Para interpretar seus valores, atribua um perfil acima.</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B534" t="str">
-        <v>Base</v>
+        <v>Perfis HDR</v>
       </c>
       <c r="C534" t="str">
-        <v>Base</v>
+        <v>Perfis HDR</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B535" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>Transferência linear</v>
       </c>
       <c r="C535" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>Transferência linear</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B536" t="str">
-        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
+        <v>Transferência não linear (PQ, HLG)</v>
       </c>
       <c r="C536" t="str">
-        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
+        <v>Transferência não linear (PQ, HLG)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B537" t="str">
-        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
+        <v>Perfis HDR — transferência linear</v>
       </c>
       <c r="C537" t="str">
-        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
+        <v>Perfis HDR — transferência linear</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B538" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
+        <v>Perfis HDR — transferência PQ / HLG</v>
       </c>
       <c r="C538" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
+        <v>Perfis HDR — transferência PQ / HLG</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B539" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
+        <v>O {format} contém luz linear, pelo que só podem ser atribuídos perfis HDR com transferência linear.</v>
       </c>
       <c r="C539" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
+        <v>O {format} contém luz linear, então só podem ser atribuídos perfis HDR com transferência linear.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B540" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
+        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis lista-os em Perfis HDR › Transferência não linear.</v>
       </c>
       <c r="C540" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
+        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis os lista em Perfis HDR › Transferência não linear.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B541" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
       </c>
       <c r="C541" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Curve at {h} stops</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B542" t="str">
-        <v>Curva a {h} stops</v>
+        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
       </c>
       <c r="C542" t="str">
-        <v>Curva a {h} stops</v>
+        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Display headroom</v>
       </c>
       <c r="B543" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Margem do ecrã</v>
       </c>
       <c r="C543" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Margem da tela</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B544" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
       <c r="C544" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B545" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>Base</v>
       </c>
       <c r="C545" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B546" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
       <c r="C546" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B547" t="str">
-        <v>Curva de tons dos cinzentos nesta margem</v>
+        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
       </c>
       <c r="C547" t="str">
-        <v>Curva de tons de cinza nesta margem</v>
+        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B548" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
       </c>
       <c r="C548" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B549" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
       </c>
       <c r="C549" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>No change</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B550" t="str">
-        <v>Sem alteração</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
       </c>
       <c r="C550" t="str">
-        <v>Sem alteração</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B551" t="str">
-        <v>Pico do ecrã a {h} stops</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
       </c>
       <c r="C551" t="str">
-        <v>Pico da tela a {h} stops</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Output at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B552" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
       <c r="C552" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B553" t="str">
-        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
+        <v>Curva a {h} stops</v>
       </c>
       <c r="C553" t="str">
-        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
+        <v>Curva a {h} stops</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Identify displays</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B554" t="str">
-        <v>Identificar ecrãs</v>
+        <v>Aplicado a {h} stops</v>
       </c>
       <c r="C554" t="str">
-        <v>Identificar telas</v>
+        <v>Aplicado a {h} stops</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B555" t="str">
-        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
       <c r="C555" t="str">
-        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>A acompanhar em que monitor está esta janela.</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
       <c r="C556" t="str">
-        <v>Acompanhando em qual monitor esta janela está.</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B557" t="str">
-        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
+        <v>Ganho (stops log2)</v>
       </c>
       <c r="C557" t="str">
-        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
+        <v>Ganho (stops log2)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B558" t="str">
-        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
+        <v>Curva de tons dos cinzentos nesta margem</v>
       </c>
       <c r="C558" t="str">
-        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
+        <v>Curva de tons de cinza nesta margem</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Could not identify displays.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B559" t="str">
-        <v>Não foi possível identificar os ecrãs.</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
       <c r="C559" t="str">
-        <v>Não foi possível identificar as telas.</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Display events</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B560" t="str">
-        <v>Eventos de ecrã</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
       <c r="C560" t="str">
-        <v>Eventos de tela</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>No change</v>
       </c>
       <c r="B561" t="str">
-        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
+        <v>Sem alteração</v>
       </c>
       <c r="C561" t="str">
-        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
+        <v>Sem alteração</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Colour primaries</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B562" t="str">
-        <v>Primárias de cor</v>
+        <v>Pico do ecrã a {h} stops</v>
       </c>
       <c r="C562" t="str">
-        <v>Primárias de cor</v>
+        <v>Pico da tela a {h} stops</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Transfer characteristics</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B563" t="str">
-        <v>Características de transferência</v>
+        <v>Saída a {h} stops</v>
       </c>
       <c r="C563" t="str">
-        <v>Características de transferência</v>
+        <v>Saída a {h} stops</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Matrix coefficients</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B564" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
       </c>
       <c r="C564" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Video full-range flag</v>
+        <v>Identify displays</v>
       </c>
       <c r="B565" t="str">
-        <v>Sinalizador de gama completa de vídeo</v>
+        <v>Identificar ecrãs</v>
       </c>
       <c r="C565" t="str">
-        <v>Sinalizador de faixa completa de vídeo</v>
+        <v>Identificar telas</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Full range</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B566" t="str">
-        <v>Gama completa</v>
+        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
       <c r="C566" t="str">
-        <v>Faixa completa</v>
+        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Narrow range</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B567" t="str">
-        <v>Gama reduzida</v>
+        <v>A acompanhar em que monitor está esta janela.</v>
       </c>
       <c r="C567" t="str">
-        <v>Faixa reduzida</v>
+        <v>Acompanhando em qual monitor esta janela está.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B568" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
       </c>
       <c r="C568" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B569" t="str">
-        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
+        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
       </c>
       <c r="C569" t="str">
-        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
+        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B570" t="str">
-        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
+        <v>Não foi possível identificar os ecrãs.</v>
       </c>
       <c r="C570" t="str">
-        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
+        <v>Não foi possível identificar as telas.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>REPORT</v>
+        <v>Display events</v>
       </c>
       <c r="B571" t="str">
-        <v>RELATÓRIO</v>
+        <v>Eventos de ecrã</v>
       </c>
       <c r="C571" t="str">
-        <v>RELATÓRIO</v>
+        <v>Eventos de tela</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>FAIL</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B572" t="str">
-        <v>REPROVADO</v>
+        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
       </c>
       <c r="C572" t="str">
-        <v>REPROVADO</v>
+        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>checks</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B573" t="str">
-        <v>verificações</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C573" t="str">
-        <v>verificações</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B574" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C574" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B575" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C575" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B576" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C576" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Powered by {lib}</v>
+        <v>Full range</v>
       </c>
       <c r="B577" t="str">
-        <v>Com {lib}</v>
+        <v>Gama completa</v>
       </c>
       <c r="C577" t="str">
-        <v>Com {lib}</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B578" t="str">
-        <v>Subscrever</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C578" t="str">
-        <v>Inscrever-se</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B579" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C579" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Get notified about new releases</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B580" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C580" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B581" t="str">
-        <v>Fechar</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C581" t="str">
-        <v>Fechar</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>REPORT</v>
       </c>
       <c r="B582" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C582" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Email address</v>
+        <v>FAIL</v>
       </c>
       <c r="B583" t="str">
-        <v>Endereço de e-mail</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C583" t="str">
-        <v>Endereço de e-mail</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>you@example.com</v>
+        <v>checks</v>
       </c>
       <c r="B584" t="str">
-        <v>voce@exemplo.com</v>
+        <v>verificações</v>
       </c>
       <c r="C584" t="str">
-        <v>voce@exemplo.com</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B585" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C585" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B586" t="str">
-        <v>(opcional)</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C586" t="str">
-        <v>(opcional)</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B587" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C587" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B588" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C588" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Cancel</v>
+        <v>Subscribe</v>
       </c>
       <c r="B589" t="str">
-        <v>Cancelar</v>
+        <v>Subscrever</v>
       </c>
       <c r="C589" t="str">
-        <v>Cancelar</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B590" t="str">
-        <v>Subscrever</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C590" t="str">
-        <v>Inscrever-se</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B591" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C591" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Close</v>
       </c>
       <c r="B592" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Fechar</v>
       </c>
       <c r="C592" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Close</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B593" t="str">
-        <v>Fechar</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C593" t="str">
-        <v>Fechar</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Privacy notice</v>
+        <v>Email address</v>
       </c>
       <c r="B594" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C594" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B595" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C595" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B596" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C596" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Please check the form and try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B597" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>(opcional)</v>
       </c>
       <c r="C597" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B598" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C598" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Network error. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B599" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C599" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Error:</v>
+        <v>Cancel</v>
       </c>
       <c r="B600" t="str">
-        <v>Erro:</v>
+        <v>Cancelar</v>
       </c>
       <c r="C600" t="str">
-        <v>Erro:</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B601" t="str">
-        <v>Converter para XML</v>
+        <v>Subscrever</v>
       </c>
       <c r="C601" t="str">
-        <v>Converter para XML</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Convert to JSON</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B602" t="str">
-        <v>Converter para JSON</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C602" t="str">
-        <v>Converter para JSON</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Convert to ICC</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B603" t="str">
-        <v>Converter para ICC</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C603" t="str">
-        <v>Converter para ICC</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B604" t="str">
-        <v>A converter para XML…</v>
+        <v>Fechar</v>
       </c>
       <c r="C604" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Converting to JSON…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B605" t="str">
-        <v>A converter para JSON…</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C605" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Converting to ICC…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B606" t="str">
-        <v>A converter para ICC…</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C606" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Load ICC profile</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B607" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C607" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B608" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C608" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Profile ID</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B609" t="str">
-        <v>ID do perfil</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C609" t="str">
-        <v>ID do perfil</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>No tags found.</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B610" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C610" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Tag Name</v>
+        <v>Error:</v>
       </c>
       <c r="B611" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Erro:</v>
       </c>
       <c r="C611" t="str">
-        <v>Nome da tag</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B612" t="str">
-        <v>ID</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C612" t="str">
-        <v>ID</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Offset</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B613" t="str">
-        <v>Deslocamento</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C613" t="str">
-        <v>Deslocamento</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Size</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B614" t="str">
-        <v>Tamanho</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C614" t="str">
-        <v>Tamanho</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Pad</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B615" t="str">
-        <v>Preenchimento</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C615" t="str">
-        <v>Preenchimento</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B616" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C616" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Type</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B617" t="str">
-        <v>Tipo</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C617" t="str">
-        <v>Tipo</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Array of {type}</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B618" t="str">
-        <v>Vetor de {type}</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C618" t="str">
-        <v>Array de {type}</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>(No content)</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B619" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C619" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>bytes</v>
+        <v>Profile ID</v>
       </c>
       <c r="B620" t="str">
-        <v>bytes</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C620" t="str">
-        <v>bytes</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Loading full description…</v>
+        <v>No tags found.</v>
       </c>
       <c r="B621" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C621" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Could not load full description:</v>
+        <v>Tag Name</v>
       </c>
       <c r="B622" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C622" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ID</v>
       </c>
       <c r="B623" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>ID</v>
       </c>
       <c r="C623" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Offset</v>
       </c>
       <c r="B624" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C624" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>No validation output</v>
+        <v>Size</v>
       </c>
       <c r="B625" t="str">
-        <v>Sem saída de validação</v>
+        <v>Tamanho</v>
       </c>
       <c r="C625" t="str">
-        <v>Sem saída de validação</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Profile is valid</v>
+        <v>Pad</v>
       </c>
       <c r="B626" t="str">
-        <v>O perfil é válido</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C626" t="str">
-        <v>O perfil é válido</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B627" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C627" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Type</v>
       </c>
       <c r="B628" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Tipo</v>
       </c>
       <c r="C628" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Critical validation error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B629" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C629" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Unknown validation status</v>
+        <v>(No content)</v>
       </c>
       <c r="B630" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C630" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>bytes</v>
       </c>
       <c r="B631" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>bytes</v>
       </c>
       <c r="C631" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B632" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C632" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B633" t="str">
-        <v>Válido</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C633" t="str">
-        <v>Válido</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Warning</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B634" t="str">
-        <v>Aviso</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C634" t="str">
-        <v>Aviso</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B635" t="str">
-        <v>Erro</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C635" t="str">
-        <v>Erro</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Unknown</v>
+        <v>No validation output</v>
       </c>
       <c r="B636" t="str">
-        <v>Desconhecido</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C636" t="str">
-        <v>Desconhecido</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Pass</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B637" t="str">
-        <v>Aprovado</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C637" t="str">
-        <v>Aprovado</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Fail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B638" t="str">
-        <v>Reprovado</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C638" t="str">
-        <v>Reprovado</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>View in context</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B639" t="str">
-        <v>Ver no contexto</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C639" t="str">
-        <v>Ver no contexto</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Validation detail</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B640" t="str">
-        <v>Detalhe de validação</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C640" t="str">
-        <v>Detalhe de validação</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Triggered by</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B641" t="str">
-        <v>Acionado por</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C641" t="str">
-        <v>Acionado por</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Field</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B642" t="str">
-        <v>Campo</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C642" t="str">
-        <v>Campo</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Current value</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B643" t="str">
-        <v>Valor atual</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C643" t="str">
-        <v>Valor atual</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Required: 0</v>
+        <v>Valid</v>
       </c>
       <c r="B644" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Válido</v>
       </c>
       <c r="C644" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Expected: {value}</v>
+        <v>Warning</v>
       </c>
       <c r="B645" t="str">
-        <v>Esperado: {value}</v>
+        <v>Aviso</v>
       </c>
       <c r="C645" t="str">
-        <v>Esperado: {value}</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Invalid</v>
+        <v>Error</v>
       </c>
       <c r="B646" t="str">
-        <v>Inválido</v>
+        <v>Erro</v>
       </c>
       <c r="C646" t="str">
-        <v>Inválido</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown</v>
       </c>
       <c r="B647" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C647" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Close</v>
+        <v>Pass</v>
       </c>
       <c r="B648" t="str">
-        <v>Fechar</v>
+        <v>Aprovado</v>
       </c>
       <c r="C648" t="str">
-        <v>Fechar</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Loading XML editor…</v>
+        <v>Fail</v>
       </c>
       <c r="B649" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Reprovado</v>
       </c>
       <c r="C649" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Loading JSON editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B650" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C650" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B651" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C651" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B652" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Acionado por</v>
       </c>
       <c r="C652" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Field</v>
       </c>
       <c r="B653" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Campo</v>
       </c>
       <c r="C653" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Current value</v>
       </c>
       <c r="B654" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Valor atual</v>
       </c>
       <c r="C654" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B655" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C655" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B656" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C656" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>indent</v>
+        <v>Invalid</v>
       </c>
       <c r="B657" t="str">
-        <v>indentação</v>
+        <v>Inválido</v>
       </c>
       <c r="C657" t="str">
-        <v>indentação</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>sort keys</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B658" t="str">
-        <v>ordenar chaves</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C658" t="str">
-        <v>ordenar chaves</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B659" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C659" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B660" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C660" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B661" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C661" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B662" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C662" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B663" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C663" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B664" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C664" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B665" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C665" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B666" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C666" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B667" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C667" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B668" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C668" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B669" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C669" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B659" t="str">
+      <c r="B670" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C659" t="str">
+      <c r="C670" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C659"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C670"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C670"/>
+  <dimension ref="A1:C693"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -6410,1382 +6410,1635 @@
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B546" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>Pré-visualização através do motor de cor</v>
       </c>
       <c r="C546" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>Pré-visualização pelo mecanismo de cor</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B547" t="str">
-        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
+        <v>Tal como criado (base {h} stops, sem ganho)</v>
       </c>
       <c r="C547" t="str">
-        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
+        <v>Como criado (base {h} stops, sem ganho)</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B548" t="str">
-        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
+        <v>Mapeado para {h} stops</v>
       </c>
       <c r="C548" t="str">
-        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
+        <v>Mapeado para {h} stops</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B549" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
+        <v>Os mesmos píxeis de teste (sinal {transfer} a subir da esquerda para a direita: cinzento, depois R, G, B, Y, C, M) através da transformação HDR do IccProfLib. Ambas as faixas estão limitadas a {r}× o branco de referência HDR, como um ecrã com {h} stops de margem as mostraria: onde a faixa de cima satura plana, a curva de ganho suaviza as altas luzes.</v>
       </c>
       <c r="C549" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
+        <v>Os mesmos pixels de teste (sinal {transfer} subindo da esquerda para a direita: cinza, depois R, G, B, Y, C, M) pela transformação HDR do IccProfLib. As duas faixas são limitadas a {r}× o branco de referência HDR, como uma tela com {h} stops de margem as mostraria: onde a faixa de cima satura plana, a curva de ganho suaviza as altas luzes.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>reference white</v>
       </c>
       <c r="B550" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
+        <v>branco de referência</v>
       </c>
       <c r="C550" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
+        <v>branco de referência</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>display peak</v>
       </c>
       <c r="B551" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
+        <v>pico do ecrã</v>
       </c>
       <c r="C551" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
+        <v>pico da tela</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B552" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>Pré-visualização indisponível: {why}</v>
       </c>
       <c r="C552" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>Pré-visualização indisponível: {why}</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Curve at {h} stops</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B553" t="str">
-        <v>Curva a {h} stops</v>
+        <v>o motor de cor não seguiu o caminho HDR para este perfil</v>
       </c>
       <c r="C553" t="str">
-        <v>Curva a {h} stops</v>
+        <v>o mecanismo de cor não seguiu o caminho HDR para este perfil</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B554" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Ganho em todas as margens</v>
       </c>
       <c r="C554" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Ganho em todas as margens</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B555" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>Ganho aplicado a uma entrada cinzenta em cada margem do ecrã: o azul comprime, o vermelho expande e o branco deixa-a igual. As linhas ponteadas marcam as curvas da etiqueta, a contínua a base e a âmbar o controlo; a diagonal tracejada é onde a entrada atinge o pico do ecrã. Clique para mover o controlo.</v>
       </c>
       <c r="C555" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>Ganho aplicado a uma entrada cinza em cada margem da tela: azul comprime, vermelho expande e branco deixa inalterado. As linhas pontilhadas marcam as curvas da tag, a contínua a base e a âmbar o controle; a diagonal tracejada é onde a entrada atinge o pico da tela. Clique para mover o controle.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>Entrada (stops relativamente ao branco de referência HDR)</v>
       </c>
       <c r="C556" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>Entrada (stops em relação ao branco de referência HDR)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B557" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>Margem do ecrã (stops)</v>
       </c>
       <c r="C557" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>Margem da tela (stops)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B558" t="str">
-        <v>Curva de tons dos cinzentos nesta margem</v>
+        <v>Ganho (stops)</v>
       </c>
       <c r="C558" t="str">
-        <v>Curva de tons de cinza nesta margem</v>
+        <v>Ganho (stops)</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B559" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Curva na etiqueta</v>
       </c>
       <c r="C559" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Curva na tag</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B560" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Base</v>
       </c>
       <c r="C560" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No change</v>
+        <v>Slider</v>
       </c>
       <c r="B561" t="str">
-        <v>Sem alteração</v>
+        <v>Controlo</v>
       </c>
       <c r="C561" t="str">
-        <v>Sem alteração</v>
+        <v>Controle</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B562" t="str">
-        <v>Pico do ecrã a {h} stops</v>
+        <v>Entrada = pico do ecrã</v>
       </c>
       <c r="C562" t="str">
-        <v>Pico da tela a {h} stops</v>
+        <v>Entrada = pico da tela</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Output at {h} stops</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B563" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Curvas tonais de cinzento por margem</v>
       </c>
       <c r="C563" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Curvas tonais de cinza por margem</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B564" t="str">
-        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
+        <v>A curva tonal de cinzento em cada margem guardada na etiqueta, colorida de baixo (azul) para alto (vermelho), com a curva do controlo em âmbar. Ambos os eixos estão em stops, pelo que a diagonal significa sem alteração.</v>
       </c>
       <c r="C564" t="str">
-        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
+        <v>A curva tonal de cinza em cada margem armazenada na tag, colorida de baixo (azul) para alto (vermelho), com a curva do controle em âmbar. Os dois eixos estão em stops, então a diagonal significa sem alteração.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Identify displays</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B565" t="str">
-        <v>Identificar ecrãs</v>
+        <v>Saída (stops relativamente ao branco de referência HDR)</v>
       </c>
       <c r="C565" t="str">
-        <v>Identificar telas</v>
+        <v>Saída (stops em relação ao branco de referência HDR)</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B566" t="str">
-        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>{h} stops</v>
       </c>
       <c r="C566" t="str">
-        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>{h} stops</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B567" t="str">
-        <v>A acompanhar em que monitor está esta janela.</v>
+        <v>{h} stops (base)</v>
       </c>
       <c r="C567" t="str">
-        <v>Acompanhando em qual monitor esta janela está.</v>
+        <v>{h} stops (base)</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B568" t="str">
-        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
+        <v>A {h} stops (controlo)</v>
       </c>
       <c r="C568" t="str">
-        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
+        <v>Em {h} stops (controle)</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B569" t="str">
-        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
       <c r="C569" t="str">
-        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Could not identify displays.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B570" t="str">
-        <v>Não foi possível identificar os ecrãs.</v>
+        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
       </c>
       <c r="C570" t="str">
-        <v>Não foi possível identificar as telas.</v>
+        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Display events</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B571" t="str">
-        <v>Eventos de ecrã</v>
+        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
       </c>
       <c r="C571" t="str">
-        <v>Eventos de tela</v>
+        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B572" t="str">
-        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
+        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
       </c>
       <c r="C572" t="str">
-        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
+        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Colour primaries</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B573" t="str">
-        <v>Primárias de cor</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
       </c>
       <c r="C573" t="str">
-        <v>Primárias de cor</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Transfer characteristics</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B574" t="str">
-        <v>Características de transferência</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
       </c>
       <c r="C574" t="str">
-        <v>Características de transferência</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Matrix coefficients</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B575" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
       <c r="C575" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Video full-range flag</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B576" t="str">
-        <v>Sinalizador de gama completa de vídeo</v>
+        <v>Curva a {h} stops</v>
       </c>
       <c r="C576" t="str">
-        <v>Sinalizador de faixa completa de vídeo</v>
+        <v>Curva a {h} stops</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Full range</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B577" t="str">
-        <v>Gama completa</v>
+        <v>Aplicado a {h} stops</v>
       </c>
       <c r="C577" t="str">
-        <v>Faixa completa</v>
+        <v>Aplicado a {h} stops</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Narrow range</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B578" t="str">
-        <v>Gama reduzida</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
       <c r="C578" t="str">
-        <v>Faixa reduzida</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B579" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
       <c r="C579" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B580" t="str">
-        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
+        <v>Ganho (stops log2)</v>
       </c>
       <c r="C580" t="str">
-        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
+        <v>Ganho (stops log2)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B581" t="str">
-        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
+        <v>Curva de tons dos cinzentos nesta margem</v>
       </c>
       <c r="C581" t="str">
-        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
+        <v>Curva de tons de cinza nesta margem</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>REPORT</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B582" t="str">
-        <v>RELATÓRIO</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
       <c r="C582" t="str">
-        <v>RELATÓRIO</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>FAIL</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B583" t="str">
-        <v>REPROVADO</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
       <c r="C583" t="str">
-        <v>REPROVADO</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>checks</v>
+        <v>No change</v>
       </c>
       <c r="B584" t="str">
-        <v>verificações</v>
+        <v>Sem alteração</v>
       </c>
       <c r="C584" t="str">
-        <v>verificações</v>
+        <v>Sem alteração</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B585" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Pico do ecrã a {h} stops</v>
       </c>
       <c r="C585" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Pico da tela a {h} stops</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B586" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Saída a {h} stops</v>
       </c>
       <c r="C586" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Saída a {h} stops</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B587" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
       </c>
       <c r="C587" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Powered by {lib}</v>
+        <v>Identify displays</v>
       </c>
       <c r="B588" t="str">
-        <v>Com {lib}</v>
+        <v>Identificar ecrãs</v>
       </c>
       <c r="C588" t="str">
-        <v>Com {lib}</v>
+        <v>Identificar telas</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Subscribe</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B589" t="str">
-        <v>Subscrever</v>
+        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
       <c r="C589" t="str">
-        <v>Inscrever-se</v>
+        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B590" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>A acompanhar em que monitor está esta janela.</v>
       </c>
       <c r="C590" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Acompanhando em qual monitor esta janela está.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Get notified about new releases</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B591" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
       </c>
       <c r="C591" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Close</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B592" t="str">
-        <v>Fechar</v>
+        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
       </c>
       <c r="C592" t="str">
-        <v>Fechar</v>
+        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B593" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Não foi possível identificar os ecrãs.</v>
       </c>
       <c r="C593" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Não foi possível identificar as telas.</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Email address</v>
+        <v>Display events</v>
       </c>
       <c r="B594" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Eventos de ecrã</v>
       </c>
       <c r="C594" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Eventos de tela</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>you@example.com</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B595" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
       </c>
       <c r="C595" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B596" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C596" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>(optional)</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B597" t="str">
-        <v>(opcional)</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C597" t="str">
-        <v>(opcional)</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B598" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C598" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B599" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C599" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Cancel</v>
+        <v>Full range</v>
       </c>
       <c r="B600" t="str">
-        <v>Cancelar</v>
+        <v>Gama completa</v>
       </c>
       <c r="C600" t="str">
-        <v>Cancelar</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B601" t="str">
-        <v>Subscrever</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C601" t="str">
-        <v>Inscrever-se</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B602" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C602" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B603" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C603" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B604" t="str">
-        <v>Fechar</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C604" t="str">
-        <v>Fechar</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Privacy notice</v>
+        <v>REPORT</v>
       </c>
       <c r="B605" t="str">
-        <v>Aviso de privacidade</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C605" t="str">
-        <v>Aviso de privacidade</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>FAIL</v>
       </c>
       <c r="B606" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C606" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>checks</v>
       </c>
       <c r="B607" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>verificações</v>
       </c>
       <c r="C607" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B608" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C608" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B609" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C609" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Network error. Please try again.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B610" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C610" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Error:</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B611" t="str">
-        <v>Erro:</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C611" t="str">
-        <v>Erro:</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B612" t="str">
-        <v>Converter para XML</v>
+        <v>Subscrever</v>
       </c>
       <c r="C612" t="str">
-        <v>Converter para XML</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Convert to JSON</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B613" t="str">
-        <v>Converter para JSON</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C613" t="str">
-        <v>Converter para JSON</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Convert to ICC</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B614" t="str">
-        <v>Converter para ICC</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C614" t="str">
-        <v>Converter para ICC</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B615" t="str">
-        <v>A converter para XML…</v>
+        <v>Fechar</v>
       </c>
       <c r="C615" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Converting to JSON…</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B616" t="str">
-        <v>A converter para JSON…</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C616" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Converting to ICC…</v>
+        <v>Email address</v>
       </c>
       <c r="B617" t="str">
-        <v>A converter para ICC…</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C617" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Load ICC profile</v>
+        <v>you@example.com</v>
       </c>
       <c r="B618" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C618" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B619" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C619" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Profile ID</v>
+        <v>(optional)</v>
       </c>
       <c r="B620" t="str">
-        <v>ID do perfil</v>
+        <v>(opcional)</v>
       </c>
       <c r="C620" t="str">
-        <v>ID do perfil</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>No tags found.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B621" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C621" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Tag Name</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B622" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C622" t="str">
-        <v>Nome da tag</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B623" t="str">
-        <v>ID</v>
+        <v>Cancelar</v>
       </c>
       <c r="C623" t="str">
-        <v>ID</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Offset</v>
+        <v>Subscribe</v>
       </c>
       <c r="B624" t="str">
-        <v>Deslocamento</v>
+        <v>Subscrever</v>
       </c>
       <c r="C624" t="str">
-        <v>Deslocamento</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Size</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B625" t="str">
-        <v>Tamanho</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C625" t="str">
-        <v>Tamanho</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Pad</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B626" t="str">
-        <v>Preenchimento</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C626" t="str">
-        <v>Preenchimento</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Bytes changed since load</v>
+        <v>Close</v>
       </c>
       <c r="B627" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Fechar</v>
       </c>
       <c r="C627" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Type</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B628" t="str">
-        <v>Tipo</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C628" t="str">
-        <v>Tipo</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Array of {type}</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B629" t="str">
-        <v>Vetor de {type}</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C629" t="str">
-        <v>Array de {type}</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>(No content)</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B630" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C630" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>bytes</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B631" t="str">
-        <v>bytes</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C631" t="str">
-        <v>bytes</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Loading full description…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B632" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C632" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Could not load full description:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B633" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C633" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error:</v>
       </c>
       <c r="B634" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Erro:</v>
       </c>
       <c r="C634" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B635" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C635" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>No validation output</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B636" t="str">
-        <v>Sem saída de validação</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C636" t="str">
-        <v>Sem saída de validação</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Profile is valid</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B637" t="str">
-        <v>O perfil é válido</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C637" t="str">
-        <v>O perfil é válido</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B638" t="str">
-        <v>O perfil tem avisos</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C638" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B639" t="str">
-        <v>O perfil não é conforme</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C639" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Critical validation error</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B640" t="str">
-        <v>Erro de validação crítico</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C640" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Unknown validation status</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B641" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C641" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B642" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C642" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B643" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C643" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Valid</v>
+        <v>No tags found.</v>
       </c>
       <c r="B644" t="str">
-        <v>Válido</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C644" t="str">
-        <v>Válido</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Warning</v>
+        <v>Tag Name</v>
       </c>
       <c r="B645" t="str">
-        <v>Aviso</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C645" t="str">
-        <v>Aviso</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
       <c r="B646" t="str">
-        <v>Erro</v>
+        <v>ID</v>
       </c>
       <c r="C646" t="str">
-        <v>Erro</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Unknown</v>
+        <v>Offset</v>
       </c>
       <c r="B647" t="str">
-        <v>Desconhecido</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C647" t="str">
-        <v>Desconhecido</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Pass</v>
+        <v>Size</v>
       </c>
       <c r="B648" t="str">
-        <v>Aprovado</v>
+        <v>Tamanho</v>
       </c>
       <c r="C648" t="str">
-        <v>Aprovado</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Fail</v>
+        <v>Pad</v>
       </c>
       <c r="B649" t="str">
-        <v>Reprovado</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C649" t="str">
-        <v>Reprovado</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>View in context</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B650" t="str">
-        <v>Ver no contexto</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C650" t="str">
-        <v>Ver no contexto</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Validation detail</v>
+        <v>Type</v>
       </c>
       <c r="B651" t="str">
-        <v>Detalhe de validação</v>
+        <v>Tipo</v>
       </c>
       <c r="C651" t="str">
-        <v>Detalhe de validação</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Triggered by</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B652" t="str">
-        <v>Acionado por</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C652" t="str">
-        <v>Acionado por</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Field</v>
+        <v>(No content)</v>
       </c>
       <c r="B653" t="str">
-        <v>Campo</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C653" t="str">
-        <v>Campo</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Current value</v>
+        <v>bytes</v>
       </c>
       <c r="B654" t="str">
-        <v>Valor atual</v>
+        <v>bytes</v>
       </c>
       <c r="C654" t="str">
-        <v>Valor atual</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Required: 0</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B655" t="str">
-        <v>Obrigatório: 0</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C655" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B656" t="str">
-        <v>Esperado: {value}</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C656" t="str">
-        <v>Esperado: {value}</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Invalid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B657" t="str">
-        <v>Inválido</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C657" t="str">
-        <v>Inválido</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B658" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C658" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Close</v>
+        <v>No validation output</v>
       </c>
       <c r="B659" t="str">
-        <v>Fechar</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C659" t="str">
-        <v>Fechar</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Loading XML editor…</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B660" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C660" t="str">
-        <v>Carregando editor XML…</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B661" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C661" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B662" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C662" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B663" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C663" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B664" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C664" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B665" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C665" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B666" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C666" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Valid</v>
       </c>
       <c r="B667" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Válido</v>
       </c>
       <c r="C667" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>indent</v>
+        <v>Warning</v>
       </c>
       <c r="B668" t="str">
-        <v>indentação</v>
+        <v>Aviso</v>
       </c>
       <c r="C668" t="str">
-        <v>indentação</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>sort keys</v>
+        <v>Error</v>
       </c>
       <c r="B669" t="str">
-        <v>ordenar chaves</v>
+        <v>Erro</v>
       </c>
       <c r="C669" t="str">
-        <v>ordenar chaves</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B670" t="str">
+        <v>Desconhecido</v>
+      </c>
+      <c r="C670" t="str">
+        <v>Desconhecido</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B671" t="str">
+        <v>Aprovado</v>
+      </c>
+      <c r="C671" t="str">
+        <v>Aprovado</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B672" t="str">
+        <v>Reprovado</v>
+      </c>
+      <c r="C672" t="str">
+        <v>Reprovado</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B673" t="str">
+        <v>Ver no contexto</v>
+      </c>
+      <c r="C673" t="str">
+        <v>Ver no contexto</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B674" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+      <c r="C674" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B675" t="str">
+        <v>Acionado por</v>
+      </c>
+      <c r="C675" t="str">
+        <v>Acionado por</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B676" t="str">
+        <v>Campo</v>
+      </c>
+      <c r="C676" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B677" t="str">
+        <v>Valor atual</v>
+      </c>
+      <c r="C677" t="str">
+        <v>Valor atual</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B678" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+      <c r="C678" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B679" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+      <c r="C679" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B680" t="str">
+        <v>Inválido</v>
+      </c>
+      <c r="C680" t="str">
+        <v>Inválido</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B681" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+      <c r="C681" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B682" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C682" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B683" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C683" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B684" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C684" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B685" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C685" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B686" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C686" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B687" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C687" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B688" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C688" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B689" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C689" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B690" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C690" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B691" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C691" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B692" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C692" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B670" t="str">
+      <c r="B693" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C670" t="str">
+      <c r="C693" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C670"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C693"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C693"/>
+  <dimension ref="A1:C700"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -6157,1888 +6157,1965 @@
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Target headroom</v>
+        <v>Linear values</v>
       </c>
       <c r="B523" t="str">
-        <v>Margem alvo</v>
+        <v>Valores lineares</v>
       </c>
       <c r="C523" t="str">
-        <v>Margem alvo</v>
+        <v>Valores lineares</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B524" t="str">
-        <v>{r}× o branco de referência ({n} stops)</v>
+        <v>Ficheiro 1,0 = branco de referência HDR</v>
       </c>
       <c r="C524" t="str">
-        <v>{r}× o branco de referência ({n} stops)</v>
+        <v>Arquivo 1,0 = branco de referência HDR</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Tone mapping</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B525" t="str">
-        <v>Tone mapping</v>
+        <v>Ficheiro 1,0 = 1 cd/m² (ICC.1 cláusula 8.10.2 a)</v>
       </c>
       <c r="C525" t="str">
-        <v>Tone mapping</v>
+        <v>Arquivo 1,0 = 1 cd/m² (ICC.1 cláusula 8.10.2 a)</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B526" t="str">
-        <v>Auto (ordem da cláusula 8.10.3)</v>
+        <v>Os ficheiros OpenEXR e Radiance HDR colocam por convenção o branco SDR em 1,0, enquanto uma transferência ICC linear lê 1,0 como 1 cd/m². Por predefinição, o ficheiro é escalado para que o seu 1,0 coincida com o branco de referência HDR do perfil.</v>
       </c>
       <c r="C526" t="str">
-        <v>Auto (ordem da cláusula 8.10.3)</v>
+        <v>Arquivos OpenEXR e Radiance HDR colocam por convenção o branco SDR em 1,0, enquanto uma transferência ICC linear lê 1,0 como 1 cd/m². Por padrão, o arquivo é escalado para que seu 1,0 caia no branco de referência HDR do perfil.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Input scale</v>
       </c>
       <c r="B527" t="str">
-        <v>Curva de ganho (HAGC)</v>
+        <v>Escala de entrada</v>
       </c>
       <c r="C527" t="str">
-        <v>Curva de ganho (HAGC)</v>
+        <v>Escala de entrada</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B528" t="str">
-        <v>Alternativa SDR pré-calculada (AToB0)</v>
+        <v>×{w} — ficheiro 1,0 = branco de referência</v>
       </c>
       <c r="C528" t="str">
-        <v>Alternativa SDR pré-calculada (AToB0)</v>
+        <v>×{w} — arquivo 1,0 = branco de referência</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B529" t="str">
-        <v>Desligado — como um CMM anterior à emenda</v>
+        <v>nenhuma — ficheiro 1,0 = 1 cd/m²</v>
       </c>
       <c r="C529" t="str">
-        <v>Desligado — como um CMM anterior à emenda</v>
+        <v>nenhuma — arquivo 1,0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Applying the profile…</v>
+        <v>Target headroom</v>
       </c>
       <c r="B530" t="str">
-        <v>A aplicar o perfil…</v>
+        <v>Margem alvo</v>
       </c>
       <c r="C530" t="str">
-        <v>Aplicando o perfil…</v>
+        <v>Margem alvo</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B531" t="str">
-        <v>O {format} contém luz linear, pelo que precisa de um perfil com transferência Linear (8).</v>
+        <v>{r}× o branco de referência ({n} stops)</v>
       </c>
       <c r="C531" t="str">
-        <v>O {format} contém luz linear, então precisa de um perfil com transferência Linear (8).</v>
+        <v>{r}× o branco de referência ({n} stops)</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B532" t="str">
-        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
+        <v>Tone mapping</v>
       </c>
       <c r="C532" t="str">
-        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
+        <v>Tone mapping</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B533" t="str">
-        <v>Para interpretar os seus valores, atribua um perfil acima.</v>
+        <v>Auto (ordem da cláusula 8.10.3)</v>
       </c>
       <c r="C533" t="str">
-        <v>Para interpretar seus valores, atribua um perfil acima.</v>
+        <v>Auto (ordem da cláusula 8.10.3)</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>HDR Profiles</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B534" t="str">
-        <v>Perfis HDR</v>
+        <v>Curva de ganho (HAGC)</v>
       </c>
       <c r="C534" t="str">
-        <v>Perfis HDR</v>
+        <v>Curva de ganho (HAGC)</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Linear transfer</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B535" t="str">
-        <v>Transferência linear</v>
+        <v>Alternativa SDR pré-calculada (AToB0)</v>
       </c>
       <c r="C535" t="str">
-        <v>Transferência linear</v>
+        <v>Alternativa SDR pré-calculada (AToB0)</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B536" t="str">
-        <v>Transferência não linear (PQ, HLG)</v>
+        <v>Desligado — como um CMM anterior à emenda</v>
       </c>
       <c r="C536" t="str">
-        <v>Transferência não linear (PQ, HLG)</v>
+        <v>Desligado — como um CMM anterior à emenda</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B537" t="str">
-        <v>Perfis HDR — transferência linear</v>
+        <v>A aplicar o perfil…</v>
       </c>
       <c r="C537" t="str">
-        <v>Perfis HDR — transferência linear</v>
+        <v>Aplicando o perfil…</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B538" t="str">
-        <v>Perfis HDR — transferência PQ / HLG</v>
+        <v>O {format} contém luz linear, pelo que precisa de um perfil com transferência Linear (8).</v>
       </c>
       <c r="C538" t="str">
-        <v>Perfis HDR — transferência PQ / HLG</v>
+        <v>O {format} contém luz linear, então precisa de um perfil com transferência Linear (8).</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B539" t="str">
-        <v>O {format} contém luz linear, pelo que só podem ser atribuídos perfis HDR com transferência linear.</v>
+        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
       </c>
       <c r="C539" t="str">
-        <v>O {format} contém luz linear, então só podem ser atribuídos perfis HDR com transferência linear.</v>
+        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B540" t="str">
-        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis lista-os em Perfis HDR › Transferência não linear.</v>
+        <v>Para interpretar os seus valores, atribua um perfil acima.</v>
       </c>
       <c r="C540" t="str">
-        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis os lista em Perfis HDR › Transferência não linear.</v>
+        <v>Para interpretar seus valores, atribua um perfil acima.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B541" t="str">
-        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
+        <v>Perfis HDR</v>
       </c>
       <c r="C541" t="str">
-        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
+        <v>Perfis HDR</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B542" t="str">
-        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
+        <v>Transferência linear</v>
       </c>
       <c r="C542" t="str">
-        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
+        <v>Transferência linear</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Display headroom</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B543" t="str">
-        <v>Margem do ecrã</v>
+        <v>Transferência não linear (PQ, HLG)</v>
       </c>
       <c r="C543" t="str">
-        <v>Margem da tela</v>
+        <v>Transferência não linear (PQ, HLG)</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B544" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>Perfis HDR — transferência linear</v>
       </c>
       <c r="C544" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>Perfis HDR — transferência linear</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B545" t="str">
-        <v>Base</v>
+        <v>Perfis HDR — transferência PQ / HLG</v>
       </c>
       <c r="C545" t="str">
-        <v>Base</v>
+        <v>Perfis HDR — transferência PQ / HLG</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Preview through the colour engine</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B546" t="str">
-        <v>Pré-visualização através do motor de cor</v>
+        <v>O {format} contém luz linear, pelo que só podem ser atribuídos perfis HDR com transferência linear.</v>
       </c>
       <c r="C546" t="str">
-        <v>Pré-visualização pelo mecanismo de cor</v>
+        <v>O {format} contém luz linear, então só podem ser atribuídos perfis HDR com transferência linear.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B547" t="str">
-        <v>Tal como criado (base {h} stops, sem ganho)</v>
+        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis lista-os em Perfis HDR › Transferência não linear.</v>
       </c>
       <c r="C547" t="str">
-        <v>Como criado (base {h} stops, sem ganho)</v>
+        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis os lista em Perfis HDR › Transferência não linear.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B548" t="str">
-        <v>Mapeado para {h} stops</v>
+        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
       </c>
       <c r="C548" t="str">
-        <v>Mapeado para {h} stops</v>
+        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B549" t="str">
-        <v>Os mesmos píxeis de teste (sinal {transfer} a subir da esquerda para a direita: cinzento, depois R, G, B, Y, C, M) através da transformação HDR do IccProfLib. Ambas as faixas estão limitadas a {r}× o branco de referência HDR, como um ecrã com {h} stops de margem as mostraria: onde a faixa de cima satura plana, a curva de ganho suaviza as altas luzes.</v>
+        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
       </c>
       <c r="C549" t="str">
-        <v>Os mesmos pixels de teste (sinal {transfer} subindo da esquerda para a direita: cinza, depois R, G, B, Y, C, M) pela transformação HDR do IccProfLib. As duas faixas são limitadas a {r}× o branco de referência HDR, como uma tela com {h} stops de margem as mostraria: onde a faixa de cima satura plana, a curva de ganho suaviza as altas luzes.</v>
+        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>reference white</v>
+        <v>Display headroom</v>
       </c>
       <c r="B550" t="str">
-        <v>branco de referência</v>
+        <v>Margem do ecrã</v>
       </c>
       <c r="C550" t="str">
-        <v>branco de referência</v>
+        <v>Margem da tela</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>display peak</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B551" t="str">
-        <v>pico do ecrã</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
       <c r="C551" t="str">
-        <v>pico da tela</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>Baseline</v>
       </c>
       <c r="B552" t="str">
-        <v>Pré-visualização indisponível: {why}</v>
+        <v>Base</v>
       </c>
       <c r="C552" t="str">
-        <v>Pré-visualização indisponível: {why}</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B553" t="str">
-        <v>o motor de cor não seguiu o caminho HDR para este perfil</v>
+        <v>Pré-visualização através do motor de cor</v>
       </c>
       <c r="C553" t="str">
-        <v>o mecanismo de cor não seguiu o caminho HDR para este perfil</v>
+        <v>Pré-visualização pelo mecanismo de cor</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Gain across every headroom</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B554" t="str">
-        <v>Ganho em todas as margens</v>
+        <v>Tal como criado (base {h} stops, sem ganho)</v>
       </c>
       <c r="C554" t="str">
-        <v>Ganho em todas as margens</v>
+        <v>Como criado (base {h} stops, sem ganho)</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B555" t="str">
-        <v>Ganho aplicado a uma entrada cinzenta em cada margem do ecrã: o azul comprime, o vermelho expande e o branco deixa-a igual. As linhas ponteadas marcam as curvas da etiqueta, a contínua a base e a âmbar o controlo; a diagonal tracejada é onde a entrada atinge o pico do ecrã. Clique para mover o controlo.</v>
+        <v>Mapeado para {h} stops</v>
       </c>
       <c r="C555" t="str">
-        <v>Ganho aplicado a uma entrada cinza em cada margem da tela: azul comprime, vermelho expande e branco deixa inalterado. As linhas pontilhadas marcam as curvas da tag, a contínua a base e a âmbar o controle; a diagonal tracejada é onde a entrada atinge o pico da tela. Clique para mover o controle.</v>
+        <v>Mapeado para {h} stops</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B556" t="str">
-        <v>Entrada (stops relativamente ao branco de referência HDR)</v>
+        <v>Os mesmos píxeis de teste (sinal {transfer} a subir da esquerda para a direita: cinzento, depois R, G, B, Y, C, M) através da transformação HDR do IccProfLib. Ambas as faixas estão limitadas a {r}× o branco de referência HDR, como um ecrã com {h} stops de margem as mostraria: onde a faixa de cima satura plana, a curva de ganho suaviza as altas luzes.</v>
       </c>
       <c r="C556" t="str">
-        <v>Entrada (stops em relação ao branco de referência HDR)</v>
+        <v>Os mesmos pixels de teste (sinal {transfer} subindo da esquerda para a direita: cinza, depois R, G, B, Y, C, M) pela transformação HDR do IccProfLib. As duas faixas são limitadas a {r}× o branco de referência HDR, como uma tela com {h} stops de margem as mostraria: onde a faixa de cima satura plana, a curva de ganho suaviza as altas luzes.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Display headroom (stops)</v>
+        <v>reference white</v>
       </c>
       <c r="B557" t="str">
-        <v>Margem do ecrã (stops)</v>
+        <v>branco de referência</v>
       </c>
       <c r="C557" t="str">
-        <v>Margem da tela (stops)</v>
+        <v>branco de referência</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Gain (stops)</v>
+        <v>display peak</v>
       </c>
       <c r="B558" t="str">
-        <v>Ganho (stops)</v>
+        <v>pico do ecrã</v>
       </c>
       <c r="C558" t="str">
-        <v>Ganho (stops)</v>
+        <v>pico da tela</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Curve in the tag</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B559" t="str">
-        <v>Curva na etiqueta</v>
+        <v>Pré-visualização indisponível: {why}</v>
       </c>
       <c r="C559" t="str">
-        <v>Curva na tag</v>
+        <v>Pré-visualização indisponível: {why}</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Baseline</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B560" t="str">
-        <v>Base</v>
+        <v>o motor de cor não seguiu o caminho HDR para este perfil</v>
       </c>
       <c r="C560" t="str">
-        <v>Base</v>
+        <v>o mecanismo de cor não seguiu o caminho HDR para este perfil</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Slider</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B561" t="str">
-        <v>Controlo</v>
+        <v>Ganho em todas as margens</v>
       </c>
       <c r="C561" t="str">
-        <v>Controle</v>
+        <v>Ganho em todas as margens</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Input = display peak</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B562" t="str">
-        <v>Entrada = pico do ecrã</v>
+        <v>Ganho aplicado a uma entrada cinzenta em cada margem do ecrã: o azul comprime, o vermelho expande e o branco deixa-a igual. As linhas ponteadas marcam as curvas da etiqueta, a contínua a base e a âmbar o controlo; a diagonal tracejada é onde a entrada atinge o pico do ecrã. Clique para mover o controlo.</v>
       </c>
       <c r="C562" t="str">
-        <v>Entrada = pico da tela</v>
+        <v>Ganho aplicado a uma entrada cinza em cada margem da tela: azul comprime, vermelho expande e branco deixa inalterado. As linhas pontilhadas marcam as curvas da tag, a contínua a base e a âmbar o controle; a diagonal tracejada é onde a entrada atinge o pico da tela. Clique para mover o controle.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B563" t="str">
-        <v>Curvas tonais de cinzento por margem</v>
+        <v>Entrada (stops relativamente ao branco de referência HDR)</v>
       </c>
       <c r="C563" t="str">
-        <v>Curvas tonais de cinza por margem</v>
+        <v>Entrada (stops em relação ao branco de referência HDR)</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B564" t="str">
-        <v>A curva tonal de cinzento em cada margem guardada na etiqueta, colorida de baixo (azul) para alto (vermelho), com a curva do controlo em âmbar. Ambos os eixos estão em stops, pelo que a diagonal significa sem alteração.</v>
+        <v>Margem do ecrã (stops)</v>
       </c>
       <c r="C564" t="str">
-        <v>A curva tonal de cinza em cada margem armazenada na tag, colorida de baixo (azul) para alto (vermelho), com a curva do controle em âmbar. Os dois eixos estão em stops, então a diagonal significa sem alteração.</v>
+        <v>Margem da tela (stops)</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B565" t="str">
-        <v>Saída (stops relativamente ao branco de referência HDR)</v>
+        <v>Ganho (stops)</v>
       </c>
       <c r="C565" t="str">
-        <v>Saída (stops em relação ao branco de referência HDR)</v>
+        <v>Ganho (stops)</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>{h} stops</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B566" t="str">
-        <v>{h} stops</v>
+        <v>Curva na etiqueta</v>
       </c>
       <c r="C566" t="str">
-        <v>{h} stops</v>
+        <v>Curva na tag</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>Baseline</v>
       </c>
       <c r="B567" t="str">
-        <v>{h} stops (base)</v>
+        <v>Base</v>
       </c>
       <c r="C567" t="str">
-        <v>{h} stops (base)</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>Slider</v>
       </c>
       <c r="B568" t="str">
-        <v>A {h} stops (controlo)</v>
+        <v>Controlo</v>
       </c>
       <c r="C568" t="str">
-        <v>Em {h} stops (controle)</v>
+        <v>Controle</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B569" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>Entrada = pico do ecrã</v>
       </c>
       <c r="C569" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>Entrada = pico da tela</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B570" t="str">
-        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
+        <v>Curvas tonais de cinzento por margem</v>
       </c>
       <c r="C570" t="str">
-        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
+        <v>Curvas tonais de cinza por margem</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B571" t="str">
-        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
+        <v>A curva tonal de cinzento em cada margem guardada na etiqueta, colorida de baixo (azul) para alto (vermelho), com a curva do controlo em âmbar. Ambos os eixos estão em stops, pelo que a diagonal significa sem alteração.</v>
       </c>
       <c r="C571" t="str">
-        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
+        <v>A curva tonal de cinza em cada margem armazenada na tag, colorida de baixo (azul) para alto (vermelho), com a curva do controle em âmbar. Os dois eixos estão em stops, então a diagonal significa sem alteração.</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B572" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
+        <v>Saída (stops relativamente ao branco de referência HDR)</v>
       </c>
       <c r="C572" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
+        <v>Saída (stops em relação ao branco de referência HDR)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B573" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
+        <v>{h} stops</v>
       </c>
       <c r="C573" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
+        <v>{h} stops</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B574" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
+        <v>{h} stops (base)</v>
       </c>
       <c r="C574" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
+        <v>{h} stops (base)</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B575" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>A {h} stops (controlo)</v>
       </c>
       <c r="C575" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>Em {h} stops (controle)</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B576" t="str">
-        <v>Curva a {h} stops</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
       <c r="C576" t="str">
-        <v>Curva a {h} stops</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Applied at {h} stops</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B577" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
       </c>
       <c r="C577" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B578" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
       </c>
       <c r="C578" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B579" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
       </c>
       <c r="C579" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B580" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
       </c>
       <c r="C580" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B581" t="str">
-        <v>Curva de tons dos cinzentos nesta margem</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
       </c>
       <c r="C581" t="str">
-        <v>Curva de tons de cinza nesta margem</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B582" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
       <c r="C582" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B583" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Curva a {h} stops</v>
       </c>
       <c r="C583" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Curva a {h} stops</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>No change</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B584" t="str">
-        <v>Sem alteração</v>
+        <v>Aplicado a {h} stops</v>
       </c>
       <c r="C584" t="str">
-        <v>Sem alteração</v>
+        <v>Aplicado a {h} stops</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B585" t="str">
-        <v>Pico do ecrã a {h} stops</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
       <c r="C585" t="str">
-        <v>Pico da tela a {h} stops</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Output at {h} stops</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B586" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
       <c r="C586" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B587" t="str">
-        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
+        <v>Ganho (stops log2)</v>
       </c>
       <c r="C587" t="str">
-        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
+        <v>Ganho (stops log2)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Identify displays</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B588" t="str">
-        <v>Identificar ecrãs</v>
+        <v>Curva de tons dos cinzentos nesta margem</v>
       </c>
       <c r="C588" t="str">
-        <v>Identificar telas</v>
+        <v>Curva de tons de cinza nesta margem</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B589" t="str">
-        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
       <c r="C589" t="str">
-        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B590" t="str">
-        <v>A acompanhar em que monitor está esta janela.</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
       <c r="C590" t="str">
-        <v>Acompanhando em qual monitor esta janela está.</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>No change</v>
       </c>
       <c r="B591" t="str">
-        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
+        <v>Sem alteração</v>
       </c>
       <c r="C591" t="str">
-        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
+        <v>Sem alteração</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B592" t="str">
-        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
+        <v>Pico do ecrã a {h} stops</v>
       </c>
       <c r="C592" t="str">
-        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
+        <v>Pico da tela a {h} stops</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Could not identify displays.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B593" t="str">
-        <v>Não foi possível identificar os ecrãs.</v>
+        <v>Saída a {h} stops</v>
       </c>
       <c r="C593" t="str">
-        <v>Não foi possível identificar as telas.</v>
+        <v>Saída a {h} stops</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Display events</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B594" t="str">
-        <v>Eventos de ecrã</v>
+        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
       </c>
       <c r="C594" t="str">
-        <v>Eventos de tela</v>
+        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B595" t="str">
-        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
+        <v>Identificar ecrãs</v>
       </c>
       <c r="C595" t="str">
-        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
+        <v>Identificar telas</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Colour primaries</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B596" t="str">
-        <v>Primárias de cor</v>
+        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
       <c r="C596" t="str">
-        <v>Primárias de cor</v>
+        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Transfer characteristics</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B597" t="str">
-        <v>Características de transferência</v>
+        <v>A acompanhar em que monitor está esta janela.</v>
       </c>
       <c r="C597" t="str">
-        <v>Características de transferência</v>
+        <v>Acompanhando em qual monitor esta janela está.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Matrix coefficients</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B598" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
       </c>
       <c r="C598" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Video full-range flag</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B599" t="str">
-        <v>Sinalizador de gama completa de vídeo</v>
+        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
       </c>
       <c r="C599" t="str">
-        <v>Sinalizador de faixa completa de vídeo</v>
+        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Full range</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B600" t="str">
-        <v>Gama completa</v>
+        <v>Não foi possível identificar os ecrãs.</v>
       </c>
       <c r="C600" t="str">
-        <v>Faixa completa</v>
+        <v>Não foi possível identificar as telas.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Narrow range</v>
+        <v>Display events</v>
       </c>
       <c r="B601" t="str">
-        <v>Gama reduzida</v>
+        <v>Eventos de ecrã</v>
       </c>
       <c r="C601" t="str">
-        <v>Faixa reduzida</v>
+        <v>Eventos de tela</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B602" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
       </c>
       <c r="C602" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B603" t="str">
-        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C603" t="str">
-        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B604" t="str">
-        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C604" t="str">
-        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>REPORT</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B605" t="str">
-        <v>RELATÓRIO</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C605" t="str">
-        <v>RELATÓRIO</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>FAIL</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B606" t="str">
-        <v>REPROVADO</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C606" t="str">
-        <v>REPROVADO</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>checks</v>
+        <v>Full range</v>
       </c>
       <c r="B607" t="str">
-        <v>verificações</v>
+        <v>Gama completa</v>
       </c>
       <c r="C607" t="str">
-        <v>verificações</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B608" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C608" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B609" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C609" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B610" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C610" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Powered by {lib}</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B611" t="str">
-        <v>Com {lib}</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C611" t="str">
-        <v>Com {lib}</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Subscribe</v>
+        <v>REPORT</v>
       </c>
       <c r="B612" t="str">
-        <v>Subscrever</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C612" t="str">
-        <v>Inscrever-se</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>FAIL</v>
       </c>
       <c r="B613" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C613" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Get notified about new releases</v>
+        <v>checks</v>
       </c>
       <c r="B614" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>verificações</v>
       </c>
       <c r="C614" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Close</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B615" t="str">
-        <v>Fechar</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C615" t="str">
-        <v>Fechar</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B616" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C616" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Email address</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B617" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C617" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>you@example.com</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B618" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C618" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Subscribe</v>
       </c>
       <c r="B619" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Subscrever</v>
       </c>
       <c r="C619" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>(optional)</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B620" t="str">
-        <v>(opcional)</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C620" t="str">
-        <v>(opcional)</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B621" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C621" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Close</v>
       </c>
       <c r="B622" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>Fechar</v>
       </c>
       <c r="C622" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Cancel</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B623" t="str">
-        <v>Cancelar</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C623" t="str">
-        <v>Cancelar</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Subscribe</v>
+        <v>Email address</v>
       </c>
       <c r="B624" t="str">
-        <v>Subscrever</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C624" t="str">
-        <v>Inscrever-se</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B625" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C625" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B626" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C626" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Close</v>
+        <v>(optional)</v>
       </c>
       <c r="B627" t="str">
-        <v>Fechar</v>
+        <v>(opcional)</v>
       </c>
       <c r="C627" t="str">
-        <v>Fechar</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Privacy notice</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B628" t="str">
-        <v>Aviso de privacidade</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C628" t="str">
-        <v>Aviso de privacidade</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B629" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C629" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Cancel</v>
       </c>
       <c r="B630" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Cancelar</v>
       </c>
       <c r="C630" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B631" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C631" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B632" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C632" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B633" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C633" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Error:</v>
+        <v>Close</v>
       </c>
       <c r="B634" t="str">
-        <v>Erro:</v>
+        <v>Fechar</v>
       </c>
       <c r="C634" t="str">
-        <v>Erro:</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Convert to XML</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B635" t="str">
-        <v>Converter para XML</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C635" t="str">
-        <v>Converter para XML</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Convert to JSON</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B636" t="str">
-        <v>Converter para JSON</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C636" t="str">
-        <v>Converter para JSON</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Convert to ICC</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B637" t="str">
-        <v>Converter para ICC</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C637" t="str">
-        <v>Converter para ICC</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Converting to XML…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B638" t="str">
-        <v>A converter para XML…</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C638" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Converting to JSON…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B639" t="str">
-        <v>A converter para JSON…</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C639" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Converting to ICC…</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B640" t="str">
-        <v>A converter para ICC…</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C640" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Load ICC profile</v>
+        <v>Error:</v>
       </c>
       <c r="B641" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Erro:</v>
       </c>
       <c r="C641" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B642" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C642" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Profile ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B643" t="str">
-        <v>ID do perfil</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C643" t="str">
-        <v>ID do perfil</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>No tags found.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B644" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C644" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Tag Name</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B645" t="str">
-        <v>Nome da etiqueta</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C645" t="str">
-        <v>Nome da tag</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B646" t="str">
-        <v>ID</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C646" t="str">
-        <v>ID</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Offset</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B647" t="str">
-        <v>Deslocamento</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C647" t="str">
-        <v>Deslocamento</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Size</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B648" t="str">
-        <v>Tamanho</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C648" t="str">
-        <v>Tamanho</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Pad</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B649" t="str">
-        <v>Preenchimento</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C649" t="str">
-        <v>Preenchimento</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile ID</v>
       </c>
       <c r="B650" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C650" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Type</v>
+        <v>No tags found.</v>
       </c>
       <c r="B651" t="str">
-        <v>Tipo</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C651" t="str">
-        <v>Tipo</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Array of {type}</v>
+        <v>Tag Name</v>
       </c>
       <c r="B652" t="str">
-        <v>Vetor de {type}</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C652" t="str">
-        <v>Array de {type}</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>(No content)</v>
+        <v>ID</v>
       </c>
       <c r="B653" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>ID</v>
       </c>
       <c r="C653" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>bytes</v>
+        <v>Offset</v>
       </c>
       <c r="B654" t="str">
-        <v>bytes</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C654" t="str">
-        <v>bytes</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Loading full description…</v>
+        <v>Size</v>
       </c>
       <c r="B655" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Tamanho</v>
       </c>
       <c r="C655" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Could not load full description:</v>
+        <v>Pad</v>
       </c>
       <c r="B656" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C656" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B657" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C657" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Type</v>
       </c>
       <c r="B658" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Tipo</v>
       </c>
       <c r="C658" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>No validation output</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B659" t="str">
-        <v>Sem saída de validação</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C659" t="str">
-        <v>Sem saída de validação</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Profile is valid</v>
+        <v>(No content)</v>
       </c>
       <c r="B660" t="str">
-        <v>O perfil é válido</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C660" t="str">
-        <v>O perfil é válido</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Profile has warning(s)</v>
+        <v>bytes</v>
       </c>
       <c r="B661" t="str">
-        <v>O perfil tem avisos</v>
+        <v>bytes</v>
       </c>
       <c r="C661" t="str">
-        <v>O perfil tem avisos</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B662" t="str">
-        <v>O perfil não é conforme</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C662" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Critical validation error</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B663" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C663" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Unknown validation status</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B664" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C664" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B665" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C665" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No warnings or errors found.</v>
+        <v>No validation output</v>
       </c>
       <c r="B666" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C666" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Valid</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B667" t="str">
-        <v>Válido</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C667" t="str">
-        <v>Válido</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Warning</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B668" t="str">
-        <v>Aviso</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C668" t="str">
-        <v>Aviso</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B669" t="str">
-        <v>Erro</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C669" t="str">
-        <v>Erro</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Unknown</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B670" t="str">
-        <v>Desconhecido</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C670" t="str">
-        <v>Desconhecido</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Pass</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B671" t="str">
-        <v>Aprovado</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C671" t="str">
-        <v>Aprovado</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Fail</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B672" t="str">
-        <v>Reprovado</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C672" t="str">
-        <v>Reprovado</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>View in context</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B673" t="str">
-        <v>Ver no contexto</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C673" t="str">
-        <v>Ver no contexto</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Validation detail</v>
+        <v>Valid</v>
       </c>
       <c r="B674" t="str">
-        <v>Detalhe de validação</v>
+        <v>Válido</v>
       </c>
       <c r="C674" t="str">
-        <v>Detalhe de validação</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Triggered by</v>
+        <v>Warning</v>
       </c>
       <c r="B675" t="str">
-        <v>Acionado por</v>
+        <v>Aviso</v>
       </c>
       <c r="C675" t="str">
-        <v>Acionado por</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Field</v>
+        <v>Error</v>
       </c>
       <c r="B676" t="str">
-        <v>Campo</v>
+        <v>Erro</v>
       </c>
       <c r="C676" t="str">
-        <v>Campo</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Current value</v>
+        <v>Unknown</v>
       </c>
       <c r="B677" t="str">
-        <v>Valor atual</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C677" t="str">
-        <v>Valor atual</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Required: 0</v>
+        <v>Pass</v>
       </c>
       <c r="B678" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Aprovado</v>
       </c>
       <c r="C678" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Expected: {value}</v>
+        <v>Fail</v>
       </c>
       <c r="B679" t="str">
-        <v>Esperado: {value}</v>
+        <v>Reprovado</v>
       </c>
       <c r="C679" t="str">
-        <v>Esperado: {value}</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Invalid</v>
+        <v>View in context</v>
       </c>
       <c r="B680" t="str">
-        <v>Inválido</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C680" t="str">
-        <v>Inválido</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Validation detail</v>
       </c>
       <c r="B681" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C681" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Close</v>
+        <v>Triggered by</v>
       </c>
       <c r="B682" t="str">
-        <v>Fechar</v>
+        <v>Acionado por</v>
       </c>
       <c r="C682" t="str">
-        <v>Fechar</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Loading XML editor…</v>
+        <v>Field</v>
       </c>
       <c r="B683" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Campo</v>
       </c>
       <c r="C683" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Current value</v>
       </c>
       <c r="B684" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Valor atual</v>
       </c>
       <c r="C684" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Required: 0</v>
       </c>
       <c r="B685" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C685" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B686" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C686" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Invalid</v>
       </c>
       <c r="B687" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Inválido</v>
       </c>
       <c r="C687" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B688" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C688" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Close</v>
       </c>
       <c r="B689" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Fechar</v>
       </c>
       <c r="C689" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B690" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C690" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>indent</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B691" t="str">
-        <v>indentação</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C691" t="str">
-        <v>indentação</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>sort keys</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B692" t="str">
-        <v>ordenar chaves</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C692" t="str">
-        <v>ordenar chaves</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B693" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C693" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B694" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C694" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B695" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C695" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B696" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C696" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B697" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C697" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B698" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C698" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B699" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C699" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B693" t="str">
+      <c r="B700" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C693" t="str">
+      <c r="C700" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C693"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C700"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -6259,10 +6259,10 @@
         <v>Tone mapping</v>
       </c>
       <c r="B532" t="str">
-        <v>Tone mapping</v>
+        <v>Mapeamento de tons</v>
       </c>
       <c r="C532" t="str">
-        <v>Tone mapping</v>
+        <v>Mapeamento de tons</v>
       </c>
     </row>
     <row r="533">

--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C700"/>
+  <dimension ref="A1:C705"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -5519,2603 +5519,2658 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Decoding…</v>
+        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
       </c>
       <c r="B465" t="str">
-        <v>A descodificar…</v>
+        <v>Este ficheiro tem {size} MB; o separador HDR abre imagens até {max} MB.</v>
       </c>
       <c r="C465" t="str">
-        <v>Decodificando…</v>
+        <v>Este arquivo tem {size} MB; a aba HDR abre imagens de até {max} MB.</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Dynamic range</v>
+        <v>Could not apply the profile:</v>
       </c>
       <c r="B466" t="str">
-        <v>Gama dinâmica</v>
+        <v>Não foi possível aplicar o perfil:</v>
       </c>
       <c r="C466" t="str">
-        <v>Faixa dinâmica</v>
+        <v>Não foi possível aplicar o perfil:</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Could not draw the image:</v>
       </c>
       <c r="B467" t="str">
-        <v>Este navegador só oferece os dois extremos, não uma mistura.</v>
+        <v>Não foi possível desenhar a imagem:</v>
       </c>
       <c r="C467" t="str">
-        <v>Este navegador oferece apenas os dois extremos, não uma mistura.</v>
+        <v>Não foi possível desenhar a imagem:</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
       </c>
       <c r="B468" t="str">
-        <v>descodificado pelo próprio profiletool, portanto independente do navegador</v>
+        <v>(estes primários não definem um espaço de cor — ignorados, usa-se Rec. 709)</v>
       </c>
       <c r="C468" t="str">
-        <v>decodificado pelo próprio profiletool, portanto independente do navegador</v>
+        <v>(estas primárias não definem um espaço de cor — ignoradas, usa-se Rec. 709)</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>this browser decodes it</v>
+        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
       </c>
       <c r="B469" t="str">
-        <v>este navegador descodifica-o</v>
+        <v>o perfil de um JPEG XL está comprimido dentro do codestream, que o profiletool ainda não descomprime</v>
       </c>
       <c r="C469" t="str">
-        <v>este navegador o decodifica</v>
+        <v>o perfil de um JPEG XL fica comprimido dentro do codestream, que o profiletool ainda não descomprime</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>this browser does not decode it</v>
+        <v>Decoding…</v>
       </c>
       <c r="B470" t="str">
-        <v>este navegador não o descodifica</v>
+        <v>A descodificar…</v>
       </c>
       <c r="C470" t="str">
-        <v>este navegador não o decodifica</v>
+        <v>Decodificando…</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B471" t="str">
-        <v>mostrar HEIC requer o Safari ou outro navegador WebKit — o Chrome e o Firefox não descodificam HEIC em nenhuma plataforma, incluindo o macOS</v>
+        <v>Gama dinâmica</v>
       </c>
       <c r="C471" t="str">
-        <v>exibir HEIC requer o Safari ou outro navegador WebKit — Chrome e Firefox não decodificam HEIC em nenhuma plataforma, inclusive no macOS</v>
+        <v>Faixa dinâmica</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B472" t="str">
-        <v>mostrar JPEG XL requer o Safari; os outros navegadores ainda não o suportam</v>
+        <v>Este navegador só oferece os dois extremos, não uma mistura.</v>
       </c>
       <c r="C472" t="str">
-        <v>exibir JPEG XL requer o Safari; outros navegadores ainda não o suportam</v>
+        <v>Este navegador oferece apenas os dois extremos, não uma mistura.</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>deferred to a later release</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B473" t="str">
-        <v>adiado para uma versão posterior</v>
+        <v>descodificado pelo próprio profiletool, portanto independente do navegador</v>
       </c>
       <c r="C473" t="str">
-        <v>adiado para uma versão futura</v>
+        <v>decodificado pelo próprio profiletool, portanto independente do navegador</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B474" t="str">
-        <v>este ecrã não indica nenhum caminho HDR, pelo que o HDR é apresentado em SDR com tone mapping</v>
+        <v>este navegador descodifica-o</v>
       </c>
       <c r="C474" t="str">
-        <v>esta tela não informa nenhum caminho HDR, então o HDR é exibido em SDR com tone mapping</v>
+        <v>este navegador o decodifica</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B475" t="str">
-        <v>este navegador não oferece um canvas HDR (requer canvas float16 ou WebGPU)</v>
+        <v>este navegador não o descodifica</v>
       </c>
       <c r="C475" t="str">
-        <v>este navegador não oferece um canvas HDR (requer canvas float16 ou WebGPU)</v>
+        <v>este navegador não o decodifica</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B476" t="str">
-        <v>o Firefox não mostra imagens HDR nem lê gain maps; o conteúdo HDR é mostrado em SDR</v>
+        <v>mostrar HEIC requer o Safari ou outro navegador WebKit — o Chrome e o Firefox não descodificam HEIC em nenhuma plataforma, incluindo o macOS</v>
       </c>
       <c r="C476" t="str">
-        <v>o Firefox não exibe imagens HDR nem lê gain maps; o conteúdo HDR é exibido em SDR</v>
+        <v>exibir HEIC requer o Safari ou outro navegador WebKit — Chrome e Firefox não decodificam HEIC em nenhuma plataforma, inclusive no macOS</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B477" t="str">
-        <v>a inspeção só precisa de analisar o contentor, não de um codec</v>
+        <v>mostrar JPEG XL requer o Safari; os outros navegadores ainda não o suportam</v>
       </c>
       <c r="C477" t="str">
-        <v>a inspeção só precisa analisar o contêiner, não de um codec</v>
+        <v>exibir JPEG XL requer o Safari; outros navegadores ainda não o suportam</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B478" t="str">
-        <v>ecrã HDR e canvas HDR estão ambos disponíveis</v>
+        <v>adiado para uma versão posterior</v>
       </c>
       <c r="C478" t="str">
-        <v>tela HDR e canvas HDR estão disponíveis</v>
+        <v>adiado para uma versão futura</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>unknown format</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B479" t="str">
-        <v>formato desconhecido</v>
+        <v>este ecrã não indica nenhum caminho HDR, pelo que o HDR é apresentado em SDR com tone mapping</v>
       </c>
       <c r="C479" t="str">
-        <v>formato desconhecido</v>
+        <v>esta tela não informa nenhum caminho HDR, então o HDR é exibido em SDR com tone mapping</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>{browser} on {os}</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B480" t="str">
-        <v>{browser} em {os}</v>
+        <v>este navegador não oferece um canvas HDR (requer canvas float16 ou WebGPU)</v>
       </c>
       <c r="C480" t="str">
-        <v>{browser} no {os}</v>
+        <v>este navegador não oferece um canvas HDR (requer canvas float16 ou WebGPU)</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B481" t="str">
-        <v>{name} · ecrã HDR detetado</v>
+        <v>o Firefox não mostra imagens HDR nem lê gain maps; o conteúdo HDR é mostrado em SDR</v>
       </c>
       <c r="C481" t="str">
-        <v>{name} · tela HDR detectada</v>
+        <v>o Firefox não exibe imagens HDR nem lê gain maps; o conteúdo HDR é exibido em SDR</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>{name} · SDR display</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B482" t="str">
-        <v>{name} · ecrã SDR</v>
+        <v>a inspeção só precisa de analisar o contentor, não de um codec</v>
       </c>
       <c r="C482" t="str">
-        <v>{name} · tela SDR</v>
+        <v>a inspeção só precisa analisar o contêiner, não de um codec</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B483" t="str">
-        <v>O WebGPU aplicou o tone mapping «{mode}», pelo que a saída fica limitada a SDR</v>
+        <v>ecrã HDR e canvas HDR estão ambos disponíveis</v>
       </c>
       <c r="C483" t="str">
-        <v>O WebGPU aplicou o tone mapping “{mode}”, então a saída fica limitada a SDR</v>
+        <v>tela HDR e canvas HDR estão disponíveis</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>unknown format</v>
       </c>
       <c r="B484" t="str">
-        <v>Este navegador não indica o tone mapping WebGPU aplicado, pelo que a saída HDR não está confirmada</v>
+        <v>formato desconhecido</v>
       </c>
       <c r="C484" t="str">
-        <v>Este navegador não informa o tone mapping WebGPU aplicado, então a saída HDR não está confirmada</v>
+        <v>formato desconhecido</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Display peak</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B485" t="str">
-        <v>Pico do ecrã</v>
+        <v>{browser} em {os}</v>
       </c>
       <c r="C485" t="str">
-        <v>Pico da tela</v>
+        <v>{browser} no {os}</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B486" t="str">
-        <v>{r}× o branco SDR ({n} stops)</v>
+        <v>{name} · ecrã HDR detetado</v>
       </c>
       <c r="C486" t="str">
-        <v>{r}× o branco SDR ({n} stops)</v>
+        <v>{name} · tela HDR detectada</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>1× — SDR display</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B487" t="str">
-        <v>1× — ecrã SDR</v>
+        <v>{name} · ecrã SDR</v>
       </c>
       <c r="C487" t="str">
-        <v>1× — tela SDR</v>
+        <v>{name} · tela SDR</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>not known</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B488" t="str">
-        <v>desconhecido</v>
+        <v>O WebGPU aplicou o tone mapping «{mode}», pelo que a saída fica limitada a SDR</v>
       </c>
       <c r="C488" t="str">
-        <v>desconhecido</v>
+        <v>O WebGPU aplicou o tone mapping “{mode}”, então a saída fica limitada a SDR</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B489" t="str">
-        <v>Este ecrã não indica HDR, pelo que o navegador mostra a imagem em SDR em ambos os extremos.</v>
+        <v>Este navegador não indica o tone mapping WebGPU aplicado, pelo que a saída HDR não está confirmada</v>
       </c>
       <c r="C489" t="str">
-        <v>Esta tela não informa HDR, então o navegador exibe a imagem em SDR nos dois extremos.</v>
+        <v>Este navegador não informa o tone mapping WebGPU aplicado, então a saída HDR não está confirmada</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>Display peak</v>
       </c>
       <c r="B490" t="str">
-        <v>Este ecrã não indica HDR, pelo que tudo o que for mais brilhante do que o branco SDR é cortado. «Ajustar ao ecrã» mostra antes a apresentação com tone mapping.</v>
+        <v>Pico do ecrã</v>
       </c>
       <c r="C490" t="str">
-        <v>Esta tela não informa HDR, então tudo que for mais brilhante que o branco SDR é cortado. “Ajustar à tela” exibe a renderização com tone mapping.</v>
+        <v>Pico da tela</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B491" t="str">
-        <v>Esta imagem pede {img}× o branco SDR, mas este ecrã só chega a {disp}×, pelo que os valores mais brilhantes são cortados. «Ajustar ao ecrã» suaviza-os até ao pico do ecrã.</v>
+        <v>{r}× o branco SDR ({n} stops)</v>
       </c>
       <c r="C491" t="str">
-        <v>Esta imagem pede {img}× o branco SDR, mas esta tela só chega a {disp}×, então valores mais brilhantes são cortados. “Ajustar à tela” os suaviza até o pico da tela.</v>
+        <v>{r}× o branco SDR ({n} stops)</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Fit to display</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B492" t="str">
-        <v>Ajustar ao ecrã</v>
+        <v>1× — ecrã SDR</v>
       </c>
       <c r="C492" t="str">
-        <v>Ajustar à tela</v>
+        <v>1× — tela SDR</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Image details</v>
+        <v>not known</v>
       </c>
       <c r="B493" t="str">
-        <v>Detalhes da imagem</v>
+        <v>desconhecido</v>
       </c>
       <c r="C493" t="str">
-        <v>Detalhes da imagem</v>
+        <v>desconhecido</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B494" t="str">
-        <v>indisponível — o navegador apresenta esta imagem e não a consegue limitar a um pico definido</v>
+        <v>Este ecrã não indica HDR, pelo que o navegador mostra a imagem em SDR em ambos os extremos.</v>
       </c>
       <c r="C494" t="str">
-        <v>indisponível — o navegador renderiza esta imagem e não consegue limitá-la a um pico definido</v>
+        <v>Esta tela não informa HDR, então o navegador exibe a imagem em SDR nos dois extremos.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>not available — this output shows nothing above SDR white</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B495" t="str">
-        <v>indisponível — esta saída não mostra nada acima do branco SDR</v>
+        <v>Este ecrã não indica HDR, pelo que tudo o que for mais brilhante do que o branco SDR é cortado. «Ajustar ao ecrã» mostra antes a apresentação com tone mapping.</v>
       </c>
       <c r="C495" t="str">
-        <v>indisponível — esta saída não mostra nada acima do branco SDR</v>
+        <v>Esta tela não informa HDR, então tudo que for mais brilhante que o branco SDR é cortado. “Ajustar à tela” exibe a renderização com tone mapping.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>not available — this display’s peak is not known</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B496" t="str">
-        <v>indisponível — o pico deste ecrã não é conhecido</v>
+        <v>Esta imagem pede {img}× o branco SDR, mas este ecrã só chega a {disp}×, pelo que os valores mais brilhantes são cortados. «Ajustar ao ecrã» suaviza-os até ao pico do ecrã.</v>
       </c>
       <c r="C496" t="str">
-        <v>indisponível — o pico desta tela não é conhecido</v>
+        <v>Esta imagem pede {img}× o branco SDR, mas esta tela só chega a {disp}×, então valores mais brilhantes são cortados. “Ajustar à tela” os suaviza até o pico da tela.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Zoom in</v>
+        <v>Fit to display</v>
       </c>
       <c r="B497" t="str">
-        <v>Aproximar</v>
+        <v>Ajustar ao ecrã</v>
       </c>
       <c r="C497" t="str">
-        <v>Aproximar</v>
+        <v>Ajustar à tela</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Zoom out</v>
+        <v>Image details</v>
       </c>
       <c r="B498" t="str">
-        <v>Afastar</v>
+        <v>Detalhes da imagem</v>
       </c>
       <c r="C498" t="str">
-        <v>Afastar</v>
+        <v>Detalhes da imagem</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Fit image</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B499" t="str">
-        <v>Ajustar imagem</v>
+        <v>indisponível — o navegador apresenta esta imagem e não a consegue limitar a um pico definido</v>
       </c>
       <c r="C499" t="str">
-        <v>Ajustar imagem</v>
+        <v>indisponível — o navegador renderiza esta imagem e não consegue limitá-la a um pico definido</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Actual pixels (1:1)</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B500" t="str">
-        <v>Píxeis reais (1:1)</v>
+        <v>indisponível — esta saída não mostra nada acima do branco SDR</v>
       </c>
       <c r="C500" t="str">
-        <v>Pixels reais (1:1)</v>
+        <v>indisponível — esta saída não mostra nada acima do branco SDR</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B501" t="str">
-        <v>Arraste para deslocar · Ctrl+roda para zoom · duplo clique para repor</v>
+        <v>indisponível — o pico deste ecrã não é conhecido</v>
       </c>
       <c r="C501" t="str">
-        <v>Arraste para mover · Ctrl+roda para zoom · clique duplo para redefinir</v>
+        <v>indisponível — o pico desta tela não é conhecido</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Drag to resize the image area; double-click to restore the default size</v>
+        <v>Zoom in</v>
       </c>
       <c r="B502" t="str">
-        <v>Arraste para redimensionar a área da imagem; duplo clique para repor o tamanho predefinido</v>
+        <v>Aproximar</v>
       </c>
       <c r="C502" t="str">
-        <v>Arraste para redimensionar a área da imagem; clique duplo para voltar ao tamanho padrão</v>
+        <v>Aproximar</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Image view</v>
+        <v>Zoom out</v>
       </c>
       <c r="B503" t="str">
-        <v>Vista da imagem</v>
+        <v>Afastar</v>
       </c>
       <c r="C503" t="str">
-        <v>Visualização da imagem</v>
+        <v>Afastar</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Fit image</v>
       </c>
       <c r="B504" t="str">
-        <v>Limita o brilho ao pico que este ecrã indica. No Windows esse valor pode atrasar-se face às mudanças de brilho.</v>
+        <v>Ajustar imagem</v>
       </c>
       <c r="C504" t="str">
-        <v>Limita o brilho ao pico que esta tela informa. No Windows esse valor pode ficar atrasado em relação às mudanças de brilho.</v>
+        <v>Ajustar imagem</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>no limit</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B505" t="str">
-        <v>sem limite</v>
+        <v>Píxeis reais (1:1)</v>
       </c>
       <c r="C505" t="str">
-        <v>sem limite</v>
+        <v>Pixels reais (1:1)</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B506" t="str">
-        <v>limite {n} stops ({r}×)</v>
+        <v>Arraste para deslocar · Ctrl+roda para zoom · duplo clique para repor</v>
       </c>
       <c r="C506" t="str">
-        <v>limite {n} stops ({r}×)</v>
+        <v>Arraste para mover · Ctrl+roda para zoom · clique duplo para redefinir</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>SDR white</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B507" t="str">
-        <v>Branco SDR</v>
+        <v>Arraste para redimensionar a área da imagem; duplo clique para repor o tamanho predefinido</v>
       </c>
       <c r="C507" t="str">
-        <v>Branco SDR</v>
+        <v>Arraste para redimensionar a área da imagem; clique duplo para voltar ao tamanho padrão</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>Image view</v>
       </c>
       <c r="B508" t="str">
-        <v>Branco SDR simples, para comparação. Num ecrã HDR, as altas luzes HDR parecem mais brilhantes do que este.</v>
+        <v>Vista da imagem</v>
       </c>
       <c r="C508" t="str">
-        <v>Branco SDR simples, para comparação. Em uma tela HDR, os realces HDR parecem mais brilhantes que este.</v>
+        <v>Visualização da imagem</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>SDR white patch</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B509" t="str">
-        <v>Amostra de branco SDR</v>
+        <v>Limita o brilho ao pico que este ecrã indica. No Windows esse valor pode atrasar-se face às mudanças de brilho.</v>
       </c>
       <c r="C509" t="str">
-        <v>Amostra de branco SDR</v>
+        <v>Limita o brilho ao pico que esta tela informa. No Windows esse valor pode ficar atrasado em relação às mudanças de brilho.</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>no limit</v>
       </c>
       <c r="B510" t="str">
-        <v>Arraste para a mover; faça duplo clique para a repor junto à imagem.</v>
+        <v>sem limite</v>
       </c>
       <c r="C510" t="str">
-        <v>Arraste para movê-la; clique duas vezes para colocá-la de volta ao lado da imagem.</v>
+        <v>sem limite</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Assign profile</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B511" t="str">
-        <v>Atribuir perfil</v>
+        <v>limite {n} stops ({r}×)</v>
       </c>
       <c r="C511" t="str">
-        <v>Atribuir perfil</v>
+        <v>limite {n} stops ({r}×)</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>None — use what the file signals</v>
+        <v>SDR white</v>
       </c>
       <c r="B512" t="str">
-        <v>Nenhum — o que o ficheiro indica</v>
+        <v>Branco SDR</v>
       </c>
       <c r="C512" t="str">
-        <v>Nenhum — o que o arquivo indica</v>
+        <v>Branco SDR</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B513" t="str">
-        <v>Perfil incorporado ({n} B)</v>
+        <v>Branco SDR simples, para comparação. Num ecrã HDR, as altas luzes HDR parecem mais brilhantes do que este.</v>
       </c>
       <c r="C513" t="str">
-        <v>Perfil incorporado ({n} B)</v>
+        <v>Branco SDR simples, para comparação. Em uma tela HDR, os realces HDR parecem mais brilhantes que este.</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B514" t="str">
-        <v>Perfis HDR no pool</v>
+        <v>Amostra de branco SDR</v>
       </c>
       <c r="C514" t="str">
-        <v>Perfis HDR no pool</v>
+        <v>Amostra de branco SDR</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B515" t="str">
-        <v>Perfil</v>
+        <v>Arraste para a mover; faça duplo clique para a repor junto à imagem.</v>
       </c>
       <c r="C515" t="str">
-        <v>Perfil</v>
+        <v>Arraste para movê-la; clique duas vezes para colocá-la de volta ao lado da imagem.</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>embedded profile</v>
+        <v>Assign profile</v>
       </c>
       <c r="B516" t="str">
-        <v>perfil incorporado</v>
+        <v>Atribuir perfil</v>
       </c>
       <c r="C516" t="str">
-        <v>perfil incorporado</v>
+        <v>Atribuir perfil</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Colour engine path</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B517" t="str">
-        <v>Caminho do motor de cor</v>
+        <v>Nenhum — o que o ficheiro indica</v>
       </c>
       <c r="C517" t="str">
-        <v>Caminho do mecanismo de cor</v>
+        <v>Nenhum — o que o arquivo indica</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B518" t="str">
-        <v>Caminho HDR, curva de ganho aplicada</v>
+        <v>Perfil incorporado ({n} B)</v>
       </c>
       <c r="C518" t="str">
-        <v>Caminho HDR, curva de ganho aplicada</v>
+        <v>Perfil incorporado ({n} B)</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B519" t="str">
-        <v>Caminho HDR, sem curva de ganho</v>
+        <v>Perfis HDR no pool</v>
       </c>
       <c r="C519" t="str">
-        <v>Caminho HDR, sem curva de ganho</v>
+        <v>Perfis HDR no pool</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>Profile</v>
       </c>
       <c r="B520" t="str">
-        <v>AToB0 pré-calculado — não é o caminho HDR</v>
+        <v>Perfil</v>
       </c>
       <c r="C520" t="str">
-        <v>AToB0 pré-calculado — não é o caminho HDR</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Transfer</v>
+        <v>embedded profile</v>
       </c>
       <c r="B521" t="str">
-        <v>Transferência</v>
+        <v>perfil incorporado</v>
       </c>
       <c r="C521" t="str">
-        <v>Transferência</v>
+        <v>perfil incorporado</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>HDR reference white</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B522" t="str">
-        <v>Branco de referência HDR</v>
+        <v>Caminho do motor de cor</v>
       </c>
       <c r="C522" t="str">
-        <v>Branco de referência HDR</v>
+        <v>Caminho do mecanismo de cor</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Linear values</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B523" t="str">
-        <v>Valores lineares</v>
+        <v>Caminho HDR, curva de ganho aplicada</v>
       </c>
       <c r="C523" t="str">
-        <v>Valores lineares</v>
+        <v>Caminho HDR, curva de ganho aplicada</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>File 1.0 = HDR reference white</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B524" t="str">
-        <v>Ficheiro 1,0 = branco de referência HDR</v>
+        <v>Caminho HDR, sem curva de ganho</v>
       </c>
       <c r="C524" t="str">
-        <v>Arquivo 1,0 = branco de referência HDR</v>
+        <v>Caminho HDR, sem curva de ganho</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B525" t="str">
-        <v>Ficheiro 1,0 = 1 cd/m² (ICC.1 cláusula 8.10.2 a)</v>
+        <v>AToB0 pré-calculado — não é o caminho HDR</v>
       </c>
       <c r="C525" t="str">
-        <v>Arquivo 1,0 = 1 cd/m² (ICC.1 cláusula 8.10.2 a)</v>
+        <v>AToB0 pré-calculado — não é o caminho HDR</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
+        <v>Transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>Os ficheiros OpenEXR e Radiance HDR colocam por convenção o branco SDR em 1,0, enquanto uma transferência ICC linear lê 1,0 como 1 cd/m². Por predefinição, o ficheiro é escalado para que o seu 1,0 coincida com o branco de referência HDR do perfil.</v>
+        <v>Transferência</v>
       </c>
       <c r="C526" t="str">
-        <v>Arquivos OpenEXR e Radiance HDR colocam por convenção o branco SDR em 1,0, enquanto uma transferência ICC linear lê 1,0 como 1 cd/m². Por padrão, o arquivo é escalado para que seu 1,0 caia no branco de referência HDR do perfil.</v>
+        <v>Transferência</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Input scale</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B527" t="str">
-        <v>Escala de entrada</v>
+        <v>Branco de referência HDR</v>
       </c>
       <c r="C527" t="str">
-        <v>Escala de entrada</v>
+        <v>Branco de referência HDR</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>×{w} — file 1.0 = reference white</v>
+        <v>Linear values</v>
       </c>
       <c r="B528" t="str">
-        <v>×{w} — ficheiro 1,0 = branco de referência</v>
+        <v>Valores lineares</v>
       </c>
       <c r="C528" t="str">
-        <v>×{w} — arquivo 1,0 = branco de referência</v>
+        <v>Valores lineares</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>none — file 1.0 = 1 cd/m²</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B529" t="str">
-        <v>nenhuma — ficheiro 1,0 = 1 cd/m²</v>
+        <v>Ficheiro 1,0 = branco de referência HDR</v>
       </c>
       <c r="C529" t="str">
-        <v>nenhuma — arquivo 1,0 = 1 cd/m²</v>
+        <v>Arquivo 1,0 = branco de referência HDR</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Target headroom</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B530" t="str">
-        <v>Margem alvo</v>
+        <v>Ficheiro 1,0 = 1 cd/m² (ICC.1 cláusula 8.10.2 a)</v>
       </c>
       <c r="C530" t="str">
-        <v>Margem alvo</v>
+        <v>Arquivo 1,0 = 1 cd/m² (ICC.1 cláusula 8.10.2 a)</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B531" t="str">
-        <v>{r}× o branco de referência ({n} stops)</v>
+        <v>Os ficheiros OpenEXR e Radiance HDR colocam por convenção o branco SDR em 1,0, enquanto uma transferência ICC linear lê 1,0 como 1 cd/m². Por predefinição, o ficheiro é escalado para que o seu 1,0 coincida com o branco de referência HDR do perfil.</v>
       </c>
       <c r="C531" t="str">
-        <v>{r}× o branco de referência ({n} stops)</v>
+        <v>Arquivos OpenEXR e Radiance HDR colocam por convenção o branco SDR em 1,0, enquanto uma transferência ICC linear lê 1,0 como 1 cd/m². Por padrão, o arquivo é escalado para que seu 1,0 caia no branco de referência HDR do perfil.</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Tone mapping</v>
+        <v>Input scale</v>
       </c>
       <c r="B532" t="str">
-        <v>Mapeamento de tons</v>
+        <v>Escala de entrada</v>
       </c>
       <c r="C532" t="str">
-        <v>Mapeamento de tons</v>
+        <v>Escala de entrada</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B533" t="str">
-        <v>Auto (ordem da cláusula 8.10.3)</v>
+        <v>×{w} — ficheiro 1,0 = branco de referência</v>
       </c>
       <c r="C533" t="str">
-        <v>Auto (ordem da cláusula 8.10.3)</v>
+        <v>×{w} — arquivo 1,0 = branco de referência</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B534" t="str">
-        <v>Curva de ganho (HAGC)</v>
+        <v>nenhuma — ficheiro 1,0 = 1 cd/m²</v>
       </c>
       <c r="C534" t="str">
-        <v>Curva de ganho (HAGC)</v>
+        <v>nenhuma — arquivo 1,0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B535" t="str">
-        <v>Alternativa SDR pré-calculada (AToB0)</v>
+        <v>Margem alvo</v>
       </c>
       <c r="C535" t="str">
-        <v>Alternativa SDR pré-calculada (AToB0)</v>
+        <v>Margem alvo</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B536" t="str">
-        <v>Desligado — como um CMM anterior à emenda</v>
+        <v>{r}× o branco de referência ({n} stops)</v>
       </c>
       <c r="C536" t="str">
-        <v>Desligado — como um CMM anterior à emenda</v>
+        <v>{r}× o branco de referência ({n} stops)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Applying the profile…</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B537" t="str">
-        <v>A aplicar o perfil…</v>
+        <v>Mapeamento de tons</v>
       </c>
       <c r="C537" t="str">
-        <v>Aplicando o perfil…</v>
+        <v>Mapeamento de tons</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B538" t="str">
-        <v>O {format} contém luz linear, pelo que precisa de um perfil com transferência Linear (8).</v>
+        <v>Auto (ordem da cláusula 8.10.3)</v>
       </c>
       <c r="C538" t="str">
-        <v>O {format} contém luz linear, então precisa de um perfil com transferência Linear (8).</v>
+        <v>Auto (ordem da cláusula 8.10.3)</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B539" t="str">
-        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
+        <v>Curva de ganho (HAGC)</v>
       </c>
       <c r="C539" t="str">
-        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
+        <v>Curva de ganho (HAGC)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B540" t="str">
-        <v>Para interpretar os seus valores, atribua um perfil acima.</v>
+        <v>Alternativa SDR pré-calculada (AToB0)</v>
       </c>
       <c r="C540" t="str">
-        <v>Para interpretar seus valores, atribua um perfil acima.</v>
+        <v>Alternativa SDR pré-calculada (AToB0)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>HDR Profiles</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B541" t="str">
-        <v>Perfis HDR</v>
+        <v>Desligado — como um CMM anterior à emenda</v>
       </c>
       <c r="C541" t="str">
-        <v>Perfis HDR</v>
+        <v>Desligado — como um CMM anterior à emenda</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Linear transfer</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B542" t="str">
-        <v>Transferência linear</v>
+        <v>A aplicar o perfil…</v>
       </c>
       <c r="C542" t="str">
-        <v>Transferência linear</v>
+        <v>Aplicando o perfil…</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B543" t="str">
-        <v>Transferência não linear (PQ, HLG)</v>
+        <v>O {format} contém luz linear, pelo que precisa de um perfil com transferência Linear (8).</v>
       </c>
       <c r="C543" t="str">
-        <v>Transferência não linear (PQ, HLG)</v>
+        <v>O {format} contém luz linear, então precisa de um perfil com transferência Linear (8).</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B544" t="str">
-        <v>Perfis HDR — transferência linear</v>
+        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
       </c>
       <c r="C544" t="str">
-        <v>Perfis HDR — transferência linear</v>
+        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B545" t="str">
-        <v>Perfis HDR — transferência PQ / HLG</v>
+        <v>Para interpretar os seus valores, atribua um perfil acima.</v>
       </c>
       <c r="C545" t="str">
-        <v>Perfis HDR — transferência PQ / HLG</v>
+        <v>Para interpretar seus valores, atribua um perfil acima.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B546" t="str">
-        <v>O {format} contém luz linear, pelo que só podem ser atribuídos perfis HDR com transferência linear.</v>
+        <v>Perfis HDR</v>
       </c>
       <c r="C546" t="str">
-        <v>O {format} contém luz linear, então só podem ser atribuídos perfis HDR com transferência linear.</v>
+        <v>Perfis HDR</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B547" t="str">
-        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis lista-os em Perfis HDR › Transferência não linear.</v>
+        <v>Transferência linear</v>
       </c>
       <c r="C547" t="str">
-        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis os lista em Perfis HDR › Transferência não linear.</v>
+        <v>Transferência linear</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B548" t="str">
-        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
+        <v>Transferência não linear (PQ, HLG)</v>
       </c>
       <c r="C548" t="str">
-        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
+        <v>Transferência não linear (PQ, HLG)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B549" t="str">
-        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
+        <v>Perfis HDR — transferência linear</v>
       </c>
       <c r="C549" t="str">
-        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
+        <v>Perfis HDR — transferência linear</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Display headroom</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>Margem do ecrã</v>
+        <v>Perfis HDR — transferência PQ / HLG</v>
       </c>
       <c r="C550" t="str">
-        <v>Margem da tela</v>
+        <v>Perfis HDR — transferência PQ / HLG</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B551" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>O {format} contém luz linear, pelo que só podem ser atribuídos perfis HDR com transferência linear.</v>
       </c>
       <c r="C551" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>O {format} contém luz linear, então só podem ser atribuídos perfis HDR com transferência linear.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Baseline</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B552" t="str">
-        <v>Base</v>
+        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis lista-os em Perfis HDR › Transferência não linear.</v>
       </c>
       <c r="C552" t="str">
-        <v>Base</v>
+        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis os lista em Perfis HDR › Transferência não linear.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Preview through the colour engine</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>Pré-visualização através do motor de cor</v>
+        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
       </c>
       <c r="C553" t="str">
-        <v>Pré-visualização pelo mecanismo de cor</v>
+        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B554" t="str">
-        <v>Tal como criado (base {h} stops, sem ganho)</v>
+        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
       </c>
       <c r="C554" t="str">
-        <v>Como criado (base {h} stops, sem ganho)</v>
+        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>Display headroom</v>
       </c>
       <c r="B555" t="str">
-        <v>Mapeado para {h} stops</v>
+        <v>Margem do ecrã</v>
       </c>
       <c r="C555" t="str">
-        <v>Mapeado para {h} stops</v>
+        <v>Margem da tela</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>Os mesmos píxeis de teste (sinal {transfer} a subir da esquerda para a direita: cinzento, depois R, G, B, Y, C, M) através da transformação HDR do IccProfLib. Ambas as faixas estão limitadas a {r}× o branco de referência HDR, como um ecrã com {h} stops de margem as mostraria: onde a faixa de cima satura plana, a curva de ganho suaviza as altas luzes.</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
       <c r="C556" t="str">
-        <v>Os mesmos pixels de teste (sinal {transfer} subindo da esquerda para a direita: cinza, depois R, G, B, Y, C, M) pela transformação HDR do IccProfLib. As duas faixas são limitadas a {r}× o branco de referência HDR, como uma tela com {h} stops de margem as mostraria: onde a faixa de cima satura plana, a curva de ganho suaviza as altas luzes.</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>reference white</v>
+        <v>Baseline</v>
       </c>
       <c r="B557" t="str">
-        <v>branco de referência</v>
+        <v>Base</v>
       </c>
       <c r="C557" t="str">
-        <v>branco de referência</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>display peak</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B558" t="str">
-        <v>pico do ecrã</v>
+        <v>Pré-visualização através do motor de cor</v>
       </c>
       <c r="C558" t="str">
-        <v>pico da tela</v>
+        <v>Pré-visualização pelo mecanismo de cor</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B559" t="str">
-        <v>Pré-visualização indisponível: {why}</v>
+        <v>Tal como criado (base {h} stops, sem ganho)</v>
       </c>
       <c r="C559" t="str">
-        <v>Pré-visualização indisponível: {why}</v>
+        <v>Como criado (base {h} stops, sem ganho)</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B560" t="str">
-        <v>o motor de cor não seguiu o caminho HDR para este perfil</v>
+        <v>Mapeado para {h} stops</v>
       </c>
       <c r="C560" t="str">
-        <v>o mecanismo de cor não seguiu o caminho HDR para este perfil</v>
+        <v>Mapeado para {h} stops</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Gain across every headroom</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B561" t="str">
-        <v>Ganho em todas as margens</v>
+        <v>Os mesmos píxeis de teste (sinal {transfer} a subir da esquerda para a direita: cinzento, depois R, G, B, Y, C, M) através da transformação HDR do IccProfLib. Ambas as faixas estão limitadas a {r}× o branco de referência HDR, como um ecrã com {h} stops de margem as mostraria: onde a faixa de cima satura plana, a curva de ganho suaviza as altas luzes.</v>
       </c>
       <c r="C561" t="str">
-        <v>Ganho em todas as margens</v>
+        <v>Os mesmos pixels de teste (sinal {transfer} subindo da esquerda para a direita: cinza, depois R, G, B, Y, C, M) pela transformação HDR do IccProfLib. As duas faixas são limitadas a {r}× o branco de referência HDR, como uma tela com {h} stops de margem as mostraria: onde a faixa de cima satura plana, a curva de ganho suaviza as altas luzes.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>reference white</v>
       </c>
       <c r="B562" t="str">
-        <v>Ganho aplicado a uma entrada cinzenta em cada margem do ecrã: o azul comprime, o vermelho expande e o branco deixa-a igual. As linhas ponteadas marcam as curvas da etiqueta, a contínua a base e a âmbar o controlo; a diagonal tracejada é onde a entrada atinge o pico do ecrã. Clique para mover o controlo.</v>
+        <v>branco de referência</v>
       </c>
       <c r="C562" t="str">
-        <v>Ganho aplicado a uma entrada cinza em cada margem da tela: azul comprime, vermelho expande e branco deixa inalterado. As linhas pontilhadas marcam as curvas da tag, a contínua a base e a âmbar o controle; a diagonal tracejada é onde a entrada atinge o pico da tela. Clique para mover o controle.</v>
+        <v>branco de referência</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>display peak</v>
       </c>
       <c r="B563" t="str">
-        <v>Entrada (stops relativamente ao branco de referência HDR)</v>
+        <v>pico do ecrã</v>
       </c>
       <c r="C563" t="str">
-        <v>Entrada (stops em relação ao branco de referência HDR)</v>
+        <v>pico da tela</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B564" t="str">
-        <v>Margem do ecrã (stops)</v>
+        <v>Pré-visualização indisponível: {why}</v>
       </c>
       <c r="C564" t="str">
-        <v>Margem da tela (stops)</v>
+        <v>Pré-visualização indisponível: {why}</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Gain (stops)</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B565" t="str">
-        <v>Ganho (stops)</v>
+        <v>o motor de cor não seguiu o caminho HDR para este perfil</v>
       </c>
       <c r="C565" t="str">
-        <v>Ganho (stops)</v>
+        <v>o mecanismo de cor não seguiu o caminho HDR para este perfil</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B566" t="str">
-        <v>Curva na etiqueta</v>
+        <v>Ganho em todas as margens</v>
       </c>
       <c r="C566" t="str">
-        <v>Curva na tag</v>
+        <v>Ganho em todas as margens</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Baseline</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B567" t="str">
-        <v>Base</v>
+        <v>Ganho aplicado a uma entrada cinzenta em cada margem do ecrã: o azul comprime, o vermelho expande e o branco deixa-a igual. As linhas ponteadas marcam as curvas da etiqueta, a contínua a base e a âmbar o controlo; a diagonal tracejada é onde a entrada atinge o pico do ecrã. Clique para mover o controlo.</v>
       </c>
       <c r="C567" t="str">
-        <v>Base</v>
+        <v>Ganho aplicado a uma entrada cinza em cada margem da tela: azul comprime, vermelho expande e branco deixa inalterado. As linhas pontilhadas marcam as curvas da tag, a contínua a base e a âmbar o controle; a diagonal tracejada é onde a entrada atinge o pico da tela. Clique para mover o controle.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Slider</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B568" t="str">
-        <v>Controlo</v>
+        <v>Entrada (stops relativamente ao branco de referência HDR)</v>
       </c>
       <c r="C568" t="str">
-        <v>Controle</v>
+        <v>Entrada (stops em relação ao branco de referência HDR)</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Input = display peak</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B569" t="str">
-        <v>Entrada = pico do ecrã</v>
+        <v>Margem do ecrã (stops)</v>
       </c>
       <c r="C569" t="str">
-        <v>Entrada = pico da tela</v>
+        <v>Margem da tela (stops)</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B570" t="str">
-        <v>Curvas tonais de cinzento por margem</v>
+        <v>Ganho (stops)</v>
       </c>
       <c r="C570" t="str">
-        <v>Curvas tonais de cinza por margem</v>
+        <v>Ganho (stops)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B571" t="str">
-        <v>A curva tonal de cinzento em cada margem guardada na etiqueta, colorida de baixo (azul) para alto (vermelho), com a curva do controlo em âmbar. Ambos os eixos estão em stops, pelo que a diagonal significa sem alteração.</v>
+        <v>Curva na etiqueta</v>
       </c>
       <c r="C571" t="str">
-        <v>A curva tonal de cinza em cada margem armazenada na tag, colorida de baixo (azul) para alto (vermelho), com a curva do controle em âmbar. Os dois eixos estão em stops, então a diagonal significa sem alteração.</v>
+        <v>Curva na tag</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B572" t="str">
-        <v>Saída (stops relativamente ao branco de referência HDR)</v>
+        <v>Base</v>
       </c>
       <c r="C572" t="str">
-        <v>Saída (stops em relação ao branco de referência HDR)</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>{h} stops</v>
+        <v>Slider</v>
       </c>
       <c r="B573" t="str">
-        <v>{h} stops</v>
+        <v>Controlo</v>
       </c>
       <c r="C573" t="str">
-        <v>{h} stops</v>
+        <v>Controle</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B574" t="str">
-        <v>{h} stops (base)</v>
+        <v>Entrada = pico do ecrã</v>
       </c>
       <c r="C574" t="str">
-        <v>{h} stops (base)</v>
+        <v>Entrada = pico da tela</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B575" t="str">
-        <v>A {h} stops (controlo)</v>
+        <v>Curvas tonais de cinzento por margem</v>
       </c>
       <c r="C575" t="str">
-        <v>Em {h} stops (controle)</v>
+        <v>Curvas tonais de cinza por margem</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B576" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>A curva tonal de cinzento em cada margem guardada na etiqueta, colorida de baixo (azul) para alto (vermelho), com a curva do controlo em âmbar. Ambos os eixos estão em stops, pelo que a diagonal significa sem alteração.</v>
       </c>
       <c r="C576" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>A curva tonal de cinza em cada margem armazenada na tag, colorida de baixo (azul) para alto (vermelho), com a curva do controle em âmbar. Os dois eixos estão em stops, então a diagonal significa sem alteração.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B577" t="str">
-        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
+        <v>Saída (stops relativamente ao branco de referência HDR)</v>
       </c>
       <c r="C577" t="str">
-        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
+        <v>Saída (stops em relação ao branco de referência HDR)</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B578" t="str">
-        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
+        <v>{h} stops</v>
       </c>
       <c r="C578" t="str">
-        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
+        <v>{h} stops</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B579" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
+        <v>{h} stops (base)</v>
       </c>
       <c r="C579" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
+        <v>{h} stops (base)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B580" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
+        <v>A {h} stops (controlo)</v>
       </c>
       <c r="C580" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
+        <v>Em {h} stops (controle)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B581" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
       <c r="C581" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B582" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
       </c>
       <c r="C582" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B583" t="str">
-        <v>Curva a {h} stops</v>
+        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
       </c>
       <c r="C583" t="str">
-        <v>Curva a {h} stops</v>
+        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Applied at {h} stops</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B584" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
       </c>
       <c r="C584" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B585" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
       </c>
       <c r="C585" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B586" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
       </c>
       <c r="C586" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B587" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
       <c r="C587" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B588" t="str">
-        <v>Curva de tons dos cinzentos nesta margem</v>
+        <v>Curva a {h} stops</v>
       </c>
       <c r="C588" t="str">
-        <v>Curva de tons de cinza nesta margem</v>
+        <v>Curva a {h} stops</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B589" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Aplicado a {h} stops</v>
       </c>
       <c r="C589" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Aplicado a {h} stops</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B590" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
       <c r="C590" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>No change</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B591" t="str">
-        <v>Sem alteração</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
       <c r="C591" t="str">
-        <v>Sem alteração</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B592" t="str">
-        <v>Pico do ecrã a {h} stops</v>
+        <v>Ganho (stops log2)</v>
       </c>
       <c r="C592" t="str">
-        <v>Pico da tela a {h} stops</v>
+        <v>Ganho (stops log2)</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Output at {h} stops</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B593" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Curva de tons dos cinzentos nesta margem</v>
       </c>
       <c r="C593" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Curva de tons de cinza nesta margem</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B594" t="str">
-        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
       <c r="C594" t="str">
-        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Identify displays</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B595" t="str">
-        <v>Identificar ecrãs</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
       <c r="C595" t="str">
-        <v>Identificar telas</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>No change</v>
       </c>
       <c r="B596" t="str">
-        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Sem alteração</v>
       </c>
       <c r="C596" t="str">
-        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Sem alteração</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B597" t="str">
-        <v>A acompanhar em que monitor está esta janela.</v>
+        <v>Pico do ecrã a {h} stops</v>
       </c>
       <c r="C597" t="str">
-        <v>Acompanhando em qual monitor esta janela está.</v>
+        <v>Pico da tela a {h} stops</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B598" t="str">
-        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
+        <v>Saída a {h} stops</v>
       </c>
       <c r="C598" t="str">
-        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
+        <v>Saída a {h} stops</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B599" t="str">
-        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
+        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
       </c>
       <c r="C599" t="str">
-        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
+        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Could not identify displays.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B600" t="str">
-        <v>Não foi possível identificar os ecrãs.</v>
+        <v>Identificar ecrãs</v>
       </c>
       <c r="C600" t="str">
-        <v>Não foi possível identificar as telas.</v>
+        <v>Identificar telas</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Display events</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B601" t="str">
-        <v>Eventos de ecrã</v>
+        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
       <c r="C601" t="str">
-        <v>Eventos de tela</v>
+        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B602" t="str">
-        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
+        <v>A acompanhar em que monitor está esta janela.</v>
       </c>
       <c r="C602" t="str">
-        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
+        <v>Acompanhando em qual monitor esta janela está.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Colour primaries</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B603" t="str">
-        <v>Primárias de cor</v>
+        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
       </c>
       <c r="C603" t="str">
-        <v>Primárias de cor</v>
+        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Transfer characteristics</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B604" t="str">
-        <v>Características de transferência</v>
+        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
       </c>
       <c r="C604" t="str">
-        <v>Características de transferência</v>
+        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Matrix coefficients</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B605" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Não foi possível identificar os ecrãs.</v>
       </c>
       <c r="C605" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Não foi possível identificar as telas.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Video full-range flag</v>
+        <v>Display events</v>
       </c>
       <c r="B606" t="str">
-        <v>Sinalizador de gama completa de vídeo</v>
+        <v>Eventos de ecrã</v>
       </c>
       <c r="C606" t="str">
-        <v>Sinalizador de faixa completa de vídeo</v>
+        <v>Eventos de tela</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Full range</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B607" t="str">
-        <v>Gama completa</v>
+        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
       </c>
       <c r="C607" t="str">
-        <v>Faixa completa</v>
+        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Narrow range</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B608" t="str">
-        <v>Gama reduzida</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C608" t="str">
-        <v>Faixa reduzida</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B609" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C609" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B610" t="str">
-        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C610" t="str">
-        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B611" t="str">
-        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C611" t="str">
-        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>REPORT</v>
+        <v>Full range</v>
       </c>
       <c r="B612" t="str">
-        <v>RELATÓRIO</v>
+        <v>Gama completa</v>
       </c>
       <c r="C612" t="str">
-        <v>RELATÓRIO</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>FAIL</v>
+        <v>Narrow range</v>
       </c>
       <c r="B613" t="str">
-        <v>REPROVADO</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C613" t="str">
-        <v>REPROVADO</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>checks</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B614" t="str">
-        <v>verificações</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C614" t="str">
-        <v>verificações</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B615" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C615" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B616" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C616" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>ICC Profile Tool</v>
+        <v>REPORT</v>
       </c>
       <c r="B617" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C617" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Powered by {lib}</v>
+        <v>FAIL</v>
       </c>
       <c r="B618" t="str">
-        <v>Com {lib}</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C618" t="str">
-        <v>Com {lib}</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B619" t="str">
-        <v>Subscrever</v>
+        <v>verificações</v>
       </c>
       <c r="C619" t="str">
-        <v>Inscrever-se</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B620" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C620" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B621" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C621" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B622" t="str">
-        <v>Fechar</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C622" t="str">
-        <v>Fechar</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B623" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C623" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Email address</v>
+        <v>Subscribe</v>
       </c>
       <c r="B624" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Subscrever</v>
       </c>
       <c r="C624" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B625" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C625" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B626" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C626" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>(optional)</v>
+        <v>Close</v>
       </c>
       <c r="B627" t="str">
-        <v>(opcional)</v>
+        <v>Fechar</v>
       </c>
       <c r="C627" t="str">
-        <v>(opcional)</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B628" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C628" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Email address</v>
       </c>
       <c r="B629" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C629" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Cancel</v>
+        <v>you@example.com</v>
       </c>
       <c r="B630" t="str">
-        <v>Cancelar</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C630" t="str">
-        <v>Cancelar</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Subscribe</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B631" t="str">
-        <v>Subscrever</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C631" t="str">
-        <v>Inscrever-se</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>(optional)</v>
       </c>
       <c r="B632" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>(opcional)</v>
       </c>
       <c r="C632" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B633" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C633" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Close</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B634" t="str">
-        <v>Fechar</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C634" t="str">
-        <v>Fechar</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Privacy notice</v>
+        <v>Cancel</v>
       </c>
       <c r="B635" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Cancelar</v>
       </c>
       <c r="C635" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B636" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C636" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B637" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C637" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B638" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C638" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B639" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Fechar</v>
       </c>
       <c r="C639" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B640" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C640" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Error:</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B641" t="str">
-        <v>Erro:</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C641" t="str">
-        <v>Erro:</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Convert to XML</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B642" t="str">
-        <v>Converter para XML</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C642" t="str">
-        <v>Converter para XML</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Convert to JSON</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B643" t="str">
-        <v>Converter para JSON</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C643" t="str">
-        <v>Converter para JSON</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Convert to ICC</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B644" t="str">
-        <v>Converter para ICC</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C644" t="str">
-        <v>Converter para ICC</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Converting to XML…</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>A converter para XML…</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C645" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Converting to JSON…</v>
+        <v>Error:</v>
       </c>
       <c r="B646" t="str">
-        <v>A converter para JSON…</v>
+        <v>Erro:</v>
       </c>
       <c r="C646" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B647" t="str">
-        <v>A converter para ICC…</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C647" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B648" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C648" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B649" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C649" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Profile ID</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B650" t="str">
-        <v>ID do perfil</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C650" t="str">
-        <v>ID do perfil</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>No tags found.</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B651" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C651" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Tag Name</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B652" t="str">
-        <v>Nome da etiqueta</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C652" t="str">
-        <v>Nome da tag</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B653" t="str">
-        <v>ID</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C653" t="str">
-        <v>ID</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Offset</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B654" t="str">
-        <v>Deslocamento</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C654" t="str">
-        <v>Deslocamento</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Size</v>
+        <v>Profile ID</v>
       </c>
       <c r="B655" t="str">
-        <v>Tamanho</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C655" t="str">
-        <v>Tamanho</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Pad</v>
+        <v>No tags found.</v>
       </c>
       <c r="B656" t="str">
-        <v>Preenchimento</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C656" t="str">
-        <v>Preenchimento</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Bytes changed since load</v>
+        <v>Tag Name</v>
       </c>
       <c r="B657" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C657" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Type</v>
+        <v>ID</v>
       </c>
       <c r="B658" t="str">
-        <v>Tipo</v>
+        <v>ID</v>
       </c>
       <c r="C658" t="str">
-        <v>Tipo</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Array of {type}</v>
+        <v>Offset</v>
       </c>
       <c r="B659" t="str">
-        <v>Vetor de {type}</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C659" t="str">
-        <v>Array de {type}</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>(No content)</v>
+        <v>Size</v>
       </c>
       <c r="B660" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Tamanho</v>
       </c>
       <c r="C660" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>bytes</v>
+        <v>Pad</v>
       </c>
       <c r="B661" t="str">
-        <v>bytes</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C661" t="str">
-        <v>bytes</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Loading full description…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B662" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C662" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Could not load full description:</v>
+        <v>Type</v>
       </c>
       <c r="B663" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Tipo</v>
       </c>
       <c r="C663" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B664" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C664" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>(No content)</v>
       </c>
       <c r="B665" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C665" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No validation output</v>
+        <v>bytes</v>
       </c>
       <c r="B666" t="str">
-        <v>Sem saída de validação</v>
+        <v>bytes</v>
       </c>
       <c r="C666" t="str">
-        <v>Sem saída de validação</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Profile is valid</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B667" t="str">
-        <v>O perfil é válido</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C667" t="str">
-        <v>O perfil é válido</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B668" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C668" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Profile is non-compliant</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B669" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C669" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Critical validation error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B670" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C670" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Unknown validation status</v>
+        <v>No validation output</v>
       </c>
       <c r="B671" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C671" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B672" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C672" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B673" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C673" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Valid</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B674" t="str">
-        <v>Válido</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C674" t="str">
-        <v>Válido</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Warning</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B675" t="str">
-        <v>Aviso</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C675" t="str">
-        <v>Aviso</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Error</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B676" t="str">
-        <v>Erro</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C676" t="str">
-        <v>Erro</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Unknown</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B677" t="str">
-        <v>Desconhecido</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C677" t="str">
-        <v>Desconhecido</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Pass</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B678" t="str">
-        <v>Aprovado</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C678" t="str">
-        <v>Aprovado</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Fail</v>
+        <v>Valid</v>
       </c>
       <c r="B679" t="str">
-        <v>Reprovado</v>
+        <v>Válido</v>
       </c>
       <c r="C679" t="str">
-        <v>Reprovado</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>View in context</v>
+        <v>Warning</v>
       </c>
       <c r="B680" t="str">
-        <v>Ver no contexto</v>
+        <v>Aviso</v>
       </c>
       <c r="C680" t="str">
-        <v>Ver no contexto</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Validation detail</v>
+        <v>Error</v>
       </c>
       <c r="B681" t="str">
-        <v>Detalhe de validação</v>
+        <v>Erro</v>
       </c>
       <c r="C681" t="str">
-        <v>Detalhe de validação</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Triggered by</v>
+        <v>Unknown</v>
       </c>
       <c r="B682" t="str">
-        <v>Acionado por</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C682" t="str">
-        <v>Acionado por</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Field</v>
+        <v>Pass</v>
       </c>
       <c r="B683" t="str">
-        <v>Campo</v>
+        <v>Aprovado</v>
       </c>
       <c r="C683" t="str">
-        <v>Campo</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Current value</v>
+        <v>Fail</v>
       </c>
       <c r="B684" t="str">
-        <v>Valor atual</v>
+        <v>Reprovado</v>
       </c>
       <c r="C684" t="str">
-        <v>Valor atual</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Required: 0</v>
+        <v>View in context</v>
       </c>
       <c r="B685" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C685" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Expected: {value}</v>
+        <v>Validation detail</v>
       </c>
       <c r="B686" t="str">
-        <v>Esperado: {value}</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C686" t="str">
-        <v>Esperado: {value}</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Invalid</v>
+        <v>Triggered by</v>
       </c>
       <c r="B687" t="str">
-        <v>Inválido</v>
+        <v>Acionado por</v>
       </c>
       <c r="C687" t="str">
-        <v>Inválido</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Field</v>
       </c>
       <c r="B688" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Campo</v>
       </c>
       <c r="C688" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Close</v>
+        <v>Current value</v>
       </c>
       <c r="B689" t="str">
-        <v>Fechar</v>
+        <v>Valor atual</v>
       </c>
       <c r="C689" t="str">
-        <v>Fechar</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Loading XML editor…</v>
+        <v>Required: 0</v>
       </c>
       <c r="B690" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C690" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B691" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C691" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Invalid</v>
       </c>
       <c r="B692" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Inválido</v>
       </c>
       <c r="C692" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B693" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C693" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Close</v>
       </c>
       <c r="B694" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Fechar</v>
       </c>
       <c r="C694" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B695" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C695" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B696" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C696" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B697" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C697" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>indent</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B698" t="str">
-        <v>indentação</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C698" t="str">
-        <v>indentação</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>sort keys</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B699" t="str">
-        <v>ordenar chaves</v>
+        <v>● edições XML por guardar</v>
       </c>
       <c r="C699" t="str">
-        <v>ordenar chaves</v>
+        <v>● edições XML não salvas</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B700" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C700" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B701" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C701" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B702" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C702" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B703" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C703" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B704" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C704" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B700" t="str">
+      <c r="B705" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C700" t="str">
+      <c r="C705" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C700"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C705"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -5112,13 +5112,13 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (incluindo JPEG com gain map), PNG — e HEIC no Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (incluindo JPEG com gain map), PNG — e HEIC e JPEG XL no Safari.</v>
       </c>
       <c r="C428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (incluindo JPEG com gain map), PNG — e HEIC no Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (incluindo JPEG com gain map), PNG — e HEIC e JPEG XL no Safari.</v>
       </c>
     </row>
     <row r="429">

--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -1528,13 +1528,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B103" t="str">
-        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e transferido.</v>
+        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e aberto; nada é transferido até clicar em Guardar perfil ICC.</v>
       </c>
       <c r="C103" t="str">
-        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e baixado.</v>
+        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e aberto; nada é baixado até você clicar em Salvar perfil ICC.</v>
       </c>
     </row>
     <row r="104">

--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C705"/>
+  <dimension ref="A1:C706"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1495,6682 +1495,6693 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sort by name</v>
+        <v>Tap to select, then tap a tab to send.</v>
       </c>
       <c r="B100" t="str">
-        <v>Ordenar por nome</v>
+        <v>Toque para selecionar e depois toque num separador para enviar.</v>
       </c>
       <c r="C100" t="str">
-        <v>Ordenar por nome</v>
+        <v>Toque para selecionar e depois toque em uma aba para enviar.</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B101" t="str">
-        <v>A–Z</v>
+        <v>Ordenar por nome</v>
       </c>
       <c r="C101" t="str">
-        <v>A–Z</v>
+        <v>Ordenar por nome</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B102" t="str">
-        <v>Novo perfil a partir de .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="C102" t="str">
-        <v>Novo perfil a partir de .cube</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B103" t="str">
-        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e aberto; nada é transferido até clicar em Guardar perfil ICC.</v>
+        <v>Novo perfil a partir de .cube</v>
       </c>
       <c r="C103" t="str">
-        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e aberto; nada é baixado até você clicar em Salvar perfil ICC.</v>
+        <v>Novo perfil a partir de .cube</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B104" t="str">
-        <v>Escolher ficheiro .cube</v>
+        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e aberto; nada é transferido até clicar em Guardar perfil ICC.</v>
       </c>
       <c r="C104" t="str">
-        <v>Escolher arquivo .cube</v>
+        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e aberto; nada é baixado até você clicar em Salvar perfil ICC.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Escolher ficheiro .cube</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Escolher arquivo .cube</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B106" t="str">
         <v>ou largue-o aqui, ou cole abaixo</v>
       </c>
-      <c r="C105" t="str">
+      <c r="C106" t="str">
         <v>ou solte-o aqui, ou cole abaixo</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str" xml:space="preserve">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B106" t="str" xml:space="preserve">
+      <c r="B107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="C106" t="str" xml:space="preserve">
+      <c r="C107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B107" t="str">
-        <v>Cancelar</v>
-      </c>
-      <c r="C107" t="str">
-        <v>Cancelar</v>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B108" t="str">
-        <v>Criar DeviceLink</v>
+        <v>Cancelar</v>
       </c>
       <c r="C108" t="str">
-        <v>Criar DeviceLink</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B109" t="str">
-        <v>A criar…</v>
+        <v>Criar DeviceLink</v>
       </c>
       <c r="C109" t="str">
-        <v>Criando…</v>
+        <v>Criar DeviceLink</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B110" t="str">
-        <v>Não foi possível ler esse ficheiro.</v>
+        <v>A criar…</v>
       </c>
       <c r="C110" t="str">
-        <v>Não foi possível ler esse arquivo.</v>
+        <v>Criando…</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B111" t="str">
-        <v>Perfil</v>
+        <v>Não foi possível ler esse ficheiro.</v>
       </c>
       <c r="C111" t="str">
-        <v>Perfil</v>
+        <v>Não foi possível ler esse arquivo.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B112" t="str">
-        <v>Comparar</v>
+        <v>Perfil</v>
       </c>
       <c r="C112" t="str">
-        <v>Comparar</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B113" t="str">
-        <v>Ligar</v>
+        <v>Comparar</v>
       </c>
       <c r="C113" t="str">
-        <v>Vincular</v>
+        <v>Comparar</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B114" t="str">
-        <v>Espectral</v>
+        <v>Ligar</v>
       </c>
       <c r="C114" t="str">
-        <v>Espectral</v>
+        <v>Vincular</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B115" t="str">
-        <v>Arraste perfis do conjunto para este separador</v>
+        <v>Espectral</v>
       </c>
       <c r="C115" t="str">
-        <v>Arraste perfis do conjunto para esta aba</v>
+        <v>Espectral</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B116" t="str">
-        <v>Remover</v>
+        <v>Arraste perfis do conjunto para este separador</v>
       </c>
       <c r="C116" t="str">
-        <v>Remover</v>
+        <v>Arraste perfis do conjunto para esta aba</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B117" t="str">
-        <v>Nenhum perfil selecionado</v>
+        <v>Remover</v>
       </c>
       <c r="C117" t="str">
-        <v>Nenhum perfil selecionado</v>
+        <v>Remover</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B118" t="str">
-        <v>Arraste um perfil do conjunto para o separador Perfil para o inspecionar.</v>
+        <v>Nenhum perfil selecionado</v>
       </c>
       <c r="C118" t="str">
-        <v>Arraste um perfil do conjunto para a aba Perfil para inspecioná-lo.</v>
+        <v>Nenhum perfil selecionado</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B119" t="str">
-        <v>Ainda nada para comparar</v>
+        <v>Arraste um perfil do conjunto para o separador Perfil para o inspecionar.</v>
       </c>
       <c r="C119" t="str">
-        <v>Ainda nada para comparar</v>
+        <v>Arraste um perfil do conjunto para a aba Perfil para inspecioná-lo.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B120" t="str">
-        <v>Arraste um ou mais perfis para o separador Comparar.</v>
+        <v>Ainda nada para comparar</v>
       </c>
       <c r="C120" t="str">
-        <v>Arraste um ou mais perfis para a aba Comparar.</v>
+        <v>Ainda nada para comparar</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B121" t="str">
-        <v>Comparação de gamut</v>
+        <v>Arraste um ou mais perfis para o separador Comparar.</v>
       </c>
       <c r="C121" t="str">
-        <v>Comparação de gamut</v>
+        <v>Arraste um ou mais perfis para a aba Comparar.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B122" t="str">
-        <v>As vistas de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
+        <v>Comparação de gamut</v>
       </c>
       <c r="C122" t="str">
-        <v>As visualizações de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
+        <v>Comparação de gamut</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B123" t="str">
-        <v>Intenção de renderização</v>
+        <v>As vistas de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
       </c>
       <c r="C123" t="str">
-        <v>Intenção de renderização</v>
+        <v>As visualizações de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B124" t="str">
-        <v>Invólucro</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C124" t="str">
-        <v>Invólucro</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B125" t="str">
-        <v>Malha de arame</v>
+        <v>Invólucro</v>
       </c>
       <c r="C125" t="str">
-        <v>Malha de arame</v>
+        <v>Invólucro</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B126" t="str">
-        <v>Números dos eixos</v>
+        <v>Malha de arame</v>
       </c>
       <c r="C126" t="str">
-        <v>Números dos eixos</v>
+        <v>Malha de arame</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B127" t="str">
-        <v>Opacidade</v>
+        <v>Números dos eixos</v>
       </c>
       <c r="C127" t="str">
-        <v>Opacidade</v>
+        <v>Números dos eixos</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B128" t="str">
-        <v>Cor</v>
+        <v>Opacidade</v>
       </c>
       <c r="C128" t="str">
-        <v>Cor</v>
+        <v>Opacidade</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B129" t="str">
-        <v>Sólido</v>
+        <v>Cor</v>
       </c>
       <c r="C129" t="str">
-        <v>Sólido</v>
+        <v>Cor</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B130" t="str">
-        <v>Por valor</v>
+        <v>Sólido</v>
       </c>
       <c r="C130" t="str">
-        <v>Por valor</v>
+        <v>Sólido</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B131" t="str">
-        <v>Por matiz</v>
+        <v>Por valor</v>
       </c>
       <c r="C131" t="str">
-        <v>Por matiz</v>
+        <v>Por valor</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B132" t="str">
-        <v>Rotação</v>
+        <v>Por matiz</v>
       </c>
       <c r="C132" t="str">
-        <v>Rotação</v>
+        <v>Por matiz</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B133" t="str">
-        <v>Prato giratório</v>
+        <v>Rotação</v>
       </c>
       <c r="C133" t="str">
-        <v>Prato giratório</v>
+        <v>Rotação</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B134" t="str">
-        <v>Órbita</v>
+        <v>Prato giratório</v>
       </c>
       <c r="C134" t="str">
-        <v>Órbita</v>
+        <v>Prato giratório</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B135" t="str">
-        <v>Velocidade de arrasto</v>
+        <v>Órbita</v>
       </c>
       <c r="C135" t="str">
-        <v>Velocidade de arrasto</v>
+        <v>Órbita</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B136" t="str">
-        <v>Rolamento</v>
+        <v>Velocidade de arrasto</v>
       </c>
       <c r="C136" t="str">
-        <v>Rolagem</v>
+        <v>Velocidade de arrasto</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B137" t="str">
-        <v>Velocidade de rolamento</v>
+        <v>Rolamento</v>
       </c>
       <c r="C137" t="str">
-        <v>Velocidade de rolagem</v>
+        <v>Rolagem</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B138" t="str">
-        <v>A construir o gamut…</v>
+        <v>Velocidade de rolamento</v>
       </c>
       <c r="C138" t="str">
-        <v>Construindo o gamut…</v>
+        <v>Velocidade de rolagem</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B139" t="str">
-        <v>sem gamut</v>
+        <v>A construir o gamut…</v>
       </c>
       <c r="C139" t="str">
-        <v>sem gamut</v>
+        <v>Construindo o gamut…</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B140" t="str">
-        <v>Mostrar / ocultar</v>
+        <v>sem gamut</v>
       </c>
       <c r="C140" t="str">
-        <v>Mostrar / ocultar</v>
+        <v>sem gamut</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B141" t="str">
-        <v>Invólucro de gamut 3D</v>
+        <v>Mostrar / ocultar</v>
       </c>
       <c r="C141" t="str">
-        <v>Invólucro de gamut 3D</v>
+        <v>Mostrar / ocultar</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B142" t="str">
-        <v>Corte de gamut 2D</v>
+        <v>Invólucro de gamut 3D</v>
       </c>
       <c r="C142" t="str">
-        <v>Corte de gamut 2D</v>
+        <v>Invólucro de gamut 3D</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B143" t="str">
-        <v>Plano</v>
+        <v>Corte de gamut 2D</v>
       </c>
       <c r="C143" t="str">
-        <v>Plano</v>
+        <v>Corte de gamut 2D</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B144" t="str">
-        <v>L*</v>
+        <v>Plano</v>
       </c>
       <c r="C144" t="str">
-        <v>L*</v>
+        <v>Plano</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="C145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="C146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B147" t="str">
-        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
+        <v>b*</v>
       </c>
       <c r="C147" t="str">
-        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B148" t="str">
-        <v>Ligação</v>
+        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
       </c>
       <c r="C148" t="str">
-        <v>Vínculo</v>
+        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B149" t="str">
-        <v>A produção de DeviceLink e as transformações multiperfil chegarão numa fase posterior.</v>
+        <v>Ligação</v>
       </c>
       <c r="C149" t="str">
-        <v>A produção de DeviceLink e as transformações multiperfil chegarão em uma fase posterior.</v>
+        <v>Vínculo</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B150" t="str">
-        <v>Mais criadores de ligações (DeviceLink, …) chegarão aqui.</v>
+        <v>A produção de DeviceLink e as transformações multiperfil chegarão numa fase posterior.</v>
       </c>
       <c r="C150" t="str">
-        <v>Mais criadores de vínculos (DeviceLink, …) chegarão aqui.</v>
+        <v>A produção de DeviceLink e as transformações multiperfil chegarão em uma fase posterior.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B151" t="str">
-        <v>Criador de ecrã V4</v>
+        <v>Mais criadores de ligações (DeviceLink, …) chegarão aqui.</v>
       </c>
       <c r="C151" t="str">
-        <v>Criador de tela V4</v>
+        <v>Mais criadores de vínculos (DeviceLink, …) chegarão aqui.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B152" t="str">
-        <v>Arraste para aqui um perfil de ecrã RGB V5 e um perfil de observador V5 para criar um perfil de ecrã V4.</v>
+        <v>Criador de ecrã V4</v>
       </c>
       <c r="C152" t="str">
-        <v>Arraste para cá um perfil de tela RGB V5 e um perfil de observador V5 para criar um perfil de tela V4.</v>
+        <v>Criador de tela V4</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B153" t="str">
-        <v>Ecrã RGB V5</v>
+        <v>Arraste para aqui um perfil de ecrã RGB V5 e um perfil de observador V5 para criar um perfil de ecrã V4.</v>
       </c>
       <c r="C153" t="str">
-        <v>Tela RGB V5</v>
+        <v>Arraste para cá um perfil de tela RGB V5 e um perfil de observador V5 para criar um perfil de tela V4.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B154" t="str">
-        <v>largue um perfil de ecrã</v>
+        <v>Ecrã RGB V5</v>
       </c>
       <c r="C154" t="str">
-        <v>solte um perfil de tela</v>
+        <v>Tela RGB V5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B155" t="str">
-        <v>Observador V5 (PCC)</v>
+        <v>largue um perfil de ecrã</v>
       </c>
       <c r="C155" t="str">
-        <v>Observador V5 (PCC)</v>
+        <v>solte um perfil de tela</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B156" t="str">
-        <v>largue um perfil de observador</v>
+        <v>Observador V5 (PCC)</v>
       </c>
       <c r="C156" t="str">
-        <v>solte um perfil de observador</v>
+        <v>Observador V5 (PCC)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B157" t="str">
-        <v>Foi ignorado um perfil que não é um ecrã RGB V5 nem um observador.</v>
+        <v>largue um perfil de observador</v>
       </c>
       <c r="C157" t="str">
-        <v>Um perfil que não é uma tela RGB V5 nem um observador foi ignorado.</v>
+        <v>solte um perfil de observador</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B158" t="str">
-        <v>Criar perfil de ecrã V4</v>
+        <v>Foi ignorado um perfil que não é um ecrã RGB V5 nem um observador.</v>
       </c>
       <c r="C158" t="str">
-        <v>Criar perfil de tela V4</v>
+        <v>Um perfil que não é uma tela RGB V5 nem um observador foi ignorado.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B159" t="str">
-        <v>Nome do perfil</v>
+        <v>Criar perfil de ecrã V4</v>
       </c>
       <c r="C159" t="str">
-        <v>Nome do perfil</v>
+        <v>Criar perfil de tela V4</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B160" t="str">
-        <v>Criar</v>
+        <v>Nome do perfil</v>
       </c>
       <c r="C160" t="str">
-        <v>Criar</v>
+        <v>Nome do perfil</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B161" t="str">
-        <v>A criar…</v>
+        <v>Criar</v>
       </c>
       <c r="C161" t="str">
-        <v>Criando…</v>
+        <v>Criar</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B162" t="str">
-        <v>«{name}» criado — adicionado ao conjunto e a este separador.</v>
+        <v>A criar…</v>
       </c>
       <c r="C162" t="str">
-        <v>«{name}» criado — adicionado ao conjunto e a esta aba.</v>
+        <v>Criando…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B163" t="str">
-        <v>Fluxo de ligação</v>
+        <v>«{name}» criado — adicionado ao conjunto e a este separador.</v>
       </c>
       <c r="C163" t="str">
-        <v>Fluxo de vinculação</v>
+        <v>«{name}» criado — adicionado ao conjunto e a esta aba.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B164" t="str">
-        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
+        <v>Fluxo de ligação</v>
       </c>
       <c r="C164" t="str">
-        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
+        <v>Fluxo de vinculação</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B165" t="str">
-        <v>Concluído</v>
+        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
       </c>
       <c r="C165" t="str">
-        <v>Concluído</v>
+        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B166" t="str">
-        <v>Largue uma imagem para transformar (TIFF/PNG/JPEG)</v>
+        <v>Concluído</v>
       </c>
       <c r="C166" t="str">
-        <v>Solte uma imagem para transformar (TIFF/PNG/JPEG)</v>
+        <v>Concluído</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B167" t="str">
-        <v>A verificar imagem…</v>
+        <v>Largue uma imagem para transformar (TIFF/PNG/JPEG)</v>
       </c>
       <c r="C167" t="str">
-        <v>Verificando imagem…</v>
+        <v>Solte uma imagem para transformar (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B168" t="str">
-        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
+        <v>A verificar imagem…</v>
       </c>
       <c r="C168" t="str">
-        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
+        <v>Verificando imagem…</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B169" t="str">
-        <v>Imagem demasiado grande ({mp} MP; limite {max} MP).</v>
+        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
       </c>
       <c r="C169" t="str">
-        <v>Imagem grande demais ({mp} MP; limite {max} MP).</v>
+        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B170" t="str">
-        <v>Transformar imagem</v>
+        <v>Imagem demasiado grande ({mp} MP; limite {max} MP).</v>
       </c>
       <c r="C170" t="str">
-        <v>Transformar imagem</v>
+        <v>Imagem grande demais ({mp} MP; limite {max} MP).</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B171" t="str">
-        <v>A transformar…</v>
+        <v>Transformar imagem</v>
       </c>
       <c r="C171" t="str">
-        <v>Transformando…</v>
+        <v>Transformar imagem</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B172" t="str">
-        <v>Largue perfis para iniciar a cadeia</v>
+        <v>A transformar…</v>
       </c>
       <c r="C172" t="str">
-        <v>Solte perfis para iniciar a cadeia</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B173" t="str">
-        <v>removido</v>
+        <v>Largue perfis para iniciar a cadeia</v>
       </c>
       <c r="C173" t="str">
-        <v>removido</v>
+        <v>Solte perfis para iniciar a cadeia</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B174" t="str">
-        <v>Mover antes</v>
+        <v>removido</v>
       </c>
       <c r="C174" t="str">
-        <v>Mover antes</v>
+        <v>removido</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B175" t="str">
-        <v>Mover depois</v>
+        <v>Mover antes</v>
       </c>
       <c r="C175" t="str">
-        <v>Mover depois</v>
+        <v>Mover antes</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B176" t="str">
-        <v>Mover para cima</v>
+        <v>Mover depois</v>
       </c>
       <c r="C176" t="str">
-        <v>Mover para cima</v>
+        <v>Mover depois</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B177" t="str">
-        <v>Mover para baixo</v>
+        <v>Mover para cima</v>
       </c>
       <c r="C177" t="str">
-        <v>Mover para baixo</v>
+        <v>Mover para cima</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B178" t="str">
-        <v>Intenção de renderização (todas)</v>
+        <v>Mover para baixo</v>
       </c>
       <c r="C178" t="str">
-        <v>Intenção de renderização (todas)</v>
+        <v>Mover para baixo</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B179" t="str">
-        <v>Intenção de renderização para esta transformação</v>
+        <v>Intenção de renderização (todas)</v>
       </c>
       <c r="C179" t="str">
-        <v>Intenção de renderização para esta transformação</v>
+        <v>Intenção de renderização (todas)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B180" t="str">
-        <v>As transformações usam intenções de renderização diferentes</v>
+        <v>Intenção de renderização para esta transformação</v>
       </c>
       <c r="C180" t="str">
-        <v>As transformações usam intenções de renderização diferentes</v>
+        <v>Intenção de renderização para esta transformação</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B181" t="str">
-        <v>Inverter direção da cadeia (inverte a transformação inicial e propaga-se por toda a cadeia)</v>
+        <v>As transformações usam intenções de renderização diferentes</v>
       </c>
       <c r="C181" t="str">
-        <v>Inverter direção da cadeia (inverte a transformação inicial e se propaga por toda a cadeia)</v>
+        <v>As transformações usam intenções de renderização diferentes</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B182" t="str">
-        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
+        <v>Inverter direção da cadeia (inverte a transformação inicial e propaga-se por toda a cadeia)</v>
       </c>
       <c r="C182" t="str">
-        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
+        <v>Inverter direção da cadeia (inverte a transformação inicial e se propaga por toda a cadeia)</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B183" t="str">
-        <v>Cadeia</v>
+        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
       </c>
       <c r="C183" t="str">
-        <v>Cadeia</v>
+        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B184" t="str">
-        <v>Não foi possível analisar a cadeia.</v>
+        <v>Cadeia</v>
       </c>
       <c r="C184" t="str">
-        <v>Não foi possível analisar a cadeia.</v>
+        <v>Cadeia</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B185" t="str">
-        <v>A verificar cadeia…</v>
+        <v>Não foi possível analisar a cadeia.</v>
       </c>
       <c r="C185" t="str">
-        <v>Verificando cadeia…</v>
+        <v>Não foi possível analisar a cadeia.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B186" t="str">
-        <v>A cadeia não liga ({detail}).</v>
+        <v>A verificar cadeia…</v>
       </c>
       <c r="C186" t="str">
-        <v>A cadeia não conecta ({detail}).</v>
+        <v>Verificando cadeia…</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>O perfil {n} não liga à etapa anterior ({detail}).</v>
+        <v>A cadeia não liga ({detail}).</v>
       </c>
       <c r="C187" t="str">
-        <v>O perfil {n} não conecta com a etapa anterior ({detail}).</v>
+        <v>A cadeia não conecta ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B188" t="str">
-        <v>Corrija a cadeia antes de processar imagens</v>
+        <v>O perfil {n} não liga à etapa anterior ({detail}).</v>
       </c>
       <c r="C188" t="str">
-        <v>Corrija a cadeia antes de processar imagens</v>
+        <v>O perfil {n} não conecta com a etapa anterior ({detail}).</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B189" t="str">
-        <v>Limpar</v>
+        <v>Corrija a cadeia antes de processar imagens</v>
       </c>
       <c r="C189" t="str">
-        <v>Limpar</v>
+        <v>Corrija a cadeia antes de processar imagens</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B190" t="str">
-        <v>Criar DeviceLink</v>
+        <v>Limpar</v>
       </c>
       <c r="C190" t="str">
-        <v>Criar DeviceLink</v>
+        <v>Limpar</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B191" t="str">
-        <v>Nome do DeviceLink</v>
+        <v>Criar DeviceLink</v>
       </c>
       <c r="C191" t="str">
-        <v>Nome do DeviceLink</v>
+        <v>Criar DeviceLink</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B192" t="str">
-        <v>A criar…</v>
+        <v>Nome do DeviceLink</v>
       </c>
       <c r="C192" t="str">
-        <v>Criando…</v>
+        <v>Nome do DeviceLink</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B193" t="str">
-        <v>Criado “{name}” — adicionado ao conjunto e a este separador.</v>
+        <v>A criar…</v>
       </c>
       <c r="C193" t="str">
-        <v>Criado “{name}” — adicionado ao conjunto e a esta aba.</v>
+        <v>Criando…</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B194" t="str">
-        <v>Largue imagens {src} para converter para {dst} — os resultados são descarregados, nada é armazenado.</v>
+        <v>Criado “{name}” — adicionado ao conjunto e a este separador.</v>
       </c>
       <c r="C194" t="str">
-        <v>Solte imagens {src} para converter para {dst} — os resultados são baixados, nada é armazenado.</v>
+        <v>Criado “{name}” — adicionado ao conjunto e a esta aba.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B195" t="str">
-        <v>Crie uma cadeia para processar imagens</v>
+        <v>Largue imagens {src} para converter para {dst} — os resultados são descarregados, nada é armazenado.</v>
       </c>
       <c r="C195" t="str">
-        <v>Crie uma cadeia para processar imagens</v>
+        <v>Solte imagens {src} para converter para {dst} — os resultados são baixados, nada é armazenado.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B196" t="str">
-        <v>Esta cadeia não começa nem termina num espaço de cor de imagem</v>
+        <v>Crie uma cadeia para processar imagens</v>
       </c>
       <c r="C196" t="str">
-        <v>Esta cadeia não começa nem termina em um espaço de cor de imagem</v>
+        <v>Crie uma cadeia para processar imagens</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B197" t="str">
-        <v>Imagem transformada guardada.</v>
+        <v>Esta cadeia não começa nem termina num espaço de cor de imagem</v>
       </c>
       <c r="C197" t="str">
-        <v>Imagem transformada salva.</v>
+        <v>Esta cadeia não começa nem termina em um espaço de cor de imagem</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B198" t="str">
-        <v>Largue um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
+        <v>Imagem transformada guardada.</v>
       </c>
       <c r="C198" t="str">
-        <v>Solte um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
+        <v>Imagem transformada salva.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B199" t="str">
-        <v>Não foi possível ler esse ficheiro.</v>
+        <v>Largue um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="C199" t="str">
-        <v>Não foi possível ler esse arquivo.</v>
+        <v>Solte um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B200" t="str">
-        <v>Ficheiro de dados demasiado grande.</v>
+        <v>Não foi possível ler esse ficheiro.</v>
       </c>
       <c r="C200" t="str">
-        <v>Arquivo de dados grande demais.</v>
+        <v>Não foi possível ler esse arquivo.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B201" t="str">
-        <v>Transformar dados</v>
+        <v>Ficheiro de dados demasiado grande.</v>
       </c>
       <c r="C201" t="str">
-        <v>Transformar dados</v>
+        <v>Arquivo de dados grande demais.</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B202" t="str">
-        <v>A transformar…</v>
+        <v>Transformar dados</v>
       </c>
       <c r="C202" t="str">
-        <v>Transformando…</v>
+        <v>Transformar dados</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B203" t="str">
-        <v>Preferir</v>
+        <v>A transformar…</v>
       </c>
       <c r="C203" t="str">
-        <v>Preferir</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B204" t="str">
-        <v>Observador</v>
+        <v>Preferir</v>
       </c>
       <c r="C204" t="str">
-        <v>Observador</v>
+        <v>Preferir</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B205" t="str">
-        <v>Iluminante</v>
+        <v>Observador</v>
       </c>
       <c r="C205" t="str">
-        <v>Iluminante</v>
+        <v>Observador</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B206" t="str">
-        <v>Condição</v>
+        <v>Iluminante</v>
       </c>
       <c r="C206" t="str">
-        <v>Condição</v>
+        <v>Iluminante</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B207" t="str">
-        <v>Filtrar {n} duplicado(s)</v>
+        <v>Condição</v>
       </c>
       <c r="C207" t="str">
-        <v>Filtrar {n} duplicado(s)</v>
+        <v>Condição</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B208" t="str">
-        <v>mediana</v>
+        <v>Filtrar {n} duplicado(s)</v>
       </c>
       <c r="C208" t="str">
-        <v>mediana</v>
+        <v>Filtrar {n} duplicado(s)</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B209" t="str">
-        <v>média</v>
+        <v>mediana</v>
       </c>
       <c r="C209" t="str">
-        <v>média</v>
+        <v>mediana</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B210" t="str">
-        <v>patches</v>
+        <v>média</v>
       </c>
       <c r="C210" t="str">
-        <v>patches</v>
+        <v>média</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B211" t="str">
-        <v>{n} duplicados</v>
+        <v>patches</v>
       </c>
       <c r="C211" t="str">
-        <v>{n} duplicados</v>
+        <v>patches</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B212" t="str">
-        <v>Resultado da transformação</v>
+        <v>{n} duplicados</v>
       </c>
       <c r="C212" t="str">
-        <v>Resultado da transformação</v>
+        <v>{n} duplicados</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Resultado da transformação</v>
       </c>
       <c r="C213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Resultado da transformação</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B214" t="str">
-        <v>A mostrar os primeiros {shown} de {total} — Guardar grava todos.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="C214" t="str">
-        <v>Mostrando os primeiros {shown} de {total} — Salvar grava todos.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B215" t="str">
-        <v>Guardar como</v>
+        <v>A mostrar os primeiros {shown} de {total} — Guardar grava todos.</v>
       </c>
       <c r="C215" t="str">
-        <v>Salvar como</v>
+        <v>Mostrando os primeiros {shown} de {total} — Salvar grava todos.</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B216" t="str">
-        <v>Guardar</v>
+        <v>Guardar como</v>
       </c>
       <c r="C216" t="str">
-        <v>Salvar</v>
+        <v>Salvar como</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B217" t="str">
-        <v>Inverter transformação</v>
+        <v>Guardar</v>
       </c>
       <c r="C217" t="str">
-        <v>Inverter transformação</v>
+        <v>Salvar</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B218" t="str">
-        <v>A inverter…</v>
+        <v>Inverter transformação</v>
       </c>
       <c r="C218" t="str">
-        <v>Invertendo…</v>
+        <v>Inverter transformação</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B219" t="str">
-        <v>Inverter</v>
+        <v>A inverter…</v>
       </c>
       <c r="C219" t="str">
-        <v>Inverter</v>
+        <v>Invertendo…</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B220" t="str">
-        <v>última etapa</v>
+        <v>Inverter</v>
       </c>
       <c r="C220" t="str">
-        <v>última etapa</v>
+        <v>Inverter</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B221" t="str">
-        <v>primeira etapa</v>
+        <v>última etapa</v>
       </c>
       <c r="C221" t="str">
-        <v>primeira etapa</v>
+        <v>última etapa</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B222" t="str">
-        <v>Dados em {in} → procurar {out}</v>
+        <v>primeira etapa</v>
       </c>
       <c r="C222" t="str">
-        <v>Dados em {in} → buscar {out}</v>
+        <v>primeira etapa</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B223" t="str">
-        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
+        <v>Dados em {in} → procurar {out}</v>
       </c>
       <c r="C223" t="str">
-        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
+        <v>Dados em {in} → buscar {out}</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B224" t="str">
-        <v>O conjunto de dados deve estar em {in}; a procura inversa produz {out} mais um custo de invertibilidade por patch.</v>
+        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
       </c>
       <c r="C224" t="str">
-        <v>O conjunto de dados deve estar em {in}; a busca inversa produz {out} mais um custo de invertibilidade por patch.</v>
+        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B225" t="str">
-        <v>Custo ΔE</v>
+        <v>O conjunto de dados deve estar em {in}; a procura inversa produz {out} mais um custo de invertibilidade por patch.</v>
       </c>
       <c r="C225" t="str">
-        <v>Custo ΔE</v>
+        <v>O conjunto de dados deve estar em {in}; a busca inversa produz {out} mais um custo de invertibilidade por patch.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B226" t="str">
-        <v>Esta imagem tem um perfil ICC incorporado.</v>
+        <v>Custo ΔE</v>
       </c>
       <c r="C226" t="str">
-        <v>Esta imagem tem um perfil ICC incorporado.</v>
+        <v>Custo ΔE</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B227" t="str">
-        <v>Extrair e adicionar à cadeia</v>
+        <v>Esta imagem tem um perfil ICC incorporado.</v>
       </c>
       <c r="C227" t="str">
-        <v>Extrair e adicionar à cadeia</v>
+        <v>Esta imagem tem um perfil ICC incorporado.</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B228" t="str">
-        <v>A extrair…</v>
+        <v>Extrair e adicionar à cadeia</v>
       </c>
       <c r="C228" t="str">
-        <v>Extraindo…</v>
+        <v>Extrair e adicionar à cadeia</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B229" t="str">
-        <v>Dispensar</v>
+        <v>A extrair…</v>
       </c>
       <c r="C229" t="str">
-        <v>Dispensar</v>
+        <v>Extraindo…</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B230" t="str">
-        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro lugar na cadeia.</v>
+        <v>Dispensar</v>
       </c>
       <c r="C230" t="str">
-        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro na cadeia.</v>
+        <v>Dispensar</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B231" t="str">
-        <v>Opções de saída de imagem</v>
+        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro lugar na cadeia.</v>
       </c>
       <c r="C231" t="str">
-        <v>Opções de saída de imagem</v>
+        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro na cadeia.</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B232" t="str">
-        <v>Codificação</v>
+        <v>Opções de saída de imagem</v>
       </c>
       <c r="C232" t="str">
-        <v>Codificação</v>
+        <v>Opções de saída de imagem</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B233" t="str">
-        <v>Igual à origem</v>
+        <v>Codificação</v>
       </c>
       <c r="C233" t="str">
-        <v>Igual à origem</v>
+        <v>Codificação</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B234" t="str">
-        <v>8 bits</v>
+        <v>Igual à origem</v>
       </c>
       <c r="C234" t="str">
-        <v>8 bits</v>
+        <v>Igual à origem</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>16 bits</v>
+        <v>8 bits</v>
       </c>
       <c r="C235" t="str">
-        <v>16 bits</v>
+        <v>8 bits</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B236" t="str">
-        <v>Flutuante (32 bits)</v>
+        <v>16 bits</v>
       </c>
       <c r="C236" t="str">
-        <v>Flutuante (32 bits)</v>
+        <v>16 bits</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B237" t="str">
-        <v>Compressão</v>
+        <v>Flutuante (32 bits)</v>
       </c>
       <c r="C237" t="str">
-        <v>Compressão</v>
+        <v>Flutuante (32 bits)</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B238" t="str">
-        <v>Nenhuma</v>
+        <v>Compressão</v>
       </c>
       <c r="C238" t="str">
-        <v>Nenhuma</v>
+        <v>Compressão</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B239" t="str">
-        <v>Planar</v>
+        <v>Nenhuma</v>
       </c>
       <c r="C239" t="str">
-        <v>Planar</v>
+        <v>Nenhuma</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B240" t="str">
-        <v>Composto</v>
+        <v>Planar</v>
       </c>
       <c r="C240" t="str">
-        <v>Composto</v>
+        <v>Planar</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B241" t="str">
-        <v>Separado</v>
+        <v>Composto</v>
       </c>
       <c r="C241" t="str">
-        <v>Separado</v>
+        <v>Composto</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B242" t="str">
-        <v>Interpolação CMM</v>
+        <v>Separado</v>
       </c>
       <c r="C242" t="str">
-        <v>Interpolação CMM</v>
+        <v>Separado</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B243" t="str">
-        <v>Tetraédrica</v>
+        <v>Interpolação CMM</v>
       </c>
       <c r="C243" t="str">
-        <v>Tetraédrica</v>
+        <v>Interpolação CMM</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B244" t="str">
-        <v>Linear</v>
+        <v>Tetraédrica</v>
       </c>
       <c r="C244" t="str">
-        <v>Linear</v>
+        <v>Tetraédrica</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B245" t="str">
-        <v>Incorporar ICC</v>
+        <v>Linear</v>
       </c>
       <c r="C245" t="str">
-        <v>Incorporar ICC</v>
+        <v>Linear</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B246" t="str">
-        <v>A codificação, a compressão e o formato planar determinam o TIFF guardado. A saída RGB/Gray mantém-se em PNG, salvo se for definida uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado).</v>
+        <v>Incorporar ICC</v>
       </c>
       <c r="C246" t="str">
-        <v>A codificação, a compressão e o formato planar determinam o TIFF salvo. A saída RGB/Gray permanece em PNG, a menos que uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado) seja definida.</v>
+        <v>Incorporar ICC</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B247" t="str">
-        <v>Montar TIFF espectral</v>
+        <v>A codificação, a compressão e o formato planar determinam o TIFF guardado. A saída RGB/Gray mantém-se em PNG, salvo se for definida uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado).</v>
       </c>
       <c r="C247" t="str">
-        <v>Montar TIFF espectral</v>
+        <v>A codificação, a compressão e o formato planar determinam o TIFF salvo. A saída RGB/Gray permanece em PNG, a menos que uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado) seja definida.</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B248" t="str">
-        <v>Largue imagens espectrais de canal único pela ordem dos canais e depois monte-as num único TIFF multicanal.</v>
+        <v>Montar TIFF espectral</v>
       </c>
       <c r="C248" t="str">
-        <v>Solte imagens espectrais de canal único na ordem dos canais e depois monte-as em um único TIFF multicanal.</v>
+        <v>Montar TIFF espectral</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B249" t="str">
-        <v>Largue imagens espectrais aqui (ou clique para escolher)</v>
+        <v>Largue imagens espectrais de canal único pela ordem dos canais e depois monte-as num único TIFF multicanal.</v>
       </c>
       <c r="C249" t="str">
-        <v>Solte imagens espectrais aqui (ou clique para escolher)</v>
+        <v>Solte imagens espectrais de canal único na ordem dos canais e depois monte-as em um único TIFF multicanal.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B250" t="str">
-        <v>can</v>
+        <v>Largue imagens espectrais aqui (ou clique para escolher)</v>
       </c>
       <c r="C250" t="str">
-        <v>can</v>
+        <v>Solte imagens espectrais aqui (ou clique para escolher)</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B251" t="str">
-        <v>Montar e guardar</v>
+        <v>can</v>
       </c>
       <c r="C251" t="str">
-        <v>Montar e salvar</v>
+        <v>can</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B252" t="str">
-        <v>A montar…</v>
+        <v>Montar e guardar</v>
       </c>
       <c r="C252" t="str">
-        <v>Montando…</v>
+        <v>Montar e salvar</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B253" t="str">
-        <v>Foram montados {n} canais.</v>
+        <v>A montar…</v>
       </c>
       <c r="C253" t="str">
-        <v>Foram montados {n} canais.</v>
+        <v>Montando…</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B254" t="str">
-        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
+        <v>Foram montados {n} canais.</v>
       </c>
       <c r="C254" t="str">
-        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
+        <v>Foram montados {n} canais.</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B255" t="str">
-        <v>Cancelar</v>
+        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
       </c>
       <c r="C255" t="str">
-        <v>Cancelar</v>
+        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B256" t="str">
-        <v>{n} ficheiro(s) não carregados</v>
+        <v>Cancelar</v>
       </c>
       <c r="C256" t="str">
-        <v>{n} arquivo(s) não carregados</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B257" t="str">
-        <v>Estes ficheiros não são perfis ICC, pelo que não foram adicionados ao conjunto:</v>
+        <v>{n} ficheiro(s) não carregados</v>
       </c>
       <c r="C257" t="str">
-        <v>Estes arquivos não são perfis ICC, portanto não foram adicionados ao conjunto:</v>
+        <v>{n} arquivo(s) não carregados</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B258" t="str">
-        <v>OK</v>
+        <v>Estes ficheiros não são perfis ICC, pelo que não foram adicionados ao conjunto:</v>
       </c>
       <c r="C258" t="str">
-        <v>OK</v>
+        <v>Estes arquivos não são perfis ICC, portanto não foram adicionados ao conjunto:</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B259" t="str">
-        <v>Largue um perfil ICC aqui</v>
+        <v>OK</v>
       </c>
       <c r="C259" t="str">
-        <v>Solte um perfil ICC aqui</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B260" t="str">
-        <v>ou</v>
+        <v>Largue um perfil ICC aqui</v>
       </c>
       <c r="C260" t="str">
-        <v>ou</v>
+        <v>Solte um perfil ICC aqui</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B261" t="str">
-        <v>Escolher ficheiro</v>
+        <v>ou</v>
       </c>
       <c r="C261" t="str">
-        <v>Escolher arquivo</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B262" t="str">
-        <v>Ficheiros .icc e .icm</v>
+        <v>Escolher ficheiro</v>
       </c>
       <c r="C262" t="str">
-        <v>Arquivos .icc e .icm</v>
+        <v>Escolher arquivo</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B263" t="str">
-        <v>Cabeçalho</v>
+        <v>Ficheiros .icc e .icm</v>
       </c>
       <c r="C263" t="str">
-        <v>Cabeçalho</v>
+        <v>Arquivos .icc e .icm</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B264" t="str">
-        <v>Etiquetas</v>
+        <v>Cabeçalho</v>
       </c>
       <c r="C264" t="str">
-        <v>Tags</v>
+        <v>Cabeçalho</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B265" t="str">
-        <v>Validação</v>
+        <v>Etiquetas</v>
       </c>
       <c r="C265" t="str">
-        <v>Validação</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B266" t="str">
-        <v>Análise</v>
+        <v>Validação</v>
       </c>
       <c r="C266" t="str">
-        <v>Análise</v>
+        <v>Validação</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B267" t="str">
-        <v>Tintagem do eixo neutro</v>
+        <v>Análise</v>
       </c>
       <c r="C267" t="str">
-        <v>Tintagem do eixo neutro</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B268" t="str">
-        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
       <c r="C268" t="str">
-        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B269" t="str">
-        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
       </c>
       <c r="C269" t="str">
-        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B270" t="str">
-        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
       <c r="C270" t="str">
-        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B271" t="str">
-        <v>Intenção de renderização</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
       <c r="C271" t="str">
-        <v>Intenção de renderização</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B272" t="str">
-        <v>% tinta</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C272" t="str">
-        <v>% tinta</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>L* out (tone)</v>
+        <v>% ink</v>
       </c>
       <c r="B273" t="str">
-        <v>L* de saída (tom)</v>
+        <v>% tinta</v>
       </c>
       <c r="C273" t="str">
-        <v>L* de saída (tom)</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Δa*b*</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B274" t="str">
-        <v>Δa*b*</v>
+        <v>L* de saída (tom)</v>
       </c>
       <c r="C274" t="str">
-        <v>Δa*b*</v>
+        <v>L* de saída (tom)</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B275" t="str">
-        <v>Colorimetria dos extremos</v>
+        <v>Δa*b*</v>
       </c>
       <c r="C275" t="str">
-        <v>Colorimetria dos extremos</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B276" t="str">
-        <v>Os extremos da gama de reprodução do perfil: o branco do suporte, o preto mais escuro que irá imprimir, a tinta que esse preto custa e o ponto em que cada matiz atinge a saturação máxima.</v>
+        <v>Colorimetria dos extremos</v>
       </c>
       <c r="C276" t="str">
-        <v>Os extremos da faixa de reprodução do perfil: o branco do suporte, o preto mais escuro que ele imprimirá, a tinta que esse preto custa e o ponto em que cada matiz atinge a saturação máxima.</v>
+        <v>Colorimetria dos extremos</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B277" t="str">
-        <v>O ponto branco é a cor com corante nulo — o suporte nu. O ponto preto obtém-se passando o preto do PCS (L*=0, a*=b*=0) pela tabela B2A selecionada para obter a tintagem que o perfil escolhe para o preto e lendo depois essa tintagem através de A2B1. A cobertura total de tinta (TAC) é a soma dessa tintagem. A colorimetria absoluta mostra a cor própria do suporte; a relativa refere-a a um branco perfeito.</v>
+        <v>Os extremos da gama de reprodução do perfil: o branco do suporte, o preto mais escuro que irá imprimir, a tinta que esse preto custa e o ponto em que cada matiz atinge a saturação máxima.</v>
       </c>
       <c r="C277" t="str">
-        <v>O ponto branco é a cor com corante nulo — o suporte nu. O ponto preto é obtido passando o preto do PCS (L*=0, a*=b*=0) pela tabela B2A selecionada para obter a tintagem que o perfil escolhe para o preto e lendo depois essa tintagem através de A2B1. A cobertura total de tinta (TAC) é a soma dessa tintagem. A colorimetria absoluta mostra a cor própria do suporte; a relativa a refere a um branco perfeito.</v>
+        <v>Os extremos da faixa de reprodução do perfil: o branco do suporte, o preto mais escuro que ele imprimirá, a tinta que esse preto custa e o ponto em que cada matiz atinge a saturação máxima.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Relative</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B278" t="str">
-        <v>Relativa</v>
+        <v>O ponto branco é a cor com corante nulo — o suporte nu. O ponto preto obtém-se passando o preto do PCS (L*=0, a*=b*=0) pela tabela B2A selecionada para obter a tintagem que o perfil escolhe para o preto e lendo depois essa tintagem através de A2B1. A cobertura total de tinta (TAC) é a soma dessa tintagem. A colorimetria absoluta mostra a cor própria do suporte; a relativa refere-a a um branco perfeito.</v>
       </c>
       <c r="C278" t="str">
-        <v>Relativa</v>
+        <v>O ponto branco é a cor com corante nulo — o suporte nu. O ponto preto é obtido passando o preto do PCS (L*=0, a*=b*=0) pela tabela B2A selecionada para obter a tintagem que o perfil escolhe para o preto e lendo depois essa tintagem através de A2B1. A cobertura total de tinta (TAC) é a soma dessa tintagem. A colorimetria absoluta mostra a cor própria do suporte; a relativa a refere a um branco perfeito.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Absolute</v>
+        <v>Relative</v>
       </c>
       <c r="B279" t="str">
-        <v>Absoluta</v>
+        <v>Relativa</v>
       </c>
       <c r="C279" t="str">
-        <v>Absoluta</v>
+        <v>Relativa</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>White point</v>
+        <v>Absolute</v>
       </c>
       <c r="B280" t="str">
-        <v>Ponto branco</v>
+        <v>Absoluta</v>
       </c>
       <c r="C280" t="str">
-        <v>Ponto branco</v>
+        <v>Absoluta</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Black point</v>
+        <v>White point</v>
       </c>
       <c r="B281" t="str">
-        <v>Ponto preto</v>
+        <v>Ponto branco</v>
       </c>
       <c r="C281" t="str">
-        <v>Ponto preto</v>
+        <v>Ponto branco</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Inking at black point</v>
+        <v>Black point</v>
       </c>
       <c r="B282" t="str">
-        <v>Tintagem no ponto preto</v>
+        <v>Ponto preto</v>
       </c>
       <c r="C282" t="str">
-        <v>Tintagem no ponto preto</v>
+        <v>Ponto preto</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TAC</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B283" t="str">
-        <v>TAC</v>
+        <v>Tintagem no ponto preto</v>
       </c>
       <c r="C283" t="str">
-        <v>TAC</v>
+        <v>Tintagem no ponto preto</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>TAC</v>
       </c>
       <c r="B284" t="str">
-        <v>Este perfil não tem etiqueta de ponto branco do meio, pelo que a colorimetria absoluta não está disponível.</v>
+        <v>TAC</v>
       </c>
       <c r="C284" t="str">
-        <v>Este perfil não tem tag de ponto branco do meio, portanto a colorimetria absoluta não está disponível.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B285" t="str">
-        <v>A colorimetria dos extremos só está disponível para perfis de saída (impressora) — pressupõe que corante nulo significa suporte nu.</v>
+        <v>Este perfil não tem etiqueta de ponto branco do meio, pelo que a colorimetria absoluta não está disponível.</v>
       </c>
       <c r="C285" t="str">
-        <v>A colorimetria dos extremos só está disponível para perfis de saída (impressora) — ela pressupõe que corante nulo significa suporte nu.</v>
+        <v>Este perfil não tem tag de ponto branco do meio, portanto a colorimetria absoluta não está disponível.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B286" t="str">
-        <v>Tinta plena vs croma máximo</v>
+        <v>A colorimetria dos extremos só está disponível para perfis de saída (impressora) — pressupõe que corante nulo significa suporte nu.</v>
       </c>
       <c r="C286" t="str">
-        <v>Tinta plena vs croma máximo</v>
+        <v>A colorimetria dos extremos só está disponível para perfis de saída (impressora) — ela pressupõe que corante nulo significa suporte nu.</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B287" t="str">
-        <v>Onde fica cada vértice de tinta e o ponto mais cromático no caminho até lá. Medido através de A2B1, pelo que estas linhas não mudam com a intenção de renderização acima. Num perfil bem comportado as duas linhas coincidem; se o croma máximo surgir antes da tinta plena, a tinta para além desse ponto apenas escurece.</v>
+        <v>Tinta plena vs croma máximo</v>
       </c>
       <c r="C287" t="str">
-        <v>Onde fica cada vértice de tinta e o ponto mais cromático no caminho até lá. Medido através de A2B1, portanto estas linhas não mudam com a intenção de renderização acima. Em um perfil bem comportado as duas linhas coincidem; se o croma máximo surgir antes da tinta plena, a tinta além desse ponto apenas escurece.</v>
+        <v>Tinta plena vs croma máximo</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Hue</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B288" t="str">
-        <v>Matiz</v>
+        <v>Onde fica cada vértice de tinta e o ponto mais cromático no caminho até lá. Medido através de A2B1, pelo que estas linhas não mudam com a intenção de renderização acima. Num perfil bem comportado as duas linhas coincidem; se o croma máximo surgir antes da tinta plena, a tinta para além desse ponto apenas escurece.</v>
       </c>
       <c r="C288" t="str">
-        <v>Matiz</v>
+        <v>Onde fica cada vértice de tinta e o ponto mais cromático no caminho até lá. Medido através de A2B1, portanto estas linhas não mudam com a intenção de renderização acima. Em um perfil bem comportado as duas linhas coincidem; se o croma máximo surgir antes da tinta plena, a tinta além desse ponto apenas escurece.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Full tone</v>
+        <v>Hue</v>
       </c>
       <c r="B289" t="str">
-        <v>Tinta plena</v>
+        <v>Matiz</v>
       </c>
       <c r="C289" t="str">
-        <v>Tinta plena</v>
+        <v>Matiz</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Max C*</v>
+        <v>Full tone</v>
       </c>
       <c r="B290" t="str">
-        <v>C* máx</v>
+        <v>Tinta plena</v>
       </c>
       <c r="C290" t="str">
-        <v>C* máx</v>
+        <v>Tinta plena</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>At ink</v>
+        <v>Max C*</v>
       </c>
       <c r="B291" t="str">
-        <v>Com tintagem</v>
+        <v>C* máx</v>
       </c>
       <c r="C291" t="str">
-        <v>Com tintagem</v>
+        <v>C* máx</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>At ink</v>
       </c>
       <c r="B292" t="str">
-        <v>O croma máximo é atingido antes da tinta plena — a tinta para além deste ponto apenas escurece.</v>
+        <v>Com tintagem</v>
       </c>
       <c r="C292" t="str">
-        <v>O croma máximo é atingido antes da tinta plena — a tinta além deste ponto apenas escurece.</v>
+        <v>Com tintagem</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B293" t="str">
-        <v>Utilização de tinta nas sombras</v>
+        <v>O croma máximo é atingido antes da tinta plena — a tinta para além deste ponto apenas escurece.</v>
       </c>
       <c r="C293" t="str">
-        <v>Uso de tinta nas sombras</v>
+        <v>O croma máximo é atingido antes da tinta plena — a tinta além deste ponto apenas escurece.</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B294" t="str">
-        <v>Quatro percursos retos no plano a*b* com uma luminosidade constante e deliberadamente escura, passados pela tabela B2A selecionada. Todas as amostras partilham a mesma L*, pelo que qualquer degrau abrupto ou inversão de um corante resulta apenas do tratamento do matiz e do croma — a assinatura de um artefacto de mapeamento de gamut nas sombras.</v>
+        <v>Utilização de tinta nas sombras</v>
       </c>
       <c r="C294" t="str">
-        <v>Quatro percursos retos no plano a*b* com uma luminosidade constante e deliberadamente escura, passados pela tabela B2A selecionada. Todas as amostras compartilham a mesma L*, portanto qualquer degrau abrupto ou inversão de um corante vem apenas do tratamento do matiz e do croma — a assinatura de um artefato de mapeamento de gamut nas sombras.</v>
+        <v>Uso de tinta nas sombras</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B295" t="str">
-        <v>A utilização de tinta nas sombras só está disponível para perfis de saída (impressora).</v>
+        <v>Quatro percursos retos no plano a*b* com uma luminosidade constante e deliberadamente escura, passados pela tabela B2A selecionada. Todas as amostras partilham a mesma L*, pelo que qualquer degrau abrupto ou inversão de um corante resulta apenas do tratamento do matiz e do croma — a assinatura de um artefacto de mapeamento de gamut nas sombras.</v>
       </c>
       <c r="C295" t="str">
-        <v>O uso de tinta nas sombras só está disponível para perfis de saída (impressora).</v>
+        <v>Quatro percursos retos no plano a*b* com uma luminosidade constante e deliberadamente escura, passados pela tabela B2A selecionada. Todas as amostras compartilham a mesma L*, portanto qualquer degrau abrupto ou inversão de um corante vem apenas do tratamento do matiz e do croma — a assinatura de um artefato de mapeamento de gamut nas sombras.</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Constant L* plane</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B296" t="str">
-        <v>Plano de L* constante</v>
+        <v>A utilização de tinta nas sombras só está disponível para perfis de saída (impressora).</v>
       </c>
       <c r="C296" t="str">
-        <v>Plano de L* constante</v>
+        <v>O uso de tinta nas sombras só está disponível para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>black-point compensated from</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B297" t="str">
-        <v>com compensação do ponto preto a partir de</v>
+        <v>Plano de L* constante</v>
       </c>
       <c r="C297" t="str">
-        <v>com compensação do ponto preto a partir de</v>
+        <v>Plano de L* constante</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Position along path</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B298" t="str">
-        <v>Posição ao longo do percurso</v>
+        <v>com compensação do ponto preto a partir de</v>
       </c>
       <c r="C298" t="str">
-        <v>Posição ao longo do percurso</v>
+        <v>com compensação do ponto preto a partir de</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Path</v>
+        <v>Position along path</v>
       </c>
       <c r="B299" t="str">
-        <v>Percurso</v>
+        <v>Posição ao longo do percurso</v>
       </c>
       <c r="C299" t="str">
-        <v>Percurso</v>
+        <v>Posição ao longo do percurso</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Primary-Inking Paths through Neutral</v>
+        <v>Path</v>
       </c>
       <c r="B300" t="str">
-        <v>Trajetos de tintagem primária pelo neutro</v>
+        <v>Percurso</v>
       </c>
       <c r="C300" t="str">
-        <v>Caminhos de entintamento primário pelo neutro</v>
+        <v>Percurso</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B301" t="str">
-        <v>Três trajetos dentro do gamute — ciano→vermelho, magenta→verde, amarelo→azul — cada um através do eixo neutro na luminosidade média das suas extremidades, através da tabela B2A selecionada. Cada amostra está dentro do gamute, pelo que, ao contrário dos trajetos de sombra, qualquer salto ou inversão de um corante é um defeito de suavidade da CLUT e não um artefacto de mapeamento de gamute.</v>
+        <v>Trajetos de tintagem primária pelo neutro</v>
       </c>
       <c r="C301" t="str">
-        <v>Três caminhos dentro do gamute — ciano→vermelho, magenta→verde, amarelo→azul — cada um através do eixo neutro na luminosidade média de suas extremidades, através da tabela B2A selecionada. Cada amostra está dentro do gamute, então, diferentemente dos caminhos de sombra, qualquer salto ou inversão de um corante é um defeito de suavidade da CLUT e não um artefato de mapeamento de gamute.</v>
+        <v>Caminhos de entintamento primário pelo neutro</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Primary-inking paths are only available for output (printer) profiles.</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B302" t="str">
-        <v>Os trajetos de tintagem primária só estão disponíveis para perfis de saída (impressora).</v>
+        <v>Três trajetos dentro do gamute — ciano→vermelho, magenta→verde, amarelo→azul — cada um através do eixo neutro na luminosidade média das suas extremidades, através da tabela B2A selecionada. Cada amostra está dentro do gamute, pelo que, ao contrário dos trajetos de sombra, qualquer salto ou inversão de um corante é um defeito de suavidade da CLUT e não um artefacto de mapeamento de gamute.</v>
       </c>
       <c r="C302" t="str">
-        <v>Os caminhos de entintamento primário só estão disponíveis para perfis de saída (impressora).</v>
+        <v>Três caminhos dentro do gamute — ciano→vermelho, magenta→verde, amarelo→azul — cada um através do eixo neutro na luminosidade média de suas extremidades, através da tabela B2A selecionada. Cada amostra está dentro do gamute, então, diferentemente dos caminhos de sombra, qualquer salto ou inversão de um corante é um defeito de suavidade da CLUT e não um artefato de mapeamento de gamute.</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Position along path (neutral at midpoint)</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B303" t="str">
-        <v>Posição ao longo do trajeto (neutro no centro)</v>
+        <v>Os trajetos de tintagem primária só estão disponíveis para perfis de saída (impressora).</v>
       </c>
       <c r="C303" t="str">
-        <v>Posição ao longo do caminho (neutro no centro)</v>
+        <v>Os caminhos de entintamento primário só estão disponíveis para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Black-point compensated for this intent.</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B304" t="str">
-        <v>Compensação de ponto preto aplicada para esta intenção.</v>
+        <v>Posição ao longo do trajeto (neutro no centro)</v>
       </c>
       <c r="C304" t="str">
-        <v>Compensação de ponto preto aplicada para esta intenção.</v>
+        <v>Posição ao longo do caminho (neutro no centro)</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Ink Usage Statistics</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B305" t="str">
-        <v>Estatísticas de utilização de tinta</v>
+        <v>Compensação de ponto preto aplicada para esta intenção.</v>
       </c>
       <c r="C305" t="str">
-        <v>Estatísticas de uso de tinta</v>
+        <v>Compensação de ponto preto aplicada para esta intenção.</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B306" t="str">
-        <v>Quanto de cada corante o perfil deposita, como soma e como quota do total — a assinatura de consumo de tinta da separação.</v>
+        <v>Estatísticas de utilização de tinta</v>
       </c>
       <c r="C306" t="str">
-        <v>Quanto de cada corante o perfil deposita, como soma e como parcela do total — a assinatura de consumo de tinta da separação.</v>
+        <v>Estatísticas de uso de tinta</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Ink usage statistics are only available for output (printer) profiles.</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B307" t="str">
-        <v>As estatísticas de utilização de tinta só estão disponíveis para perfis de saída (impressora).</v>
+        <v>Quanto de cada corante o perfil deposita, como soma e como quota do total — a assinatura de consumo de tinta da separação.</v>
       </c>
       <c r="C307" t="str">
-        <v>As estatísticas de uso de tinta só estão disponíveis para perfis de saída (impressora).</v>
+        <v>Quanto de cada corante o perfil deposita, como soma e como parcela do total — a assinatura de consumo de tinta da separação.</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Neutral axis</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B308" t="str">
-        <v>Eixo neutro</v>
+        <v>As estatísticas de utilização de tinta só estão disponíveis para perfis de saída (impressora).</v>
       </c>
       <c r="C308" t="str">
-        <v>Eixo neutro</v>
+        <v>As estatísticas de uso de tinta só estão disponíveis para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Mean coverage</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B309" t="str">
-        <v>Cobertura média</v>
+        <v>Eixo neutro</v>
       </c>
       <c r="C309" t="str">
-        <v>Cobertura média</v>
+        <v>Eixo neutro</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Share of ink</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B310" t="str">
-        <v>Quota de tinta</v>
+        <v>Cobertura média</v>
       </c>
       <c r="C310" t="str">
-        <v>Parcela de tinta</v>
+        <v>Cobertura média</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
+        <v>Share of ink</v>
       </c>
       <c r="B311" t="str">
-        <v>A quota de tinta é a impressão digital da construção do neutro — a fração de cada corante no total de tinta depositada, independentemente do número de amostras.</v>
+        <v>Quota de tinta</v>
       </c>
       <c r="C311" t="str">
-        <v>A parcela de tinta é a impressão digital da construção do neutro — a fração de cada corante no total de tinta depositada, independentemente do número de amostras.</v>
+        <v>Parcela de tinta</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>On &amp; in-gamut points</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B312" t="str">
-        <v>Pontos dentro do gamute</v>
+        <v>A quota de tinta é a impressão digital da construção do neutro — a fração de cada corante no total de tinta depositada, independentemente do número de amostras.</v>
       </c>
       <c r="C312" t="str">
-        <v>Pontos dentro do gamute</v>
+        <v>A parcela de tinta é a impressão digital da construção do neutro — a fração de cada corante no total de tinta depositada, independentemente do número de amostras.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B313" t="str">
-        <v>A utilização de tinta em todas as cores do gamute necessita da fronteira de gamute do lado B2A, ainda não implementada — pendente.</v>
+        <v>Pontos dentro do gamute</v>
       </c>
       <c r="C313" t="str">
-        <v>O uso de tinta em todas as cores do gamute precisa da fronteira de gamute do lado B2A, ainda não implementada — pendente.</v>
+        <v>Pontos dentro do gamute</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>No colorant data to summarize.</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B314" t="str">
-        <v>Sem dados de corante para resumir.</v>
+        <v>A utilização de tinta em todas as cores do gamute necessita da fronteira de gamute do lado B2A, ainda não implementada — pendente.</v>
       </c>
       <c r="C314" t="str">
-        <v>Sem dados de corante para resumir.</v>
+        <v>O uso de tinta em todas as cores do gamute precisa da fronteira de gamute do lado B2A, ainda não implementada — pendente.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B315" t="str">
-        <v>Selecione uma tabela B2A (PCS→dispositivo) abaixo para ver também uma imagem em tons de cinzento da cobertura de tinta de cada corante.</v>
+        <v>Sem dados de corante para resumir.</v>
       </c>
       <c r="C315" t="str">
-        <v>Selecione uma tabela B2A (PCS→dispositivo) abaixo para ver também uma imagem em tons de cinza da cobertura de tinta de cada corante.</v>
+        <v>Sem dados de corante para resumir.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B316" t="str">
-        <v>Cobertura de tinta de cada corante sobre a mesma grelha (mais escuro = mais tinta).</v>
+        <v>Selecione uma tabela B2A (PCS→dispositivo) abaixo para ver também uma imagem em tons de cinzento da cobertura de tinta de cada corante.</v>
       </c>
       <c r="C316" t="str">
-        <v>Cobertura de tinta de cada corante sobre a mesma grade (mais escuro = mais tinta).</v>
+        <v>Selecione uma tabela B2A (PCS→dispositivo) abaixo para ver também uma imagem em tons de cinza da cobertura de tinta de cada corante.</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Cyan</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B317" t="str">
-        <v>Ciano</v>
+        <v>Cobertura de tinta de cada corante sobre a mesma grelha (mais escuro = mais tinta).</v>
       </c>
       <c r="C317" t="str">
-        <v>Ciano</v>
+        <v>Cobertura de tinta de cada corante sobre a mesma grade (mais escuro = mais tinta).</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
       <c r="B318" t="str">
-        <v>Magenta</v>
+        <v>Ciano</v>
       </c>
       <c r="C318" t="str">
-        <v>Magenta</v>
+        <v>Ciano</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Yellow</v>
+        <v>Magenta</v>
       </c>
       <c r="B319" t="str">
-        <v>Amarelo</v>
+        <v>Magenta</v>
       </c>
       <c r="C319" t="str">
-        <v>Amarelo</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Red</v>
+        <v>Yellow</v>
       </c>
       <c r="B320" t="str">
-        <v>Vermelho</v>
+        <v>Amarelo</v>
       </c>
       <c r="C320" t="str">
-        <v>Vermelho</v>
+        <v>Amarelo</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="B321" t="str">
-        <v>Verde</v>
+        <v>Vermelho</v>
       </c>
       <c r="C321" t="str">
-        <v>Verde</v>
+        <v>Vermelho</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blue</v>
+        <v>Green</v>
       </c>
       <c r="B322" t="str">
-        <v>Azul</v>
+        <v>Verde</v>
       </c>
       <c r="C322" t="str">
-        <v>Azul</v>
+        <v>Verde</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Black</v>
+        <v>Blue</v>
       </c>
       <c r="B323" t="str">
-        <v>Preto</v>
+        <v>Azul</v>
       </c>
       <c r="C323" t="str">
-        <v>Preto</v>
+        <v>Azul</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Perceptual</v>
+        <v>Black</v>
       </c>
       <c r="B324" t="str">
-        <v>Perceptual</v>
+        <v>Preto</v>
       </c>
       <c r="C324" t="str">
-        <v>Perceptual</v>
+        <v>Preto</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B325" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Perceptual</v>
       </c>
       <c r="C325" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B326" t="str">
-        <v>Saturação</v>
+        <v>Colorimétrico relativo</v>
       </c>
       <c r="C326" t="str">
-        <v>Saturação</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B327" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Saturação</v>
       </c>
       <c r="C327" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Saturação</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B328" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>Colorimétrico absoluto</v>
       </c>
       <c r="C328" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B329" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>Estatísticas do perfil</v>
       </c>
       <c r="C329" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>Estatísticas do perfil</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B330" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
       <c r="C330" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B331" t="str">
-        <v>Intenção de renderização</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
       </c>
       <c r="C331" t="str">
-        <v>Intenção de renderização</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B332" t="str">
-        <v>Volume de gamute (ΔE³)</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C332" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B333" t="str">
-        <v>ΔE de percurso</v>
+        <v>Volume de gamute (ΔE³)</v>
       </c>
       <c r="C333" t="str">
-        <v>ΔE de percurso</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B334" t="str">
-        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
+        <v>ΔE de percurso</v>
       </c>
       <c r="C334" t="str">
-        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
+        <v>ΔE de percurso</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B335" t="str">
-        <v>média</v>
+        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
       </c>
       <c r="C335" t="str">
-        <v>média</v>
+        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B336" t="str">
-        <v>P90</v>
+        <v>média</v>
       </c>
       <c r="C336" t="str">
-        <v>P90</v>
+        <v>média</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B337" t="str">
-        <v>máx.</v>
+        <v>P90</v>
       </c>
       <c r="C337" t="str">
-        <v>máx.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B338" t="str">
-        <v>A analisar…</v>
+        <v>máx.</v>
       </c>
       <c r="C338" t="str">
-        <v>Analisando…</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B339" t="str">
-        <v>Análise</v>
+        <v>A analisar…</v>
       </c>
       <c r="C339" t="str">
-        <v>Análise</v>
+        <v>Analisando…</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B340" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>Análise</v>
       </c>
       <c r="C340" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B341" t="str">
-        <v>Gráfico</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
       <c r="C341" t="str">
-        <v>Gráfico</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B342" t="str">
-        <v>Saída em bruto</v>
+        <v>Gráfico</v>
       </c>
       <c r="C342" t="str">
-        <v>Saída bruta</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B343" t="str">
-        <v>XML</v>
+        <v>Saída em bruto</v>
       </c>
       <c r="C343" t="str">
-        <v>XML</v>
+        <v>Saída bruta</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="C344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B345" t="str">
-        <v>Curvas</v>
+        <v>JSON</v>
       </c>
       <c r="C345" t="str">
-        <v>Curvas</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B346" t="str">
-        <v>Curvas de entrada</v>
+        <v>Curvas</v>
       </c>
       <c r="C346" t="str">
-        <v>Curvas de entrada</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B347" t="str">
-        <v>Curvas de saída</v>
+        <v>Curvas de entrada</v>
       </c>
       <c r="C347" t="str">
-        <v>Curvas de saída</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B348" t="str">
-        <v>Imagem CLUT</v>
+        <v>Curvas de saída</v>
       </c>
       <c r="C348" t="str">
-        <v>Imagem CLUT</v>
+        <v>Curvas de saída</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B349" t="str">
-        <v>Imagem de gamut</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C349" t="str">
-        <v>Imagem de gamut</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B350" t="str">
-        <v>Cromaticidade</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C350" t="str">
-        <v>Cromaticidade</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B351" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Cromaticidade</v>
       </c>
       <c r="C351" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Cromaticidade</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B352" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Gráfico de dispersão</v>
       </c>
       <c r="C352" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Gráfico de dispersão</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B353" t="str">
-        <v>Tabela da curva</v>
+        <v>Curva de resposta tonal</v>
       </c>
       <c r="C353" t="str">
-        <v>Tabela da curva</v>
+        <v>Curva de resposta tonal</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B354" t="str">
-        <v>Tabelas</v>
+        <v>Tabela da curva</v>
       </c>
       <c r="C354" t="str">
-        <v>Tabelas</v>
+        <v>Tabela da curva</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B355" t="str">
-        <v>Dados</v>
+        <v>Tabelas</v>
       </c>
       <c r="C355" t="str">
-        <v>Dados</v>
+        <v>Tabelas</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B356" t="str">
-        <v>Avaliar</v>
+        <v>Dados</v>
       </c>
       <c r="C356" t="str">
-        <v>Avaliar</v>
+        <v>Dados</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B357" t="str">
-        <v>A carregar…</v>
+        <v>Avaliar</v>
       </c>
       <c r="C357" t="str">
-        <v>Carregando…</v>
+        <v>Avaliar</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B358" t="str">
-        <v>Entrada</v>
+        <v>A carregar…</v>
       </c>
       <c r="C358" t="str">
-        <v>Entrada</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B359" t="str">
-        <v>Saída</v>
+        <v>Entrada</v>
       </c>
       <c r="C359" t="str">
-        <v>Saída</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B360" t="str">
-        <v>Vírgula flutuante</v>
+        <v>Saída</v>
       </c>
       <c r="C360" t="str">
-        <v>Ponto flutuante</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B361" t="str">
-        <v>Ponto da grelha</v>
+        <v>Vírgula flutuante</v>
       </c>
       <c r="C361" t="str">
-        <v>Ponto da grade</v>
+        <v>Ponto flutuante</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B362" t="str">
-        <v>Normalizado</v>
+        <v>Ponto da grelha</v>
       </c>
       <c r="C362" t="str">
-        <v>Normalizado</v>
+        <v>Ponto da grade</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B363" t="str">
-        <v>Legível</v>
+        <v>Normalizado</v>
       </c>
       <c r="C363" t="str">
-        <v>Legível</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B364" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Legível</v>
       </c>
       <c r="C364" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Legível</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B365" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dispositivo → PCS</v>
       </c>
       <c r="C365" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B366" t="str">
-        <v>Sem grelha CLUT</v>
+        <v>PCS → Dispositivo</v>
       </c>
       <c r="C366" t="str">
-        <v>Sem grade CLUT</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B367" t="str">
-        <v>A carregar…</v>
+        <v>Sem grelha CLUT</v>
       </c>
       <c r="C367" t="str">
-        <v>Carregando…</v>
+        <v>Sem grade CLUT</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B368" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>A carregar…</v>
       </c>
       <c r="C368" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B369" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
       <c r="C369" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B370" t="str">
-        <v>Não foi possível obter o perfil de</v>
+        <v>URL de perfil inválido:</v>
       </c>
       <c r="C370" t="str">
-        <v>Não foi possível buscar o perfil de</v>
+        <v>URL de perfil inválido:</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B371" t="str">
-        <v>Carregar um perfil ICC a partir deste site externo?</v>
+        <v>Não foi possível obter o perfil de</v>
       </c>
       <c r="C371" t="str">
-        <v>Carregar um perfil ICC deste site externo?</v>
+        <v>Não foi possível buscar o perfil de</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B372" t="str">
-        <v>A carregar o relatório Profile Assessment WG…</v>
+        <v>Carregar um perfil ICC a partir deste site externo?</v>
       </c>
       <c r="C372" t="str">
-        <v>Carregando o relatório Profile Assessment WG…</v>
+        <v>Carregar um perfil ICC deste site externo?</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B373" t="str">
-        <v>A executar as verificações Profile Assessment WG…</v>
+        <v>A carregar o relatório Profile Assessment WG…</v>
       </c>
       <c r="C373" t="str">
-        <v>Executando as verificações Profile Assessment WG…</v>
+        <v>Carregando o relatório Profile Assessment WG…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B374" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>A executar as verificações Profile Assessment WG…</v>
       </c>
       <c r="C374" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Executando as verificações Profile Assessment WG…</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B375" t="str">
-        <v>Segurança</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
       <c r="C375" t="str">
-        <v>Segurança</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B376" t="str">
-        <v>Conformidade</v>
+        <v>Segurança</v>
       </c>
       <c r="C376" t="str">
-        <v>Conformidade</v>
+        <v>Segurança</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B377" t="str">
-        <v>Qualidade</v>
+        <v>Conformidade</v>
       </c>
       <c r="C377" t="str">
-        <v>Qualidade</v>
+        <v>Conformidade</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>HDR</v>
+        <v>Quality</v>
       </c>
       <c r="B378" t="str">
-        <v>HDR</v>
+        <v>Qualidade</v>
       </c>
       <c r="C378" t="str">
-        <v>HDR</v>
+        <v>Qualidade</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Code points</v>
+        <v>HDR</v>
       </c>
       <c r="B379" t="str">
-        <v>Pontos de código</v>
+        <v>HDR</v>
       </c>
       <c r="C379" t="str">
-        <v>Pontos de código</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Gain curve</v>
+        <v>Code points</v>
       </c>
       <c r="B380" t="str">
-        <v>Curva de ganho</v>
+        <v>Pontos de código</v>
       </c>
       <c r="C380" t="str">
-        <v>Curva de ganho</v>
+        <v>Pontos de código</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Environment</v>
+        <v>Gain curve</v>
       </c>
       <c r="B381" t="str">
-        <v>Ambiente</v>
+        <v>Curva de ganho</v>
       </c>
       <c r="C381" t="str">
-        <v>Ambiente</v>
+        <v>Curva de ganho</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Showing the SDR fallback</v>
+        <v>Environment</v>
       </c>
       <c r="B382" t="str">
-        <v>A mostrar o recurso SDR</v>
+        <v>Ambiente</v>
       </c>
       <c r="C382" t="str">
-        <v>Mostrando o fallback SDR</v>
+        <v>Ambiente</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>HDR Profile in the chain</v>
+        <v>Showing the SDR fallback</v>
       </c>
       <c r="B383" t="str">
-        <v>Perfil HDR na cadeia</v>
+        <v>A mostrar o recurso SDR</v>
       </c>
       <c r="C383" t="str">
-        <v>Perfil HDR na cadeia</v>
+        <v>Mostrando o fallback SDR</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
+        <v>HDR Profile in the chain</v>
       </c>
       <c r="B384" t="str">
-        <v>As transformações através de um perfil HDR usam o seu AToB0Tag — a renderização SDR fixada exigida pela cláusula 8.10.6 — porque a cláusula 8.10.1 não lhe deixa etiquetas TRC. O resultado é esse recurso, não comportamento HDR.</v>
+        <v>Perfil HDR na cadeia</v>
       </c>
       <c r="C384" t="str">
-        <v>As transformações através de um perfil HDR usam seu AToB0Tag — a renderização SDR fixada exigida pela cláusula 8.10.6 — porque a cláusula 8.10.1 não lhe deixa tags TRC. O resultado é esse fallback, não comportamento HDR.</v>
+        <v>Perfil HDR na cadeia</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
+        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B385" t="str">
-        <v>São perfis HDR, sem etiquetas TRC, pelo que o gamut é construído a partir do AToB0Tag — a renderização SDR fixada que a cláusula 8.10.6 exige a consumidores sem processamento HDR. Não é o gamut HDR do perfil, que não pode ser desenhado num PCS limitado.</v>
+        <v>As transformações através de um perfil HDR usam o seu AToB0Tag — a renderização SDR fixada exigida pela cláusula 8.10.6 — porque a cláusula 8.10.1 não lhe deixa etiquetas TRC. O resultado é esse recurso, não comportamento HDR.</v>
       </c>
       <c r="C385" t="str">
-        <v>São perfis HDR, sem tags TRC, então o gamut é construído a partir do AToB0Tag — a renderização SDR fixada que a cláusula 8.10.6 exige de consumidores sem processamento HDR. Não é o gamut HDR do perfil, que não pode ser desenhado em um PCS limitado.</v>
+        <v>As transformações através de um perfil HDR usam seu AToB0Tag — a renderização SDR fixada exigida pela cláusula 8.10.6 — porque a cláusula 8.10.1 não lhe deixa tags TRC. O resultado é esse fallback, não comportamento HDR.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Detecting…</v>
+        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B386" t="str">
-        <v>A detetar…</v>
+        <v>São perfis HDR, sem etiquetas TRC, pelo que o gamut é construído a partir do AToB0Tag — a renderização SDR fixada que a cláusula 8.10.6 exige a consumidores sem processamento HDR. Não é o gamut HDR do perfil, que não pode ser desenhado num PCS limitado.</v>
       </c>
       <c r="C386" t="str">
-        <v>Detectando…</v>
+        <v>São perfis HDR, sem tags TRC, então o gamut é construído a partir do AToB0Tag — a renderização SDR fixada que a cláusula 8.10.6 exige de consumidores sem processamento HDR. Não é o gamut HDR do perfil, que não pode ser desenhado em um PCS limitado.</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Could not detect environment.</v>
+        <v>Detecting…</v>
       </c>
       <c r="B387" t="str">
-        <v>Não foi possível detetar o ambiente.</v>
+        <v>A detetar…</v>
       </c>
       <c r="C387" t="str">
-        <v>Não foi possível detectar o ambiente.</v>
+        <v>Detectando…</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>HDR display</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B388" t="str">
-        <v>Ecrã HDR</v>
+        <v>Não foi possível detetar o ambiente.</v>
       </c>
       <c r="C388" t="str">
-        <v>Tela HDR</v>
+        <v>Não foi possível detectar o ambiente.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Wide gamut</v>
+        <v>HDR display</v>
       </c>
       <c r="B389" t="str">
-        <v>Gamut alargado</v>
+        <v>Ecrã HDR</v>
       </c>
       <c r="C389" t="str">
-        <v>Gamut amplo</v>
+        <v>Tela HDR</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>HDR canvas path</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B390" t="str">
-        <v>Caminho de canvas HDR</v>
+        <v>Gamut alargado</v>
       </c>
       <c r="C390" t="str">
-        <v>Caminho de canvas HDR</v>
+        <v>Gamut amplo</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>sRGB</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B391" t="str">
-        <v>sRGB</v>
+        <v>Caminho de canvas HDR</v>
       </c>
       <c r="C391" t="str">
-        <v>sRGB</v>
+        <v>Caminho de canvas HDR</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>none</v>
+        <v>sRGB</v>
       </c>
       <c r="B392" t="str">
-        <v>nenhum</v>
+        <v>sRGB</v>
       </c>
       <c r="C392" t="str">
-        <v>nenhum</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>yes</v>
+        <v>none</v>
       </c>
       <c r="B393" t="str">
-        <v>sim</v>
+        <v>nenhum</v>
       </c>
       <c r="C393" t="str">
-        <v>sim</v>
+        <v>nenhum</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="B394" t="str">
-        <v>não</v>
+        <v>sim</v>
       </c>
       <c r="C394" t="str">
-        <v>não</v>
+        <v>sim</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>not reported</v>
+        <v>no</v>
       </c>
       <c r="B395" t="str">
-        <v>não reportado</v>
+        <v>não</v>
       </c>
       <c r="C395" t="str">
-        <v>não informado</v>
+        <v>não</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Format</v>
+        <v>not reported</v>
       </c>
       <c r="B396" t="str">
-        <v>Formato</v>
+        <v>não reportado</v>
       </c>
       <c r="C396" t="str">
-        <v>Formato</v>
+        <v>não informado</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Inspect</v>
+        <v>Format</v>
       </c>
       <c r="B397" t="str">
-        <v>Inspecionar</v>
+        <v>Formato</v>
       </c>
       <c r="C397" t="str">
-        <v>Inspecionar</v>
+        <v>Formato</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Display</v>
+        <v>Inspect</v>
       </c>
       <c r="B398" t="str">
-        <v>Mostrar</v>
+        <v>Inspecionar</v>
       </c>
       <c r="C398" t="str">
-        <v>Exibir</v>
+        <v>Inspecionar</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>HDR</v>
+        <v>Display</v>
       </c>
       <c r="B399" t="str">
-        <v>HDR</v>
+        <v>Mostrar</v>
       </c>
       <c r="C399" t="str">
-        <v>HDR</v>
+        <v>Exibir</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Read the embedded ICC profile — needs no codec</v>
+        <v>HDR</v>
       </c>
       <c r="B400" t="str">
-        <v>Ler o perfil ICC incorporado — não precisa de codec</v>
+        <v>HDR</v>
       </c>
       <c r="C400" t="str">
-        <v>Ler o perfil ICC incorporado — não precisa de codec</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Show the pixels</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B401" t="str">
-        <v>Mostrar os pixels</v>
+        <v>Ler o perfil ICC incorporado — não precisa de codec</v>
       </c>
       <c r="C401" t="str">
-        <v>Mostrar os pixels</v>
+        <v>Ler o perfil ICC incorporado — não precisa de codec</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Render brighter-than-white</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B402" t="str">
-        <v>Representar mais claro do que o branco</v>
+        <v>Mostrar os pixels</v>
       </c>
       <c r="C402" t="str">
-        <v>Renderizar mais claro que o branco</v>
+        <v>Mostrar os pixels</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Decoded by profiletool itself, so browser-independent</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B403" t="str">
-        <v>Descodificado pelo profiletool, logo independente do navegador</v>
+        <v>Representar mais claro do que o branco</v>
       </c>
       <c r="C403" t="str">
-        <v>Decodificado pelo profiletool, portanto independente do navegador</v>
+        <v>Renderizar mais claro que o branco</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B404" t="str">
-        <v>Este navegador não indicou a margem HDR do ecrã, apenas se existe um caminho HDR.</v>
+        <v>Descodificado pelo profiletool, logo independente do navegador</v>
       </c>
       <c r="C404" t="str">
-        <v>Este navegador não informou a margem HDR da tela, apenas se existe um caminho HDR.</v>
+        <v>Decodificado pelo profiletool, portanto independente do navegador</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Browser flags</v>
+        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
       </c>
       <c r="B405" t="str">
-        <v>Flags do navegador</v>
+        <v>Este navegador não indicou a margem HDR do ecrã, apenas se existe um caminho HDR.</v>
       </c>
       <c r="C405" t="str">
-        <v>Flags do navegador</v>
+        <v>Este navegador não informou a margem HDR da tela, apenas se existe um caminho HDR.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>on</v>
+        <v>Browser flags</v>
       </c>
       <c r="B406" t="str">
-        <v>ativa</v>
+        <v>Flags do navegador</v>
       </c>
       <c r="C406" t="str">
-        <v>ativada</v>
+        <v>Flags do navegador</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>not enabled</v>
+        <v>on</v>
       </c>
       <c r="B407" t="str">
-        <v>não ativa</v>
+        <v>ativa</v>
       </c>
       <c r="C407" t="str">
-        <v>não ativada</v>
+        <v>ativada</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>cannot be detected here</v>
+        <v>not enabled</v>
       </c>
       <c r="B408" t="str">
-        <v>não é possível detetar aqui</v>
+        <v>não ativa</v>
       </c>
       <c r="C408" t="str">
-        <v>não é possível detectar aqui</v>
+        <v>não ativada</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
+        <v>cannot be detected here</v>
       </c>
       <c r="B409" t="str">
-        <v>Necessário para renderização HDR neste navegador: sem WebGPU, o canvas HDR é a única via. A inspeção de perfis funciona sem isto.</v>
+        <v>não é possível detetar aqui</v>
       </c>
       <c r="C409" t="str">
-        <v>Necessário para renderização HDR neste navegador: sem WebGPU, o canvas HDR é a única via. A inspeção de perfis funciona sem isso.</v>
+        <v>não é possível detectar aqui</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
+        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
       </c>
       <c r="B410" t="str">
-        <v>Opcional: o HDR pode ser renderizado via WebGPU, mas isto acrescenta a via canvas HDR e permite ao profiletool ler a margem HDR real do ecrã.</v>
+        <v>Necessário para renderização HDR neste navegador: sem WebGPU, o canvas HDR é a única via. A inspeção de perfis funciona sem isto.</v>
       </c>
       <c r="C410" t="str">
-        <v>Opcional: o HDR pode ser renderizado via WebGPU, mas isto adiciona a via canvas HDR e permite ao profiletool ler a margem HDR real da tela.</v>
+        <v>Necessário para renderização HDR neste navegador: sem WebGPU, o canvas HDR é a única via. A inspeção de perfis funciona sem isso.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
+        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
       </c>
       <c r="B411" t="str">
-        <v>As páginas web não podem abrir páginas de flags. Cole isto na barra de endereço, escolha Enabled e reinicie o navegador.</v>
+        <v>Opcional: o HDR pode ser renderizado via WebGPU, mas isto acrescenta a via canvas HDR e permite ao profiletool ler a margem HDR real do ecrã.</v>
       </c>
       <c r="C411" t="str">
-        <v>Páginas web não podem abrir páginas de flags. Cole isto na barra de endereço, escolha Enabled e reinicie o navegador.</v>
+        <v>Opcional: o HDR pode ser renderizado via WebGPU, mas isto adiciona a via canvas HDR e permite ao profiletool ler a margem HDR real da tela.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Copy</v>
+        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
       </c>
       <c r="B412" t="str">
-        <v>Copiar</v>
+        <v>As páginas web não podem abrir páginas de flags. Cole isto na barra de endereço, escolha Enabled e reinicie o navegador.</v>
       </c>
       <c r="C412" t="str">
-        <v>Copiar</v>
+        <v>Páginas web não podem abrir páginas de flags. Cole isto na barra de endereço, escolha Enabled e reinicie o navegador.</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Copied</v>
+        <v>Copy</v>
       </c>
       <c r="B413" t="str">
-        <v>Copiado</v>
+        <v>Copiar</v>
       </c>
       <c r="C413" t="str">
-        <v>Copiado</v>
+        <v>Copiar</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Copy failed — select the address and copy it.</v>
+        <v>Copied</v>
       </c>
       <c r="B414" t="str">
-        <v>Falha ao copiar — selecione o endereço e copie-o.</v>
+        <v>Copiado</v>
       </c>
       <c r="C414" t="str">
-        <v>Falha ao copiar — selecione o endereço e copie.</v>
+        <v>Copiado</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Pixel ratio</v>
+        <v>Copy failed — select the address and copy it.</v>
       </c>
       <c r="B415" t="str">
-        <v>Relação de píxeis</v>
+        <v>Falha ao copiar — selecione o endereço e copie-o.</v>
       </c>
       <c r="C415" t="str">
-        <v>Proporção de pixels</v>
+        <v>Falha ao copiar — selecione o endereço e copie.</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Current monitor</v>
+        <v>Pixel ratio</v>
       </c>
       <c r="B416" t="str">
-        <v>Monitor atual</v>
+        <v>Relação de píxeis</v>
       </c>
       <c r="C416" t="str">
-        <v>Monitor atual</v>
+        <v>Proporção de pixels</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>unnamed</v>
+        <v>Current monitor</v>
       </c>
       <c r="B417" t="str">
-        <v>sem nome</v>
+        <v>Monitor atual</v>
       </c>
       <c r="C417" t="str">
-        <v>sem nome</v>
+        <v>Monitor atual</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>primary</v>
+        <v>unnamed</v>
       </c>
       <c r="B418" t="str">
-        <v>principal</v>
+        <v>sem nome</v>
       </c>
       <c r="C418" t="str">
-        <v>principal</v>
+        <v>sem nome</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>built-in</v>
+        <v>primary</v>
       </c>
       <c r="B419" t="str">
-        <v>integrado</v>
+        <v>principal</v>
       </c>
       <c r="C419" t="str">
-        <v>integrado</v>
+        <v>principal</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>HDR headroom</v>
+        <v>built-in</v>
       </c>
       <c r="B420" t="str">
-        <v>Margem HDR</v>
+        <v>integrado</v>
       </c>
       <c r="C420" t="str">
-        <v>Margem HDR</v>
+        <v>integrado</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>not exposed by this browser</v>
+        <v>HDR headroom</v>
       </c>
       <c r="B421" t="str">
-        <v>não exposta por este navegador</v>
+        <v>Margem HDR</v>
       </c>
       <c r="C421" t="str">
-        <v>não exposta por este navegador</v>
+        <v>Margem HDR</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
+        <v>not exposed by this browser</v>
       </c>
       <c r="B422" t="str">
-        <v>O Chromium indica isto em stops: log₂ da luminância máxima do ecrã ÷ o nível de branco SDR. No Windows só é atualizado quando o Chrome volta a ler o ecrã — janela movida para outro ecrã ou Chrome reativado — e não quando o brilho muda.</v>
+        <v>não exposta por este navegador</v>
       </c>
       <c r="C422" t="str">
-        <v>O Chromium informa isso em stops: log₂ do brilho máximo da tela ÷ o nível de branco SDR. No Windows, só é atualizado quando o Chrome relê a tela — janela movida para outra tela ou Chrome reativado — e não quando o brilho muda.</v>
+        <v>não exposta por este navegador</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>{stops} stops (≈{ratio}× SDR white)</v>
+        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
       </c>
       <c r="B423" t="str">
-        <v>{stops} stops (≈{ratio}× o branco SDR)</v>
+        <v>O Chromium indica isto em stops: log₂ da luminância máxima do ecrã ÷ o nível de branco SDR. No Windows só é atualizado quando o Chrome volta a ler o ecrã — janela movida para outro ecrã ou Chrome reativado — e não quando o brilho muda.</v>
       </c>
       <c r="C423" t="str">
-        <v>{stops} stops (≈{ratio}× o branco SDR)</v>
+        <v>O Chromium informa isso em stops: log₂ do brilho máximo da tela ÷ o nível de branco SDR. No Windows, só é atualizado quando o Chrome relê a tela — janela movida para outra tela ou Chrome reativado — e não quando o brilho muda.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>HDR</v>
+        <v>{stops} stops (≈{ratio}× SDR white)</v>
       </c>
       <c r="B424" t="str">
-        <v>HDR</v>
+        <v>{stops} stops (≈{ratio}× o branco SDR)</v>
       </c>
       <c r="C424" t="str">
-        <v>HDR</v>
+        <v>{stops} stops (≈{ratio}× o branco SDR)</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Gain at a display headroom</v>
+        <v>HDR</v>
       </c>
       <c r="B425" t="str">
-        <v>Ganho para uma margem do ecrã</v>
+        <v>HDR</v>
       </c>
       <c r="C425" t="str">
-        <v>Ganho para uma margem da tela</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
+        <v>Gain at a display headroom</v>
       </c>
       <c r="B426" t="str">
-        <v>Veja uma imagem HDR neste ecrã. Os ficheiros que o navegador consegue descodificar são mostrados pelo próprio navegador; o OpenEXR e o Radiance HDR são descodificados e apresentados pelo profiletool.</v>
+        <v>Ganho para uma margem do ecrã</v>
       </c>
       <c r="C426" t="str">
-        <v>Veja uma imagem HDR nesta tela. Arquivos que o navegador consegue decodificar são exibidos pelo próprio navegador; o OpenEXR e o Radiance HDR são decodificados e renderizados pelo profiletool.</v>
+        <v>Ganho para uma margem da tela</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Drop an HDR image here, or click to choose one</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
       </c>
       <c r="B427" t="str">
-        <v>Largue aqui uma imagem HDR ou clique para escolher uma</v>
+        <v>Veja uma imagem HDR neste ecrã. Os ficheiros que o navegador consegue descodificar são mostrados pelo próprio navegador; o OpenEXR e o Radiance HDR são descodificados e apresentados pelo profiletool.</v>
       </c>
       <c r="C427" t="str">
-        <v>Solte uma imagem HDR aqui ou clique para escolher uma</v>
+        <v>Veja uma imagem HDR nesta tela. Arquivos que o navegador consegue decodificar são exibidos pelo próprio navegador; o OpenEXR e o Radiance HDR são decodificados e renderizados pelo profiletool.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
+        <v>Drop an HDR image here, or click to choose one</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (incluindo JPEG com gain map), PNG — e HEIC e JPEG XL no Safari.</v>
+        <v>Largue aqui uma imagem HDR ou clique para escolher uma</v>
       </c>
       <c r="C428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (incluindo JPEG com gain map), PNG — e HEIC e JPEG XL no Safari.</v>
+        <v>Solte uma imagem HDR aqui ou clique para escolher uma</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Choose another</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
       </c>
       <c r="B429" t="str">
-        <v>Escolher outra</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (incluindo JPEG com gain map), PNG — e HEIC e JPEG XL no Safari.</v>
       </c>
       <c r="C429" t="str">
-        <v>Escolher outra</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (incluindo JPEG com gain map), PNG — e HEIC e JPEG XL no Safari.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Clear</v>
+        <v>Choose another</v>
       </c>
       <c r="B430" t="str">
-        <v>Limpar</v>
+        <v>Escolher outra</v>
       </c>
       <c r="C430" t="str">
-        <v>Limpar</v>
+        <v>Escolher outra</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Embedded ICC profile</v>
+        <v>Clear</v>
       </c>
       <c r="B431" t="str">
-        <v>Perfil ICC incorporado</v>
+        <v>Limpar</v>
       </c>
       <c r="C431" t="str">
-        <v>Perfil ICC incorporado</v>
+        <v>Limpar</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>none — OpenEXR states colour through chromaticities</v>
+        <v>Embedded ICC profile</v>
       </c>
       <c r="B432" t="str">
-        <v>nenhum — o OpenEXR indica a cor através de cromaticidades</v>
+        <v>Perfil ICC incorporado</v>
       </c>
       <c r="C432" t="str">
-        <v>nenhum — o OpenEXR informa a cor por cromaticidades</v>
+        <v>Perfil ICC incorporado</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
+        <v>none — OpenEXR states colour through chromaticities</v>
       </c>
       <c r="B433" t="str">
-        <v>nenhum — o Radiance HDR indica a cor através do cabeçalho PRIMARIES</v>
+        <v>nenhum — o OpenEXR indica a cor através de cromaticidades</v>
       </c>
       <c r="C433" t="str">
-        <v>nenhum — o Radiance HDR informa a cor pelo cabeçalho PRIMARIES</v>
+        <v>nenhum — o OpenEXR informa a cor por cromaticidades</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>checking…</v>
+        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
       </c>
       <c r="B434" t="str">
-        <v>a verificar…</v>
+        <v>nenhum — o Radiance HDR indica a cor através do cabeçalho PRIMARIES</v>
       </c>
       <c r="C434" t="str">
-        <v>verificando…</v>
+        <v>nenhum — o Radiance HDR informa a cor pelo cabeçalho PRIMARIES</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>none</v>
+        <v>checking…</v>
       </c>
       <c r="B435" t="str">
-        <v>nenhum</v>
+        <v>a verificar…</v>
       </c>
       <c r="C435" t="str">
-        <v>nenhum</v>
+        <v>verificando…</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Open in Profile tab</v>
+        <v>none</v>
       </c>
       <c r="B436" t="str">
-        <v>Abrir no separador Perfil</v>
+        <v>nenhum</v>
       </c>
       <c r="C436" t="str">
-        <v>Abrir na aba Perfil</v>
+        <v>nenhum</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Gain map</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B437" t="str">
-        <v>Mapa de ganho</v>
+        <v>Abrir no separador Perfil</v>
       </c>
       <c r="C437" t="str">
-        <v>Mapa de ganho</v>
+        <v>Abrir na aba Perfil</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>detected, not decoded</v>
+        <v>Gain map</v>
       </c>
       <c r="B438" t="str">
-        <v>detetado, não descodificado</v>
+        <v>Mapa de ganho</v>
       </c>
       <c r="C438" t="str">
-        <v>detectado, não decodificado</v>
+        <v>Mapa de ganho</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>That is not an image. Load profiles through the Profiles pane.</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B439" t="str">
-        <v>Isso não é uma imagem. Carregue perfis através do painel Perfis.</v>
+        <v>detetado, não descodificado</v>
       </c>
       <c r="C439" t="str">
-        <v>Isso não é uma imagem. Carregue perfis pelo painel Perfis.</v>
+        <v>detectado, não decodificado</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Not an image format profiletool recognises.</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B440" t="str">
-        <v>Não é um formato de imagem que o profiletool reconheça.</v>
+        <v>Isso não é uma imagem. Carregue perfis através do painel Perfis.</v>
       </c>
       <c r="C440" t="str">
-        <v>Não é um formato de imagem que o profiletool reconheça.</v>
+        <v>Isso não é uma imagem. Carregue perfis pelo painel Perfis.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B441" t="str">
-        <v>Os píxeis TIFF ainda não são mostrados aqui: os navegadores não descodificam TIFF, e a forma de codificar HDR num TIFF de 16 bits ainda não está decidida (fase 4.3). O perfil incorporado pode ser inspecionado.</v>
+        <v>Não é um formato de imagem que o profiletool reconheça.</v>
       </c>
       <c r="C441" t="str">
-        <v>Os pixels TIFF ainda não são exibidos aqui: os navegadores não decodificam TIFF, e a forma de codificar HDR em um TIFF de 16 bits ainda não foi decidida (fase 4.3). O perfil incorporado pode ser inspecionado.</v>
+        <v>Não é um formato de imagem que o profiletool reconheça.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Cannot display this image here:</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B442" t="str">
-        <v>Não é possível mostrar esta imagem aqui:</v>
+        <v>Os píxeis TIFF ainda não são mostrados aqui: os navegadores não descodificam TIFF, e a forma de codificar HDR num TIFF de 16 bits ainda não está decidida (fase 4.3). O perfil incorporado pode ser inspecionado.</v>
       </c>
       <c r="C442" t="str">
-        <v>Não é possível exibir esta imagem aqui:</v>
+        <v>Os pixels TIFF ainda não são exibidos aqui: os navegadores não decodificam TIFF, e a forma de codificar HDR em um TIFF de 16 bits ainda não foi decidida (fase 4.3). O perfil incorporado pode ser inspecionado.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Its embedded profile can still be inspected.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B443" t="str">
-        <v>O perfil incorporado pode ainda assim ser inspecionado.</v>
+        <v>Não é possível mostrar esta imagem aqui:</v>
       </c>
       <c r="C443" t="str">
-        <v>O perfil incorporado ainda pode ser inspecionado.</v>
+        <v>Não é possível exibir esta imagem aqui:</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Shown by</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B444" t="str">
-        <v>Mostrado por</v>
+        <v>O perfil incorporado pode ainda assim ser inspecionado.</v>
       </c>
       <c r="C444" t="str">
-        <v>Exibido por</v>
+        <v>O perfil incorporado ainda pode ser inspecionado.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>the browser</v>
+        <v>Shown by</v>
       </c>
       <c r="B445" t="str">
-        <v>o navegador</v>
+        <v>Mostrado por</v>
       </c>
       <c r="C445" t="str">
-        <v>o navegador</v>
+        <v>Exibido por</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>profiletool</v>
+        <v>the browser</v>
       </c>
       <c r="B446" t="str">
-        <v>profiletool</v>
+        <v>o navegador</v>
       </c>
       <c r="C446" t="str">
-        <v>profiletool</v>
+        <v>o navegador</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>HDR display</v>
+        <v>profiletool</v>
       </c>
       <c r="B447" t="str">
-        <v>Ecrã HDR</v>
+        <v>profiletool</v>
       </c>
       <c r="C447" t="str">
-        <v>Tela HDR</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
+        <v>HDR display</v>
       </c>
       <c r="B448" t="str">
-        <v>Os navegadores ignoram o HDR indicado apenas por um perfil ICC incorporado, pelo que esta imagem pode parecer baça e plana.</v>
+        <v>Ecrã HDR</v>
       </c>
       <c r="C448" t="str">
-        <v>Os navegadores ignoram HDR indicado apenas por um perfil ICC incorporado, então esta imagem pode parecer apagada e sem contraste.</v>
+        <v>Tela HDR</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B449" t="str">
-        <v>Este navegador não consegue alternar uma imagem entre SDR e HDR, pelo que é mostrada tal como o navegador a apresenta.</v>
+        <v>Os navegadores ignoram o HDR indicado apenas por um perfil ICC incorporado, pelo que esta imagem pode parecer baça e plana.</v>
       </c>
       <c r="C449" t="str">
-        <v>Este navegador não consegue alternar uma imagem entre SDR e HDR, então ela é exibida como o navegador a renderiza.</v>
+        <v>Os navegadores ignoram HDR indicado apenas por um perfil ICC incorporado, então esta imagem pode parecer apagada e sem contraste.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>The browser could not decode this image.</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B450" t="str">
-        <v>O navegador não conseguiu descodificar esta imagem.</v>
+        <v>Este navegador não consegue alternar uma imagem entre SDR e HDR, pelo que é mostrada tal como o navegador a apresenta.</v>
       </c>
       <c r="C450" t="str">
-        <v>O navegador não conseguiu decodificar esta imagem.</v>
+        <v>Este navegador não consegue alternar uma imagem entre SDR e HDR, então ela é exibida como o navegador a renderiza.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Output</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B451" t="str">
-        <v>Saída</v>
+        <v>O navegador não conseguiu descodificar esta imagem.</v>
       </c>
       <c r="C451" t="str">
-        <v>Saída</v>
+        <v>O navegador não conseguiu decodificar esta imagem.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>HDR canvas (float16)</v>
+        <v>Output</v>
       </c>
       <c r="B452" t="str">
-        <v>Canvas HDR (float16)</v>
+        <v>Saída</v>
       </c>
       <c r="C452" t="str">
-        <v>Canvas HDR (float16)</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>WebGPU (extended range)</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B453" t="str">
-        <v>WebGPU (gama alargada)</v>
+        <v>Canvas HDR (float16)</v>
       </c>
       <c r="C453" t="str">
-        <v>WebGPU (faixa estendida)</v>
+        <v>Canvas HDR (float16)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>SDR canvas (tone-mapped)</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B454" t="str">
-        <v>Canvas SDR (tone mapping)</v>
+        <v>WebGPU (gama alargada)</v>
       </c>
       <c r="C454" t="str">
-        <v>Canvas SDR (tone mapping)</v>
+        <v>WebGPU (faixa estendida)</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Size</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B455" t="str">
-        <v>Tamanho</v>
+        <v>Canvas SDR (tone mapping)</v>
       </c>
       <c r="C455" t="str">
-        <v>Tamanho</v>
+        <v>Canvas SDR (tone mapping)</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Brightest pixel</v>
+        <v>Size</v>
       </c>
       <c r="B456" t="str">
-        <v>Píxel mais brilhante</v>
+        <v>Tamanho</v>
       </c>
       <c r="C456" t="str">
-        <v>Pixel mais brilhante</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>{n}× SDR white</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B457" t="str">
-        <v>{n}× o branco SDR</v>
+        <v>Píxel mais brilhante</v>
       </c>
       <c r="C457" t="str">
-        <v>{n}× o branco SDR</v>
+        <v>Pixel mais brilhante</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Chromaticities</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B458" t="str">
-        <v>Cromaticidades</v>
+        <v>{n}× o branco SDR</v>
       </c>
       <c r="C458" t="str">
-        <v>Cromaticidades</v>
+        <v>{n}× o branco SDR</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>not stated — Rec. 709 assumed</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B459" t="str">
-        <v>não indicadas — assume-se Rec. 709</v>
+        <v>Cromaticidades</v>
       </c>
       <c r="C459" t="str">
-        <v>não informadas — assume-se Rec. 709</v>
+        <v>Cromaticidades</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>{from} was not available here ({why}); using the next output.</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B460" t="str">
-        <v>{from} não está disponível aqui ({why}); é usada a saída seguinte.</v>
+        <v>não indicadas — assume-se Rec. 709</v>
       </c>
       <c r="C460" t="str">
-        <v>{from} não está disponível aqui ({why}); usando a próxima saída.</v>
+        <v>não informadas — assume-se Rec. 709</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B461" t="str">
-        <v>Esta saída não consegue transportar valores mais brilhantes do que o branco, pelo que é mostrada a apresentação SDR com tone mapping.</v>
+        <v>{from} não está disponível aqui ({why}); é usada a saída seguinte.</v>
       </c>
       <c r="C461" t="str">
-        <v>Esta saída não consegue transportar valores mais brilhantes que o branco, então é exibida a renderização SDR com tone mapping.</v>
+        <v>{from} não está disponível aqui ({why}); usando a próxima saída.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Exposure</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B462" t="str">
-        <v>Exposição</v>
+        <v>Esta saída não consegue transportar valores mais brilhantes do que o branco, pelo que é mostrada a apresentação SDR com tone mapping.</v>
       </c>
       <c r="C462" t="str">
-        <v>Exposição</v>
+        <v>Esta saída não consegue transportar valores mais brilhantes que o branco, então é exibida a renderização SDR com tone mapping.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>{n} stops</v>
+        <v>Exposure</v>
       </c>
       <c r="B463" t="str">
-        <v>{n} stops</v>
+        <v>Exposição</v>
       </c>
       <c r="C463" t="str">
-        <v>{n} stops</v>
+        <v>Exposição</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Could not decode:</v>
+        <v>{n} stops</v>
       </c>
       <c r="B464" t="str">
-        <v>Não foi possível descodificar:</v>
+        <v>{n} stops</v>
       </c>
       <c r="C464" t="str">
-        <v>Não foi possível decodificar:</v>
+        <v>{n} stops</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B465" t="str">
-        <v>Este ficheiro tem {size} MB; o separador HDR abre imagens até {max} MB.</v>
+        <v>Não foi possível descodificar:</v>
       </c>
       <c r="C465" t="str">
-        <v>Este arquivo tem {size} MB; a aba HDR abre imagens de até {max} MB.</v>
+        <v>Não foi possível decodificar:</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Could not apply the profile:</v>
+        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
       </c>
       <c r="B466" t="str">
-        <v>Não foi possível aplicar o perfil:</v>
+        <v>Este ficheiro tem {size} MB; o separador HDR abre imagens até {max} MB.</v>
       </c>
       <c r="C466" t="str">
-        <v>Não foi possível aplicar o perfil:</v>
+        <v>Este arquivo tem {size} MB; a aba HDR abre imagens de até {max} MB.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Could not draw the image:</v>
+        <v>Could not apply the profile:</v>
       </c>
       <c r="B467" t="str">
-        <v>Não foi possível desenhar a imagem:</v>
+        <v>Não foi possível aplicar o perfil:</v>
       </c>
       <c r="C467" t="str">
-        <v>Não foi possível desenhar a imagem:</v>
+        <v>Não foi possível aplicar o perfil:</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
+        <v>Could not draw the image:</v>
       </c>
       <c r="B468" t="str">
-        <v>(estes primários não definem um espaço de cor — ignorados, usa-se Rec. 709)</v>
+        <v>Não foi possível desenhar a imagem:</v>
       </c>
       <c r="C468" t="str">
-        <v>(estas primárias não definem um espaço de cor — ignoradas, usa-se Rec. 709)</v>
+        <v>Não foi possível desenhar a imagem:</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
+        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
       </c>
       <c r="B469" t="str">
-        <v>o perfil de um JPEG XL está comprimido dentro do codestream, que o profiletool ainda não descomprime</v>
+        <v>(estes primários não definem um espaço de cor — ignorados, usa-se Rec. 709)</v>
       </c>
       <c r="C469" t="str">
-        <v>o perfil de um JPEG XL fica comprimido dentro do codestream, que o profiletool ainda não descomprime</v>
+        <v>(estas primárias não definem um espaço de cor — ignoradas, usa-se Rec. 709)</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Decoding…</v>
+        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
       </c>
       <c r="B470" t="str">
-        <v>A descodificar…</v>
+        <v>o perfil de um JPEG XL está comprimido dentro do codestream, que o profiletool ainda não descomprime</v>
       </c>
       <c r="C470" t="str">
-        <v>Decodificando…</v>
+        <v>o perfil de um JPEG XL fica comprimido dentro do codestream, que o profiletool ainda não descomprime</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Dynamic range</v>
+        <v>Decoding…</v>
       </c>
       <c r="B471" t="str">
-        <v>Gama dinâmica</v>
+        <v>A descodificar…</v>
       </c>
       <c r="C471" t="str">
-        <v>Faixa dinâmica</v>
+        <v>Decodificando…</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B472" t="str">
-        <v>Este navegador só oferece os dois extremos, não uma mistura.</v>
+        <v>Gama dinâmica</v>
       </c>
       <c r="C472" t="str">
-        <v>Este navegador oferece apenas os dois extremos, não uma mistura.</v>
+        <v>Faixa dinâmica</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B473" t="str">
-        <v>descodificado pelo próprio profiletool, portanto independente do navegador</v>
+        <v>Este navegador só oferece os dois extremos, não uma mistura.</v>
       </c>
       <c r="C473" t="str">
-        <v>decodificado pelo próprio profiletool, portanto independente do navegador</v>
+        <v>Este navegador oferece apenas os dois extremos, não uma mistura.</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this browser decodes it</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B474" t="str">
-        <v>este navegador descodifica-o</v>
+        <v>descodificado pelo próprio profiletool, portanto independente do navegador</v>
       </c>
       <c r="C474" t="str">
-        <v>este navegador o decodifica</v>
+        <v>decodificado pelo próprio profiletool, portanto independente do navegador</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>this browser does not decode it</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B475" t="str">
-        <v>este navegador não o descodifica</v>
+        <v>este navegador descodifica-o</v>
       </c>
       <c r="C475" t="str">
-        <v>este navegador não o decodifica</v>
+        <v>este navegador o decodifica</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B476" t="str">
-        <v>mostrar HEIC requer o Safari ou outro navegador WebKit — o Chrome e o Firefox não descodificam HEIC em nenhuma plataforma, incluindo o macOS</v>
+        <v>este navegador não o descodifica</v>
       </c>
       <c r="C476" t="str">
-        <v>exibir HEIC requer o Safari ou outro navegador WebKit — Chrome e Firefox não decodificam HEIC em nenhuma plataforma, inclusive no macOS</v>
+        <v>este navegador não o decodifica</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B477" t="str">
-        <v>mostrar JPEG XL requer o Safari; os outros navegadores ainda não o suportam</v>
+        <v>mostrar HEIC requer o Safari ou outro navegador WebKit — o Chrome e o Firefox não descodificam HEIC em nenhuma plataforma, incluindo o macOS</v>
       </c>
       <c r="C477" t="str">
-        <v>exibir JPEG XL requer o Safari; outros navegadores ainda não o suportam</v>
+        <v>exibir HEIC requer o Safari ou outro navegador WebKit — Chrome e Firefox não decodificam HEIC em nenhuma plataforma, inclusive no macOS</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>deferred to a later release</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B478" t="str">
-        <v>adiado para uma versão posterior</v>
+        <v>mostrar JPEG XL requer o Safari; os outros navegadores ainda não o suportam</v>
       </c>
       <c r="C478" t="str">
-        <v>adiado para uma versão futura</v>
+        <v>exibir JPEG XL requer o Safari; outros navegadores ainda não o suportam</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B479" t="str">
-        <v>este ecrã não indica nenhum caminho HDR, pelo que o HDR é apresentado em SDR com tone mapping</v>
+        <v>adiado para uma versão posterior</v>
       </c>
       <c r="C479" t="str">
-        <v>esta tela não informa nenhum caminho HDR, então o HDR é exibido em SDR com tone mapping</v>
+        <v>adiado para uma versão futura</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B480" t="str">
-        <v>este navegador não oferece um canvas HDR (requer canvas float16 ou WebGPU)</v>
+        <v>este ecrã não indica nenhum caminho HDR, pelo que o HDR é apresentado em SDR com tone mapping</v>
       </c>
       <c r="C480" t="str">
-        <v>este navegador não oferece um canvas HDR (requer canvas float16 ou WebGPU)</v>
+        <v>esta tela não informa nenhum caminho HDR, então o HDR é exibido em SDR com tone mapping</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B481" t="str">
-        <v>o Firefox não mostra imagens HDR nem lê gain maps; o conteúdo HDR é mostrado em SDR</v>
+        <v>este navegador não oferece um canvas HDR (requer canvas float16 ou WebGPU)</v>
       </c>
       <c r="C481" t="str">
-        <v>o Firefox não exibe imagens HDR nem lê gain maps; o conteúdo HDR é exibido em SDR</v>
+        <v>este navegador não oferece um canvas HDR (requer canvas float16 ou WebGPU)</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B482" t="str">
-        <v>a inspeção só precisa de analisar o contentor, não de um codec</v>
+        <v>o Firefox não mostra imagens HDR nem lê gain maps; o conteúdo HDR é mostrado em SDR</v>
       </c>
       <c r="C482" t="str">
-        <v>a inspeção só precisa analisar o contêiner, não de um codec</v>
+        <v>o Firefox não exibe imagens HDR nem lê gain maps; o conteúdo HDR é exibido em SDR</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B483" t="str">
-        <v>ecrã HDR e canvas HDR estão ambos disponíveis</v>
+        <v>a inspeção só precisa de analisar o contentor, não de um codec</v>
       </c>
       <c r="C483" t="str">
-        <v>tela HDR e canvas HDR estão disponíveis</v>
+        <v>a inspeção só precisa analisar o contêiner, não de um codec</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>unknown format</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B484" t="str">
-        <v>formato desconhecido</v>
+        <v>ecrã HDR e canvas HDR estão ambos disponíveis</v>
       </c>
       <c r="C484" t="str">
-        <v>formato desconhecido</v>
+        <v>tela HDR e canvas HDR estão disponíveis</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>{browser} on {os}</v>
+        <v>unknown format</v>
       </c>
       <c r="B485" t="str">
-        <v>{browser} em {os}</v>
+        <v>formato desconhecido</v>
       </c>
       <c r="C485" t="str">
-        <v>{browser} no {os}</v>
+        <v>formato desconhecido</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B486" t="str">
-        <v>{name} · ecrã HDR detetado</v>
+        <v>{browser} em {os}</v>
       </c>
       <c r="C486" t="str">
-        <v>{name} · tela HDR detectada</v>
+        <v>{browser} no {os}</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>{name} · SDR display</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B487" t="str">
-        <v>{name} · ecrã SDR</v>
+        <v>{name} · ecrã HDR detetado</v>
       </c>
       <c r="C487" t="str">
-        <v>{name} · tela SDR</v>
+        <v>{name} · tela HDR detectada</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B488" t="str">
-        <v>O WebGPU aplicou o tone mapping «{mode}», pelo que a saída fica limitada a SDR</v>
+        <v>{name} · ecrã SDR</v>
       </c>
       <c r="C488" t="str">
-        <v>O WebGPU aplicou o tone mapping “{mode}”, então a saída fica limitada a SDR</v>
+        <v>{name} · tela SDR</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B489" t="str">
-        <v>Este navegador não indica o tone mapping WebGPU aplicado, pelo que a saída HDR não está confirmada</v>
+        <v>O WebGPU aplicou o tone mapping «{mode}», pelo que a saída fica limitada a SDR</v>
       </c>
       <c r="C489" t="str">
-        <v>Este navegador não informa o tone mapping WebGPU aplicado, então a saída HDR não está confirmada</v>
+        <v>O WebGPU aplicou o tone mapping “{mode}”, então a saída fica limitada a SDR</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Display peak</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B490" t="str">
-        <v>Pico do ecrã</v>
+        <v>Este navegador não indica o tone mapping WebGPU aplicado, pelo que a saída HDR não está confirmada</v>
       </c>
       <c r="C490" t="str">
-        <v>Pico da tela</v>
+        <v>Este navegador não informa o tone mapping WebGPU aplicado, então a saída HDR não está confirmada</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>Display peak</v>
       </c>
       <c r="B491" t="str">
-        <v>{r}× o branco SDR ({n} stops)</v>
+        <v>Pico do ecrã</v>
       </c>
       <c r="C491" t="str">
-        <v>{r}× o branco SDR ({n} stops)</v>
+        <v>Pico da tela</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>1× — SDR display</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B492" t="str">
-        <v>1× — ecrã SDR</v>
+        <v>{r}× o branco SDR ({n} stops)</v>
       </c>
       <c r="C492" t="str">
-        <v>1× — tela SDR</v>
+        <v>{r}× o branco SDR ({n} stops)</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>not known</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B493" t="str">
-        <v>desconhecido</v>
+        <v>1× — ecrã SDR</v>
       </c>
       <c r="C493" t="str">
-        <v>desconhecido</v>
+        <v>1× — tela SDR</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>not known</v>
       </c>
       <c r="B494" t="str">
-        <v>Este ecrã não indica HDR, pelo que o navegador mostra a imagem em SDR em ambos os extremos.</v>
+        <v>desconhecido</v>
       </c>
       <c r="C494" t="str">
-        <v>Esta tela não informa HDR, então o navegador exibe a imagem em SDR nos dois extremos.</v>
+        <v>desconhecido</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B495" t="str">
-        <v>Este ecrã não indica HDR, pelo que tudo o que for mais brilhante do que o branco SDR é cortado. «Ajustar ao ecrã» mostra antes a apresentação com tone mapping.</v>
+        <v>Este ecrã não indica HDR, pelo que o navegador mostra a imagem em SDR em ambos os extremos.</v>
       </c>
       <c r="C495" t="str">
-        <v>Esta tela não informa HDR, então tudo que for mais brilhante que o branco SDR é cortado. “Ajustar à tela” exibe a renderização com tone mapping.</v>
+        <v>Esta tela não informa HDR, então o navegador exibe a imagem em SDR nos dois extremos.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B496" t="str">
-        <v>Esta imagem pede {img}× o branco SDR, mas este ecrã só chega a {disp}×, pelo que os valores mais brilhantes são cortados. «Ajustar ao ecrã» suaviza-os até ao pico do ecrã.</v>
+        <v>Este ecrã não indica HDR, pelo que tudo o que for mais brilhante do que o branco SDR é cortado. «Ajustar ao ecrã» mostra antes a apresentação com tone mapping.</v>
       </c>
       <c r="C496" t="str">
-        <v>Esta imagem pede {img}× o branco SDR, mas esta tela só chega a {disp}×, então valores mais brilhantes são cortados. “Ajustar à tela” os suaviza até o pico da tela.</v>
+        <v>Esta tela não informa HDR, então tudo que for mais brilhante que o branco SDR é cortado. “Ajustar à tela” exibe a renderização com tone mapping.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Fit to display</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B497" t="str">
-        <v>Ajustar ao ecrã</v>
+        <v>Esta imagem pede {img}× o branco SDR, mas este ecrã só chega a {disp}×, pelo que os valores mais brilhantes são cortados. «Ajustar ao ecrã» suaviza-os até ao pico do ecrã.</v>
       </c>
       <c r="C497" t="str">
-        <v>Ajustar à tela</v>
+        <v>Esta imagem pede {img}× o branco SDR, mas esta tela só chega a {disp}×, então valores mais brilhantes são cortados. “Ajustar à tela” os suaviza até o pico da tela.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Image details</v>
+        <v>Fit to display</v>
       </c>
       <c r="B498" t="str">
-        <v>Detalhes da imagem</v>
+        <v>Ajustar ao ecrã</v>
       </c>
       <c r="C498" t="str">
-        <v>Detalhes da imagem</v>
+        <v>Ajustar à tela</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
+        <v>Image details</v>
       </c>
       <c r="B499" t="str">
-        <v>indisponível — o navegador apresenta esta imagem e não a consegue limitar a um pico definido</v>
+        <v>Detalhes da imagem</v>
       </c>
       <c r="C499" t="str">
-        <v>indisponível — o navegador renderiza esta imagem e não consegue limitá-la a um pico definido</v>
+        <v>Detalhes da imagem</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>not available — this output shows nothing above SDR white</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B500" t="str">
-        <v>indisponível — esta saída não mostra nada acima do branco SDR</v>
+        <v>indisponível — o navegador apresenta esta imagem e não a consegue limitar a um pico definido</v>
       </c>
       <c r="C500" t="str">
-        <v>indisponível — esta saída não mostra nada acima do branco SDR</v>
+        <v>indisponível — o navegador renderiza esta imagem e não consegue limitá-la a um pico definido</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>not available — this display’s peak is not known</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B501" t="str">
-        <v>indisponível — o pico deste ecrã não é conhecido</v>
+        <v>indisponível — esta saída não mostra nada acima do branco SDR</v>
       </c>
       <c r="C501" t="str">
-        <v>indisponível — o pico desta tela não é conhecido</v>
+        <v>indisponível — esta saída não mostra nada acima do branco SDR</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Zoom in</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B502" t="str">
-        <v>Aproximar</v>
+        <v>indisponível — o pico deste ecrã não é conhecido</v>
       </c>
       <c r="C502" t="str">
-        <v>Aproximar</v>
+        <v>indisponível — o pico desta tela não é conhecido</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Zoom out</v>
+        <v>Zoom in</v>
       </c>
       <c r="B503" t="str">
-        <v>Afastar</v>
+        <v>Aproximar</v>
       </c>
       <c r="C503" t="str">
-        <v>Afastar</v>
+        <v>Aproximar</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Fit image</v>
+        <v>Zoom out</v>
       </c>
       <c r="B504" t="str">
-        <v>Ajustar imagem</v>
+        <v>Afastar</v>
       </c>
       <c r="C504" t="str">
-        <v>Ajustar imagem</v>
+        <v>Afastar</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Actual pixels (1:1)</v>
+        <v>Fit image</v>
       </c>
       <c r="B505" t="str">
-        <v>Píxeis reais (1:1)</v>
+        <v>Ajustar imagem</v>
       </c>
       <c r="C505" t="str">
-        <v>Pixels reais (1:1)</v>
+        <v>Ajustar imagem</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B506" t="str">
-        <v>Arraste para deslocar · Ctrl+roda para zoom · duplo clique para repor</v>
+        <v>Píxeis reais (1:1)</v>
       </c>
       <c r="C506" t="str">
-        <v>Arraste para mover · Ctrl+roda para zoom · clique duplo para redefinir</v>
+        <v>Pixels reais (1:1)</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Drag to resize the image area; double-click to restore the default size</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B507" t="str">
-        <v>Arraste para redimensionar a área da imagem; duplo clique para repor o tamanho predefinido</v>
+        <v>Arraste para deslocar · Ctrl+roda para zoom · duplo clique para repor</v>
       </c>
       <c r="C507" t="str">
-        <v>Arraste para redimensionar a área da imagem; clique duplo para voltar ao tamanho padrão</v>
+        <v>Arraste para mover · Ctrl+roda para zoom · clique duplo para redefinir</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Image view</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B508" t="str">
-        <v>Vista da imagem</v>
+        <v>Arraste para redimensionar a área da imagem; duplo clique para repor o tamanho predefinido</v>
       </c>
       <c r="C508" t="str">
-        <v>Visualização da imagem</v>
+        <v>Arraste para redimensionar a área da imagem; clique duplo para voltar ao tamanho padrão</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Image view</v>
       </c>
       <c r="B509" t="str">
-        <v>Limita o brilho ao pico que este ecrã indica. No Windows esse valor pode atrasar-se face às mudanças de brilho.</v>
+        <v>Vista da imagem</v>
       </c>
       <c r="C509" t="str">
-        <v>Limita o brilho ao pico que esta tela informa. No Windows esse valor pode ficar atrasado em relação às mudanças de brilho.</v>
+        <v>Visualização da imagem</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>no limit</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B510" t="str">
-        <v>sem limite</v>
+        <v>Limita o brilho ao pico que este ecrã indica. No Windows esse valor pode atrasar-se face às mudanças de brilho.</v>
       </c>
       <c r="C510" t="str">
-        <v>sem limite</v>
+        <v>Limita o brilho ao pico que esta tela informa. No Windows esse valor pode ficar atrasado em relação às mudanças de brilho.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>no limit</v>
       </c>
       <c r="B511" t="str">
-        <v>limite {n} stops ({r}×)</v>
+        <v>sem limite</v>
       </c>
       <c r="C511" t="str">
-        <v>limite {n} stops ({r}×)</v>
+        <v>sem limite</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>SDR white</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B512" t="str">
-        <v>Branco SDR</v>
+        <v>limite {n} stops ({r}×)</v>
       </c>
       <c r="C512" t="str">
-        <v>Branco SDR</v>
+        <v>limite {n} stops ({r}×)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>SDR white</v>
       </c>
       <c r="B513" t="str">
-        <v>Branco SDR simples, para comparação. Num ecrã HDR, as altas luzes HDR parecem mais brilhantes do que este.</v>
+        <v>Branco SDR</v>
       </c>
       <c r="C513" t="str">
-        <v>Branco SDR simples, para comparação. Em uma tela HDR, os realces HDR parecem mais brilhantes que este.</v>
+        <v>Branco SDR</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>SDR white patch</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B514" t="str">
-        <v>Amostra de branco SDR</v>
+        <v>Branco SDR simples, para comparação. Num ecrã HDR, as altas luzes HDR parecem mais brilhantes do que este.</v>
       </c>
       <c r="C514" t="str">
-        <v>Amostra de branco SDR</v>
+        <v>Branco SDR simples, para comparação. Em uma tela HDR, os realces HDR parecem mais brilhantes que este.</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B515" t="str">
-        <v>Arraste para a mover; faça duplo clique para a repor junto à imagem.</v>
+        <v>Amostra de branco SDR</v>
       </c>
       <c r="C515" t="str">
-        <v>Arraste para movê-la; clique duas vezes para colocá-la de volta ao lado da imagem.</v>
+        <v>Amostra de branco SDR</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Assign profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B516" t="str">
-        <v>Atribuir perfil</v>
+        <v>Arraste para a mover; faça duplo clique para a repor junto à imagem.</v>
       </c>
       <c r="C516" t="str">
-        <v>Atribuir perfil</v>
+        <v>Arraste para movê-la; clique duas vezes para colocá-la de volta ao lado da imagem.</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>None — use what the file signals</v>
+        <v>Assign profile</v>
       </c>
       <c r="B517" t="str">
-        <v>Nenhum — o que o ficheiro indica</v>
+        <v>Atribuir perfil</v>
       </c>
       <c r="C517" t="str">
-        <v>Nenhum — o que o arquivo indica</v>
+        <v>Atribuir perfil</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B518" t="str">
-        <v>Perfil incorporado ({n} B)</v>
+        <v>Nenhum — o que o ficheiro indica</v>
       </c>
       <c r="C518" t="str">
-        <v>Perfil incorporado ({n} B)</v>
+        <v>Nenhum — o que o arquivo indica</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B519" t="str">
-        <v>Perfis HDR no pool</v>
+        <v>Perfil incorporado ({n} B)</v>
       </c>
       <c r="C519" t="str">
-        <v>Perfis HDR no pool</v>
+        <v>Perfil incorporado ({n} B)</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Profile</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B520" t="str">
-        <v>Perfil</v>
+        <v>Perfis HDR no pool</v>
       </c>
       <c r="C520" t="str">
-        <v>Perfil</v>
+        <v>Perfis HDR no pool</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>embedded profile</v>
+        <v>Profile</v>
       </c>
       <c r="B521" t="str">
-        <v>perfil incorporado</v>
+        <v>Perfil</v>
       </c>
       <c r="C521" t="str">
-        <v>perfil incorporado</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Colour engine path</v>
+        <v>embedded profile</v>
       </c>
       <c r="B522" t="str">
-        <v>Caminho do motor de cor</v>
+        <v>perfil incorporado</v>
       </c>
       <c r="C522" t="str">
-        <v>Caminho do mecanismo de cor</v>
+        <v>perfil incorporado</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B523" t="str">
-        <v>Caminho HDR, curva de ganho aplicada</v>
+        <v>Caminho do motor de cor</v>
       </c>
       <c r="C523" t="str">
-        <v>Caminho HDR, curva de ganho aplicada</v>
+        <v>Caminho do mecanismo de cor</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B524" t="str">
-        <v>Caminho HDR, sem curva de ganho</v>
+        <v>Caminho HDR, curva de ganho aplicada</v>
       </c>
       <c r="C524" t="str">
-        <v>Caminho HDR, sem curva de ganho</v>
+        <v>Caminho HDR, curva de ganho aplicada</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B525" t="str">
-        <v>AToB0 pré-calculado — não é o caminho HDR</v>
+        <v>Caminho HDR, sem curva de ganho</v>
       </c>
       <c r="C525" t="str">
-        <v>AToB0 pré-calculado — não é o caminho HDR</v>
+        <v>Caminho HDR, sem curva de ganho</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Transfer</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B526" t="str">
-        <v>Transferência</v>
+        <v>AToB0 pré-calculado — não é o caminho HDR</v>
       </c>
       <c r="C526" t="str">
-        <v>Transferência</v>
+        <v>AToB0 pré-calculado — não é o caminho HDR</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>HDR reference white</v>
+        <v>Transfer</v>
       </c>
       <c r="B527" t="str">
-        <v>Branco de referência HDR</v>
+        <v>Transferência</v>
       </c>
       <c r="C527" t="str">
-        <v>Branco de referência HDR</v>
+        <v>Transferência</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Linear values</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B528" t="str">
-        <v>Valores lineares</v>
+        <v>Branco de referência HDR</v>
       </c>
       <c r="C528" t="str">
-        <v>Valores lineares</v>
+        <v>Branco de referência HDR</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>File 1.0 = HDR reference white</v>
+        <v>Linear values</v>
       </c>
       <c r="B529" t="str">
-        <v>Ficheiro 1,0 = branco de referência HDR</v>
+        <v>Valores lineares</v>
       </c>
       <c r="C529" t="str">
-        <v>Arquivo 1,0 = branco de referência HDR</v>
+        <v>Valores lineares</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B530" t="str">
-        <v>Ficheiro 1,0 = 1 cd/m² (ICC.1 cláusula 8.10.2 a)</v>
+        <v>Ficheiro 1,0 = branco de referência HDR</v>
       </c>
       <c r="C530" t="str">
-        <v>Arquivo 1,0 = 1 cd/m² (ICC.1 cláusula 8.10.2 a)</v>
+        <v>Arquivo 1,0 = branco de referência HDR</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B531" t="str">
-        <v>Os ficheiros OpenEXR e Radiance HDR colocam por convenção o branco SDR em 1,0, enquanto uma transferência ICC linear lê 1,0 como 1 cd/m². Por predefinição, o ficheiro é escalado para que o seu 1,0 coincida com o branco de referência HDR do perfil.</v>
+        <v>Ficheiro 1,0 = 1 cd/m² (ICC.1 cláusula 8.10.2 a)</v>
       </c>
       <c r="C531" t="str">
-        <v>Arquivos OpenEXR e Radiance HDR colocam por convenção o branco SDR em 1,0, enquanto uma transferência ICC linear lê 1,0 como 1 cd/m². Por padrão, o arquivo é escalado para que seu 1,0 caia no branco de referência HDR do perfil.</v>
+        <v>Arquivo 1,0 = 1 cd/m² (ICC.1 cláusula 8.10.2 a)</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Input scale</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B532" t="str">
-        <v>Escala de entrada</v>
+        <v>Os ficheiros OpenEXR e Radiance HDR colocam por convenção o branco SDR em 1,0, enquanto uma transferência ICC linear lê 1,0 como 1 cd/m². Por predefinição, o ficheiro é escalado para que o seu 1,0 coincida com o branco de referência HDR do perfil.</v>
       </c>
       <c r="C532" t="str">
-        <v>Escala de entrada</v>
+        <v>Arquivos OpenEXR e Radiance HDR colocam por convenção o branco SDR em 1,0, enquanto uma transferência ICC linear lê 1,0 como 1 cd/m². Por padrão, o arquivo é escalado para que seu 1,0 caia no branco de referência HDR do perfil.</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>×{w} — file 1.0 = reference white</v>
+        <v>Input scale</v>
       </c>
       <c r="B533" t="str">
-        <v>×{w} — ficheiro 1,0 = branco de referência</v>
+        <v>Escala de entrada</v>
       </c>
       <c r="C533" t="str">
-        <v>×{w} — arquivo 1,0 = branco de referência</v>
+        <v>Escala de entrada</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>none — file 1.0 = 1 cd/m²</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B534" t="str">
-        <v>nenhuma — ficheiro 1,0 = 1 cd/m²</v>
+        <v>×{w} — ficheiro 1,0 = branco de referência</v>
       </c>
       <c r="C534" t="str">
-        <v>nenhuma — arquivo 1,0 = 1 cd/m²</v>
+        <v>×{w} — arquivo 1,0 = branco de referência</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Target headroom</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B535" t="str">
-        <v>Margem alvo</v>
+        <v>nenhuma — ficheiro 1,0 = 1 cd/m²</v>
       </c>
       <c r="C535" t="str">
-        <v>Margem alvo</v>
+        <v>nenhuma — arquivo 1,0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B536" t="str">
-        <v>{r}× o branco de referência ({n} stops)</v>
+        <v>Margem alvo</v>
       </c>
       <c r="C536" t="str">
-        <v>{r}× o branco de referência ({n} stops)</v>
+        <v>Margem alvo</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B537" t="str">
-        <v>Mapeamento de tons</v>
+        <v>{r}× o branco de referência ({n} stops)</v>
       </c>
       <c r="C537" t="str">
-        <v>Mapeamento de tons</v>
+        <v>{r}× o branco de referência ({n} stops)</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B538" t="str">
-        <v>Auto (ordem da cláusula 8.10.3)</v>
+        <v>Mapeamento de tons</v>
       </c>
       <c r="C538" t="str">
-        <v>Auto (ordem da cláusula 8.10.3)</v>
+        <v>Mapeamento de tons</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B539" t="str">
-        <v>Curva de ganho (HAGC)</v>
+        <v>Auto (ordem da cláusula 8.10.3)</v>
       </c>
       <c r="C539" t="str">
-        <v>Curva de ganho (HAGC)</v>
+        <v>Auto (ordem da cláusula 8.10.3)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B540" t="str">
-        <v>Alternativa SDR pré-calculada (AToB0)</v>
+        <v>Curva de ganho (HAGC)</v>
       </c>
       <c r="C540" t="str">
-        <v>Alternativa SDR pré-calculada (AToB0)</v>
+        <v>Curva de ganho (HAGC)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B541" t="str">
-        <v>Desligado — como um CMM anterior à emenda</v>
+        <v>Alternativa SDR pré-calculada (AToB0)</v>
       </c>
       <c r="C541" t="str">
-        <v>Desligado — como um CMM anterior à emenda</v>
+        <v>Alternativa SDR pré-calculada (AToB0)</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Applying the profile…</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B542" t="str">
-        <v>A aplicar o perfil…</v>
+        <v>Desligado — como um CMM anterior à emenda</v>
       </c>
       <c r="C542" t="str">
-        <v>Aplicando o perfil…</v>
+        <v>Desligado — como um CMM anterior à emenda</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B543" t="str">
-        <v>O {format} contém luz linear, pelo que precisa de um perfil com transferência Linear (8).</v>
+        <v>A aplicar o perfil…</v>
       </c>
       <c r="C543" t="str">
-        <v>O {format} contém luz linear, então precisa de um perfil com transferência Linear (8).</v>
+        <v>Aplicando o perfil…</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B544" t="str">
-        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
+        <v>O {format} contém luz linear, pelo que precisa de um perfil com transferência Linear (8).</v>
       </c>
       <c r="C544" t="str">
-        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
+        <v>O {format} contém luz linear, então precisa de um perfil com transferência Linear (8).</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B545" t="str">
-        <v>Para interpretar os seus valores, atribua um perfil acima.</v>
+        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
       </c>
       <c r="C545" t="str">
-        <v>Para interpretar seus valores, atribua um perfil acima.</v>
+        <v>Atribuir um perfil requer uma imagem RGB de 3 canais.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>HDR Profiles</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B546" t="str">
-        <v>Perfis HDR</v>
+        <v>Para interpretar os seus valores, atribua um perfil acima.</v>
       </c>
       <c r="C546" t="str">
-        <v>Perfis HDR</v>
+        <v>Para interpretar seus valores, atribua um perfil acima.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Linear transfer</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B547" t="str">
-        <v>Transferência linear</v>
+        <v>Perfis HDR</v>
       </c>
       <c r="C547" t="str">
-        <v>Transferência linear</v>
+        <v>Perfis HDR</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B548" t="str">
-        <v>Transferência não linear (PQ, HLG)</v>
+        <v>Transferência linear</v>
       </c>
       <c r="C548" t="str">
-        <v>Transferência não linear (PQ, HLG)</v>
+        <v>Transferência linear</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B549" t="str">
-        <v>Perfis HDR — transferência linear</v>
+        <v>Transferência não linear (PQ, HLG)</v>
       </c>
       <c r="C549" t="str">
-        <v>Perfis HDR — transferência linear</v>
+        <v>Transferência não linear (PQ, HLG)</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>Perfis HDR — transferência PQ / HLG</v>
+        <v>Perfis HDR — transferência linear</v>
       </c>
       <c r="C550" t="str">
-        <v>Perfis HDR — transferência PQ / HLG</v>
+        <v>Perfis HDR — transferência linear</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B551" t="str">
-        <v>O {format} contém luz linear, pelo que só podem ser atribuídos perfis HDR com transferência linear.</v>
+        <v>Perfis HDR — transferência PQ / HLG</v>
       </c>
       <c r="C551" t="str">
-        <v>O {format} contém luz linear, então só podem ser atribuídos perfis HDR com transferência linear.</v>
+        <v>Perfis HDR — transferência PQ / HLG</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B552" t="str">
-        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis lista-os em Perfis HDR › Transferência não linear.</v>
+        <v>O {format} contém luz linear, pelo que só podem ser atribuídos perfis HDR com transferência linear.</v>
       </c>
       <c r="C552" t="str">
-        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis os lista em Perfis HDR › Transferência não linear.</v>
+        <v>O {format} contém luz linear, então só podem ser atribuídos perfis HDR com transferência linear.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
+        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis lista-os em Perfis HDR › Transferência não linear.</v>
       </c>
       <c r="C553" t="str">
-        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
+        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis os lista em Perfis HDR › Transferência não linear.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B554" t="str">
-        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
+        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
       </c>
       <c r="C554" t="str">
-        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
+        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B555" t="str">
-        <v>Margem do ecrã</v>
+        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
       </c>
       <c r="C555" t="str">
-        <v>Margem da tela</v>
+        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B556" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>Margem do ecrã</v>
       </c>
       <c r="C556" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>Margem da tela</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B557" t="str">
-        <v>Base</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
       <c r="C557" t="str">
-        <v>Base</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Preview through the colour engine</v>
+        <v>Baseline</v>
       </c>
       <c r="B558" t="str">
-        <v>Pré-visualização através do motor de cor</v>
+        <v>Base</v>
       </c>
       <c r="C558" t="str">
-        <v>Pré-visualização pelo mecanismo de cor</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B559" t="str">
-        <v>Tal como criado (base {h} stops, sem ganho)</v>
+        <v>Pré-visualização através do motor de cor</v>
       </c>
       <c r="C559" t="str">
-        <v>Como criado (base {h} stops, sem ganho)</v>
+        <v>Pré-visualização pelo mecanismo de cor</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B560" t="str">
-        <v>Mapeado para {h} stops</v>
+        <v>Tal como criado (base {h} stops, sem ganho)</v>
       </c>
       <c r="C560" t="str">
-        <v>Mapeado para {h} stops</v>
+        <v>Como criado (base {h} stops, sem ganho)</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B561" t="str">
-        <v>Os mesmos píxeis de teste (sinal {transfer} a subir da esquerda para a direita: cinzento, depois R, G, B, Y, C, M) através da transformação HDR do IccProfLib. Ambas as faixas estão limitadas a {r}× o branco de referência HDR, como um ecrã com {h} stops de margem as mostraria: onde a faixa de cima satura plana, a curva de ganho suaviza as altas luzes.</v>
+        <v>Mapeado para {h} stops</v>
       </c>
       <c r="C561" t="str">
-        <v>Os mesmos pixels de teste (sinal {transfer} subindo da esquerda para a direita: cinza, depois R, G, B, Y, C, M) pela transformação HDR do IccProfLib. As duas faixas são limitadas a {r}× o branco de referência HDR, como uma tela com {h} stops de margem as mostraria: onde a faixa de cima satura plana, a curva de ganho suaviza as altas luzes.</v>
+        <v>Mapeado para {h} stops</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>reference white</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B562" t="str">
-        <v>branco de referência</v>
+        <v>Os mesmos píxeis de teste (sinal {transfer} a subir da esquerda para a direita: cinzento, depois R, G, B, Y, C, M) através da transformação HDR do IccProfLib. Ambas as faixas estão limitadas a {r}× o branco de referência HDR, como um ecrã com {h} stops de margem as mostraria: onde a faixa de cima satura plana, a curva de ganho suaviza as altas luzes.</v>
       </c>
       <c r="C562" t="str">
-        <v>branco de referência</v>
+        <v>Os mesmos pixels de teste (sinal {transfer} subindo da esquerda para a direita: cinza, depois R, G, B, Y, C, M) pela transformação HDR do IccProfLib. As duas faixas são limitadas a {r}× o branco de referência HDR, como uma tela com {h} stops de margem as mostraria: onde a faixa de cima satura plana, a curva de ganho suaviza as altas luzes.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>display peak</v>
+        <v>reference white</v>
       </c>
       <c r="B563" t="str">
-        <v>pico do ecrã</v>
+        <v>branco de referência</v>
       </c>
       <c r="C563" t="str">
-        <v>pico da tela</v>
+        <v>branco de referência</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>display peak</v>
       </c>
       <c r="B564" t="str">
-        <v>Pré-visualização indisponível: {why}</v>
+        <v>pico do ecrã</v>
       </c>
       <c r="C564" t="str">
-        <v>Pré-visualização indisponível: {why}</v>
+        <v>pico da tela</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B565" t="str">
-        <v>o motor de cor não seguiu o caminho HDR para este perfil</v>
+        <v>Pré-visualização indisponível: {why}</v>
       </c>
       <c r="C565" t="str">
-        <v>o mecanismo de cor não seguiu o caminho HDR para este perfil</v>
+        <v>Pré-visualização indisponível: {why}</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Gain across every headroom</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B566" t="str">
-        <v>Ganho em todas as margens</v>
+        <v>o motor de cor não seguiu o caminho HDR para este perfil</v>
       </c>
       <c r="C566" t="str">
-        <v>Ganho em todas as margens</v>
+        <v>o mecanismo de cor não seguiu o caminho HDR para este perfil</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B567" t="str">
-        <v>Ganho aplicado a uma entrada cinzenta em cada margem do ecrã: o azul comprime, o vermelho expande e o branco deixa-a igual. As linhas ponteadas marcam as curvas da etiqueta, a contínua a base e a âmbar o controlo; a diagonal tracejada é onde a entrada atinge o pico do ecrã. Clique para mover o controlo.</v>
+        <v>Ganho em todas as margens</v>
       </c>
       <c r="C567" t="str">
-        <v>Ganho aplicado a uma entrada cinza em cada margem da tela: azul comprime, vermelho expande e branco deixa inalterado. As linhas pontilhadas marcam as curvas da tag, a contínua a base e a âmbar o controle; a diagonal tracejada é onde a entrada atinge o pico da tela. Clique para mover o controle.</v>
+        <v>Ganho em todas as margens</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B568" t="str">
-        <v>Entrada (stops relativamente ao branco de referência HDR)</v>
+        <v>Ganho aplicado a uma entrada cinzenta em cada margem do ecrã: o azul comprime, o vermelho expande e o branco deixa-a igual. As linhas ponteadas marcam as curvas da etiqueta, a contínua a base e a âmbar o controlo; a diagonal tracejada é onde a entrada atinge o pico do ecrã. Clique para mover o controlo.</v>
       </c>
       <c r="C568" t="str">
-        <v>Entrada (stops em relação ao branco de referência HDR)</v>
+        <v>Ganho aplicado a uma entrada cinza em cada margem da tela: azul comprime, vermelho expande e branco deixa inalterado. As linhas pontilhadas marcam as curvas da tag, a contínua a base e a âmbar o controle; a diagonal tracejada é onde a entrada atinge o pico da tela. Clique para mover o controle.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B569" t="str">
-        <v>Margem do ecrã (stops)</v>
+        <v>Entrada (stops relativamente ao branco de referência HDR)</v>
       </c>
       <c r="C569" t="str">
-        <v>Margem da tela (stops)</v>
+        <v>Entrada (stops em relação ao branco de referência HDR)</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Gain (stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B570" t="str">
-        <v>Ganho (stops)</v>
+        <v>Margem do ecrã (stops)</v>
       </c>
       <c r="C570" t="str">
-        <v>Ganho (stops)</v>
+        <v>Margem da tela (stops)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B571" t="str">
-        <v>Curva na etiqueta</v>
+        <v>Ganho (stops)</v>
       </c>
       <c r="C571" t="str">
-        <v>Curva na tag</v>
+        <v>Ganho (stops)</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Baseline</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B572" t="str">
-        <v>Base</v>
+        <v>Curva na etiqueta</v>
       </c>
       <c r="C572" t="str">
-        <v>Base</v>
+        <v>Curva na tag</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Slider</v>
+        <v>Baseline</v>
       </c>
       <c r="B573" t="str">
-        <v>Controlo</v>
+        <v>Base</v>
       </c>
       <c r="C573" t="str">
-        <v>Controle</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Input = display peak</v>
+        <v>Slider</v>
       </c>
       <c r="B574" t="str">
-        <v>Entrada = pico do ecrã</v>
+        <v>Controlo</v>
       </c>
       <c r="C574" t="str">
-        <v>Entrada = pico da tela</v>
+        <v>Controle</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B575" t="str">
-        <v>Curvas tonais de cinzento por margem</v>
+        <v>Entrada = pico do ecrã</v>
       </c>
       <c r="C575" t="str">
-        <v>Curvas tonais de cinza por margem</v>
+        <v>Entrada = pico da tela</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B576" t="str">
-        <v>A curva tonal de cinzento em cada margem guardada na etiqueta, colorida de baixo (azul) para alto (vermelho), com a curva do controlo em âmbar. Ambos os eixos estão em stops, pelo que a diagonal significa sem alteração.</v>
+        <v>Curvas tonais de cinzento por margem</v>
       </c>
       <c r="C576" t="str">
-        <v>A curva tonal de cinza em cada margem armazenada na tag, colorida de baixo (azul) para alto (vermelho), com a curva do controle em âmbar. Os dois eixos estão em stops, então a diagonal significa sem alteração.</v>
+        <v>Curvas tonais de cinza por margem</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B577" t="str">
-        <v>Saída (stops relativamente ao branco de referência HDR)</v>
+        <v>A curva tonal de cinzento em cada margem guardada na etiqueta, colorida de baixo (azul) para alto (vermelho), com a curva do controlo em âmbar. Ambos os eixos estão em stops, pelo que a diagonal significa sem alteração.</v>
       </c>
       <c r="C577" t="str">
-        <v>Saída (stops em relação ao branco de referência HDR)</v>
+        <v>A curva tonal de cinza em cada margem armazenada na tag, colorida de baixo (azul) para alto (vermelho), com a curva do controle em âmbar. Os dois eixos estão em stops, então a diagonal significa sem alteração.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>{h} stops</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B578" t="str">
-        <v>{h} stops</v>
+        <v>Saída (stops relativamente ao branco de referência HDR)</v>
       </c>
       <c r="C578" t="str">
-        <v>{h} stops</v>
+        <v>Saída (stops em relação ao branco de referência HDR)</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>{h} stops</v>
       </c>
       <c r="B579" t="str">
-        <v>{h} stops (base)</v>
+        <v>{h} stops</v>
       </c>
       <c r="C579" t="str">
-        <v>{h} stops (base)</v>
+        <v>{h} stops</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B580" t="str">
-        <v>A {h} stops (controlo)</v>
+        <v>{h} stops (base)</v>
       </c>
       <c r="C580" t="str">
-        <v>Em {h} stops (controle)</v>
+        <v>{h} stops (base)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B581" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>A {h} stops (controlo)</v>
       </c>
       <c r="C581" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>Em {h} stops (controle)</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B582" t="str">
-        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
       <c r="C582" t="str">
-        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B583" t="str">
-        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
+        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
       </c>
       <c r="C583" t="str">
-        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
+        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B584" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
+        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
       </c>
       <c r="C584" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
+        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B585" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
+        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
       </c>
       <c r="C585" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
+        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B586" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
       </c>
       <c r="C586" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B587" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
       </c>
       <c r="C587" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B588" t="str">
-        <v>Curva a {h} stops</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
       <c r="C588" t="str">
-        <v>Curva a {h} stops</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B589" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Curva a {h} stops</v>
       </c>
       <c r="C589" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Curva a {h} stops</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B590" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>Aplicado a {h} stops</v>
       </c>
       <c r="C590" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>Aplicado a {h} stops</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B591" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
       <c r="C591" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B592" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
       <c r="C592" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B593" t="str">
-        <v>Curva de tons dos cinzentos nesta margem</v>
+        <v>Ganho (stops log2)</v>
       </c>
       <c r="C593" t="str">
-        <v>Curva de tons de cinza nesta margem</v>
+        <v>Ganho (stops log2)</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B594" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Curva de tons dos cinzentos nesta margem</v>
       </c>
       <c r="C594" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Curva de tons de cinza nesta margem</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B595" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
       <c r="C595" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B596" t="str">
-        <v>Sem alteração</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
       <c r="C596" t="str">
-        <v>Sem alteração</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B597" t="str">
-        <v>Pico do ecrã a {h} stops</v>
+        <v>Sem alteração</v>
       </c>
       <c r="C597" t="str">
-        <v>Pico da tela a {h} stops</v>
+        <v>Sem alteração</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B598" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Pico do ecrã a {h} stops</v>
       </c>
       <c r="C598" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Pico da tela a {h} stops</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B599" t="str">
-        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
+        <v>Saída a {h} stops</v>
       </c>
       <c r="C599" t="str">
-        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
+        <v>Saída a {h} stops</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B600" t="str">
-        <v>Identificar ecrãs</v>
+        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
       </c>
       <c r="C600" t="str">
-        <v>Identificar telas</v>
+        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B601" t="str">
-        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Identificar ecrãs</v>
       </c>
       <c r="C601" t="str">
-        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Identificar telas</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B602" t="str">
-        <v>A acompanhar em que monitor está esta janela.</v>
+        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
       <c r="C602" t="str">
-        <v>Acompanhando em qual monitor esta janela está.</v>
+        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B603" t="str">
-        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
+        <v>A acompanhar em que monitor está esta janela.</v>
       </c>
       <c r="C603" t="str">
-        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
+        <v>Acompanhando em qual monitor esta janela está.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B604" t="str">
-        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
+        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
       </c>
       <c r="C604" t="str">
-        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
+        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B605" t="str">
-        <v>Não foi possível identificar os ecrãs.</v>
+        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
       </c>
       <c r="C605" t="str">
-        <v>Não foi possível identificar as telas.</v>
+        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B606" t="str">
-        <v>Eventos de ecrã</v>
+        <v>Não foi possível identificar os ecrãs.</v>
       </c>
       <c r="C606" t="str">
-        <v>Eventos de tela</v>
+        <v>Não foi possível identificar as telas.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B607" t="str">
-        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
+        <v>Eventos de ecrã</v>
       </c>
       <c r="C607" t="str">
-        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
+        <v>Eventos de tela</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B608" t="str">
-        <v>Primárias de cor</v>
+        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
       </c>
       <c r="C608" t="str">
-        <v>Primárias de cor</v>
+        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B609" t="str">
-        <v>Características de transferência</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C609" t="str">
-        <v>Características de transferência</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B610" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C610" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B611" t="str">
-        <v>Sinalizador de gama completa de vídeo</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C611" t="str">
-        <v>Sinalizador de faixa completa de vídeo</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B612" t="str">
-        <v>Gama completa</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C612" t="str">
-        <v>Faixa completa</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B613" t="str">
-        <v>Gama reduzida</v>
+        <v>Gama completa</v>
       </c>
       <c r="C613" t="str">
-        <v>Faixa reduzida</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B614" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C614" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B615" t="str">
-        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C615" t="str">
-        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B616" t="str">
-        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C616" t="str">
-        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B617" t="str">
-        <v>RELATÓRIO</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C617" t="str">
-        <v>RELATÓRIO</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B618" t="str">
-        <v>REPROVADO</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C618" t="str">
-        <v>REPROVADO</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B619" t="str">
-        <v>verificações</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C619" t="str">
-        <v>verificações</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B620" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>verificações</v>
       </c>
       <c r="C620" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B621" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C621" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B622" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C622" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B623" t="str">
-        <v>Com {lib}</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C623" t="str">
-        <v>Com {lib}</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B624" t="str">
-        <v>Subscrever</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C624" t="str">
-        <v>Inscrever-se</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B625" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Subscrever</v>
       </c>
       <c r="C625" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B626" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C626" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B627" t="str">
-        <v>Fechar</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C627" t="str">
-        <v>Fechar</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B628" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Fechar</v>
       </c>
       <c r="C628" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B629" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C629" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B630" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C630" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B631" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C631" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B632" t="str">
-        <v>(opcional)</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C632" t="str">
-        <v>(opcional)</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B633" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>(opcional)</v>
       </c>
       <c r="C633" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B634" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C634" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B635" t="str">
-        <v>Cancelar</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C635" t="str">
-        <v>Cancelar</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B636" t="str">
-        <v>Subscrever</v>
+        <v>Cancelar</v>
       </c>
       <c r="C636" t="str">
-        <v>Inscrever-se</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B637" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C637" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B638" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C638" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B639" t="str">
-        <v>Fechar</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C639" t="str">
-        <v>Fechar</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B640" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Fechar</v>
       </c>
       <c r="C640" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B641" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C641" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B642" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C642" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B643" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C643" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B644" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C644" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C645" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B646" t="str">
-        <v>Erro:</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C646" t="str">
-        <v>Erro:</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B647" t="str">
-        <v>Converter para XML</v>
+        <v>Erro:</v>
       </c>
       <c r="C647" t="str">
-        <v>Converter para XML</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B648" t="str">
-        <v>Converter para JSON</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C648" t="str">
-        <v>Converter para JSON</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B649" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C649" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B650" t="str">
-        <v>A converter para XML…</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C650" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B651" t="str">
-        <v>A converter para JSON…</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C651" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B652" t="str">
-        <v>A converter para ICC…</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C652" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B653" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C653" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B654" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C654" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B655" t="str">
-        <v>ID do perfil</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C655" t="str">
-        <v>ID do perfil</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B656" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C656" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B657" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C657" t="str">
-        <v>Nome da tag</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B658" t="str">
-        <v>ID</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C658" t="str">
-        <v>ID</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B659" t="str">
-        <v>Deslocamento</v>
+        <v>ID</v>
       </c>
       <c r="C659" t="str">
-        <v>Deslocamento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B660" t="str">
-        <v>Tamanho</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C660" t="str">
-        <v>Tamanho</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B661" t="str">
-        <v>Preenchimento</v>
+        <v>Tamanho</v>
       </c>
       <c r="C661" t="str">
-        <v>Preenchimento</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B662" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C662" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B663" t="str">
-        <v>Tipo</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C663" t="str">
-        <v>Tipo</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B664" t="str">
-        <v>Vetor de {type}</v>
+        <v>Tipo</v>
       </c>
       <c r="C664" t="str">
-        <v>Array de {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B665" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C665" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B666" t="str">
-        <v>bytes</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C666" t="str">
-        <v>bytes</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B667" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>bytes</v>
       </c>
       <c r="C667" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B668" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C668" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B669" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C669" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B670" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C670" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B671" t="str">
-        <v>Sem saída de validação</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C671" t="str">
-        <v>Sem saída de validação</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B672" t="str">
-        <v>O perfil é válido</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C672" t="str">
-        <v>O perfil é válido</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B673" t="str">
-        <v>O perfil tem avisos</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C673" t="str">
-        <v>O perfil tem avisos</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B674" t="str">
-        <v>O perfil não é conforme</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C674" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B675" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C675" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B676" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C676" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B677" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C677" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B678" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C678" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B679" t="str">
-        <v>Válido</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C679" t="str">
-        <v>Válido</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B680" t="str">
-        <v>Aviso</v>
+        <v>Válido</v>
       </c>
       <c r="C680" t="str">
-        <v>Aviso</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B681" t="str">
-        <v>Erro</v>
+        <v>Aviso</v>
       </c>
       <c r="C681" t="str">
-        <v>Erro</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B682" t="str">
-        <v>Desconhecido</v>
+        <v>Erro</v>
       </c>
       <c r="C682" t="str">
-        <v>Desconhecido</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B683" t="str">
-        <v>Aprovado</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C683" t="str">
-        <v>Aprovado</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B684" t="str">
-        <v>Reprovado</v>
+        <v>Aprovado</v>
       </c>
       <c r="C684" t="str">
-        <v>Reprovado</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B685" t="str">
-        <v>Ver no contexto</v>
+        <v>Reprovado</v>
       </c>
       <c r="C685" t="str">
-        <v>Ver no contexto</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B686" t="str">
-        <v>Detalhe de validação</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C686" t="str">
-        <v>Detalhe de validação</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B687" t="str">
-        <v>Acionado por</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C687" t="str">
-        <v>Acionado por</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B688" t="str">
-        <v>Campo</v>
+        <v>Acionado por</v>
       </c>
       <c r="C688" t="str">
-        <v>Campo</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B689" t="str">
-        <v>Valor atual</v>
+        <v>Campo</v>
       </c>
       <c r="C689" t="str">
-        <v>Valor atual</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B690" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Valor atual</v>
       </c>
       <c r="C690" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B691" t="str">
-        <v>Esperado: {value}</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C691" t="str">
-        <v>Esperado: {value}</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B692" t="str">
-        <v>Inválido</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C692" t="str">
-        <v>Inválido</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B693" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Inválido</v>
       </c>
       <c r="C693" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B694" t="str">
-        <v>Fechar</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C694" t="str">
-        <v>Fechar</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B695" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Fechar</v>
       </c>
       <c r="C695" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B696" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C696" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B697" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C697" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B698" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C698" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B699" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C699" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B700" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>● edições XML por guardar</v>
       </c>
       <c r="C700" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>● edições XML não salvas</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B701" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições JSON por guardar</v>
       </c>
       <c r="C701" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições JSON não salvas</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B702" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
       <c r="C702" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B703" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
       <c r="C703" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B704" t="str">
-        <v>ordenar chaves</v>
+        <v>indentação</v>
       </c>
       <c r="C704" t="str">
-        <v>ordenar chaves</v>
+        <v>indentação</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B705" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C705" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B705" t="str">
+      <c r="B706" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C705" t="str">
+      <c r="C706" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C705"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C706"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C466"/>
+  <dimension ref="A1:C467"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1495,4053 +1495,4064 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sort by name</v>
+        <v>Tap to select, then tap a tab to send.</v>
       </c>
       <c r="B100" t="str">
-        <v>Ordenar por nome</v>
+        <v>Toque para selecionar e depois toque num separador para enviar.</v>
       </c>
       <c r="C100" t="str">
-        <v>Ordenar por nome</v>
+        <v>Toque para selecionar e depois toque em uma aba para enviar.</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B101" t="str">
-        <v>A–Z</v>
+        <v>Ordenar por nome</v>
       </c>
       <c r="C101" t="str">
-        <v>A–Z</v>
+        <v>Ordenar por nome</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B102" t="str">
-        <v>Novo perfil a partir de .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="C102" t="str">
-        <v>Novo perfil a partir de .cube</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B103" t="str">
-        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e aberto; nada é transferido até clicar em Guardar perfil ICC.</v>
+        <v>Novo perfil a partir de .cube</v>
       </c>
       <c r="C103" t="str">
-        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e aberto; nada é baixado até você clicar em Salvar perfil ICC.</v>
+        <v>Novo perfil a partir de .cube</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B104" t="str">
-        <v>Escolher ficheiro .cube</v>
+        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e aberto; nada é transferido até clicar em Guardar perfil ICC.</v>
       </c>
       <c r="C104" t="str">
-        <v>Escolher arquivo .cube</v>
+        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e aberto; nada é baixado até você clicar em Salvar perfil ICC.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Escolher ficheiro .cube</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Escolher arquivo .cube</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B106" t="str">
         <v>ou largue-o aqui, ou cole abaixo</v>
       </c>
-      <c r="C105" t="str">
+      <c r="C106" t="str">
         <v>ou solte-o aqui, ou cole abaixo</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str" xml:space="preserve">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B106" t="str" xml:space="preserve">
+      <c r="B107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="C106" t="str" xml:space="preserve">
+      <c r="C107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B107" t="str">
-        <v>Cancelar</v>
-      </c>
-      <c r="C107" t="str">
-        <v>Cancelar</v>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B108" t="str">
-        <v>Criar DeviceLink</v>
+        <v>Cancelar</v>
       </c>
       <c r="C108" t="str">
-        <v>Criar DeviceLink</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B109" t="str">
-        <v>A criar…</v>
+        <v>Criar DeviceLink</v>
       </c>
       <c r="C109" t="str">
-        <v>Criando…</v>
+        <v>Criar DeviceLink</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B110" t="str">
-        <v>Não foi possível ler esse ficheiro.</v>
+        <v>A criar…</v>
       </c>
       <c r="C110" t="str">
-        <v>Não foi possível ler esse arquivo.</v>
+        <v>Criando…</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B111" t="str">
-        <v>Perfil</v>
+        <v>Não foi possível ler esse ficheiro.</v>
       </c>
       <c r="C111" t="str">
-        <v>Perfil</v>
+        <v>Não foi possível ler esse arquivo.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B112" t="str">
-        <v>Comparar</v>
+        <v>Perfil</v>
       </c>
       <c r="C112" t="str">
-        <v>Comparar</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B113" t="str">
-        <v>Ligar</v>
+        <v>Comparar</v>
       </c>
       <c r="C113" t="str">
-        <v>Vincular</v>
+        <v>Comparar</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B114" t="str">
-        <v>Espectral</v>
+        <v>Ligar</v>
       </c>
       <c r="C114" t="str">
-        <v>Espectral</v>
+        <v>Vincular</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B115" t="str">
-        <v>Arraste perfis do conjunto para este separador</v>
+        <v>Espectral</v>
       </c>
       <c r="C115" t="str">
-        <v>Arraste perfis do conjunto para esta aba</v>
+        <v>Espectral</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B116" t="str">
-        <v>Remover</v>
+        <v>Arraste perfis do conjunto para este separador</v>
       </c>
       <c r="C116" t="str">
-        <v>Remover</v>
+        <v>Arraste perfis do conjunto para esta aba</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B117" t="str">
-        <v>Nenhum perfil selecionado</v>
+        <v>Remover</v>
       </c>
       <c r="C117" t="str">
-        <v>Nenhum perfil selecionado</v>
+        <v>Remover</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B118" t="str">
-        <v>Arraste um perfil do conjunto para o separador Perfil para o inspecionar.</v>
+        <v>Nenhum perfil selecionado</v>
       </c>
       <c r="C118" t="str">
-        <v>Arraste um perfil do conjunto para a aba Perfil para inspecioná-lo.</v>
+        <v>Nenhum perfil selecionado</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B119" t="str">
-        <v>Ainda nada para comparar</v>
+        <v>Arraste um perfil do conjunto para o separador Perfil para o inspecionar.</v>
       </c>
       <c r="C119" t="str">
-        <v>Ainda nada para comparar</v>
+        <v>Arraste um perfil do conjunto para a aba Perfil para inspecioná-lo.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B120" t="str">
-        <v>Arraste um ou mais perfis para o separador Comparar.</v>
+        <v>Ainda nada para comparar</v>
       </c>
       <c r="C120" t="str">
-        <v>Arraste um ou mais perfis para a aba Comparar.</v>
+        <v>Ainda nada para comparar</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B121" t="str">
-        <v>Comparação de gamut</v>
+        <v>Arraste um ou mais perfis para o separador Comparar.</v>
       </c>
       <c r="C121" t="str">
-        <v>Comparação de gamut</v>
+        <v>Arraste um ou mais perfis para a aba Comparar.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B122" t="str">
-        <v>As vistas de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
+        <v>Comparação de gamut</v>
       </c>
       <c r="C122" t="str">
-        <v>As visualizações de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
+        <v>Comparação de gamut</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B123" t="str">
-        <v>Intenção de renderização</v>
+        <v>As vistas de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
       </c>
       <c r="C123" t="str">
-        <v>Intenção de renderização</v>
+        <v>As visualizações de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B124" t="str">
-        <v>Invólucro</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C124" t="str">
-        <v>Invólucro</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B125" t="str">
-        <v>Malha de arame</v>
+        <v>Invólucro</v>
       </c>
       <c r="C125" t="str">
-        <v>Malha de arame</v>
+        <v>Invólucro</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B126" t="str">
-        <v>Números dos eixos</v>
+        <v>Malha de arame</v>
       </c>
       <c r="C126" t="str">
-        <v>Números dos eixos</v>
+        <v>Malha de arame</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B127" t="str">
-        <v>Opacidade</v>
+        <v>Números dos eixos</v>
       </c>
       <c r="C127" t="str">
-        <v>Opacidade</v>
+        <v>Números dos eixos</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B128" t="str">
-        <v>Cor</v>
+        <v>Opacidade</v>
       </c>
       <c r="C128" t="str">
-        <v>Cor</v>
+        <v>Opacidade</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B129" t="str">
-        <v>Sólido</v>
+        <v>Cor</v>
       </c>
       <c r="C129" t="str">
-        <v>Sólido</v>
+        <v>Cor</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B130" t="str">
-        <v>Por valor</v>
+        <v>Sólido</v>
       </c>
       <c r="C130" t="str">
-        <v>Por valor</v>
+        <v>Sólido</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B131" t="str">
-        <v>Por matiz</v>
+        <v>Por valor</v>
       </c>
       <c r="C131" t="str">
-        <v>Por matiz</v>
+        <v>Por valor</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B132" t="str">
-        <v>Rotação</v>
+        <v>Por matiz</v>
       </c>
       <c r="C132" t="str">
-        <v>Rotação</v>
+        <v>Por matiz</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B133" t="str">
-        <v>Prato giratório</v>
+        <v>Rotação</v>
       </c>
       <c r="C133" t="str">
-        <v>Prato giratório</v>
+        <v>Rotação</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B134" t="str">
-        <v>Órbita</v>
+        <v>Prato giratório</v>
       </c>
       <c r="C134" t="str">
-        <v>Órbita</v>
+        <v>Prato giratório</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B135" t="str">
-        <v>Velocidade de arrasto</v>
+        <v>Órbita</v>
       </c>
       <c r="C135" t="str">
-        <v>Velocidade de arrasto</v>
+        <v>Órbita</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B136" t="str">
-        <v>Rolamento</v>
+        <v>Velocidade de arrasto</v>
       </c>
       <c r="C136" t="str">
-        <v>Rolagem</v>
+        <v>Velocidade de arrasto</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B137" t="str">
-        <v>Velocidade de rolamento</v>
+        <v>Rolamento</v>
       </c>
       <c r="C137" t="str">
-        <v>Velocidade de rolagem</v>
+        <v>Rolagem</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B138" t="str">
-        <v>A construir o gamut…</v>
+        <v>Velocidade de rolamento</v>
       </c>
       <c r="C138" t="str">
-        <v>Construindo o gamut…</v>
+        <v>Velocidade de rolagem</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B139" t="str">
-        <v>sem gamut</v>
+        <v>A construir o gamut…</v>
       </c>
       <c r="C139" t="str">
-        <v>sem gamut</v>
+        <v>Construindo o gamut…</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B140" t="str">
-        <v>Mostrar / ocultar</v>
+        <v>sem gamut</v>
       </c>
       <c r="C140" t="str">
-        <v>Mostrar / ocultar</v>
+        <v>sem gamut</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B141" t="str">
-        <v>Invólucro de gamut 3D</v>
+        <v>Mostrar / ocultar</v>
       </c>
       <c r="C141" t="str">
-        <v>Invólucro de gamut 3D</v>
+        <v>Mostrar / ocultar</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B142" t="str">
-        <v>Corte de gamut 2D</v>
+        <v>Invólucro de gamut 3D</v>
       </c>
       <c r="C142" t="str">
-        <v>Corte de gamut 2D</v>
+        <v>Invólucro de gamut 3D</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B143" t="str">
-        <v>Plano</v>
+        <v>Corte de gamut 2D</v>
       </c>
       <c r="C143" t="str">
-        <v>Plano</v>
+        <v>Corte de gamut 2D</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B144" t="str">
-        <v>L*</v>
+        <v>Plano</v>
       </c>
       <c r="C144" t="str">
-        <v>L*</v>
+        <v>Plano</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="C145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="C146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B147" t="str">
-        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
+        <v>b*</v>
       </c>
       <c r="C147" t="str">
-        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B148" t="str">
-        <v>Ligação</v>
+        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
       </c>
       <c r="C148" t="str">
-        <v>Vínculo</v>
+        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B149" t="str">
-        <v>A produção de DeviceLink e as transformações multiperfil chegarão numa fase posterior.</v>
+        <v>Ligação</v>
       </c>
       <c r="C149" t="str">
-        <v>A produção de DeviceLink e as transformações multiperfil chegarão em uma fase posterior.</v>
+        <v>Vínculo</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B150" t="str">
-        <v>Mais criadores de ligações (DeviceLink, …) chegarão aqui.</v>
+        <v>A produção de DeviceLink e as transformações multiperfil chegarão numa fase posterior.</v>
       </c>
       <c r="C150" t="str">
-        <v>Mais criadores de vínculos (DeviceLink, …) chegarão aqui.</v>
+        <v>A produção de DeviceLink e as transformações multiperfil chegarão em uma fase posterior.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B151" t="str">
-        <v>Criador de ecrã V4</v>
+        <v>Mais criadores de ligações (DeviceLink, …) chegarão aqui.</v>
       </c>
       <c r="C151" t="str">
-        <v>Criador de tela V4</v>
+        <v>Mais criadores de vínculos (DeviceLink, …) chegarão aqui.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B152" t="str">
-        <v>Arraste para aqui um perfil de ecrã RGB V5 e um perfil de observador V5 para criar um perfil de ecrã V4.</v>
+        <v>Criador de ecrã V4</v>
       </c>
       <c r="C152" t="str">
-        <v>Arraste para cá um perfil de tela RGB V5 e um perfil de observador V5 para criar um perfil de tela V4.</v>
+        <v>Criador de tela V4</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B153" t="str">
-        <v>Ecrã RGB V5</v>
+        <v>Arraste para aqui um perfil de ecrã RGB V5 e um perfil de observador V5 para criar um perfil de ecrã V4.</v>
       </c>
       <c r="C153" t="str">
-        <v>Tela RGB V5</v>
+        <v>Arraste para cá um perfil de tela RGB V5 e um perfil de observador V5 para criar um perfil de tela V4.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B154" t="str">
-        <v>largue um perfil de ecrã</v>
+        <v>Ecrã RGB V5</v>
       </c>
       <c r="C154" t="str">
-        <v>solte um perfil de tela</v>
+        <v>Tela RGB V5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B155" t="str">
-        <v>Observador V5 (PCC)</v>
+        <v>largue um perfil de ecrã</v>
       </c>
       <c r="C155" t="str">
-        <v>Observador V5 (PCC)</v>
+        <v>solte um perfil de tela</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B156" t="str">
-        <v>largue um perfil de observador</v>
+        <v>Observador V5 (PCC)</v>
       </c>
       <c r="C156" t="str">
-        <v>solte um perfil de observador</v>
+        <v>Observador V5 (PCC)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B157" t="str">
-        <v>Foi ignorado um perfil que não é um ecrã RGB V5 nem um observador.</v>
+        <v>largue um perfil de observador</v>
       </c>
       <c r="C157" t="str">
-        <v>Um perfil que não é uma tela RGB V5 nem um observador foi ignorado.</v>
+        <v>solte um perfil de observador</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B158" t="str">
-        <v>Criar perfil de ecrã V4</v>
+        <v>Foi ignorado um perfil que não é um ecrã RGB V5 nem um observador.</v>
       </c>
       <c r="C158" t="str">
-        <v>Criar perfil de tela V4</v>
+        <v>Um perfil que não é uma tela RGB V5 nem um observador foi ignorado.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B159" t="str">
-        <v>Nome do perfil</v>
+        <v>Criar perfil de ecrã V4</v>
       </c>
       <c r="C159" t="str">
-        <v>Nome do perfil</v>
+        <v>Criar perfil de tela V4</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B160" t="str">
-        <v>Criar</v>
+        <v>Nome do perfil</v>
       </c>
       <c r="C160" t="str">
-        <v>Criar</v>
+        <v>Nome do perfil</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B161" t="str">
-        <v>A criar…</v>
+        <v>Criar</v>
       </c>
       <c r="C161" t="str">
-        <v>Criando…</v>
+        <v>Criar</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B162" t="str">
-        <v>«{name}» criado — adicionado ao conjunto e a este separador.</v>
+        <v>A criar…</v>
       </c>
       <c r="C162" t="str">
-        <v>«{name}» criado — adicionado ao conjunto e a esta aba.</v>
+        <v>Criando…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B163" t="str">
-        <v>Fluxo de ligação</v>
+        <v>«{name}» criado — adicionado ao conjunto e a este separador.</v>
       </c>
       <c r="C163" t="str">
-        <v>Fluxo de vinculação</v>
+        <v>«{name}» criado — adicionado ao conjunto e a esta aba.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B164" t="str">
-        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
+        <v>Fluxo de ligação</v>
       </c>
       <c r="C164" t="str">
-        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
+        <v>Fluxo de vinculação</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B165" t="str">
-        <v>Concluído</v>
+        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
       </c>
       <c r="C165" t="str">
-        <v>Concluído</v>
+        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B166" t="str">
-        <v>Largue uma imagem para transformar (TIFF/PNG/JPEG)</v>
+        <v>Concluído</v>
       </c>
       <c r="C166" t="str">
-        <v>Solte uma imagem para transformar (TIFF/PNG/JPEG)</v>
+        <v>Concluído</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B167" t="str">
-        <v>A verificar imagem…</v>
+        <v>Largue uma imagem para transformar (TIFF/PNG/JPEG)</v>
       </c>
       <c r="C167" t="str">
-        <v>Verificando imagem…</v>
+        <v>Solte uma imagem para transformar (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B168" t="str">
-        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
+        <v>A verificar imagem…</v>
       </c>
       <c r="C168" t="str">
-        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
+        <v>Verificando imagem…</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B169" t="str">
-        <v>Imagem demasiado grande ({mp} MP; limite {max} MP).</v>
+        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
       </c>
       <c r="C169" t="str">
-        <v>Imagem grande demais ({mp} MP; limite {max} MP).</v>
+        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B170" t="str">
-        <v>Transformar imagem</v>
+        <v>Imagem demasiado grande ({mp} MP; limite {max} MP).</v>
       </c>
       <c r="C170" t="str">
-        <v>Transformar imagem</v>
+        <v>Imagem grande demais ({mp} MP; limite {max} MP).</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B171" t="str">
-        <v>A transformar…</v>
+        <v>Transformar imagem</v>
       </c>
       <c r="C171" t="str">
-        <v>Transformando…</v>
+        <v>Transformar imagem</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B172" t="str">
-        <v>Largue perfis para iniciar a cadeia</v>
+        <v>A transformar…</v>
       </c>
       <c r="C172" t="str">
-        <v>Solte perfis para iniciar a cadeia</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B173" t="str">
-        <v>removido</v>
+        <v>Largue perfis para iniciar a cadeia</v>
       </c>
       <c r="C173" t="str">
-        <v>removido</v>
+        <v>Solte perfis para iniciar a cadeia</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B174" t="str">
-        <v>Mover antes</v>
+        <v>removido</v>
       </c>
       <c r="C174" t="str">
-        <v>Mover antes</v>
+        <v>removido</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B175" t="str">
-        <v>Mover depois</v>
+        <v>Mover antes</v>
       </c>
       <c r="C175" t="str">
-        <v>Mover depois</v>
+        <v>Mover antes</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B176" t="str">
-        <v>Mover para cima</v>
+        <v>Mover depois</v>
       </c>
       <c r="C176" t="str">
-        <v>Mover para cima</v>
+        <v>Mover depois</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B177" t="str">
-        <v>Mover para baixo</v>
+        <v>Mover para cima</v>
       </c>
       <c r="C177" t="str">
-        <v>Mover para baixo</v>
+        <v>Mover para cima</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B178" t="str">
-        <v>Intenção de renderização (todas)</v>
+        <v>Mover para baixo</v>
       </c>
       <c r="C178" t="str">
-        <v>Intenção de renderização (todas)</v>
+        <v>Mover para baixo</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B179" t="str">
-        <v>Intenção de renderização para esta transformação</v>
+        <v>Intenção de renderização (todas)</v>
       </c>
       <c r="C179" t="str">
-        <v>Intenção de renderização para esta transformação</v>
+        <v>Intenção de renderização (todas)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B180" t="str">
-        <v>As transformações usam intenções de renderização diferentes</v>
+        <v>Intenção de renderização para esta transformação</v>
       </c>
       <c r="C180" t="str">
-        <v>As transformações usam intenções de renderização diferentes</v>
+        <v>Intenção de renderização para esta transformação</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B181" t="str">
-        <v>Inverter direção da cadeia (inverte a transformação inicial e propaga-se por toda a cadeia)</v>
+        <v>As transformações usam intenções de renderização diferentes</v>
       </c>
       <c r="C181" t="str">
-        <v>Inverter direção da cadeia (inverte a transformação inicial e se propaga por toda a cadeia)</v>
+        <v>As transformações usam intenções de renderização diferentes</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B182" t="str">
-        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
+        <v>Inverter direção da cadeia (inverte a transformação inicial e propaga-se por toda a cadeia)</v>
       </c>
       <c r="C182" t="str">
-        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
+        <v>Inverter direção da cadeia (inverte a transformação inicial e se propaga por toda a cadeia)</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B183" t="str">
-        <v>Cadeia</v>
+        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
       </c>
       <c r="C183" t="str">
-        <v>Cadeia</v>
+        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B184" t="str">
-        <v>Não foi possível analisar a cadeia.</v>
+        <v>Cadeia</v>
       </c>
       <c r="C184" t="str">
-        <v>Não foi possível analisar a cadeia.</v>
+        <v>Cadeia</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B185" t="str">
-        <v>A verificar cadeia…</v>
+        <v>Não foi possível analisar a cadeia.</v>
       </c>
       <c r="C185" t="str">
-        <v>Verificando cadeia…</v>
+        <v>Não foi possível analisar a cadeia.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B186" t="str">
-        <v>A cadeia não liga ({detail}).</v>
+        <v>A verificar cadeia…</v>
       </c>
       <c r="C186" t="str">
-        <v>A cadeia não conecta ({detail}).</v>
+        <v>Verificando cadeia…</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>O perfil {n} não liga à etapa anterior ({detail}).</v>
+        <v>A cadeia não liga ({detail}).</v>
       </c>
       <c r="C187" t="str">
-        <v>O perfil {n} não conecta com a etapa anterior ({detail}).</v>
+        <v>A cadeia não conecta ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B188" t="str">
-        <v>Corrija a cadeia antes de processar imagens</v>
+        <v>O perfil {n} não liga à etapa anterior ({detail}).</v>
       </c>
       <c r="C188" t="str">
-        <v>Corrija a cadeia antes de processar imagens</v>
+        <v>O perfil {n} não conecta com a etapa anterior ({detail}).</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B189" t="str">
-        <v>Limpar</v>
+        <v>Corrija a cadeia antes de processar imagens</v>
       </c>
       <c r="C189" t="str">
-        <v>Limpar</v>
+        <v>Corrija a cadeia antes de processar imagens</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B190" t="str">
-        <v>Criar DeviceLink</v>
+        <v>Limpar</v>
       </c>
       <c r="C190" t="str">
-        <v>Criar DeviceLink</v>
+        <v>Limpar</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B191" t="str">
-        <v>Nome do DeviceLink</v>
+        <v>Criar DeviceLink</v>
       </c>
       <c r="C191" t="str">
-        <v>Nome do DeviceLink</v>
+        <v>Criar DeviceLink</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B192" t="str">
-        <v>A criar…</v>
+        <v>Nome do DeviceLink</v>
       </c>
       <c r="C192" t="str">
-        <v>Criando…</v>
+        <v>Nome do DeviceLink</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B193" t="str">
-        <v>Criado “{name}” — adicionado ao conjunto e a este separador.</v>
+        <v>A criar…</v>
       </c>
       <c r="C193" t="str">
-        <v>Criado “{name}” — adicionado ao conjunto e a esta aba.</v>
+        <v>Criando…</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B194" t="str">
-        <v>Largue imagens {src} para converter para {dst} — os resultados são descarregados, nada é armazenado.</v>
+        <v>Criado “{name}” — adicionado ao conjunto e a este separador.</v>
       </c>
       <c r="C194" t="str">
-        <v>Solte imagens {src} para converter para {dst} — os resultados são baixados, nada é armazenado.</v>
+        <v>Criado “{name}” — adicionado ao conjunto e a esta aba.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B195" t="str">
-        <v>Crie uma cadeia para processar imagens</v>
+        <v>Largue imagens {src} para converter para {dst} — os resultados são descarregados, nada é armazenado.</v>
       </c>
       <c r="C195" t="str">
-        <v>Crie uma cadeia para processar imagens</v>
+        <v>Solte imagens {src} para converter para {dst} — os resultados são baixados, nada é armazenado.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B196" t="str">
-        <v>Esta cadeia não começa nem termina num espaço de cor de imagem</v>
+        <v>Crie uma cadeia para processar imagens</v>
       </c>
       <c r="C196" t="str">
-        <v>Esta cadeia não começa nem termina em um espaço de cor de imagem</v>
+        <v>Crie uma cadeia para processar imagens</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B197" t="str">
-        <v>Imagem transformada guardada.</v>
+        <v>Esta cadeia não começa nem termina num espaço de cor de imagem</v>
       </c>
       <c r="C197" t="str">
-        <v>Imagem transformada salva.</v>
+        <v>Esta cadeia não começa nem termina em um espaço de cor de imagem</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B198" t="str">
-        <v>Largue um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
+        <v>Imagem transformada guardada.</v>
       </c>
       <c r="C198" t="str">
-        <v>Solte um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
+        <v>Imagem transformada salva.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B199" t="str">
-        <v>Não foi possível ler esse ficheiro.</v>
+        <v>Largue um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="C199" t="str">
-        <v>Não foi possível ler esse arquivo.</v>
+        <v>Solte um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B200" t="str">
-        <v>Ficheiro de dados demasiado grande.</v>
+        <v>Não foi possível ler esse ficheiro.</v>
       </c>
       <c r="C200" t="str">
-        <v>Arquivo de dados grande demais.</v>
+        <v>Não foi possível ler esse arquivo.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B201" t="str">
-        <v>Transformar dados</v>
+        <v>Ficheiro de dados demasiado grande.</v>
       </c>
       <c r="C201" t="str">
-        <v>Transformar dados</v>
+        <v>Arquivo de dados grande demais.</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B202" t="str">
-        <v>A transformar…</v>
+        <v>Transformar dados</v>
       </c>
       <c r="C202" t="str">
-        <v>Transformando…</v>
+        <v>Transformar dados</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B203" t="str">
-        <v>Preferir</v>
+        <v>A transformar…</v>
       </c>
       <c r="C203" t="str">
-        <v>Preferir</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B204" t="str">
-        <v>Observador</v>
+        <v>Preferir</v>
       </c>
       <c r="C204" t="str">
-        <v>Observador</v>
+        <v>Preferir</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B205" t="str">
-        <v>Iluminante</v>
+        <v>Observador</v>
       </c>
       <c r="C205" t="str">
-        <v>Iluminante</v>
+        <v>Observador</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B206" t="str">
-        <v>Condição</v>
+        <v>Iluminante</v>
       </c>
       <c r="C206" t="str">
-        <v>Condição</v>
+        <v>Iluminante</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B207" t="str">
-        <v>Filtrar {n} duplicado(s)</v>
+        <v>Condição</v>
       </c>
       <c r="C207" t="str">
-        <v>Filtrar {n} duplicado(s)</v>
+        <v>Condição</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B208" t="str">
-        <v>mediana</v>
+        <v>Filtrar {n} duplicado(s)</v>
       </c>
       <c r="C208" t="str">
-        <v>mediana</v>
+        <v>Filtrar {n} duplicado(s)</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B209" t="str">
-        <v>média</v>
+        <v>mediana</v>
       </c>
       <c r="C209" t="str">
-        <v>média</v>
+        <v>mediana</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B210" t="str">
-        <v>patches</v>
+        <v>média</v>
       </c>
       <c r="C210" t="str">
-        <v>patches</v>
+        <v>média</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B211" t="str">
-        <v>{n} duplicados</v>
+        <v>patches</v>
       </c>
       <c r="C211" t="str">
-        <v>{n} duplicados</v>
+        <v>patches</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B212" t="str">
-        <v>Resultado da transformação</v>
+        <v>{n} duplicados</v>
       </c>
       <c r="C212" t="str">
-        <v>Resultado da transformação</v>
+        <v>{n} duplicados</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Resultado da transformação</v>
       </c>
       <c r="C213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Resultado da transformação</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B214" t="str">
-        <v>A mostrar os primeiros {shown} de {total} — Guardar grava todos.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="C214" t="str">
-        <v>Mostrando os primeiros {shown} de {total} — Salvar grava todos.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B215" t="str">
-        <v>Guardar como</v>
+        <v>A mostrar os primeiros {shown} de {total} — Guardar grava todos.</v>
       </c>
       <c r="C215" t="str">
-        <v>Salvar como</v>
+        <v>Mostrando os primeiros {shown} de {total} — Salvar grava todos.</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B216" t="str">
-        <v>Guardar</v>
+        <v>Guardar como</v>
       </c>
       <c r="C216" t="str">
-        <v>Salvar</v>
+        <v>Salvar como</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B217" t="str">
-        <v>Inverter transformação</v>
+        <v>Guardar</v>
       </c>
       <c r="C217" t="str">
-        <v>Inverter transformação</v>
+        <v>Salvar</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B218" t="str">
-        <v>A inverter…</v>
+        <v>Inverter transformação</v>
       </c>
       <c r="C218" t="str">
-        <v>Invertendo…</v>
+        <v>Inverter transformação</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B219" t="str">
-        <v>Inverter</v>
+        <v>A inverter…</v>
       </c>
       <c r="C219" t="str">
-        <v>Inverter</v>
+        <v>Invertendo…</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B220" t="str">
-        <v>última etapa</v>
+        <v>Inverter</v>
       </c>
       <c r="C220" t="str">
-        <v>última etapa</v>
+        <v>Inverter</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B221" t="str">
-        <v>primeira etapa</v>
+        <v>última etapa</v>
       </c>
       <c r="C221" t="str">
-        <v>primeira etapa</v>
+        <v>última etapa</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B222" t="str">
-        <v>Dados em {in} → procurar {out}</v>
+        <v>primeira etapa</v>
       </c>
       <c r="C222" t="str">
-        <v>Dados em {in} → buscar {out}</v>
+        <v>primeira etapa</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B223" t="str">
-        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
+        <v>Dados em {in} → procurar {out}</v>
       </c>
       <c r="C223" t="str">
-        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
+        <v>Dados em {in} → buscar {out}</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B224" t="str">
-        <v>O conjunto de dados deve estar em {in}; a procura inversa produz {out} mais um custo de invertibilidade por patch.</v>
+        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
       </c>
       <c r="C224" t="str">
-        <v>O conjunto de dados deve estar em {in}; a busca inversa produz {out} mais um custo de invertibilidade por patch.</v>
+        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B225" t="str">
-        <v>Custo ΔE</v>
+        <v>O conjunto de dados deve estar em {in}; a procura inversa produz {out} mais um custo de invertibilidade por patch.</v>
       </c>
       <c r="C225" t="str">
-        <v>Custo ΔE</v>
+        <v>O conjunto de dados deve estar em {in}; a busca inversa produz {out} mais um custo de invertibilidade por patch.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B226" t="str">
-        <v>Esta imagem tem um perfil ICC incorporado.</v>
+        <v>Custo ΔE</v>
       </c>
       <c r="C226" t="str">
-        <v>Esta imagem tem um perfil ICC incorporado.</v>
+        <v>Custo ΔE</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B227" t="str">
-        <v>Extrair e adicionar à cadeia</v>
+        <v>Esta imagem tem um perfil ICC incorporado.</v>
       </c>
       <c r="C227" t="str">
-        <v>Extrair e adicionar à cadeia</v>
+        <v>Esta imagem tem um perfil ICC incorporado.</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B228" t="str">
-        <v>A extrair…</v>
+        <v>Extrair e adicionar à cadeia</v>
       </c>
       <c r="C228" t="str">
-        <v>Extraindo…</v>
+        <v>Extrair e adicionar à cadeia</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B229" t="str">
-        <v>Dispensar</v>
+        <v>A extrair…</v>
       </c>
       <c r="C229" t="str">
-        <v>Dispensar</v>
+        <v>Extraindo…</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B230" t="str">
-        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro lugar na cadeia.</v>
+        <v>Dispensar</v>
       </c>
       <c r="C230" t="str">
-        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro na cadeia.</v>
+        <v>Dispensar</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B231" t="str">
-        <v>Opções de saída de imagem</v>
+        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro lugar na cadeia.</v>
       </c>
       <c r="C231" t="str">
-        <v>Opções de saída de imagem</v>
+        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro na cadeia.</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B232" t="str">
-        <v>Codificação</v>
+        <v>Opções de saída de imagem</v>
       </c>
       <c r="C232" t="str">
-        <v>Codificação</v>
+        <v>Opções de saída de imagem</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B233" t="str">
-        <v>Igual à origem</v>
+        <v>Codificação</v>
       </c>
       <c r="C233" t="str">
-        <v>Igual à origem</v>
+        <v>Codificação</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B234" t="str">
-        <v>8 bits</v>
+        <v>Igual à origem</v>
       </c>
       <c r="C234" t="str">
-        <v>8 bits</v>
+        <v>Igual à origem</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>16 bits</v>
+        <v>8 bits</v>
       </c>
       <c r="C235" t="str">
-        <v>16 bits</v>
+        <v>8 bits</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B236" t="str">
-        <v>Flutuante (32 bits)</v>
+        <v>16 bits</v>
       </c>
       <c r="C236" t="str">
-        <v>Flutuante (32 bits)</v>
+        <v>16 bits</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B237" t="str">
-        <v>Compressão</v>
+        <v>Flutuante (32 bits)</v>
       </c>
       <c r="C237" t="str">
-        <v>Compressão</v>
+        <v>Flutuante (32 bits)</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B238" t="str">
-        <v>Nenhuma</v>
+        <v>Compressão</v>
       </c>
       <c r="C238" t="str">
-        <v>Nenhuma</v>
+        <v>Compressão</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B239" t="str">
-        <v>Planar</v>
+        <v>Nenhuma</v>
       </c>
       <c r="C239" t="str">
-        <v>Planar</v>
+        <v>Nenhuma</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B240" t="str">
-        <v>Composto</v>
+        <v>Planar</v>
       </c>
       <c r="C240" t="str">
-        <v>Composto</v>
+        <v>Planar</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B241" t="str">
-        <v>Separado</v>
+        <v>Composto</v>
       </c>
       <c r="C241" t="str">
-        <v>Separado</v>
+        <v>Composto</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B242" t="str">
-        <v>Interpolação CMM</v>
+        <v>Separado</v>
       </c>
       <c r="C242" t="str">
-        <v>Interpolação CMM</v>
+        <v>Separado</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B243" t="str">
-        <v>Tetraédrica</v>
+        <v>Interpolação CMM</v>
       </c>
       <c r="C243" t="str">
-        <v>Tetraédrica</v>
+        <v>Interpolação CMM</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B244" t="str">
-        <v>Linear</v>
+        <v>Tetraédrica</v>
       </c>
       <c r="C244" t="str">
-        <v>Linear</v>
+        <v>Tetraédrica</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B245" t="str">
-        <v>Incorporar ICC</v>
+        <v>Linear</v>
       </c>
       <c r="C245" t="str">
-        <v>Incorporar ICC</v>
+        <v>Linear</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B246" t="str">
-        <v>A codificação, a compressão e o formato planar determinam o TIFF guardado. A saída RGB/Gray mantém-se em PNG, salvo se for definida uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado).</v>
+        <v>Incorporar ICC</v>
       </c>
       <c r="C246" t="str">
-        <v>A codificação, a compressão e o formato planar determinam o TIFF salvo. A saída RGB/Gray permanece em PNG, a menos que uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado) seja definida.</v>
+        <v>Incorporar ICC</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B247" t="str">
-        <v>Montar TIFF espectral</v>
+        <v>A codificação, a compressão e o formato planar determinam o TIFF guardado. A saída RGB/Gray mantém-se em PNG, salvo se for definida uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado).</v>
       </c>
       <c r="C247" t="str">
-        <v>Montar TIFF espectral</v>
+        <v>A codificação, a compressão e o formato planar determinam o TIFF salvo. A saída RGB/Gray permanece em PNG, a menos que uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado) seja definida.</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B248" t="str">
-        <v>Largue imagens espectrais de canal único pela ordem dos canais e depois monte-as num único TIFF multicanal.</v>
+        <v>Montar TIFF espectral</v>
       </c>
       <c r="C248" t="str">
-        <v>Solte imagens espectrais de canal único na ordem dos canais e depois monte-as em um único TIFF multicanal.</v>
+        <v>Montar TIFF espectral</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B249" t="str">
-        <v>Largue imagens espectrais aqui (ou clique para escolher)</v>
+        <v>Largue imagens espectrais de canal único pela ordem dos canais e depois monte-as num único TIFF multicanal.</v>
       </c>
       <c r="C249" t="str">
-        <v>Solte imagens espectrais aqui (ou clique para escolher)</v>
+        <v>Solte imagens espectrais de canal único na ordem dos canais e depois monte-as em um único TIFF multicanal.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B250" t="str">
-        <v>can</v>
+        <v>Largue imagens espectrais aqui (ou clique para escolher)</v>
       </c>
       <c r="C250" t="str">
-        <v>can</v>
+        <v>Solte imagens espectrais aqui (ou clique para escolher)</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B251" t="str">
-        <v>Montar e guardar</v>
+        <v>can</v>
       </c>
       <c r="C251" t="str">
-        <v>Montar e salvar</v>
+        <v>can</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B252" t="str">
-        <v>A montar…</v>
+        <v>Montar e guardar</v>
       </c>
       <c r="C252" t="str">
-        <v>Montando…</v>
+        <v>Montar e salvar</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B253" t="str">
-        <v>Foram montados {n} canais.</v>
+        <v>A montar…</v>
       </c>
       <c r="C253" t="str">
-        <v>Foram montados {n} canais.</v>
+        <v>Montando…</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B254" t="str">
-        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
+        <v>Foram montados {n} canais.</v>
       </c>
       <c r="C254" t="str">
-        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
+        <v>Foram montados {n} canais.</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B255" t="str">
-        <v>Cancelar</v>
+        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
       </c>
       <c r="C255" t="str">
-        <v>Cancelar</v>
+        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B256" t="str">
-        <v>{n} ficheiro(s) não carregados</v>
+        <v>Cancelar</v>
       </c>
       <c r="C256" t="str">
-        <v>{n} arquivo(s) não carregados</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B257" t="str">
-        <v>Estes ficheiros não são perfis ICC, pelo que não foram adicionados ao conjunto:</v>
+        <v>{n} ficheiro(s) não carregados</v>
       </c>
       <c r="C257" t="str">
-        <v>Estes arquivos não são perfis ICC, portanto não foram adicionados ao conjunto:</v>
+        <v>{n} arquivo(s) não carregados</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B258" t="str">
-        <v>OK</v>
+        <v>Estes ficheiros não são perfis ICC, pelo que não foram adicionados ao conjunto:</v>
       </c>
       <c r="C258" t="str">
-        <v>OK</v>
+        <v>Estes arquivos não são perfis ICC, portanto não foram adicionados ao conjunto:</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B259" t="str">
-        <v>Largue um perfil ICC aqui</v>
+        <v>OK</v>
       </c>
       <c r="C259" t="str">
-        <v>Solte um perfil ICC aqui</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B260" t="str">
-        <v>ou</v>
+        <v>Largue um perfil ICC aqui</v>
       </c>
       <c r="C260" t="str">
-        <v>ou</v>
+        <v>Solte um perfil ICC aqui</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B261" t="str">
-        <v>Escolher ficheiro</v>
+        <v>ou</v>
       </c>
       <c r="C261" t="str">
-        <v>Escolher arquivo</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B262" t="str">
-        <v>Ficheiros .icc e .icm</v>
+        <v>Escolher ficheiro</v>
       </c>
       <c r="C262" t="str">
-        <v>Arquivos .icc e .icm</v>
+        <v>Escolher arquivo</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B263" t="str">
-        <v>Cabeçalho</v>
+        <v>Ficheiros .icc e .icm</v>
       </c>
       <c r="C263" t="str">
-        <v>Cabeçalho</v>
+        <v>Arquivos .icc e .icm</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B264" t="str">
-        <v>Etiquetas</v>
+        <v>Cabeçalho</v>
       </c>
       <c r="C264" t="str">
-        <v>Tags</v>
+        <v>Cabeçalho</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B265" t="str">
-        <v>Validação</v>
+        <v>Etiquetas</v>
       </c>
       <c r="C265" t="str">
-        <v>Validação</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B266" t="str">
-        <v>Análise</v>
+        <v>Validação</v>
       </c>
       <c r="C266" t="str">
-        <v>Análise</v>
+        <v>Validação</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B267" t="str">
-        <v>Tintagem do eixo neutro</v>
+        <v>Análise</v>
       </c>
       <c r="C267" t="str">
-        <v>Tintagem do eixo neutro</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B268" t="str">
-        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
       <c r="C268" t="str">
-        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B269" t="str">
-        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
       </c>
       <c r="C269" t="str">
-        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B270" t="str">
-        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
       <c r="C270" t="str">
-        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B271" t="str">
-        <v>Intenção de renderização</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
       <c r="C271" t="str">
-        <v>Intenção de renderização</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B272" t="str">
-        <v>% tinta</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C272" t="str">
-        <v>% tinta</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>L* out (tone)</v>
+        <v>% ink</v>
       </c>
       <c r="B273" t="str">
-        <v>L* de saída (tom)</v>
+        <v>% tinta</v>
       </c>
       <c r="C273" t="str">
-        <v>L* de saída (tom)</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Δa*b*</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B274" t="str">
-        <v>Δa*b*</v>
+        <v>L* de saída (tom)</v>
       </c>
       <c r="C274" t="str">
-        <v>Δa*b*</v>
+        <v>L* de saída (tom)</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B275" t="str">
-        <v>Colorimetria dos extremos</v>
+        <v>Δa*b*</v>
       </c>
       <c r="C275" t="str">
-        <v>Colorimetria dos extremos</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B276" t="str">
-        <v>Os extremos da gama de reprodução do perfil: o branco do suporte, o preto mais escuro que irá imprimir, a tinta que esse preto custa e o ponto em que cada matiz atinge a saturação máxima.</v>
+        <v>Colorimetria dos extremos</v>
       </c>
       <c r="C276" t="str">
-        <v>Os extremos da faixa de reprodução do perfil: o branco do suporte, o preto mais escuro que ele imprimirá, a tinta que esse preto custa e o ponto em que cada matiz atinge a saturação máxima.</v>
+        <v>Colorimetria dos extremos</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B277" t="str">
-        <v>O ponto branco é a cor com corante nulo — o suporte nu. O ponto preto obtém-se passando o preto do PCS (L*=0, a*=b*=0) pela tabela B2A selecionada para obter a tintagem que o perfil escolhe para o preto e lendo depois essa tintagem através de A2B1. A cobertura total de tinta (TAC) é a soma dessa tintagem. A colorimetria absoluta mostra a cor própria do suporte; a relativa refere-a a um branco perfeito.</v>
+        <v>Os extremos da gama de reprodução do perfil: o branco do suporte, o preto mais escuro que irá imprimir, a tinta que esse preto custa e o ponto em que cada matiz atinge a saturação máxima.</v>
       </c>
       <c r="C277" t="str">
-        <v>O ponto branco é a cor com corante nulo — o suporte nu. O ponto preto é obtido passando o preto do PCS (L*=0, a*=b*=0) pela tabela B2A selecionada para obter a tintagem que o perfil escolhe para o preto e lendo depois essa tintagem através de A2B1. A cobertura total de tinta (TAC) é a soma dessa tintagem. A colorimetria absoluta mostra a cor própria do suporte; a relativa a refere a um branco perfeito.</v>
+        <v>Os extremos da faixa de reprodução do perfil: o branco do suporte, o preto mais escuro que ele imprimirá, a tinta que esse preto custa e o ponto em que cada matiz atinge a saturação máxima.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Relative</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B278" t="str">
-        <v>Relativa</v>
+        <v>O ponto branco é a cor com corante nulo — o suporte nu. O ponto preto obtém-se passando o preto do PCS (L*=0, a*=b*=0) pela tabela B2A selecionada para obter a tintagem que o perfil escolhe para o preto e lendo depois essa tintagem através de A2B1. A cobertura total de tinta (TAC) é a soma dessa tintagem. A colorimetria absoluta mostra a cor própria do suporte; a relativa refere-a a um branco perfeito.</v>
       </c>
       <c r="C278" t="str">
-        <v>Relativa</v>
+        <v>O ponto branco é a cor com corante nulo — o suporte nu. O ponto preto é obtido passando o preto do PCS (L*=0, a*=b*=0) pela tabela B2A selecionada para obter a tintagem que o perfil escolhe para o preto e lendo depois essa tintagem através de A2B1. A cobertura total de tinta (TAC) é a soma dessa tintagem. A colorimetria absoluta mostra a cor própria do suporte; a relativa a refere a um branco perfeito.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Absolute</v>
+        <v>Relative</v>
       </c>
       <c r="B279" t="str">
-        <v>Absoluta</v>
+        <v>Relativa</v>
       </c>
       <c r="C279" t="str">
-        <v>Absoluta</v>
+        <v>Relativa</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>White point</v>
+        <v>Absolute</v>
       </c>
       <c r="B280" t="str">
-        <v>Ponto branco</v>
+        <v>Absoluta</v>
       </c>
       <c r="C280" t="str">
-        <v>Ponto branco</v>
+        <v>Absoluta</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Black point</v>
+        <v>White point</v>
       </c>
       <c r="B281" t="str">
-        <v>Ponto preto</v>
+        <v>Ponto branco</v>
       </c>
       <c r="C281" t="str">
-        <v>Ponto preto</v>
+        <v>Ponto branco</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Inking at black point</v>
+        <v>Black point</v>
       </c>
       <c r="B282" t="str">
-        <v>Tintagem no ponto preto</v>
+        <v>Ponto preto</v>
       </c>
       <c r="C282" t="str">
-        <v>Tintagem no ponto preto</v>
+        <v>Ponto preto</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TAC</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B283" t="str">
-        <v>TAC</v>
+        <v>Tintagem no ponto preto</v>
       </c>
       <c r="C283" t="str">
-        <v>TAC</v>
+        <v>Tintagem no ponto preto</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>TAC</v>
       </c>
       <c r="B284" t="str">
-        <v>Este perfil não tem etiqueta de ponto branco do meio, pelo que a colorimetria absoluta não está disponível.</v>
+        <v>TAC</v>
       </c>
       <c r="C284" t="str">
-        <v>Este perfil não tem tag de ponto branco do meio, portanto a colorimetria absoluta não está disponível.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B285" t="str">
-        <v>A colorimetria dos extremos só está disponível para perfis de saída (impressora) — pressupõe que corante nulo significa suporte nu.</v>
+        <v>Este perfil não tem etiqueta de ponto branco do meio, pelo que a colorimetria absoluta não está disponível.</v>
       </c>
       <c r="C285" t="str">
-        <v>A colorimetria dos extremos só está disponível para perfis de saída (impressora) — ela pressupõe que corante nulo significa suporte nu.</v>
+        <v>Este perfil não tem tag de ponto branco do meio, portanto a colorimetria absoluta não está disponível.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B286" t="str">
-        <v>Tinta plena vs croma máximo</v>
+        <v>A colorimetria dos extremos só está disponível para perfis de saída (impressora) — pressupõe que corante nulo significa suporte nu.</v>
       </c>
       <c r="C286" t="str">
-        <v>Tinta plena vs croma máximo</v>
+        <v>A colorimetria dos extremos só está disponível para perfis de saída (impressora) — ela pressupõe que corante nulo significa suporte nu.</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B287" t="str">
-        <v>Onde fica cada vértice de tinta e o ponto mais cromático no caminho até lá. Medido através de A2B1, pelo que estas linhas não mudam com a intenção de renderização acima. Num perfil bem comportado as duas linhas coincidem; se o croma máximo surgir antes da tinta plena, a tinta para além desse ponto apenas escurece.</v>
+        <v>Tinta plena vs croma máximo</v>
       </c>
       <c r="C287" t="str">
-        <v>Onde fica cada vértice de tinta e o ponto mais cromático no caminho até lá. Medido através de A2B1, portanto estas linhas não mudam com a intenção de renderização acima. Em um perfil bem comportado as duas linhas coincidem; se o croma máximo surgir antes da tinta plena, a tinta além desse ponto apenas escurece.</v>
+        <v>Tinta plena vs croma máximo</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Hue</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B288" t="str">
-        <v>Matiz</v>
+        <v>Onde fica cada vértice de tinta e o ponto mais cromático no caminho até lá. Medido através de A2B1, pelo que estas linhas não mudam com a intenção de renderização acima. Num perfil bem comportado as duas linhas coincidem; se o croma máximo surgir antes da tinta plena, a tinta para além desse ponto apenas escurece.</v>
       </c>
       <c r="C288" t="str">
-        <v>Matiz</v>
+        <v>Onde fica cada vértice de tinta e o ponto mais cromático no caminho até lá. Medido através de A2B1, portanto estas linhas não mudam com a intenção de renderização acima. Em um perfil bem comportado as duas linhas coincidem; se o croma máximo surgir antes da tinta plena, a tinta além desse ponto apenas escurece.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Full tone</v>
+        <v>Hue</v>
       </c>
       <c r="B289" t="str">
-        <v>Tinta plena</v>
+        <v>Matiz</v>
       </c>
       <c r="C289" t="str">
-        <v>Tinta plena</v>
+        <v>Matiz</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Max C*</v>
+        <v>Full tone</v>
       </c>
       <c r="B290" t="str">
-        <v>C* máx</v>
+        <v>Tinta plena</v>
       </c>
       <c r="C290" t="str">
-        <v>C* máx</v>
+        <v>Tinta plena</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>At ink</v>
+        <v>Max C*</v>
       </c>
       <c r="B291" t="str">
-        <v>Com tintagem</v>
+        <v>C* máx</v>
       </c>
       <c r="C291" t="str">
-        <v>Com tintagem</v>
+        <v>C* máx</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>At ink</v>
       </c>
       <c r="B292" t="str">
-        <v>O croma máximo é atingido antes da tinta plena — a tinta para além deste ponto apenas escurece.</v>
+        <v>Com tintagem</v>
       </c>
       <c r="C292" t="str">
-        <v>O croma máximo é atingido antes da tinta plena — a tinta além deste ponto apenas escurece.</v>
+        <v>Com tintagem</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B293" t="str">
-        <v>Utilização de tinta nas sombras</v>
+        <v>O croma máximo é atingido antes da tinta plena — a tinta para além deste ponto apenas escurece.</v>
       </c>
       <c r="C293" t="str">
-        <v>Uso de tinta nas sombras</v>
+        <v>O croma máximo é atingido antes da tinta plena — a tinta além deste ponto apenas escurece.</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B294" t="str">
-        <v>Quatro percursos retos no plano a*b* com uma luminosidade constante e deliberadamente escura, passados pela tabela B2A selecionada. Todas as amostras partilham a mesma L*, pelo que qualquer degrau abrupto ou inversão de um corante resulta apenas do tratamento do matiz e do croma — a assinatura de um artefacto de mapeamento de gamut nas sombras.</v>
+        <v>Utilização de tinta nas sombras</v>
       </c>
       <c r="C294" t="str">
-        <v>Quatro percursos retos no plano a*b* com uma luminosidade constante e deliberadamente escura, passados pela tabela B2A selecionada. Todas as amostras compartilham a mesma L*, portanto qualquer degrau abrupto ou inversão de um corante vem apenas do tratamento do matiz e do croma — a assinatura de um artefato de mapeamento de gamut nas sombras.</v>
+        <v>Uso de tinta nas sombras</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B295" t="str">
-        <v>A utilização de tinta nas sombras só está disponível para perfis de saída (impressora).</v>
+        <v>Quatro percursos retos no plano a*b* com uma luminosidade constante e deliberadamente escura, passados pela tabela B2A selecionada. Todas as amostras partilham a mesma L*, pelo que qualquer degrau abrupto ou inversão de um corante resulta apenas do tratamento do matiz e do croma — a assinatura de um artefacto de mapeamento de gamut nas sombras.</v>
       </c>
       <c r="C295" t="str">
-        <v>O uso de tinta nas sombras só está disponível para perfis de saída (impressora).</v>
+        <v>Quatro percursos retos no plano a*b* com uma luminosidade constante e deliberadamente escura, passados pela tabela B2A selecionada. Todas as amostras compartilham a mesma L*, portanto qualquer degrau abrupto ou inversão de um corante vem apenas do tratamento do matiz e do croma — a assinatura de um artefato de mapeamento de gamut nas sombras.</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Constant L* plane</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B296" t="str">
-        <v>Plano de L* constante</v>
+        <v>A utilização de tinta nas sombras só está disponível para perfis de saída (impressora).</v>
       </c>
       <c r="C296" t="str">
-        <v>Plano de L* constante</v>
+        <v>O uso de tinta nas sombras só está disponível para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>black-point compensated from</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B297" t="str">
-        <v>com compensação do ponto preto a partir de</v>
+        <v>Plano de L* constante</v>
       </c>
       <c r="C297" t="str">
-        <v>com compensação do ponto preto a partir de</v>
+        <v>Plano de L* constante</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Position along path</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B298" t="str">
-        <v>Posição ao longo do percurso</v>
+        <v>com compensação do ponto preto a partir de</v>
       </c>
       <c r="C298" t="str">
-        <v>Posição ao longo do percurso</v>
+        <v>com compensação do ponto preto a partir de</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Path</v>
+        <v>Position along path</v>
       </c>
       <c r="B299" t="str">
-        <v>Percurso</v>
+        <v>Posição ao longo do percurso</v>
       </c>
       <c r="C299" t="str">
-        <v>Percurso</v>
+        <v>Posição ao longo do percurso</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Primary-Inking Paths through Neutral</v>
+        <v>Path</v>
       </c>
       <c r="B300" t="str">
-        <v>Trajetos de tintagem primária pelo neutro</v>
+        <v>Percurso</v>
       </c>
       <c r="C300" t="str">
-        <v>Caminhos de entintamento primário pelo neutro</v>
+        <v>Percurso</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B301" t="str">
-        <v>Três trajetos dentro do gamute — ciano→vermelho, magenta→verde, amarelo→azul — cada um através do eixo neutro na luminosidade média das suas extremidades, através da tabela B2A selecionada. Cada amostra está dentro do gamute, pelo que, ao contrário dos trajetos de sombra, qualquer salto ou inversão de um corante é um defeito de suavidade da CLUT e não um artefacto de mapeamento de gamute.</v>
+        <v>Trajetos de tintagem primária pelo neutro</v>
       </c>
       <c r="C301" t="str">
-        <v>Três caminhos dentro do gamute — ciano→vermelho, magenta→verde, amarelo→azul — cada um através do eixo neutro na luminosidade média de suas extremidades, através da tabela B2A selecionada. Cada amostra está dentro do gamute, então, diferentemente dos caminhos de sombra, qualquer salto ou inversão de um corante é um defeito de suavidade da CLUT e não um artefato de mapeamento de gamute.</v>
+        <v>Caminhos de entintamento primário pelo neutro</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Primary-inking paths are only available for output (printer) profiles.</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B302" t="str">
-        <v>Os trajetos de tintagem primária só estão disponíveis para perfis de saída (impressora).</v>
+        <v>Três trajetos dentro do gamute — ciano→vermelho, magenta→verde, amarelo→azul — cada um através do eixo neutro na luminosidade média das suas extremidades, através da tabela B2A selecionada. Cada amostra está dentro do gamute, pelo que, ao contrário dos trajetos de sombra, qualquer salto ou inversão de um corante é um defeito de suavidade da CLUT e não um artefacto de mapeamento de gamute.</v>
       </c>
       <c r="C302" t="str">
-        <v>Os caminhos de entintamento primário só estão disponíveis para perfis de saída (impressora).</v>
+        <v>Três caminhos dentro do gamute — ciano→vermelho, magenta→verde, amarelo→azul — cada um através do eixo neutro na luminosidade média de suas extremidades, através da tabela B2A selecionada. Cada amostra está dentro do gamute, então, diferentemente dos caminhos de sombra, qualquer salto ou inversão de um corante é um defeito de suavidade da CLUT e não um artefato de mapeamento de gamute.</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Position along path (neutral at midpoint)</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B303" t="str">
-        <v>Posição ao longo do trajeto (neutro no centro)</v>
+        <v>Os trajetos de tintagem primária só estão disponíveis para perfis de saída (impressora).</v>
       </c>
       <c r="C303" t="str">
-        <v>Posição ao longo do caminho (neutro no centro)</v>
+        <v>Os caminhos de entintamento primário só estão disponíveis para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Black-point compensated for this intent.</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B304" t="str">
-        <v>Compensação de ponto preto aplicada para esta intenção.</v>
+        <v>Posição ao longo do trajeto (neutro no centro)</v>
       </c>
       <c r="C304" t="str">
-        <v>Compensação de ponto preto aplicada para esta intenção.</v>
+        <v>Posição ao longo do caminho (neutro no centro)</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Ink Usage Statistics</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B305" t="str">
-        <v>Estatísticas de utilização de tinta</v>
+        <v>Compensação de ponto preto aplicada para esta intenção.</v>
       </c>
       <c r="C305" t="str">
-        <v>Estatísticas de uso de tinta</v>
+        <v>Compensação de ponto preto aplicada para esta intenção.</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B306" t="str">
-        <v>Quanto de cada corante o perfil deposita, como soma e como quota do total — a assinatura de consumo de tinta da separação.</v>
+        <v>Estatísticas de utilização de tinta</v>
       </c>
       <c r="C306" t="str">
-        <v>Quanto de cada corante o perfil deposita, como soma e como parcela do total — a assinatura de consumo de tinta da separação.</v>
+        <v>Estatísticas de uso de tinta</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Ink usage statistics are only available for output (printer) profiles.</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B307" t="str">
-        <v>As estatísticas de utilização de tinta só estão disponíveis para perfis de saída (impressora).</v>
+        <v>Quanto de cada corante o perfil deposita, como soma e como quota do total — a assinatura de consumo de tinta da separação.</v>
       </c>
       <c r="C307" t="str">
-        <v>As estatísticas de uso de tinta só estão disponíveis para perfis de saída (impressora).</v>
+        <v>Quanto de cada corante o perfil deposita, como soma e como parcela do total — a assinatura de consumo de tinta da separação.</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Neutral axis</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B308" t="str">
-        <v>Eixo neutro</v>
+        <v>As estatísticas de utilização de tinta só estão disponíveis para perfis de saída (impressora).</v>
       </c>
       <c r="C308" t="str">
-        <v>Eixo neutro</v>
+        <v>As estatísticas de uso de tinta só estão disponíveis para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Mean coverage</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B309" t="str">
-        <v>Cobertura média</v>
+        <v>Eixo neutro</v>
       </c>
       <c r="C309" t="str">
-        <v>Cobertura média</v>
+        <v>Eixo neutro</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Share of ink</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B310" t="str">
-        <v>Quota de tinta</v>
+        <v>Cobertura média</v>
       </c>
       <c r="C310" t="str">
-        <v>Parcela de tinta</v>
+        <v>Cobertura média</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
+        <v>Share of ink</v>
       </c>
       <c r="B311" t="str">
-        <v>A quota de tinta é a impressão digital da construção do neutro — a fração de cada corante no total de tinta depositada, independentemente do número de amostras.</v>
+        <v>Quota de tinta</v>
       </c>
       <c r="C311" t="str">
-        <v>A parcela de tinta é a impressão digital da construção do neutro — a fração de cada corante no total de tinta depositada, independentemente do número de amostras.</v>
+        <v>Parcela de tinta</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>On &amp; in-gamut points</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B312" t="str">
-        <v>Pontos dentro do gamute</v>
+        <v>A quota de tinta é a impressão digital da construção do neutro — a fração de cada corante no total de tinta depositada, independentemente do número de amostras.</v>
       </c>
       <c r="C312" t="str">
-        <v>Pontos dentro do gamute</v>
+        <v>A parcela de tinta é a impressão digital da construção do neutro — a fração de cada corante no total de tinta depositada, independentemente do número de amostras.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B313" t="str">
-        <v>A utilização de tinta em todas as cores do gamute necessita da fronteira de gamute do lado B2A, ainda não implementada — pendente.</v>
+        <v>Pontos dentro do gamute</v>
       </c>
       <c r="C313" t="str">
-        <v>O uso de tinta em todas as cores do gamute precisa da fronteira de gamute do lado B2A, ainda não implementada — pendente.</v>
+        <v>Pontos dentro do gamute</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>No colorant data to summarize.</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B314" t="str">
-        <v>Sem dados de corante para resumir.</v>
+        <v>A utilização de tinta em todas as cores do gamute necessita da fronteira de gamute do lado B2A, ainda não implementada — pendente.</v>
       </c>
       <c r="C314" t="str">
-        <v>Sem dados de corante para resumir.</v>
+        <v>O uso de tinta em todas as cores do gamute precisa da fronteira de gamute do lado B2A, ainda não implementada — pendente.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B315" t="str">
-        <v>Selecione uma tabela B2A (PCS→dispositivo) abaixo para ver também uma imagem em tons de cinzento da cobertura de tinta de cada corante.</v>
+        <v>Sem dados de corante para resumir.</v>
       </c>
       <c r="C315" t="str">
-        <v>Selecione uma tabela B2A (PCS→dispositivo) abaixo para ver também uma imagem em tons de cinza da cobertura de tinta de cada corante.</v>
+        <v>Sem dados de corante para resumir.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B316" t="str">
-        <v>Cobertura de tinta de cada corante sobre a mesma grelha (mais escuro = mais tinta).</v>
+        <v>Selecione uma tabela B2A (PCS→dispositivo) abaixo para ver também uma imagem em tons de cinzento da cobertura de tinta de cada corante.</v>
       </c>
       <c r="C316" t="str">
-        <v>Cobertura de tinta de cada corante sobre a mesma grade (mais escuro = mais tinta).</v>
+        <v>Selecione uma tabela B2A (PCS→dispositivo) abaixo para ver também uma imagem em tons de cinza da cobertura de tinta de cada corante.</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Cyan</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B317" t="str">
-        <v>Ciano</v>
+        <v>Cobertura de tinta de cada corante sobre a mesma grelha (mais escuro = mais tinta).</v>
       </c>
       <c r="C317" t="str">
-        <v>Ciano</v>
+        <v>Cobertura de tinta de cada corante sobre a mesma grade (mais escuro = mais tinta).</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
       <c r="B318" t="str">
-        <v>Magenta</v>
+        <v>Ciano</v>
       </c>
       <c r="C318" t="str">
-        <v>Magenta</v>
+        <v>Ciano</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Yellow</v>
+        <v>Magenta</v>
       </c>
       <c r="B319" t="str">
-        <v>Amarelo</v>
+        <v>Magenta</v>
       </c>
       <c r="C319" t="str">
-        <v>Amarelo</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Red</v>
+        <v>Yellow</v>
       </c>
       <c r="B320" t="str">
-        <v>Vermelho</v>
+        <v>Amarelo</v>
       </c>
       <c r="C320" t="str">
-        <v>Vermelho</v>
+        <v>Amarelo</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="B321" t="str">
-        <v>Verde</v>
+        <v>Vermelho</v>
       </c>
       <c r="C321" t="str">
-        <v>Verde</v>
+        <v>Vermelho</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blue</v>
+        <v>Green</v>
       </c>
       <c r="B322" t="str">
-        <v>Azul</v>
+        <v>Verde</v>
       </c>
       <c r="C322" t="str">
-        <v>Azul</v>
+        <v>Verde</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Black</v>
+        <v>Blue</v>
       </c>
       <c r="B323" t="str">
-        <v>Preto</v>
+        <v>Azul</v>
       </c>
       <c r="C323" t="str">
-        <v>Preto</v>
+        <v>Azul</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Perceptual</v>
+        <v>Black</v>
       </c>
       <c r="B324" t="str">
-        <v>Perceptual</v>
+        <v>Preto</v>
       </c>
       <c r="C324" t="str">
-        <v>Perceptual</v>
+        <v>Preto</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B325" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Perceptual</v>
       </c>
       <c r="C325" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B326" t="str">
-        <v>Saturação</v>
+        <v>Colorimétrico relativo</v>
       </c>
       <c r="C326" t="str">
-        <v>Saturação</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B327" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Saturação</v>
       </c>
       <c r="C327" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Saturação</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B328" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>Colorimétrico absoluto</v>
       </c>
       <c r="C328" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B329" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>Estatísticas do perfil</v>
       </c>
       <c r="C329" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>Estatísticas do perfil</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B330" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
       <c r="C330" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B331" t="str">
-        <v>Intenção de renderização</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
       </c>
       <c r="C331" t="str">
-        <v>Intenção de renderização</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B332" t="str">
-        <v>Volume de gamute (ΔE³)</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C332" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B333" t="str">
-        <v>ΔE de percurso</v>
+        <v>Volume de gamute (ΔE³)</v>
       </c>
       <c r="C333" t="str">
-        <v>ΔE de percurso</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B334" t="str">
-        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
+        <v>ΔE de percurso</v>
       </c>
       <c r="C334" t="str">
-        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
+        <v>ΔE de percurso</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B335" t="str">
-        <v>média</v>
+        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
       </c>
       <c r="C335" t="str">
-        <v>média</v>
+        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B336" t="str">
-        <v>P90</v>
+        <v>média</v>
       </c>
       <c r="C336" t="str">
-        <v>P90</v>
+        <v>média</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B337" t="str">
-        <v>máx.</v>
+        <v>P90</v>
       </c>
       <c r="C337" t="str">
-        <v>máx.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B338" t="str">
-        <v>A analisar…</v>
+        <v>máx.</v>
       </c>
       <c r="C338" t="str">
-        <v>Analisando…</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B339" t="str">
-        <v>Análise</v>
+        <v>A analisar…</v>
       </c>
       <c r="C339" t="str">
-        <v>Análise</v>
+        <v>Analisando…</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B340" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>Análise</v>
       </c>
       <c r="C340" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B341" t="str">
-        <v>Gráfico</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
       <c r="C341" t="str">
-        <v>Gráfico</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B342" t="str">
-        <v>Saída em bruto</v>
+        <v>Gráfico</v>
       </c>
       <c r="C342" t="str">
-        <v>Saída bruta</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B343" t="str">
-        <v>XML</v>
+        <v>Saída em bruto</v>
       </c>
       <c r="C343" t="str">
-        <v>XML</v>
+        <v>Saída bruta</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="C344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B345" t="str">
-        <v>Curvas</v>
+        <v>JSON</v>
       </c>
       <c r="C345" t="str">
-        <v>Curvas</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B346" t="str">
-        <v>Curvas de entrada</v>
+        <v>Curvas</v>
       </c>
       <c r="C346" t="str">
-        <v>Curvas de entrada</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B347" t="str">
-        <v>Curvas de saída</v>
+        <v>Curvas de entrada</v>
       </c>
       <c r="C347" t="str">
-        <v>Curvas de saída</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B348" t="str">
-        <v>Imagem CLUT</v>
+        <v>Curvas de saída</v>
       </c>
       <c r="C348" t="str">
-        <v>Imagem CLUT</v>
+        <v>Curvas de saída</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B349" t="str">
-        <v>Imagem de gamut</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C349" t="str">
-        <v>Imagem de gamut</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B350" t="str">
-        <v>Cromaticidade</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C350" t="str">
-        <v>Cromaticidade</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B351" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Cromaticidade</v>
       </c>
       <c r="C351" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Cromaticidade</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B352" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Gráfico de dispersão</v>
       </c>
       <c r="C352" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Gráfico de dispersão</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B353" t="str">
-        <v>Tabela da curva</v>
+        <v>Curva de resposta tonal</v>
       </c>
       <c r="C353" t="str">
-        <v>Tabela da curva</v>
+        <v>Curva de resposta tonal</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B354" t="str">
-        <v>Tabelas</v>
+        <v>Tabela da curva</v>
       </c>
       <c r="C354" t="str">
-        <v>Tabelas</v>
+        <v>Tabela da curva</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B355" t="str">
-        <v>Dados</v>
+        <v>Tabelas</v>
       </c>
       <c r="C355" t="str">
-        <v>Dados</v>
+        <v>Tabelas</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B356" t="str">
-        <v>Avaliar</v>
+        <v>Dados</v>
       </c>
       <c r="C356" t="str">
-        <v>Avaliar</v>
+        <v>Dados</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B357" t="str">
-        <v>A carregar…</v>
+        <v>Avaliar</v>
       </c>
       <c r="C357" t="str">
-        <v>Carregando…</v>
+        <v>Avaliar</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B358" t="str">
-        <v>Entrada</v>
+        <v>A carregar…</v>
       </c>
       <c r="C358" t="str">
-        <v>Entrada</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B359" t="str">
-        <v>Saída</v>
+        <v>Entrada</v>
       </c>
       <c r="C359" t="str">
-        <v>Saída</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B360" t="str">
-        <v>Vírgula flutuante</v>
+        <v>Saída</v>
       </c>
       <c r="C360" t="str">
-        <v>Ponto flutuante</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B361" t="str">
-        <v>Ponto da grelha</v>
+        <v>Vírgula flutuante</v>
       </c>
       <c r="C361" t="str">
-        <v>Ponto da grade</v>
+        <v>Ponto flutuante</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B362" t="str">
-        <v>Normalizado</v>
+        <v>Ponto da grelha</v>
       </c>
       <c r="C362" t="str">
-        <v>Normalizado</v>
+        <v>Ponto da grade</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B363" t="str">
-        <v>Legível</v>
+        <v>Normalizado</v>
       </c>
       <c r="C363" t="str">
-        <v>Legível</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B364" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Legível</v>
       </c>
       <c r="C364" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Legível</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B365" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dispositivo → PCS</v>
       </c>
       <c r="C365" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B366" t="str">
-        <v>Sem grelha CLUT</v>
+        <v>PCS → Dispositivo</v>
       </c>
       <c r="C366" t="str">
-        <v>Sem grade CLUT</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B367" t="str">
-        <v>A carregar…</v>
+        <v>Sem grelha CLUT</v>
       </c>
       <c r="C367" t="str">
-        <v>Carregando…</v>
+        <v>Sem grade CLUT</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B368" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>A carregar…</v>
       </c>
       <c r="C368" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B369" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
       <c r="C369" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B370" t="str">
-        <v>Não foi possível obter o perfil de</v>
+        <v>URL de perfil inválido:</v>
       </c>
       <c r="C370" t="str">
-        <v>Não foi possível buscar o perfil de</v>
+        <v>URL de perfil inválido:</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B371" t="str">
-        <v>Carregar um perfil ICC a partir deste site externo?</v>
+        <v>Não foi possível obter o perfil de</v>
       </c>
       <c r="C371" t="str">
-        <v>Carregar um perfil ICC deste site externo?</v>
+        <v>Não foi possível buscar o perfil de</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B372" t="str">
-        <v>A carregar o relatório Profile Assessment WG…</v>
+        <v>Carregar um perfil ICC a partir deste site externo?</v>
       </c>
       <c r="C372" t="str">
-        <v>Carregando o relatório Profile Assessment WG…</v>
+        <v>Carregar um perfil ICC deste site externo?</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B373" t="str">
-        <v>A executar as verificações Profile Assessment WG…</v>
+        <v>A carregar o relatório Profile Assessment WG…</v>
       </c>
       <c r="C373" t="str">
-        <v>Executando as verificações Profile Assessment WG…</v>
+        <v>Carregando o relatório Profile Assessment WG…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B374" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>A executar as verificações Profile Assessment WG…</v>
       </c>
       <c r="C374" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Executando as verificações Profile Assessment WG…</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B375" t="str">
-        <v>Segurança</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
       <c r="C375" t="str">
-        <v>Segurança</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B376" t="str">
-        <v>Conformidade</v>
+        <v>Segurança</v>
       </c>
       <c r="C376" t="str">
-        <v>Conformidade</v>
+        <v>Segurança</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B377" t="str">
-        <v>Qualidade</v>
+        <v>Conformidade</v>
       </c>
       <c r="C377" t="str">
-        <v>Qualidade</v>
+        <v>Conformidade</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B378" t="str">
-        <v>RELATÓRIO</v>
+        <v>Qualidade</v>
       </c>
       <c r="C378" t="str">
-        <v>RELATÓRIO</v>
+        <v>Qualidade</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B379" t="str">
-        <v>REPROVADO</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C379" t="str">
-        <v>REPROVADO</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B380" t="str">
-        <v>verificações</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C380" t="str">
-        <v>verificações</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B381" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>verificações</v>
       </c>
       <c r="C381" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B382" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C382" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B383" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C383" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B384" t="str">
-        <v>Com {lib}</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C384" t="str">
-        <v>Com {lib}</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B385" t="str">
-        <v>Subscrever</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C385" t="str">
-        <v>Inscrever-se</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B386" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Subscrever</v>
       </c>
       <c r="C386" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B387" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C387" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B388" t="str">
-        <v>Fechar</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C388" t="str">
-        <v>Fechar</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B389" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Fechar</v>
       </c>
       <c r="C389" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B390" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C390" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B391" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C391" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B392" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C392" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B393" t="str">
-        <v>(opcional)</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C393" t="str">
-        <v>(opcional)</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B394" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>(opcional)</v>
       </c>
       <c r="C394" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B395" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C395" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B396" t="str">
-        <v>Cancelar</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C396" t="str">
-        <v>Cancelar</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B397" t="str">
-        <v>Subscrever</v>
+        <v>Cancelar</v>
       </c>
       <c r="C397" t="str">
-        <v>Inscrever-se</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B398" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C398" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B399" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C399" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B400" t="str">
-        <v>Fechar</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C400" t="str">
-        <v>Fechar</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B401" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Fechar</v>
       </c>
       <c r="C401" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B402" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C402" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B403" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C403" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B404" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C404" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B405" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C405" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B406" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C406" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B407" t="str">
-        <v>Erro:</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C407" t="str">
-        <v>Erro:</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B408" t="str">
-        <v>Converter para XML</v>
+        <v>Erro:</v>
       </c>
       <c r="C408" t="str">
-        <v>Converter para XML</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B409" t="str">
-        <v>Converter para JSON</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C409" t="str">
-        <v>Converter para JSON</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B410" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C410" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B411" t="str">
-        <v>A converter para XML…</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C411" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B412" t="str">
-        <v>A converter para JSON…</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C412" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B413" t="str">
-        <v>A converter para ICC…</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C413" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B414" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C414" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B415" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C415" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B416" t="str">
-        <v>ID do perfil</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C416" t="str">
-        <v>ID do perfil</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B417" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C417" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B418" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C418" t="str">
-        <v>Nome da tag</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B419" t="str">
-        <v>ID</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C419" t="str">
-        <v>ID</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B420" t="str">
-        <v>Deslocamento</v>
+        <v>ID</v>
       </c>
       <c r="C420" t="str">
-        <v>Deslocamento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B421" t="str">
-        <v>Tamanho</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C421" t="str">
-        <v>Tamanho</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B422" t="str">
-        <v>Preenchimento</v>
+        <v>Tamanho</v>
       </c>
       <c r="C422" t="str">
-        <v>Preenchimento</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B423" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C423" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B424" t="str">
-        <v>Tipo</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C424" t="str">
-        <v>Tipo</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B425" t="str">
-        <v>Vetor de {type}</v>
+        <v>Tipo</v>
       </c>
       <c r="C425" t="str">
-        <v>Array de {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B426" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C426" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B427" t="str">
-        <v>bytes</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C427" t="str">
-        <v>bytes</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B428" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>bytes</v>
       </c>
       <c r="C428" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B429" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C429" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B430" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C430" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B431" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C431" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B432" t="str">
-        <v>Sem saída de validação</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C432" t="str">
-        <v>Sem saída de validação</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B433" t="str">
-        <v>O perfil é válido</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C433" t="str">
-        <v>O perfil é válido</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B434" t="str">
-        <v>O perfil tem avisos</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C434" t="str">
-        <v>O perfil tem avisos</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B435" t="str">
-        <v>O perfil não é conforme</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C435" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B436" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C436" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B437" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C437" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B438" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C438" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B439" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C439" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B440" t="str">
-        <v>Válido</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C440" t="str">
-        <v>Válido</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B441" t="str">
-        <v>Aviso</v>
+        <v>Válido</v>
       </c>
       <c r="C441" t="str">
-        <v>Aviso</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B442" t="str">
-        <v>Erro</v>
+        <v>Aviso</v>
       </c>
       <c r="C442" t="str">
-        <v>Erro</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B443" t="str">
-        <v>Desconhecido</v>
+        <v>Erro</v>
       </c>
       <c r="C443" t="str">
-        <v>Desconhecido</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B444" t="str">
-        <v>Aprovado</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C444" t="str">
-        <v>Aprovado</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B445" t="str">
-        <v>Reprovado</v>
+        <v>Aprovado</v>
       </c>
       <c r="C445" t="str">
-        <v>Reprovado</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B446" t="str">
-        <v>Ver no contexto</v>
+        <v>Reprovado</v>
       </c>
       <c r="C446" t="str">
-        <v>Ver no contexto</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B447" t="str">
-        <v>Detalhe de validação</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C447" t="str">
-        <v>Detalhe de validação</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B448" t="str">
-        <v>Acionado por</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C448" t="str">
-        <v>Acionado por</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B449" t="str">
-        <v>Campo</v>
+        <v>Acionado por</v>
       </c>
       <c r="C449" t="str">
-        <v>Campo</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B450" t="str">
-        <v>Valor atual</v>
+        <v>Campo</v>
       </c>
       <c r="C450" t="str">
-        <v>Valor atual</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B451" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Valor atual</v>
       </c>
       <c r="C451" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B452" t="str">
-        <v>Esperado: {value}</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C452" t="str">
-        <v>Esperado: {value}</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B453" t="str">
-        <v>Inválido</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C453" t="str">
-        <v>Inválido</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B454" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Inválido</v>
       </c>
       <c r="C454" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B455" t="str">
-        <v>Fechar</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C455" t="str">
-        <v>Fechar</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B456" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Fechar</v>
       </c>
       <c r="C456" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B457" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C457" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B458" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C458" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B459" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C459" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B460" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C460" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B461" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>● edições XML por guardar</v>
       </c>
       <c r="C461" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>● edições XML não salvas</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B462" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições JSON por guardar</v>
       </c>
       <c r="C462" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições JSON não salvas</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B463" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
       <c r="C463" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B464" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
       <c r="C464" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B465" t="str">
-        <v>ordenar chaves</v>
+        <v>indentação</v>
       </c>
       <c r="C465" t="str">
-        <v>ordenar chaves</v>
+        <v>indentação</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B466" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C466" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B466" t="str">
+      <c r="B467" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C466" t="str">
+      <c r="C467" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C466"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C467"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C706"/>
+  <dimension ref="A1:C707"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4628,35 +4628,35 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>HDR Profile in the chain</v>
+        <v>HDR ColorSpace Profile in the chain</v>
       </c>
       <c r="B384" t="str">
-        <v>Perfil HDR na cadeia</v>
+        <v>Perfil HDR ColorSpace na cadeia</v>
       </c>
       <c r="C384" t="str">
-        <v>Perfil HDR na cadeia</v>
+        <v>Perfil HDR ColorSpace na cadeia</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
+        <v>Transforms through an HDR ColorSpace Profile use its AToB0Tag — the baked SDR rendering required by clause 8.7.1.5 — because a ColorSpace profile has no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B385" t="str">
-        <v>As transformações através de um perfil HDR usam o seu AToB0Tag — a renderização SDR fixada exigida pela cláusula 8.10.6 — porque a cláusula 8.10.1 não lhe deixa etiquetas TRC. O resultado é esse recurso, não comportamento HDR.</v>
+        <v>As transformações através de um perfil HDR ColorSpace usam o seu AToB0Tag — a renderização SDR fixada exigida pela cláusula 8.7.1.5 — porque um perfil ColorSpace não tem etiquetas TRC. O resultado é esse recurso, não comportamento HDR.</v>
       </c>
       <c r="C385" t="str">
-        <v>As transformações através de um perfil HDR usam seu AToB0Tag — a renderização SDR fixada exigida pela cláusula 8.10.6 — porque a cláusula 8.10.1 não lhe deixa tags TRC. O resultado é esse fallback, não comportamento HDR.</v>
+        <v>As transformações através de um perfil HDR ColorSpace usam seu AToB0Tag — a renderização SDR fixada exigida pela cláusula 8.7.1.5 — porque um perfil ColorSpace não tem tags TRC. O resultado é esse fallback, não comportamento HDR.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
+        <v>These are HDR ColorSpace Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.7.1.5 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B386" t="str">
-        <v>São perfis HDR, sem etiquetas TRC, pelo que o gamut é construído a partir do AToB0Tag — a renderização SDR fixada que a cláusula 8.10.6 exige a consumidores sem processamento HDR. Não é o gamut HDR do perfil, que não pode ser desenhado num PCS limitado.</v>
+        <v>São perfis HDR ColorSpace, sem etiquetas TRC, pelo que o gamut é construído a partir do AToB0Tag — a renderização SDR fixada que a cláusula 8.7.1.5 exige a consumidores sem processamento HDR. Não é o gamut HDR do perfil, que não pode ser desenhado num PCS limitado.</v>
       </c>
       <c r="C386" t="str">
-        <v>São perfis HDR, sem tags TRC, então o gamut é construído a partir do AToB0Tag — a renderização SDR fixada que a cláusula 8.10.6 exige de consumidores sem processamento HDR. Não é o gamut HDR do perfil, que não pode ser desenhado em um PCS limitado.</v>
+        <v>São perfis HDR ColorSpace, sem tags TRC, então o gamut é construído a partir do AToB0Tag — a renderização SDR fixada que a cláusula 8.7.1.5 exige de consumidores sem processamento HDR. Não é o gamut HDR do perfil, que não pode ser desenhado em um PCS limitado.</v>
       </c>
     </row>
     <row r="387">
@@ -6245,13 +6245,13 @@
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.7.1.2 a)</v>
       </c>
       <c r="B531" t="str">
-        <v>Ficheiro 1,0 = 1 cd/m² (ICC.1 cláusula 8.10.2 a)</v>
+        <v>Ficheiro 1,0 = 1 cd/m² (ICC.1 cláusula 8.7.1.2 a)</v>
       </c>
       <c r="C531" t="str">
-        <v>Arquivo 1,0 = 1 cd/m² (ICC.1 cláusula 8.10.2 a)</v>
+        <v>Arquivo 1,0 = 1 cd/m² (ICC.1 cláusula 8.7.1.2 a)</v>
       </c>
     </row>
     <row r="532">
@@ -6333,13 +6333,13 @@
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Auto (clause 8.7.1.3 ranking)</v>
       </c>
       <c r="B539" t="str">
-        <v>Auto (ordem da cláusula 8.10.3)</v>
+        <v>Auto (ordem da cláusula 8.7.1.3)</v>
       </c>
       <c r="C539" t="str">
-        <v>Auto (ordem da cláusula 8.10.3)</v>
+        <v>Auto (ordem da cláusula 8.7.1.3)</v>
       </c>
     </row>
     <row r="540">
@@ -6421,13 +6421,13 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>HDR Profiles</v>
+        <v>HDR ColorSpace Profiles</v>
       </c>
       <c r="B547" t="str">
-        <v>Perfis HDR</v>
+        <v>Perfis HDR ColorSpace</v>
       </c>
       <c r="C547" t="str">
-        <v>Perfis HDR</v>
+        <v>Perfis HDR ColorSpace</v>
       </c>
     </row>
     <row r="548">
@@ -6454,1734 +6454,1745 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>HDR ColorSpace Profiles — Linear transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>Perfis HDR — transferência linear</v>
+        <v>Perfis HDR ColorSpace — transferência linear</v>
       </c>
       <c r="C550" t="str">
-        <v>Perfis HDR — transferência linear</v>
+        <v>Perfis HDR ColorSpace — transferência linear</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR ColorSpace Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B551" t="str">
-        <v>Perfis HDR — transferência PQ / HLG</v>
+        <v>Perfis HDR ColorSpace — transferência PQ / HLG</v>
       </c>
       <c r="C551" t="str">
-        <v>Perfis HDR — transferência PQ / HLG</v>
+        <v>Perfis HDR ColorSpace — transferência PQ / HLG</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>{format} holds linear light, so only HDR ColorSpace Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B552" t="str">
-        <v>O {format} contém luz linear, pelo que só podem ser atribuídos perfis HDR com transferência linear.</v>
+        <v>O {format} contém luz linear, pelo que só podem ser atribuídos perfis HDR ColorSpace com transferência linear.</v>
       </c>
       <c r="C552" t="str">
-        <v>O {format} contém luz linear, então só podem ser atribuídos perfis HDR com transferência linear.</v>
+        <v>O {format} contém luz linear, então só podem ser atribuídos perfis HDR ColorSpace com transferência linear.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{n} PQ/HLG HDR ColorSpace Profile(s) in the pool are not offered — the Profiles pane lists them under HDR ColorSpace Profiles › Non-linear transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis lista-os em Perfis HDR › Transferência não linear.</v>
+        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis lista-os em Perfis HDR ColorSpace › Transferência não linear.</v>
       </c>
       <c r="C553" t="str">
-        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis os lista em Perfis HDR › Transferência não linear.</v>
+        <v>{n} perfil(is) HDR PQ/HLG no pool não são oferecidos — o painel Perfis os lista em Perfis HDR ColorSpace › Transferência não linear.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>There is no Linear-transfer HDR ColorSpace Profile in the pool yet; the Profiles pane groups HDR ColorSpace Profiles by transfer.</v>
       </c>
       <c r="B554" t="str">
-        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
+        <v>Ainda não há nenhum perfil HDR ColorSpace com transferência linear no pool; o painel Perfis agrupa os perfis HDR ColorSpace por transferência.</v>
       </c>
       <c r="C554" t="str">
-        <v>Ainda não há nenhum perfil HDR com transferência linear no pool; o painel Perfis agrupa os perfis HDR por transferência.</v>
+        <v>Ainda não há nenhum perfil HDR ColorSpace com transferência linear no pool; o painel Perfis agrupa os perfis HDR ColorSpace por transferência.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Unspecified primaries: no HDR path in this build</v>
       </c>
       <c r="B555" t="str">
-        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.10.3).</v>
+        <v>Primárias não especificadas: sem caminho HDR nesta versão</v>
       </c>
       <c r="C555" t="str">
-        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.10.3).</v>
+        <v>Primárias não especificadas: sem caminho HDR nesta versão</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.7.1.3).</v>
       </c>
       <c r="B556" t="str">
-        <v>Margem do ecrã</v>
+        <v>O IccProfLib recusa aplicar esta curva de ganho: {why}. Um CMM recorre ao descritor de tone mapping seguinte (cláusula 8.7.1.3).</v>
       </c>
       <c r="C556" t="str">
-        <v>Margem da tela</v>
+        <v>O IccProfLib se recusa a aplicar esta curva de ganho: {why}. Um CMM recorre ao próximo descritor de tone mapping (cláusula 8.7.1.3).</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B557" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>Margem do ecrã</v>
       </c>
       <c r="C557" t="str">
-        <v>{n} stops (≈{r}× o branco de referência)</v>
+        <v>Margem da tela</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B558" t="str">
-        <v>Base</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
       <c r="C558" t="str">
-        <v>Base</v>
+        <v>{n} stops (≈{r}× o branco de referência)</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Preview through the colour engine</v>
+        <v>Baseline</v>
       </c>
       <c r="B559" t="str">
-        <v>Pré-visualização através do motor de cor</v>
+        <v>Base</v>
       </c>
       <c r="C559" t="str">
-        <v>Pré-visualização pelo mecanismo de cor</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B560" t="str">
-        <v>Tal como criado (base {h} stops, sem ganho)</v>
+        <v>Pré-visualização através do motor de cor</v>
       </c>
       <c r="C560" t="str">
-        <v>Como criado (base {h} stops, sem ganho)</v>
+        <v>Pré-visualização pelo mecanismo de cor</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B561" t="str">
-        <v>Mapeado para {h} stops</v>
+        <v>Tal como criado (base {h} stops, sem ganho)</v>
       </c>
       <c r="C561" t="str">
-        <v>Mapeado para {h} stops</v>
+        <v>Como criado (base {h} stops, sem ganho)</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B562" t="str">
-        <v>Os mesmos píxeis de teste (sinal {transfer} a subir da esquerda para a direita: cinzento, depois R, G, B, Y, C, M) através da transformação HDR do IccProfLib. Ambas as faixas estão limitadas a {r}× o branco de referência HDR, como um ecrã com {h} stops de margem as mostraria: onde a faixa de cima satura plana, a curva de ganho suaviza as altas luzes.</v>
+        <v>Mapeado para {h} stops</v>
       </c>
       <c r="C562" t="str">
-        <v>Os mesmos pixels de teste (sinal {transfer} subindo da esquerda para a direita: cinza, depois R, G, B, Y, C, M) pela transformação HDR do IccProfLib. As duas faixas são limitadas a {r}× o branco de referência HDR, como uma tela com {h} stops de margem as mostraria: onde a faixa de cima satura plana, a curva de ganho suaviza as altas luzes.</v>
+        <v>Mapeado para {h} stops</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>reference white</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B563" t="str">
-        <v>branco de referência</v>
+        <v>Os mesmos píxeis de teste (sinal {transfer} a subir da esquerda para a direita: cinzento, depois R, G, B, Y, C, M) através da transformação HDR do IccProfLib. Ambas as faixas estão limitadas a {r}× o branco de referência HDR, como um ecrã com {h} stops de margem as mostraria: onde a faixa de cima satura plana, a curva de ganho suaviza as altas luzes.</v>
       </c>
       <c r="C563" t="str">
-        <v>branco de referência</v>
+        <v>Os mesmos pixels de teste (sinal {transfer} subindo da esquerda para a direita: cinza, depois R, G, B, Y, C, M) pela transformação HDR do IccProfLib. As duas faixas são limitadas a {r}× o branco de referência HDR, como uma tela com {h} stops de margem as mostraria: onde a faixa de cima satura plana, a curva de ganho suaviza as altas luzes.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>display peak</v>
+        <v>reference white</v>
       </c>
       <c r="B564" t="str">
-        <v>pico do ecrã</v>
+        <v>branco de referência</v>
       </c>
       <c r="C564" t="str">
-        <v>pico da tela</v>
+        <v>branco de referência</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>display peak</v>
       </c>
       <c r="B565" t="str">
-        <v>Pré-visualização indisponível: {why}</v>
+        <v>pico do ecrã</v>
       </c>
       <c r="C565" t="str">
-        <v>Pré-visualização indisponível: {why}</v>
+        <v>pico da tela</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B566" t="str">
-        <v>o motor de cor não seguiu o caminho HDR para este perfil</v>
+        <v>Pré-visualização indisponível: {why}</v>
       </c>
       <c r="C566" t="str">
-        <v>o mecanismo de cor não seguiu o caminho HDR para este perfil</v>
+        <v>Pré-visualização indisponível: {why}</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Gain across every headroom</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B567" t="str">
-        <v>Ganho em todas as margens</v>
+        <v>o motor de cor não seguiu o caminho HDR para este perfil</v>
       </c>
       <c r="C567" t="str">
-        <v>Ganho em todas as margens</v>
+        <v>o mecanismo de cor não seguiu o caminho HDR para este perfil</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B568" t="str">
-        <v>Ganho aplicado a uma entrada cinzenta em cada margem do ecrã: o azul comprime, o vermelho expande e o branco deixa-a igual. As linhas ponteadas marcam as curvas da etiqueta, a contínua a base e a âmbar o controlo; a diagonal tracejada é onde a entrada atinge o pico do ecrã. Clique para mover o controlo.</v>
+        <v>Ganho em todas as margens</v>
       </c>
       <c r="C568" t="str">
-        <v>Ganho aplicado a uma entrada cinza em cada margem da tela: azul comprime, vermelho expande e branco deixa inalterado. As linhas pontilhadas marcam as curvas da tag, a contínua a base e a âmbar o controle; a diagonal tracejada é onde a entrada atinge o pico da tela. Clique para mover o controle.</v>
+        <v>Ganho em todas as margens</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B569" t="str">
-        <v>Entrada (stops relativamente ao branco de referência HDR)</v>
+        <v>Ganho aplicado a uma entrada cinzenta em cada margem do ecrã: o azul comprime, o vermelho expande e o branco deixa-a igual. As linhas ponteadas marcam as curvas da etiqueta, a contínua a base e a âmbar o controlo; a diagonal tracejada é onde a entrada atinge o pico do ecrã. Clique para mover o controlo.</v>
       </c>
       <c r="C569" t="str">
-        <v>Entrada (stops em relação ao branco de referência HDR)</v>
+        <v>Ganho aplicado a uma entrada cinza em cada margem da tela: azul comprime, vermelho expande e branco deixa inalterado. As linhas pontilhadas marcam as curvas da tag, a contínua a base e a âmbar o controle; a diagonal tracejada é onde a entrada atinge o pico da tela. Clique para mover o controle.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B570" t="str">
-        <v>Margem do ecrã (stops)</v>
+        <v>Entrada (stops relativamente ao branco de referência HDR)</v>
       </c>
       <c r="C570" t="str">
-        <v>Margem da tela (stops)</v>
+        <v>Entrada (stops em relação ao branco de referência HDR)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Gain (stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B571" t="str">
-        <v>Ganho (stops)</v>
+        <v>Margem do ecrã (stops)</v>
       </c>
       <c r="C571" t="str">
-        <v>Ganho (stops)</v>
+        <v>Margem da tela (stops)</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B572" t="str">
-        <v>Curva na etiqueta</v>
+        <v>Ganho (stops)</v>
       </c>
       <c r="C572" t="str">
-        <v>Curva na tag</v>
+        <v>Ganho (stops)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Baseline</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B573" t="str">
-        <v>Base</v>
+        <v>Curva na etiqueta</v>
       </c>
       <c r="C573" t="str">
-        <v>Base</v>
+        <v>Curva na tag</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Slider</v>
+        <v>Baseline</v>
       </c>
       <c r="B574" t="str">
-        <v>Controlo</v>
+        <v>Base</v>
       </c>
       <c r="C574" t="str">
-        <v>Controle</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Input = display peak</v>
+        <v>Slider</v>
       </c>
       <c r="B575" t="str">
-        <v>Entrada = pico do ecrã</v>
+        <v>Controlo</v>
       </c>
       <c r="C575" t="str">
-        <v>Entrada = pico da tela</v>
+        <v>Controle</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B576" t="str">
-        <v>Curvas tonais de cinzento por margem</v>
+        <v>Entrada = pico do ecrã</v>
       </c>
       <c r="C576" t="str">
-        <v>Curvas tonais de cinza por margem</v>
+        <v>Entrada = pico da tela</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B577" t="str">
-        <v>A curva tonal de cinzento em cada margem guardada na etiqueta, colorida de baixo (azul) para alto (vermelho), com a curva do controlo em âmbar. Ambos os eixos estão em stops, pelo que a diagonal significa sem alteração.</v>
+        <v>Curvas tonais de cinzento por margem</v>
       </c>
       <c r="C577" t="str">
-        <v>A curva tonal de cinza em cada margem armazenada na tag, colorida de baixo (azul) para alto (vermelho), com a curva do controle em âmbar. Os dois eixos estão em stops, então a diagonal significa sem alteração.</v>
+        <v>Curvas tonais de cinza por margem</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B578" t="str">
-        <v>Saída (stops relativamente ao branco de referência HDR)</v>
+        <v>A curva tonal de cinzento em cada margem guardada na etiqueta, colorida de baixo (azul) para alto (vermelho), com a curva do controlo em âmbar. Ambos os eixos estão em stops, pelo que a diagonal significa sem alteração.</v>
       </c>
       <c r="C578" t="str">
-        <v>Saída (stops em relação ao branco de referência HDR)</v>
+        <v>A curva tonal de cinza em cada margem armazenada na tag, colorida de baixo (azul) para alto (vermelho), com a curva do controle em âmbar. Os dois eixos estão em stops, então a diagonal significa sem alteração.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>{h} stops</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B579" t="str">
-        <v>{h} stops</v>
+        <v>Saída (stops relativamente ao branco de referência HDR)</v>
       </c>
       <c r="C579" t="str">
-        <v>{h} stops</v>
+        <v>Saída (stops em relação ao branco de referência HDR)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>{h} stops</v>
       </c>
       <c r="B580" t="str">
-        <v>{h} stops (base)</v>
+        <v>{h} stops</v>
       </c>
       <c r="C580" t="str">
-        <v>{h} stops (base)</v>
+        <v>{h} stops</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B581" t="str">
-        <v>A {h} stops (controlo)</v>
+        <v>{h} stops (base)</v>
       </c>
       <c r="C581" t="str">
-        <v>Em {h} stops (controle)</v>
+        <v>{h} stops (base)</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B582" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>A {h} stops (controlo)</v>
       </c>
       <c r="C582" t="str">
-        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
+        <v>Em {h} stops (controle)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B583" t="str">
-        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
       <c r="C583" t="str">
-        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
+        <v>Curvas no tag, por margem: {list} stops. Base {b} stops, branco de referência HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B584" t="str">
-        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
+        <v>Esta margem está fora do intervalo das curvas do tag, pelo que a curva mais próxima é usada sem alterações — a biblioteca não extrapola para além delas.</v>
       </c>
       <c r="C584" t="str">
-        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
+        <v>Esta margem está fora da faixa de curvas do tag, então a curva mais próxima é usada sem alteração — a biblioteca não extrapola além delas.</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B585" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
+        <v>Alguns declives são derivados (PCHIP), não guardados no tag. Essa derivação reconstrói uma cláusula SMPTE, pelo que a forma dessas curvas é provisória.</v>
       </c>
       <c r="C585" t="str">
-        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
+        <v>Algumas inclinações são derivadas (PCHIP), não armazenadas no tag. Essa derivação reconstrói uma cláusula SMPTE, então trate a forma dessas curvas como provisória.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B586" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
+        <v>O tag pede tone mapping sobre o branco de referência, pelo que as curvas são construídas pela biblioteca em vez de lidas do ficheiro (uma construção de um rascunho de comité).</v>
       </c>
       <c r="C586" t="str">
-        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
+        <v>O tag pede tone mapping sobre o branco de referência, então as curvas são construídas pela biblioteca em vez de lidas do arquivo (uma construção de um rascunho de comitê).</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B587" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor do ecrã.</v>
       </c>
       <c r="C587" t="str">
-        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
+        <v>Sem imagens alternativas: o tag não pede tone mapping, apenas um limite ao volume de cor da tela.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B588" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, pelo que não há uma única curva de ganho a desenhar. A curva de tons abaixo continua exata.</v>
       </c>
       <c r="C588" t="str">
-        <v>Curva a {h} stops (sem ganho)</v>
+        <v>As duas curvas misturadas nesta margem combinam os canais de forma diferente, então não há uma única curva de ganho para desenhar. A curva de tons abaixo continua exata.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B589" t="str">
-        <v>Curva a {h} stops</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
       <c r="C589" t="str">
-        <v>Curva a {h} stops</v>
+        <v>Curva a {h} stops (sem ganho)</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B590" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Curva a {h} stops</v>
       </c>
       <c r="C590" t="str">
-        <v>Aplicado a {h} stops</v>
+        <v>Curva a {h} stops</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B591" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>Aplicado a {h} stops</v>
       </c>
       <c r="C591" t="str">
-        <v>Ganho aplicado nesta margem</v>
+        <v>Aplicado a {h} stops</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B592" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
       <c r="C592" t="str">
-        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
+        <v>Ganho aplicado nesta margem</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B593" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
       <c r="C593" t="str">
-        <v>Ganho (stops log2)</v>
+        <v>Entrada misturada (linear, 1,0 = branco de referência HDR)</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B594" t="str">
-        <v>Curva de tons dos cinzentos nesta margem</v>
+        <v>Ganho (stops log2)</v>
       </c>
       <c r="C594" t="str">
-        <v>Curva de tons de cinza nesta margem</v>
+        <v>Ganho (stops log2)</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B595" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Curva de tons dos cinzentos nesta margem</v>
       </c>
       <c r="C595" t="str">
-        <v>Entrada (× branco de referência HDR)</v>
+        <v>Curva de tons de cinza nesta margem</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B596" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
       <c r="C596" t="str">
-        <v>Saída (× branco de referência HDR)</v>
+        <v>Entrada (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B597" t="str">
-        <v>Sem alteração</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
       <c r="C597" t="str">
-        <v>Sem alteração</v>
+        <v>Saída (× branco de referência HDR)</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B598" t="str">
-        <v>Pico do ecrã a {h} stops</v>
+        <v>Sem alteração</v>
       </c>
       <c r="C598" t="str">
-        <v>Pico da tela a {h} stops</v>
+        <v>Sem alteração</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B599" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Pico do ecrã a {h} stops</v>
       </c>
       <c r="C599" t="str">
-        <v>Saída a {h} stops</v>
+        <v>Pico da tela a {h} stops</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B600" t="str">
-        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
+        <v>Saída a {h} stops</v>
       </c>
       <c r="C600" t="str">
-        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
+        <v>Saída a {h} stops</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B601" t="str">
-        <v>Identificar ecrãs</v>
+        <v>HDR, gama e relação de píxeis atualizam-se quando a janela passa para um ecrã onde diferem.</v>
       </c>
       <c r="C601" t="str">
-        <v>Identificar telas</v>
+        <v>HDR, gama e proporção de pixels são atualizados quando a janela vai para uma tela onde diferem.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B602" t="str">
-        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Identificar ecrãs</v>
       </c>
       <c r="C602" t="str">
-        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
+        <v>Identificar telas</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B603" t="str">
-        <v>A acompanhar em que monitor está esta janela.</v>
+        <v>Pede permissão para saber em que monitor está esta janela, para que o painel também se atualize entre ecrãs semelhantes e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
       <c r="C603" t="str">
-        <v>Acompanhando em qual monitor esta janela está.</v>
+        <v>Pede permissão para saber em qual monitor esta janela está, para que o painel também atualize entre telas parecidas e mostre a margem HDR onde o navegador a expõe.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B604" t="str">
-        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
+        <v>A acompanhar em que monitor está esta janela.</v>
       </c>
       <c r="C604" t="str">
-        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
+        <v>Acompanhando em qual monitor esta janela está.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B605" t="str">
-        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
+        <v>A permissão para identificar ecrãs foi recusada. Pode ser alterada nas definições deste site.</v>
       </c>
       <c r="C605" t="str">
-        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
+        <v>A permissão para identificar telas foi negada. Ela pode ser alterada nas configurações deste site.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B606" t="str">
-        <v>Não foi possível identificar os ecrãs.</v>
+        <v>Este navegador não consegue identificar ecrãs; aplica-se apenas a atualização automática acima.</v>
       </c>
       <c r="C606" t="str">
-        <v>Não foi possível identificar as telas.</v>
+        <v>Este navegador não consegue identificar telas; vale apenas a atualização automática acima.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B607" t="str">
-        <v>Eventos de ecrã</v>
+        <v>Não foi possível identificar os ecrãs.</v>
       </c>
       <c r="C607" t="str">
-        <v>Eventos de tela</v>
+        <v>Não foi possível identificar as telas.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B608" t="str">
-        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
+        <v>Eventos de ecrã</v>
       </c>
       <c r="C608" t="str">
-        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
+        <v>Eventos de tela</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B609" t="str">
-        <v>Primárias de cor</v>
+        <v>Ainda sem eventos. Arraste a janela para outro monitor.</v>
       </c>
       <c r="C609" t="str">
-        <v>Primárias de cor</v>
+        <v>Nenhum evento ainda. Arraste a janela para outro monitor.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B610" t="str">
-        <v>Características de transferência</v>
+        <v>Primárias de cor</v>
       </c>
       <c r="C610" t="str">
-        <v>Características de transferência</v>
+        <v>Primárias de cor</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B611" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Características de transferência</v>
       </c>
       <c r="C611" t="str">
-        <v>Coeficientes de matriz</v>
+        <v>Características de transferência</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B612" t="str">
-        <v>Sinalizador de gama completa de vídeo</v>
+        <v>Coeficientes de matriz</v>
       </c>
       <c r="C612" t="str">
-        <v>Sinalizador de faixa completa de vídeo</v>
+        <v>Coeficientes de matriz</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B613" t="str">
-        <v>Gama completa</v>
+        <v>Sinalizador de gama completa de vídeo</v>
       </c>
       <c r="C613" t="str">
-        <v>Faixa completa</v>
+        <v>Sinalizador de faixa completa de vídeo</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B614" t="str">
-        <v>Gama reduzida</v>
+        <v>Gama completa</v>
       </c>
       <c r="C614" t="str">
-        <v>Faixa reduzida</v>
+        <v>Faixa completa</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B615" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Gama reduzida</v>
       </c>
       <c r="C615" t="str">
-        <v>não atribuído pela UIT-T H.273</v>
+        <v>Faixa reduzida</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B616" t="str">
-        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
       <c r="C616" t="str">
-        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
+        <v>não atribuído pela UIT-T H.273</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B617" t="str">
-        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
+        <v>As primárias 2 (Não especificado) remetem para o próprio perfil: as primárias vêm das etiquetas de corante e não desta etiqueta.</v>
       </c>
       <c r="C617" t="str">
-        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
+        <v>As primárias 2 (Não especificado) remetem ao próprio perfil: as primárias vêm das tags de corante e não desta tag.</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B618" t="str">
-        <v>RELATÓRIO</v>
+        <v>Os quatro bytes reservados desta etiqueta não são todos zero.</v>
       </c>
       <c r="C618" t="str">
-        <v>RELATÓRIO</v>
+        <v>Os quatro bytes reservados desta tag não são todos zero.</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B619" t="str">
-        <v>REPROVADO</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C619" t="str">
-        <v>REPROVADO</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B620" t="str">
-        <v>verificações</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C620" t="str">
-        <v>verificações</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B621" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>verificações</v>
       </c>
       <c r="C621" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B622" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C622" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B623" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C623" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B624" t="str">
-        <v>Com {lib}</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C624" t="str">
-        <v>Com {lib}</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B625" t="str">
-        <v>Subscrever</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C625" t="str">
-        <v>Inscrever-se</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B626" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Subscrever</v>
       </c>
       <c r="C626" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B627" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C627" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B628" t="str">
-        <v>Fechar</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C628" t="str">
-        <v>Fechar</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B629" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Fechar</v>
       </c>
       <c r="C629" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B630" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C630" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B631" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C631" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B632" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C632" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B633" t="str">
-        <v>(opcional)</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C633" t="str">
-        <v>(opcional)</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B634" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>(opcional)</v>
       </c>
       <c r="C634" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B635" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C635" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B636" t="str">
-        <v>Cancelar</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C636" t="str">
-        <v>Cancelar</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B637" t="str">
-        <v>Subscrever</v>
+        <v>Cancelar</v>
       </c>
       <c r="C637" t="str">
-        <v>Inscrever-se</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B638" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C638" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B639" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C639" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B640" t="str">
-        <v>Fechar</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C640" t="str">
-        <v>Fechar</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B641" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Fechar</v>
       </c>
       <c r="C641" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B642" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C642" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B643" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C643" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B644" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C644" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C645" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B646" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C646" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B647" t="str">
-        <v>Erro:</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C647" t="str">
-        <v>Erro:</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B648" t="str">
-        <v>Converter para XML</v>
+        <v>Erro:</v>
       </c>
       <c r="C648" t="str">
-        <v>Converter para XML</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B649" t="str">
-        <v>Converter para JSON</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C649" t="str">
-        <v>Converter para JSON</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B650" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C650" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B651" t="str">
-        <v>A converter para XML…</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C651" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B652" t="str">
-        <v>A converter para JSON…</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C652" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B653" t="str">
-        <v>A converter para ICC…</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C653" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B654" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C654" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B655" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C655" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B656" t="str">
-        <v>ID do perfil</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C656" t="str">
-        <v>ID do perfil</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B657" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C657" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B658" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C658" t="str">
-        <v>Nome da tag</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B659" t="str">
-        <v>ID</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C659" t="str">
-        <v>ID</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B660" t="str">
-        <v>Deslocamento</v>
+        <v>ID</v>
       </c>
       <c r="C660" t="str">
-        <v>Deslocamento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B661" t="str">
-        <v>Tamanho</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C661" t="str">
-        <v>Tamanho</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B662" t="str">
-        <v>Preenchimento</v>
+        <v>Tamanho</v>
       </c>
       <c r="C662" t="str">
-        <v>Preenchimento</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B663" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C663" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B664" t="str">
-        <v>Tipo</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C664" t="str">
-        <v>Tipo</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B665" t="str">
-        <v>Vetor de {type}</v>
+        <v>Tipo</v>
       </c>
       <c r="C665" t="str">
-        <v>Array de {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B666" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C666" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B667" t="str">
-        <v>bytes</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C667" t="str">
-        <v>bytes</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B668" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>bytes</v>
       </c>
       <c r="C668" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B669" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C669" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B670" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C670" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B671" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C671" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B672" t="str">
-        <v>Sem saída de validação</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C672" t="str">
-        <v>Sem saída de validação</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B673" t="str">
-        <v>O perfil é válido</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C673" t="str">
-        <v>O perfil é válido</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B674" t="str">
-        <v>O perfil tem avisos</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C674" t="str">
-        <v>O perfil tem avisos</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B675" t="str">
-        <v>O perfil não é conforme</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C675" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B676" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C676" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B677" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C677" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B678" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C678" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B679" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C679" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B680" t="str">
-        <v>Válido</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C680" t="str">
-        <v>Válido</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B681" t="str">
-        <v>Aviso</v>
+        <v>Válido</v>
       </c>
       <c r="C681" t="str">
-        <v>Aviso</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B682" t="str">
-        <v>Erro</v>
+        <v>Aviso</v>
       </c>
       <c r="C682" t="str">
-        <v>Erro</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B683" t="str">
-        <v>Desconhecido</v>
+        <v>Erro</v>
       </c>
       <c r="C683" t="str">
-        <v>Desconhecido</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B684" t="str">
-        <v>Aprovado</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C684" t="str">
-        <v>Aprovado</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B685" t="str">
-        <v>Reprovado</v>
+        <v>Aprovado</v>
       </c>
       <c r="C685" t="str">
-        <v>Reprovado</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B686" t="str">
-        <v>Ver no contexto</v>
+        <v>Reprovado</v>
       </c>
       <c r="C686" t="str">
-        <v>Ver no contexto</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B687" t="str">
-        <v>Detalhe de validação</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C687" t="str">
-        <v>Detalhe de validação</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B688" t="str">
-        <v>Acionado por</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C688" t="str">
-        <v>Acionado por</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B689" t="str">
-        <v>Campo</v>
+        <v>Acionado por</v>
       </c>
       <c r="C689" t="str">
-        <v>Campo</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B690" t="str">
-        <v>Valor atual</v>
+        <v>Campo</v>
       </c>
       <c r="C690" t="str">
-        <v>Valor atual</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B691" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Valor atual</v>
       </c>
       <c r="C691" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B692" t="str">
-        <v>Esperado: {value}</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C692" t="str">
-        <v>Esperado: {value}</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B693" t="str">
-        <v>Inválido</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C693" t="str">
-        <v>Inválido</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B694" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Inválido</v>
       </c>
       <c r="C694" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B695" t="str">
-        <v>Fechar</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C695" t="str">
-        <v>Fechar</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B696" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Fechar</v>
       </c>
       <c r="C696" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B697" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C697" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B698" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C698" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B699" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C699" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B700" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C700" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B701" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>● edições XML por guardar</v>
       </c>
       <c r="C701" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>● edições XML não salvas</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B702" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições JSON por guardar</v>
       </c>
       <c r="C702" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições JSON não salvas</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B703" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
       <c r="C703" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B704" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
       <c r="C704" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B705" t="str">
-        <v>ordenar chaves</v>
+        <v>indentação</v>
       </c>
       <c r="C705" t="str">
-        <v>ordenar chaves</v>
+        <v>indentação</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B706" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C706" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B706" t="str">
+      <c r="B707" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C706" t="str">
+      <c r="C707" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C706"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C707"/>
   </ignoredErrors>
 </worksheet>
 </file>